--- a/Pruebas/Archivos/Template/Colombia/Template_HRC_Cenco.xlsx
+++ b/Pruebas/Archivos/Template/Colombia/Template_HRC_Cenco.xlsx
@@ -479,7 +479,7 @@
     <col width="27" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="53" customWidth="1" min="9" max="9"/>
+    <col width="58" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -583,7 +583,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>15/10/2025</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="I264" s="11" t="inlineStr">
         <is>
-          <t>DEVOLUCION MERCANCI AAAA- DEVOLUCION MERCANCI AAAA-</t>
+          <t>DEV DEVOLUCION MERCANCI AAAA- RANCHO</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="I265" s="11" t="inlineStr">
         <is>
-          <t>DEVOLUCION MERCANCI AAAA- DEVOLUCION MERCANCI AAAA-</t>
+          <t>DEV DEVOLUCION MERCANCI AAAA- PERFUME</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="I266" s="11" t="inlineStr">
         <is>
-          <t>DROGUE DEVOLUCIONES</t>
+          <t>DND DSCTO 20.171.100.014.225 DEVOLUCIONES DROGUE</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="I267" s="11" t="inlineStr">
         <is>
-          <t>DROGUE DEVOLUCIONES</t>
+          <t>DND DSCTO 20.181.100.045.651 DEVOLUCIONES DROGUE</t>
         </is>
       </c>
     </row>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="I268" s="11" t="inlineStr">
         <is>
-          <t>DROGUE DSTO COMERCIAL FIJO</t>
+          <t>DCF DSCTO 20.171.100.014.225 DSTO COMERCIAL FIJO DROGUE</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="I269" s="11" t="inlineStr">
         <is>
-          <t>DROGUE DSTO COMERCIAL FIJO</t>
+          <t>DCF DSCTO 20.181.100.032.054 DSTO COMERCIAL FIJO DROGUE</t>
         </is>
       </c>
     </row>
@@ -6009,7 +6009,7 @@
       </c>
       <c r="I270" s="11" t="inlineStr">
         <is>
-          <t>DROGUE DSTO COMERCIAL FIJO</t>
+          <t>DCF DSCTO 20.181.100.045.651 DSTO COMERCIAL FIJO DROGUE</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="I271" s="11" t="inlineStr">
         <is>
-          <t>FACT PROVEED VPP2 2020716</t>
+          <t>VPP2 2020716</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="I272" s="11" t="inlineStr">
         <is>
-          <t>PERFUME DESCUENTO CALENDARI</t>
+          <t>DCA DSCTO 20.251.200.196.961 DESCUENTO CALENDARI PERFUME</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="I273" s="11" t="inlineStr">
         <is>
-          <t>PERFUME DEVOLUCIONES</t>
+          <t>DND DSCTO 20.171.200.014.220 DEVOLUCIONES PERFUME</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="I274" s="11" t="inlineStr">
         <is>
-          <t>PERFUME DSTO COMERCIAL FIJO</t>
+          <t>DCF DSCTO 20.171.200.014.220 DSTO COMERCIAL FIJO PERFUME</t>
         </is>
       </c>
     </row>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="I275" s="11" t="inlineStr">
         <is>
-          <t>PERFUME DSTO COMERCIAL FIJO</t>
+          <t>DCF DSCTO 20.181.200.033.536 DSTO COMERCIAL FIJO PERFUME</t>
         </is>
       </c>
     </row>
@@ -6207,7 +6207,7 @@
       </c>
       <c r="I276" s="11" t="inlineStr">
         <is>
-          <t>PLATOS DESCUENTO APERTURA</t>
+          <t>DAT DSCTO 20.252.600.197.745 DESCUENTO APERTURA PLATOS</t>
         </is>
       </c>
     </row>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="I277" s="11" t="inlineStr">
         <is>
-          <t>PLATOS DESCUENTO COMPRAS</t>
+          <t>DCC DSCTO 20.222.600.126.372 DESCUENTO COMPRAS PLATOS</t>
         </is>
       </c>
     </row>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="I278" s="11" t="inlineStr">
         <is>
-          <t>PLATOS DSTO COMERCIAL FIJO</t>
+          <t>DCF DSCTO 20.222.600.126.372 DSTO COMERCIAL FIJO PLATOS</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="I279" s="11" t="inlineStr">
         <is>
-          <t>RANCHO DESCUENTO</t>
+          <t>RPL DSCTO 0 DESCUENTO RANCHO</t>
         </is>
       </c>
     </row>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="I280" s="11" t="inlineStr">
         <is>
-          <t>RANCHO DESCUENTO CALENDARI</t>
+          <t>DCA DSCTO 20.251.400.197.145 DESCUENTO CALENDARI RANCHO</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="I281" s="11" t="inlineStr">
         <is>
-          <t>RANCHO DESCUENTO CALENDARI</t>
+          <t>DCA DSCTO 20.251.400.197.146 DESCUENTO CALENDARI RANCHO</t>
         </is>
       </c>
     </row>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="I282" s="11" t="inlineStr">
         <is>
-          <t>RANCHO DESCUENTO CALENDARI</t>
+          <t>DCA DSCTO 20.251.400.197.147 DESCUENTO CALENDARI RANCHO</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="I283" s="11" t="inlineStr">
         <is>
-          <t>RANCHO DESCUENTO CALENDARI</t>
+          <t>DCA DSCTO 20.251.400.197.148 DESCUENTO CALENDARI RANCHO</t>
         </is>
       </c>
     </row>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="I284" s="11" t="inlineStr">
         <is>
-          <t>RANCHO DESCUENTO EN PRIMER</t>
+          <t>DPC DSCTO 0 DESCUENTO EN PRIMER RANCHO</t>
         </is>
       </c>
     </row>
@@ -7362,14 +7362,14 @@
       </c>
       <c r="I311" s="11" t="inlineStr">
         <is>
-          <t>Costo de Transferen Costo de Transferen</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="C312" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Descuento Cliente</t>
         </is>
       </c>
       <c r="D312" s="10" t="inlineStr">

--- a/Pruebas/Archivos/Template/Colombia/Template_HRC_Cenco.xlsx
+++ b/Pruebas/Archivos/Template/Colombia/Template_HRC_Cenco.xlsx
@@ -583,7 +583,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>24/10/2025</t>
+          <t>30/10/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">

--- a/Pruebas/Archivos/Template/Colombia/Template_HRC_Cenco.xlsx
+++ b/Pruebas/Archivos/Template/Colombia/Template_HRC_Cenco.xlsx
@@ -583,7 +583,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>30/10/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">

--- a/Pruebas/Archivos/Template/Colombia/Template_HRC_Cenco.xlsx
+++ b/Pruebas/Archivos/Template/Colombia/Template_HRC_Cenco.xlsx
@@ -543,8 +543,10 @@
           <t>Codigo de Cliente</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
-        <v>10267301</v>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>10267301.0</t>
+        </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>

--- a/Pruebas/Archivos/Template/Colombia/Template_HRC_Cenco.xlsx
+++ b/Pruebas/Archivos/Template/Colombia/Template_HRC_Cenco.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I482"/>
+  <dimension ref="A1:I481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -543,10 +543,8 @@
           <t>Codigo de Cliente</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>10267301.0</t>
-        </is>
+      <c r="D8" s="4" t="n">
+        <v>10267301</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -585,7 +583,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>26/11/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5981,16 +5979,16 @@
       </c>
       <c r="D273" s="10" t="inlineStr">
         <is>
-          <t>PMP128777746</t>
+          <t>PMP1287828</t>
         </is>
       </c>
       <c r="E273" s="6" t="n">
-        <v>1037493</v>
+        <v>74107639</v>
       </c>
       <c r="F273" s="10" t="inlineStr"/>
       <c r="G273" s="10" t="inlineStr"/>
       <c r="H273" s="6" t="n">
-        <v>1037493</v>
+        <v>74107639</v>
       </c>
       <c r="I273" s="11" t="inlineStr"/>
     </row>
@@ -6002,16 +6000,16 @@
       </c>
       <c r="D274" s="10" t="inlineStr">
         <is>
-          <t>PMP1287828</t>
+          <t>PMP1287829</t>
         </is>
       </c>
       <c r="E274" s="6" t="n">
-        <v>74107639</v>
+        <v>1247668</v>
       </c>
       <c r="F274" s="10" t="inlineStr"/>
       <c r="G274" s="10" t="inlineStr"/>
       <c r="H274" s="6" t="n">
-        <v>74107639</v>
+        <v>1247668</v>
       </c>
       <c r="I274" s="11" t="inlineStr"/>
     </row>
@@ -6023,16 +6021,16 @@
       </c>
       <c r="D275" s="10" t="inlineStr">
         <is>
-          <t>PMP1287829</t>
+          <t>PMP1287832</t>
         </is>
       </c>
       <c r="E275" s="6" t="n">
-        <v>1247668</v>
+        <v>1320847</v>
       </c>
       <c r="F275" s="10" t="inlineStr"/>
       <c r="G275" s="10" t="inlineStr"/>
       <c r="H275" s="6" t="n">
-        <v>1247668</v>
+        <v>1320847</v>
       </c>
       <c r="I275" s="11" t="inlineStr"/>
     </row>
@@ -6044,16 +6042,16 @@
       </c>
       <c r="D276" s="10" t="inlineStr">
         <is>
-          <t>PMP1287832</t>
+          <t>PMP1287840</t>
         </is>
       </c>
       <c r="E276" s="6" t="n">
-        <v>1320847</v>
+        <v>3227009</v>
       </c>
       <c r="F276" s="10" t="inlineStr"/>
       <c r="G276" s="10" t="inlineStr"/>
       <c r="H276" s="6" t="n">
-        <v>1320847</v>
+        <v>3227009</v>
       </c>
       <c r="I276" s="11" t="inlineStr"/>
     </row>
@@ -6065,16 +6063,16 @@
       </c>
       <c r="D277" s="10" t="inlineStr">
         <is>
-          <t>PMP1287840</t>
+          <t>PMP1287902</t>
         </is>
       </c>
       <c r="E277" s="6" t="n">
-        <v>3227009</v>
+        <v>6399365.1</v>
       </c>
       <c r="F277" s="10" t="inlineStr"/>
       <c r="G277" s="10" t="inlineStr"/>
       <c r="H277" s="6" t="n">
-        <v>3227009</v>
+        <v>6399365.1</v>
       </c>
       <c r="I277" s="11" t="inlineStr"/>
     </row>
@@ -6086,16 +6084,16 @@
       </c>
       <c r="D278" s="10" t="inlineStr">
         <is>
-          <t>PMP1287902</t>
+          <t>PMP1287903</t>
         </is>
       </c>
       <c r="E278" s="6" t="n">
-        <v>6399365.1</v>
+        <v>15015558.82</v>
       </c>
       <c r="F278" s="10" t="inlineStr"/>
       <c r="G278" s="10" t="inlineStr"/>
       <c r="H278" s="6" t="n">
-        <v>6399365.1</v>
+        <v>15015558.82</v>
       </c>
       <c r="I278" s="11" t="inlineStr"/>
     </row>
@@ -6107,16 +6105,16 @@
       </c>
       <c r="D279" s="10" t="inlineStr">
         <is>
-          <t>PMP1287903</t>
+          <t>PMP1287904</t>
         </is>
       </c>
       <c r="E279" s="6" t="n">
-        <v>15015558.82</v>
+        <v>1789999.44</v>
       </c>
       <c r="F279" s="10" t="inlineStr"/>
       <c r="G279" s="10" t="inlineStr"/>
       <c r="H279" s="6" t="n">
-        <v>15015558.82</v>
+        <v>1789999.44</v>
       </c>
       <c r="I279" s="11" t="inlineStr"/>
     </row>
@@ -6128,16 +6126,16 @@
       </c>
       <c r="D280" s="10" t="inlineStr">
         <is>
-          <t>PMP1287904</t>
+          <t>PMP1287905</t>
         </is>
       </c>
       <c r="E280" s="6" t="n">
-        <v>1789999.44</v>
+        <v>2011591.78</v>
       </c>
       <c r="F280" s="10" t="inlineStr"/>
       <c r="G280" s="10" t="inlineStr"/>
       <c r="H280" s="6" t="n">
-        <v>1789999.44</v>
+        <v>2011591.78</v>
       </c>
       <c r="I280" s="11" t="inlineStr"/>
     </row>
@@ -6149,16 +6147,16 @@
       </c>
       <c r="D281" s="10" t="inlineStr">
         <is>
-          <t>PMP1287905</t>
+          <t>PMP1287906</t>
         </is>
       </c>
       <c r="E281" s="6" t="n">
-        <v>2011591.78</v>
+        <v>30134724.48</v>
       </c>
       <c r="F281" s="10" t="inlineStr"/>
       <c r="G281" s="10" t="inlineStr"/>
       <c r="H281" s="6" t="n">
-        <v>2011591.78</v>
+        <v>30134724.48</v>
       </c>
       <c r="I281" s="11" t="inlineStr"/>
     </row>
@@ -6170,16 +6168,16 @@
       </c>
       <c r="D282" s="10" t="inlineStr">
         <is>
-          <t>PMP1287906</t>
+          <t>PMP1287907</t>
         </is>
       </c>
       <c r="E282" s="6" t="n">
-        <v>30134724.48</v>
+        <v>350399.84</v>
       </c>
       <c r="F282" s="10" t="inlineStr"/>
       <c r="G282" s="10" t="inlineStr"/>
       <c r="H282" s="6" t="n">
-        <v>30134724.48</v>
+        <v>350399.84</v>
       </c>
       <c r="I282" s="11" t="inlineStr"/>
     </row>
@@ -6191,16 +6189,16 @@
       </c>
       <c r="D283" s="10" t="inlineStr">
         <is>
-          <t>PMP1287907</t>
+          <t>PMP1287908</t>
         </is>
       </c>
       <c r="E283" s="6" t="n">
-        <v>350399.84</v>
+        <v>22208692.88</v>
       </c>
       <c r="F283" s="10" t="inlineStr"/>
       <c r="G283" s="10" t="inlineStr"/>
       <c r="H283" s="6" t="n">
-        <v>350399.84</v>
+        <v>22208692.88</v>
       </c>
       <c r="I283" s="11" t="inlineStr"/>
     </row>
@@ -6212,16 +6210,16 @@
       </c>
       <c r="D284" s="10" t="inlineStr">
         <is>
-          <t>PMP1287908</t>
+          <t>PMP1287909</t>
         </is>
       </c>
       <c r="E284" s="6" t="n">
-        <v>22208692.88</v>
+        <v>3356758.4</v>
       </c>
       <c r="F284" s="10" t="inlineStr"/>
       <c r="G284" s="10" t="inlineStr"/>
       <c r="H284" s="6" t="n">
-        <v>22208692.88</v>
+        <v>3356758.4</v>
       </c>
       <c r="I284" s="11" t="inlineStr"/>
     </row>
@@ -6233,16 +6231,16 @@
       </c>
       <c r="D285" s="10" t="inlineStr">
         <is>
-          <t>PMP1287909</t>
+          <t>PMP1287910</t>
         </is>
       </c>
       <c r="E285" s="6" t="n">
-        <v>3356758.4</v>
+        <v>1652220.24</v>
       </c>
       <c r="F285" s="10" t="inlineStr"/>
       <c r="G285" s="10" t="inlineStr"/>
       <c r="H285" s="6" t="n">
-        <v>3356758.4</v>
+        <v>1652220.24</v>
       </c>
       <c r="I285" s="11" t="inlineStr"/>
     </row>
@@ -6254,16 +6252,16 @@
       </c>
       <c r="D286" s="10" t="inlineStr">
         <is>
-          <t>PMP1287910</t>
+          <t>PMP1287911</t>
         </is>
       </c>
       <c r="E286" s="6" t="n">
-        <v>1652220.24</v>
+        <v>8419652.6</v>
       </c>
       <c r="F286" s="10" t="inlineStr"/>
       <c r="G286" s="10" t="inlineStr"/>
       <c r="H286" s="6" t="n">
-        <v>1652220.24</v>
+        <v>8419652.6</v>
       </c>
       <c r="I286" s="11" t="inlineStr"/>
     </row>
@@ -6275,16 +6273,16 @@
       </c>
       <c r="D287" s="10" t="inlineStr">
         <is>
-          <t>PMP1287911</t>
+          <t>PMP1287912</t>
         </is>
       </c>
       <c r="E287" s="6" t="n">
-        <v>8419652.6</v>
+        <v>10155439.94</v>
       </c>
       <c r="F287" s="10" t="inlineStr"/>
       <c r="G287" s="10" t="inlineStr"/>
       <c r="H287" s="6" t="n">
-        <v>8419652.6</v>
+        <v>10155439.94</v>
       </c>
       <c r="I287" s="11" t="inlineStr"/>
     </row>
@@ -6296,16 +6294,16 @@
       </c>
       <c r="D288" s="10" t="inlineStr">
         <is>
-          <t>PMP1287912</t>
+          <t>PMP1287913</t>
         </is>
       </c>
       <c r="E288" s="6" t="n">
-        <v>10155439.94</v>
+        <v>9254987.08</v>
       </c>
       <c r="F288" s="10" t="inlineStr"/>
       <c r="G288" s="10" t="inlineStr"/>
       <c r="H288" s="6" t="n">
-        <v>10155439.94</v>
+        <v>9254987.08</v>
       </c>
       <c r="I288" s="11" t="inlineStr"/>
     </row>
@@ -6317,16 +6315,16 @@
       </c>
       <c r="D289" s="10" t="inlineStr">
         <is>
-          <t>PMP1287913</t>
+          <t>PMP1287914</t>
         </is>
       </c>
       <c r="E289" s="6" t="n">
-        <v>9254987.08</v>
+        <v>47830822.72</v>
       </c>
       <c r="F289" s="10" t="inlineStr"/>
       <c r="G289" s="10" t="inlineStr"/>
       <c r="H289" s="6" t="n">
-        <v>9254987.08</v>
+        <v>47830822.72</v>
       </c>
       <c r="I289" s="11" t="inlineStr"/>
     </row>
@@ -6338,16 +6336,16 @@
       </c>
       <c r="D290" s="10" t="inlineStr">
         <is>
-          <t>PMP1287914</t>
+          <t>PMP1287915</t>
         </is>
       </c>
       <c r="E290" s="6" t="n">
-        <v>47830822.72</v>
+        <v>805242</v>
       </c>
       <c r="F290" s="10" t="inlineStr"/>
       <c r="G290" s="10" t="inlineStr"/>
       <c r="H290" s="6" t="n">
-        <v>47830822.72</v>
+        <v>805242</v>
       </c>
       <c r="I290" s="11" t="inlineStr"/>
     </row>
@@ -6359,16 +6357,16 @@
       </c>
       <c r="D291" s="10" t="inlineStr">
         <is>
-          <t>PMP1287915</t>
+          <t>PMP1287916</t>
         </is>
       </c>
       <c r="E291" s="6" t="n">
-        <v>805242</v>
+        <v>8525729.9</v>
       </c>
       <c r="F291" s="10" t="inlineStr"/>
       <c r="G291" s="10" t="inlineStr"/>
       <c r="H291" s="6" t="n">
-        <v>805242</v>
+        <v>8525729.9</v>
       </c>
       <c r="I291" s="11" t="inlineStr"/>
     </row>
@@ -6380,16 +6378,16 @@
       </c>
       <c r="D292" s="10" t="inlineStr">
         <is>
-          <t>PMP1287916</t>
+          <t>PMP1287917</t>
         </is>
       </c>
       <c r="E292" s="6" t="n">
-        <v>8525729.9</v>
+        <v>74511554.95999999</v>
       </c>
       <c r="F292" s="10" t="inlineStr"/>
       <c r="G292" s="10" t="inlineStr"/>
       <c r="H292" s="6" t="n">
-        <v>8525729.9</v>
+        <v>74511554.95999999</v>
       </c>
       <c r="I292" s="11" t="inlineStr"/>
     </row>
@@ -6401,16 +6399,16 @@
       </c>
       <c r="D293" s="10" t="inlineStr">
         <is>
-          <t>PMP1287917</t>
+          <t>PMP1287918</t>
         </is>
       </c>
       <c r="E293" s="6" t="n">
-        <v>74511554.95999999</v>
+        <v>1121344.06</v>
       </c>
       <c r="F293" s="10" t="inlineStr"/>
       <c r="G293" s="10" t="inlineStr"/>
       <c r="H293" s="6" t="n">
-        <v>74511554.95999999</v>
+        <v>1121344.06</v>
       </c>
       <c r="I293" s="11" t="inlineStr"/>
     </row>
@@ -6422,16 +6420,16 @@
       </c>
       <c r="D294" s="10" t="inlineStr">
         <is>
-          <t>PMP1287918</t>
+          <t>PMP1287919</t>
         </is>
       </c>
       <c r="E294" s="6" t="n">
-        <v>1121344.06</v>
+        <v>482499.76</v>
       </c>
       <c r="F294" s="10" t="inlineStr"/>
       <c r="G294" s="10" t="inlineStr"/>
       <c r="H294" s="6" t="n">
-        <v>1121344.06</v>
+        <v>482499.76</v>
       </c>
       <c r="I294" s="11" t="inlineStr"/>
     </row>
@@ -6443,16 +6441,16 @@
       </c>
       <c r="D295" s="10" t="inlineStr">
         <is>
-          <t>PMP1287919</t>
+          <t>PMP1287920</t>
         </is>
       </c>
       <c r="E295" s="6" t="n">
-        <v>482499.76</v>
+        <v>9163311.24</v>
       </c>
       <c r="F295" s="10" t="inlineStr"/>
       <c r="G295" s="10" t="inlineStr"/>
       <c r="H295" s="6" t="n">
-        <v>482499.76</v>
+        <v>9163311.24</v>
       </c>
       <c r="I295" s="11" t="inlineStr"/>
     </row>
@@ -6464,16 +6462,16 @@
       </c>
       <c r="D296" s="10" t="inlineStr">
         <is>
-          <t>PMP1287920</t>
+          <t>PMP1287921</t>
         </is>
       </c>
       <c r="E296" s="6" t="n">
-        <v>9163311.24</v>
+        <v>45864789.2</v>
       </c>
       <c r="F296" s="10" t="inlineStr"/>
       <c r="G296" s="10" t="inlineStr"/>
       <c r="H296" s="6" t="n">
-        <v>9163311.24</v>
+        <v>45864789.2</v>
       </c>
       <c r="I296" s="11" t="inlineStr"/>
     </row>
@@ -6485,16 +6483,16 @@
       </c>
       <c r="D297" s="10" t="inlineStr">
         <is>
-          <t>PMP1287921</t>
+          <t>PMP1287922</t>
         </is>
       </c>
       <c r="E297" s="6" t="n">
-        <v>45864789.2</v>
+        <v>18830857</v>
       </c>
       <c r="F297" s="10" t="inlineStr"/>
       <c r="G297" s="10" t="inlineStr"/>
       <c r="H297" s="6" t="n">
-        <v>45864789.2</v>
+        <v>18830857</v>
       </c>
       <c r="I297" s="11" t="inlineStr"/>
     </row>
@@ -6506,16 +6504,16 @@
       </c>
       <c r="D298" s="10" t="inlineStr">
         <is>
-          <t>PMP1287922</t>
+          <t>PMP1287923</t>
         </is>
       </c>
       <c r="E298" s="6" t="n">
-        <v>18830857</v>
+        <v>2849442.34</v>
       </c>
       <c r="F298" s="10" t="inlineStr"/>
       <c r="G298" s="10" t="inlineStr"/>
       <c r="H298" s="6" t="n">
-        <v>18830857</v>
+        <v>2849442.34</v>
       </c>
       <c r="I298" s="11" t="inlineStr"/>
     </row>
@@ -6527,16 +6525,16 @@
       </c>
       <c r="D299" s="10" t="inlineStr">
         <is>
-          <t>PMP1287923</t>
+          <t>PMP1287924</t>
         </is>
       </c>
       <c r="E299" s="6" t="n">
-        <v>2849442.34</v>
+        <v>3643403.36</v>
       </c>
       <c r="F299" s="10" t="inlineStr"/>
       <c r="G299" s="10" t="inlineStr"/>
       <c r="H299" s="6" t="n">
-        <v>2849442.34</v>
+        <v>3643403.36</v>
       </c>
       <c r="I299" s="11" t="inlineStr"/>
     </row>
@@ -6548,16 +6546,16 @@
       </c>
       <c r="D300" s="10" t="inlineStr">
         <is>
-          <t>PMP1287924</t>
+          <t>PMP1287925</t>
         </is>
       </c>
       <c r="E300" s="6" t="n">
-        <v>3643403.36</v>
+        <v>35508391.7</v>
       </c>
       <c r="F300" s="10" t="inlineStr"/>
       <c r="G300" s="10" t="inlineStr"/>
       <c r="H300" s="6" t="n">
-        <v>3643403.36</v>
+        <v>35508391.7</v>
       </c>
       <c r="I300" s="11" t="inlineStr"/>
     </row>
@@ -6569,16 +6567,16 @@
       </c>
       <c r="D301" s="10" t="inlineStr">
         <is>
-          <t>PMP1287925</t>
+          <t>PMP1287926</t>
         </is>
       </c>
       <c r="E301" s="6" t="n">
-        <v>35508391.7</v>
+        <v>3699116.6</v>
       </c>
       <c r="F301" s="10" t="inlineStr"/>
       <c r="G301" s="10" t="inlineStr"/>
       <c r="H301" s="6" t="n">
-        <v>35508391.7</v>
+        <v>3699116.6</v>
       </c>
       <c r="I301" s="11" t="inlineStr"/>
     </row>
@@ -6590,16 +6588,16 @@
       </c>
       <c r="D302" s="10" t="inlineStr">
         <is>
-          <t>PMP1287926</t>
+          <t>PMP1287927</t>
         </is>
       </c>
       <c r="E302" s="6" t="n">
-        <v>3699116.6</v>
+        <v>26720655.32</v>
       </c>
       <c r="F302" s="10" t="inlineStr"/>
       <c r="G302" s="10" t="inlineStr"/>
       <c r="H302" s="6" t="n">
-        <v>3699116.6</v>
+        <v>26720655.32</v>
       </c>
       <c r="I302" s="11" t="inlineStr"/>
     </row>
@@ -6611,16 +6609,16 @@
       </c>
       <c r="D303" s="10" t="inlineStr">
         <is>
-          <t>PMP1287927</t>
+          <t>PMP1287928</t>
         </is>
       </c>
       <c r="E303" s="6" t="n">
-        <v>26720655.32</v>
+        <v>47391727.46</v>
       </c>
       <c r="F303" s="10" t="inlineStr"/>
       <c r="G303" s="10" t="inlineStr"/>
       <c r="H303" s="6" t="n">
-        <v>26720655.32</v>
+        <v>47391727.46</v>
       </c>
       <c r="I303" s="11" t="inlineStr"/>
     </row>
@@ -6632,16 +6630,16 @@
       </c>
       <c r="D304" s="10" t="inlineStr">
         <is>
-          <t>PMP1287928</t>
+          <t>PMP1287929</t>
         </is>
       </c>
       <c r="E304" s="6" t="n">
-        <v>47391727.46</v>
+        <v>12084981.6</v>
       </c>
       <c r="F304" s="10" t="inlineStr"/>
       <c r="G304" s="10" t="inlineStr"/>
       <c r="H304" s="6" t="n">
-        <v>47391727.46</v>
+        <v>12084981.6</v>
       </c>
       <c r="I304" s="11" t="inlineStr"/>
     </row>
@@ -6653,16 +6651,16 @@
       </c>
       <c r="D305" s="10" t="inlineStr">
         <is>
-          <t>PMP1287929</t>
+          <t>PMP1287930</t>
         </is>
       </c>
       <c r="E305" s="6" t="n">
-        <v>12084981.6</v>
+        <v>7245456.9</v>
       </c>
       <c r="F305" s="10" t="inlineStr"/>
       <c r="G305" s="10" t="inlineStr"/>
       <c r="H305" s="6" t="n">
-        <v>12084981.6</v>
+        <v>7245456.9</v>
       </c>
       <c r="I305" s="11" t="inlineStr"/>
     </row>
@@ -6674,16 +6672,16 @@
       </c>
       <c r="D306" s="10" t="inlineStr">
         <is>
-          <t>PMP1287930</t>
+          <t>PMP1287931</t>
         </is>
       </c>
       <c r="E306" s="6" t="n">
-        <v>7245456.9</v>
+        <v>1699030.16</v>
       </c>
       <c r="F306" s="10" t="inlineStr"/>
       <c r="G306" s="10" t="inlineStr"/>
       <c r="H306" s="6" t="n">
-        <v>7245456.9</v>
+        <v>1699030.16</v>
       </c>
       <c r="I306" s="11" t="inlineStr"/>
     </row>
@@ -6695,16 +6693,16 @@
       </c>
       <c r="D307" s="10" t="inlineStr">
         <is>
-          <t>PMP1287931</t>
+          <t>PMP1287932</t>
         </is>
       </c>
       <c r="E307" s="6" t="n">
-        <v>1699030.16</v>
+        <v>7705372.76</v>
       </c>
       <c r="F307" s="10" t="inlineStr"/>
       <c r="G307" s="10" t="inlineStr"/>
       <c r="H307" s="6" t="n">
-        <v>1699030.16</v>
+        <v>7705372.76</v>
       </c>
       <c r="I307" s="11" t="inlineStr"/>
     </row>
@@ -6716,16 +6714,16 @@
       </c>
       <c r="D308" s="10" t="inlineStr">
         <is>
-          <t>PMP1287932</t>
+          <t>PMP1287933</t>
         </is>
       </c>
       <c r="E308" s="6" t="n">
-        <v>7705372.76</v>
+        <v>5353502.2</v>
       </c>
       <c r="F308" s="10" t="inlineStr"/>
       <c r="G308" s="10" t="inlineStr"/>
       <c r="H308" s="6" t="n">
-        <v>7705372.76</v>
+        <v>5353502.2</v>
       </c>
       <c r="I308" s="11" t="inlineStr"/>
     </row>
@@ -6737,16 +6735,16 @@
       </c>
       <c r="D309" s="10" t="inlineStr">
         <is>
-          <t>PMP1287933</t>
+          <t>PMP1287941</t>
         </is>
       </c>
       <c r="E309" s="6" t="n">
-        <v>5353502.2</v>
+        <v>91532952.95999999</v>
       </c>
       <c r="F309" s="10" t="inlineStr"/>
       <c r="G309" s="10" t="inlineStr"/>
       <c r="H309" s="6" t="n">
-        <v>5353502.2</v>
+        <v>91532952.95999999</v>
       </c>
       <c r="I309" s="11" t="inlineStr"/>
     </row>
@@ -6758,16 +6756,16 @@
       </c>
       <c r="D310" s="10" t="inlineStr">
         <is>
-          <t>PMP1287941</t>
+          <t>PMP1287942</t>
         </is>
       </c>
       <c r="E310" s="6" t="n">
-        <v>91532952.95999999</v>
+        <v>1555511.66</v>
       </c>
       <c r="F310" s="10" t="inlineStr"/>
       <c r="G310" s="10" t="inlineStr"/>
       <c r="H310" s="6" t="n">
-        <v>91532952.95999999</v>
+        <v>1555511.66</v>
       </c>
       <c r="I310" s="11" t="inlineStr"/>
     </row>
@@ -6779,16 +6777,16 @@
       </c>
       <c r="D311" s="10" t="inlineStr">
         <is>
-          <t>PMP1287942</t>
+          <t>PMP1287943</t>
         </is>
       </c>
       <c r="E311" s="6" t="n">
-        <v>1555511.66</v>
+        <v>3452491</v>
       </c>
       <c r="F311" s="10" t="inlineStr"/>
       <c r="G311" s="10" t="inlineStr"/>
       <c r="H311" s="6" t="n">
-        <v>1555511.66</v>
+        <v>3452491</v>
       </c>
       <c r="I311" s="11" t="inlineStr"/>
     </row>
@@ -6800,16 +6798,16 @@
       </c>
       <c r="D312" s="10" t="inlineStr">
         <is>
-          <t>PMP1287943</t>
+          <t>PMP1287944</t>
         </is>
       </c>
       <c r="E312" s="6" t="n">
-        <v>3452491</v>
+        <v>5725834.48</v>
       </c>
       <c r="F312" s="10" t="inlineStr"/>
       <c r="G312" s="10" t="inlineStr"/>
       <c r="H312" s="6" t="n">
-        <v>3452491</v>
+        <v>5725834.48</v>
       </c>
       <c r="I312" s="11" t="inlineStr"/>
     </row>
@@ -6821,16 +6819,16 @@
       </c>
       <c r="D313" s="10" t="inlineStr">
         <is>
-          <t>PMP1287944</t>
+          <t>PMP1287945</t>
         </is>
       </c>
       <c r="E313" s="6" t="n">
-        <v>5725834.48</v>
+        <v>538998.6</v>
       </c>
       <c r="F313" s="10" t="inlineStr"/>
       <c r="G313" s="10" t="inlineStr"/>
       <c r="H313" s="6" t="n">
-        <v>5725834.48</v>
+        <v>538998.6</v>
       </c>
       <c r="I313" s="11" t="inlineStr"/>
     </row>
@@ -6842,16 +6840,16 @@
       </c>
       <c r="D314" s="10" t="inlineStr">
         <is>
-          <t>PMP1287945</t>
+          <t>PMP1287946</t>
         </is>
       </c>
       <c r="E314" s="6" t="n">
-        <v>538998.6</v>
+        <v>1980696.5</v>
       </c>
       <c r="F314" s="10" t="inlineStr"/>
       <c r="G314" s="10" t="inlineStr"/>
       <c r="H314" s="6" t="n">
-        <v>538998.6</v>
+        <v>1980696.5</v>
       </c>
       <c r="I314" s="11" t="inlineStr"/>
     </row>
@@ -6863,16 +6861,16 @@
       </c>
       <c r="D315" s="10" t="inlineStr">
         <is>
-          <t>PMP1287946</t>
+          <t>PMP1287947</t>
         </is>
       </c>
       <c r="E315" s="6" t="n">
-        <v>1980696.5</v>
+        <v>122718448.04</v>
       </c>
       <c r="F315" s="10" t="inlineStr"/>
       <c r="G315" s="10" t="inlineStr"/>
       <c r="H315" s="6" t="n">
-        <v>1980696.5</v>
+        <v>122718448.04</v>
       </c>
       <c r="I315" s="11" t="inlineStr"/>
     </row>
@@ -6884,16 +6882,16 @@
       </c>
       <c r="D316" s="10" t="inlineStr">
         <is>
-          <t>PMP1287947</t>
+          <t>PMP1287948</t>
         </is>
       </c>
       <c r="E316" s="6" t="n">
-        <v>122718448.04</v>
+        <v>3745477.2</v>
       </c>
       <c r="F316" s="10" t="inlineStr"/>
       <c r="G316" s="10" t="inlineStr"/>
       <c r="H316" s="6" t="n">
-        <v>122718448.04</v>
+        <v>3745477.2</v>
       </c>
       <c r="I316" s="11" t="inlineStr"/>
     </row>
@@ -6905,16 +6903,16 @@
       </c>
       <c r="D317" s="10" t="inlineStr">
         <is>
-          <t>PMP1287948</t>
+          <t>PMP1287949</t>
         </is>
       </c>
       <c r="E317" s="6" t="n">
-        <v>3745477.2</v>
+        <v>129467596.7</v>
       </c>
       <c r="F317" s="10" t="inlineStr"/>
       <c r="G317" s="10" t="inlineStr"/>
       <c r="H317" s="6" t="n">
-        <v>3745477.2</v>
+        <v>129467596.7</v>
       </c>
       <c r="I317" s="11" t="inlineStr"/>
     </row>
@@ -6926,16 +6924,16 @@
       </c>
       <c r="D318" s="10" t="inlineStr">
         <is>
-          <t>PMP1287949</t>
+          <t>PMP1287950</t>
         </is>
       </c>
       <c r="E318" s="6" t="n">
-        <v>129467596.7</v>
+        <v>9733345.6</v>
       </c>
       <c r="F318" s="10" t="inlineStr"/>
       <c r="G318" s="10" t="inlineStr"/>
       <c r="H318" s="6" t="n">
-        <v>129467596.7</v>
+        <v>9733345.6</v>
       </c>
       <c r="I318" s="11" t="inlineStr"/>
     </row>
@@ -6947,16 +6945,16 @@
       </c>
       <c r="D319" s="10" t="inlineStr">
         <is>
-          <t>PMP1287950</t>
+          <t>PMP1287951</t>
         </is>
       </c>
       <c r="E319" s="6" t="n">
-        <v>9733345.6</v>
+        <v>327458353.16</v>
       </c>
       <c r="F319" s="10" t="inlineStr"/>
       <c r="G319" s="10" t="inlineStr"/>
       <c r="H319" s="6" t="n">
-        <v>9733345.6</v>
+        <v>327458353.16</v>
       </c>
       <c r="I319" s="11" t="inlineStr"/>
     </row>
@@ -6968,16 +6966,16 @@
       </c>
       <c r="D320" s="10" t="inlineStr">
         <is>
-          <t>PMP1287951</t>
+          <t>PMP1287952</t>
         </is>
       </c>
       <c r="E320" s="6" t="n">
-        <v>327458353.16</v>
+        <v>28101905.68</v>
       </c>
       <c r="F320" s="10" t="inlineStr"/>
       <c r="G320" s="10" t="inlineStr"/>
       <c r="H320" s="6" t="n">
-        <v>327458353.16</v>
+        <v>28101905.68</v>
       </c>
       <c r="I320" s="11" t="inlineStr"/>
     </row>
@@ -6989,16 +6987,16 @@
       </c>
       <c r="D321" s="10" t="inlineStr">
         <is>
-          <t>PMP1287952</t>
+          <t>PMP1287953</t>
         </is>
       </c>
       <c r="E321" s="6" t="n">
-        <v>28101905.68</v>
+        <v>1102527.74</v>
       </c>
       <c r="F321" s="10" t="inlineStr"/>
       <c r="G321" s="10" t="inlineStr"/>
       <c r="H321" s="6" t="n">
-        <v>28101905.68</v>
+        <v>1102527.74</v>
       </c>
       <c r="I321" s="11" t="inlineStr"/>
     </row>
@@ -7010,16 +7008,16 @@
       </c>
       <c r="D322" s="10" t="inlineStr">
         <is>
-          <t>PMP1287953</t>
+          <t>PMP1287954</t>
         </is>
       </c>
       <c r="E322" s="6" t="n">
-        <v>1102527.74</v>
+        <v>83249216.12</v>
       </c>
       <c r="F322" s="10" t="inlineStr"/>
       <c r="G322" s="10" t="inlineStr"/>
       <c r="H322" s="6" t="n">
-        <v>1102527.74</v>
+        <v>83249216.12</v>
       </c>
       <c r="I322" s="11" t="inlineStr"/>
     </row>
@@ -7031,16 +7029,16 @@
       </c>
       <c r="D323" s="10" t="inlineStr">
         <is>
-          <t>PMP1287954</t>
+          <t>PMP1287955</t>
         </is>
       </c>
       <c r="E323" s="6" t="n">
-        <v>83249216.12</v>
+        <v>8815143.4</v>
       </c>
       <c r="F323" s="10" t="inlineStr"/>
       <c r="G323" s="10" t="inlineStr"/>
       <c r="H323" s="6" t="n">
-        <v>83249216.12</v>
+        <v>8815143.4</v>
       </c>
       <c r="I323" s="11" t="inlineStr"/>
     </row>
@@ -7052,16 +7050,16 @@
       </c>
       <c r="D324" s="10" t="inlineStr">
         <is>
-          <t>PMP1287955</t>
+          <t>PMP1287956</t>
         </is>
       </c>
       <c r="E324" s="6" t="n">
-        <v>8815143.4</v>
+        <v>42615074.1</v>
       </c>
       <c r="F324" s="10" t="inlineStr"/>
       <c r="G324" s="10" t="inlineStr"/>
       <c r="H324" s="6" t="n">
-        <v>8815143.4</v>
+        <v>42615074.1</v>
       </c>
       <c r="I324" s="11" t="inlineStr"/>
     </row>
@@ -7073,16 +7071,16 @@
       </c>
       <c r="D325" s="10" t="inlineStr">
         <is>
-          <t>PMP1287956</t>
+          <t>PMP1287957</t>
         </is>
       </c>
       <c r="E325" s="6" t="n">
-        <v>42615074.1</v>
+        <v>5664991.2</v>
       </c>
       <c r="F325" s="10" t="inlineStr"/>
       <c r="G325" s="10" t="inlineStr"/>
       <c r="H325" s="6" t="n">
-        <v>42615074.1</v>
+        <v>5664991.2</v>
       </c>
       <c r="I325" s="11" t="inlineStr"/>
     </row>
@@ -7094,16 +7092,16 @@
       </c>
       <c r="D326" s="10" t="inlineStr">
         <is>
-          <t>PMP1287957</t>
+          <t>PMP1288418</t>
         </is>
       </c>
       <c r="E326" s="6" t="n">
-        <v>5664991.2</v>
+        <v>327689421.73</v>
       </c>
       <c r="F326" s="10" t="inlineStr"/>
       <c r="G326" s="10" t="inlineStr"/>
       <c r="H326" s="6" t="n">
-        <v>5664991.2</v>
+        <v>327689421.73</v>
       </c>
       <c r="I326" s="11" t="inlineStr"/>
     </row>
@@ -7115,16 +7113,16 @@
       </c>
       <c r="D327" s="10" t="inlineStr">
         <is>
-          <t>PMP1288418</t>
+          <t>PMP1288698</t>
         </is>
       </c>
       <c r="E327" s="6" t="n">
-        <v>327689421.73</v>
+        <v>3290589.96</v>
       </c>
       <c r="F327" s="10" t="inlineStr"/>
       <c r="G327" s="10" t="inlineStr"/>
       <c r="H327" s="6" t="n">
-        <v>327689421.73</v>
+        <v>3290589.96</v>
       </c>
       <c r="I327" s="11" t="inlineStr"/>
     </row>
@@ -7136,16 +7134,16 @@
       </c>
       <c r="D328" s="10" t="inlineStr">
         <is>
-          <t>PMP1288698</t>
+          <t>PMP1288699</t>
         </is>
       </c>
       <c r="E328" s="6" t="n">
-        <v>3290589.96</v>
+        <v>10071045.24</v>
       </c>
       <c r="F328" s="10" t="inlineStr"/>
       <c r="G328" s="10" t="inlineStr"/>
       <c r="H328" s="6" t="n">
-        <v>3290589.96</v>
+        <v>10071045.24</v>
       </c>
       <c r="I328" s="11" t="inlineStr"/>
     </row>
@@ -7157,16 +7155,16 @@
       </c>
       <c r="D329" s="10" t="inlineStr">
         <is>
-          <t>PMP1288699</t>
+          <t>PMP1288700</t>
         </is>
       </c>
       <c r="E329" s="6" t="n">
-        <v>10071045.24</v>
+        <v>23124865</v>
       </c>
       <c r="F329" s="10" t="inlineStr"/>
       <c r="G329" s="10" t="inlineStr"/>
       <c r="H329" s="6" t="n">
-        <v>10071045.24</v>
+        <v>23124865</v>
       </c>
       <c r="I329" s="11" t="inlineStr"/>
     </row>
@@ -7178,16 +7176,16 @@
       </c>
       <c r="D330" s="10" t="inlineStr">
         <is>
-          <t>PMP1288700</t>
+          <t>PMP1288727</t>
         </is>
       </c>
       <c r="E330" s="6" t="n">
-        <v>23124865</v>
+        <v>63136753.48</v>
       </c>
       <c r="F330" s="10" t="inlineStr"/>
       <c r="G330" s="10" t="inlineStr"/>
       <c r="H330" s="6" t="n">
-        <v>23124865</v>
+        <v>63136753.48</v>
       </c>
       <c r="I330" s="11" t="inlineStr"/>
     </row>
@@ -7199,16 +7197,16 @@
       </c>
       <c r="D331" s="10" t="inlineStr">
         <is>
-          <t>PMP1288727</t>
+          <t>PMP1288728</t>
         </is>
       </c>
       <c r="E331" s="6" t="n">
-        <v>63136753.48</v>
+        <v>56858705.52</v>
       </c>
       <c r="F331" s="10" t="inlineStr"/>
       <c r="G331" s="10" t="inlineStr"/>
       <c r="H331" s="6" t="n">
-        <v>63136753.48</v>
+        <v>56858705.52</v>
       </c>
       <c r="I331" s="11" t="inlineStr"/>
     </row>
@@ -7220,16 +7218,16 @@
       </c>
       <c r="D332" s="10" t="inlineStr">
         <is>
-          <t>PMP1288728</t>
+          <t>PMP1288729</t>
         </is>
       </c>
       <c r="E332" s="6" t="n">
-        <v>56858705.52</v>
+        <v>8630705.82</v>
       </c>
       <c r="F332" s="10" t="inlineStr"/>
       <c r="G332" s="10" t="inlineStr"/>
       <c r="H332" s="6" t="n">
-        <v>56858705.52</v>
+        <v>8630705.82</v>
       </c>
       <c r="I332" s="11" t="inlineStr"/>
     </row>
@@ -7241,16 +7239,16 @@
       </c>
       <c r="D333" s="10" t="inlineStr">
         <is>
-          <t>PMP1288729</t>
+          <t>PMP1288730</t>
         </is>
       </c>
       <c r="E333" s="6" t="n">
-        <v>8630705.82</v>
+        <v>1954996.28</v>
       </c>
       <c r="F333" s="10" t="inlineStr"/>
       <c r="G333" s="10" t="inlineStr"/>
       <c r="H333" s="6" t="n">
-        <v>8630705.82</v>
+        <v>1954996.28</v>
       </c>
       <c r="I333" s="11" t="inlineStr"/>
     </row>
@@ -7262,16 +7260,16 @@
       </c>
       <c r="D334" s="10" t="inlineStr">
         <is>
-          <t>PMP1288730</t>
+          <t>PMP1288731</t>
         </is>
       </c>
       <c r="E334" s="6" t="n">
-        <v>1954996.28</v>
+        <v>29388682.31</v>
       </c>
       <c r="F334" s="10" t="inlineStr"/>
       <c r="G334" s="10" t="inlineStr"/>
       <c r="H334" s="6" t="n">
-        <v>1954996.28</v>
+        <v>29388682.31</v>
       </c>
       <c r="I334" s="11" t="inlineStr"/>
     </row>
@@ -7283,16 +7281,16 @@
       </c>
       <c r="D335" s="10" t="inlineStr">
         <is>
-          <t>PMP1288731</t>
+          <t>PMP1288918</t>
         </is>
       </c>
       <c r="E335" s="6" t="n">
-        <v>29388682.31</v>
+        <v>2630888</v>
       </c>
       <c r="F335" s="10" t="inlineStr"/>
       <c r="G335" s="10" t="inlineStr"/>
       <c r="H335" s="6" t="n">
-        <v>29388682.31</v>
+        <v>2630888</v>
       </c>
       <c r="I335" s="11" t="inlineStr"/>
     </row>
@@ -7304,16 +7302,16 @@
       </c>
       <c r="D336" s="10" t="inlineStr">
         <is>
-          <t>PMP1288918</t>
+          <t>PMP1288919</t>
         </is>
       </c>
       <c r="E336" s="6" t="n">
-        <v>2630888</v>
+        <v>8823195</v>
       </c>
       <c r="F336" s="10" t="inlineStr"/>
       <c r="G336" s="10" t="inlineStr"/>
       <c r="H336" s="6" t="n">
-        <v>2630888</v>
+        <v>8823195</v>
       </c>
       <c r="I336" s="11" t="inlineStr"/>
     </row>
@@ -7325,16 +7323,16 @@
       </c>
       <c r="D337" s="10" t="inlineStr">
         <is>
-          <t>PMP1288919</t>
+          <t>PMP1288921</t>
         </is>
       </c>
       <c r="E337" s="6" t="n">
-        <v>8823195</v>
+        <v>3185627.4</v>
       </c>
       <c r="F337" s="10" t="inlineStr"/>
       <c r="G337" s="10" t="inlineStr"/>
       <c r="H337" s="6" t="n">
-        <v>8823195</v>
+        <v>3185627.4</v>
       </c>
       <c r="I337" s="11" t="inlineStr"/>
     </row>
@@ -7346,16 +7344,16 @@
       </c>
       <c r="D338" s="10" t="inlineStr">
         <is>
-          <t>PMP1288921</t>
+          <t>PMP1288923</t>
         </is>
       </c>
       <c r="E338" s="6" t="n">
-        <v>3185627.4</v>
+        <v>6591930</v>
       </c>
       <c r="F338" s="10" t="inlineStr"/>
       <c r="G338" s="10" t="inlineStr"/>
       <c r="H338" s="6" t="n">
-        <v>3185627.4</v>
+        <v>6591930</v>
       </c>
       <c r="I338" s="11" t="inlineStr"/>
     </row>
@@ -7367,16 +7365,16 @@
       </c>
       <c r="D339" s="10" t="inlineStr">
         <is>
-          <t>PMP1288923</t>
+          <t>PMP1288926</t>
         </is>
       </c>
       <c r="E339" s="6" t="n">
-        <v>6591930</v>
+        <v>8299876.24</v>
       </c>
       <c r="F339" s="10" t="inlineStr"/>
       <c r="G339" s="10" t="inlineStr"/>
       <c r="H339" s="6" t="n">
-        <v>6591930</v>
+        <v>8299876.24</v>
       </c>
       <c r="I339" s="11" t="inlineStr"/>
     </row>
@@ -7388,16 +7386,16 @@
       </c>
       <c r="D340" s="10" t="inlineStr">
         <is>
-          <t>PMP1288926</t>
+          <t>PMP1288985</t>
         </is>
       </c>
       <c r="E340" s="6" t="n">
-        <v>8299876.24</v>
+        <v>28010960</v>
       </c>
       <c r="F340" s="10" t="inlineStr"/>
       <c r="G340" s="10" t="inlineStr"/>
       <c r="H340" s="6" t="n">
-        <v>8299876.24</v>
+        <v>28010960</v>
       </c>
       <c r="I340" s="11" t="inlineStr"/>
     </row>
@@ -7409,16 +7407,16 @@
       </c>
       <c r="D341" s="10" t="inlineStr">
         <is>
-          <t>PMP1288985</t>
+          <t>PMP1288986</t>
         </is>
       </c>
       <c r="E341" s="6" t="n">
-        <v>28010960</v>
+        <v>2337305</v>
       </c>
       <c r="F341" s="10" t="inlineStr"/>
       <c r="G341" s="10" t="inlineStr"/>
       <c r="H341" s="6" t="n">
-        <v>28010960</v>
+        <v>2337305</v>
       </c>
       <c r="I341" s="11" t="inlineStr"/>
     </row>
@@ -7430,16 +7428,16 @@
       </c>
       <c r="D342" s="10" t="inlineStr">
         <is>
-          <t>PMP1288986</t>
+          <t>PMP1288987</t>
         </is>
       </c>
       <c r="E342" s="6" t="n">
-        <v>2337305</v>
+        <v>66857791.84</v>
       </c>
       <c r="F342" s="10" t="inlineStr"/>
       <c r="G342" s="10" t="inlineStr"/>
       <c r="H342" s="6" t="n">
-        <v>2337305</v>
+        <v>66857791.84</v>
       </c>
       <c r="I342" s="11" t="inlineStr"/>
     </row>
@@ -7451,16 +7449,16 @@
       </c>
       <c r="D343" s="10" t="inlineStr">
         <is>
-          <t>PMP1288987</t>
+          <t>PMP1288988</t>
         </is>
       </c>
       <c r="E343" s="6" t="n">
-        <v>66857791.84</v>
+        <v>1460219</v>
       </c>
       <c r="F343" s="10" t="inlineStr"/>
       <c r="G343" s="10" t="inlineStr"/>
       <c r="H343" s="6" t="n">
-        <v>66857791.84</v>
+        <v>1460219</v>
       </c>
       <c r="I343" s="11" t="inlineStr"/>
     </row>
@@ -7472,16 +7470,16 @@
       </c>
       <c r="D344" s="10" t="inlineStr">
         <is>
-          <t>PMP1288988</t>
+          <t>PMP1288989</t>
         </is>
       </c>
       <c r="E344" s="6" t="n">
-        <v>1460219</v>
+        <v>18417964.8</v>
       </c>
       <c r="F344" s="10" t="inlineStr"/>
       <c r="G344" s="10" t="inlineStr"/>
       <c r="H344" s="6" t="n">
-        <v>1460219</v>
+        <v>18417964.8</v>
       </c>
       <c r="I344" s="11" t="inlineStr"/>
     </row>
@@ -7493,16 +7491,16 @@
       </c>
       <c r="D345" s="10" t="inlineStr">
         <is>
-          <t>PMP1288989</t>
+          <t>PMP1289244</t>
         </is>
       </c>
       <c r="E345" s="6" t="n">
-        <v>18417964.8</v>
+        <v>14222973.9</v>
       </c>
       <c r="F345" s="10" t="inlineStr"/>
       <c r="G345" s="10" t="inlineStr"/>
       <c r="H345" s="6" t="n">
-        <v>18417964.8</v>
+        <v>14222973.9</v>
       </c>
       <c r="I345" s="11" t="inlineStr"/>
     </row>
@@ -7514,16 +7512,16 @@
       </c>
       <c r="D346" s="10" t="inlineStr">
         <is>
-          <t>PMP1289244</t>
+          <t>PMP1289245</t>
         </is>
       </c>
       <c r="E346" s="6" t="n">
-        <v>14222973.9</v>
+        <v>8971591.359999999</v>
       </c>
       <c r="F346" s="10" t="inlineStr"/>
       <c r="G346" s="10" t="inlineStr"/>
       <c r="H346" s="6" t="n">
-        <v>14222973.9</v>
+        <v>8971591.359999999</v>
       </c>
       <c r="I346" s="11" t="inlineStr"/>
     </row>
@@ -7535,16 +7533,16 @@
       </c>
       <c r="D347" s="10" t="inlineStr">
         <is>
-          <t>PMP1289245</t>
+          <t>PMP1289246</t>
         </is>
       </c>
       <c r="E347" s="6" t="n">
-        <v>8971591.359999999</v>
+        <v>3796938.12</v>
       </c>
       <c r="F347" s="10" t="inlineStr"/>
       <c r="G347" s="10" t="inlineStr"/>
       <c r="H347" s="6" t="n">
-        <v>8971591.359999999</v>
+        <v>3796938.12</v>
       </c>
       <c r="I347" s="11" t="inlineStr"/>
     </row>
@@ -7556,16 +7554,16 @@
       </c>
       <c r="D348" s="10" t="inlineStr">
         <is>
-          <t>PMP1289246</t>
+          <t>PMP1289247</t>
         </is>
       </c>
       <c r="E348" s="6" t="n">
-        <v>3796938.12</v>
+        <v>6385710.32</v>
       </c>
       <c r="F348" s="10" t="inlineStr"/>
       <c r="G348" s="10" t="inlineStr"/>
       <c r="H348" s="6" t="n">
-        <v>3796938.12</v>
+        <v>6385710.32</v>
       </c>
       <c r="I348" s="11" t="inlineStr"/>
     </row>
@@ -7577,16 +7575,16 @@
       </c>
       <c r="D349" s="10" t="inlineStr">
         <is>
-          <t>PMP1289247</t>
+          <t>PMP1289248</t>
         </is>
       </c>
       <c r="E349" s="6" t="n">
-        <v>6385710.32</v>
+        <v>29688104.92</v>
       </c>
       <c r="F349" s="10" t="inlineStr"/>
       <c r="G349" s="10" t="inlineStr"/>
       <c r="H349" s="6" t="n">
-        <v>6385710.32</v>
+        <v>29688104.92</v>
       </c>
       <c r="I349" s="11" t="inlineStr"/>
     </row>
@@ -7598,16 +7596,16 @@
       </c>
       <c r="D350" s="10" t="inlineStr">
         <is>
-          <t>PMP1289248</t>
+          <t>PMP1289249</t>
         </is>
       </c>
       <c r="E350" s="6" t="n">
-        <v>29688104.92</v>
+        <v>14831505.84</v>
       </c>
       <c r="F350" s="10" t="inlineStr"/>
       <c r="G350" s="10" t="inlineStr"/>
       <c r="H350" s="6" t="n">
-        <v>29688104.92</v>
+        <v>14831505.84</v>
       </c>
       <c r="I350" s="11" t="inlineStr"/>
     </row>
@@ -7619,16 +7617,16 @@
       </c>
       <c r="D351" s="10" t="inlineStr">
         <is>
-          <t>PMP1289249</t>
+          <t>PMP1289250</t>
         </is>
       </c>
       <c r="E351" s="6" t="n">
-        <v>14831505.84</v>
+        <v>2260318.86</v>
       </c>
       <c r="F351" s="10" t="inlineStr"/>
       <c r="G351" s="10" t="inlineStr"/>
       <c r="H351" s="6" t="n">
-        <v>14831505.84</v>
+        <v>2260318.86</v>
       </c>
       <c r="I351" s="11" t="inlineStr"/>
     </row>
@@ -7640,16 +7638,16 @@
       </c>
       <c r="D352" s="10" t="inlineStr">
         <is>
-          <t>PMP1289250</t>
+          <t>PMP1289251</t>
         </is>
       </c>
       <c r="E352" s="6" t="n">
-        <v>2260318.86</v>
+        <v>79485214.06999999</v>
       </c>
       <c r="F352" s="10" t="inlineStr"/>
       <c r="G352" s="10" t="inlineStr"/>
       <c r="H352" s="6" t="n">
-        <v>2260318.86</v>
+        <v>79485214.06999999</v>
       </c>
       <c r="I352" s="11" t="inlineStr"/>
     </row>
@@ -7661,16 +7659,16 @@
       </c>
       <c r="D353" s="10" t="inlineStr">
         <is>
-          <t>PMP1289251</t>
+          <t>PMP1289252</t>
         </is>
       </c>
       <c r="E353" s="6" t="n">
-        <v>79485214.06999999</v>
+        <v>157321871.06</v>
       </c>
       <c r="F353" s="10" t="inlineStr"/>
       <c r="G353" s="10" t="inlineStr"/>
       <c r="H353" s="6" t="n">
-        <v>79485214.06999999</v>
+        <v>157321871.06</v>
       </c>
       <c r="I353" s="11" t="inlineStr"/>
     </row>
@@ -7682,16 +7680,16 @@
       </c>
       <c r="D354" s="10" t="inlineStr">
         <is>
-          <t>PMP1289252</t>
+          <t>PMP1289253</t>
         </is>
       </c>
       <c r="E354" s="6" t="n">
-        <v>157321871.06</v>
+        <v>161169208.42</v>
       </c>
       <c r="F354" s="10" t="inlineStr"/>
       <c r="G354" s="10" t="inlineStr"/>
       <c r="H354" s="6" t="n">
-        <v>157321871.06</v>
+        <v>161169208.42</v>
       </c>
       <c r="I354" s="11" t="inlineStr"/>
     </row>
@@ -7703,16 +7701,16 @@
       </c>
       <c r="D355" s="10" t="inlineStr">
         <is>
-          <t>PMP1289253</t>
+          <t>PMP1289323</t>
         </is>
       </c>
       <c r="E355" s="6" t="n">
-        <v>161169208.42</v>
+        <v>9840654.6</v>
       </c>
       <c r="F355" s="10" t="inlineStr"/>
       <c r="G355" s="10" t="inlineStr"/>
       <c r="H355" s="6" t="n">
-        <v>161169208.42</v>
+        <v>9840654.6</v>
       </c>
       <c r="I355" s="11" t="inlineStr"/>
     </row>
@@ -7724,16 +7722,16 @@
       </c>
       <c r="D356" s="10" t="inlineStr">
         <is>
-          <t>PMP1289323</t>
+          <t>PMP1289324</t>
         </is>
       </c>
       <c r="E356" s="6" t="n">
-        <v>9840654.6</v>
+        <v>43111610.9</v>
       </c>
       <c r="F356" s="10" t="inlineStr"/>
       <c r="G356" s="10" t="inlineStr"/>
       <c r="H356" s="6" t="n">
-        <v>9840654.6</v>
+        <v>43111610.9</v>
       </c>
       <c r="I356" s="11" t="inlineStr"/>
     </row>
@@ -7745,16 +7743,16 @@
       </c>
       <c r="D357" s="10" t="inlineStr">
         <is>
-          <t>PMP1289324</t>
+          <t>PMP1289325</t>
         </is>
       </c>
       <c r="E357" s="6" t="n">
-        <v>43111610.9</v>
+        <v>10771988.08</v>
       </c>
       <c r="F357" s="10" t="inlineStr"/>
       <c r="G357" s="10" t="inlineStr"/>
       <c r="H357" s="6" t="n">
-        <v>43111610.9</v>
+        <v>10771988.08</v>
       </c>
       <c r="I357" s="11" t="inlineStr"/>
     </row>
@@ -7766,16 +7764,16 @@
       </c>
       <c r="D358" s="10" t="inlineStr">
         <is>
-          <t>PMP1289325</t>
+          <t>PMP1289326</t>
         </is>
       </c>
       <c r="E358" s="6" t="n">
-        <v>10771988.08</v>
+        <v>68234331.56</v>
       </c>
       <c r="F358" s="10" t="inlineStr"/>
       <c r="G358" s="10" t="inlineStr"/>
       <c r="H358" s="6" t="n">
-        <v>10771988.08</v>
+        <v>68234331.56</v>
       </c>
       <c r="I358" s="11" t="inlineStr"/>
     </row>
@@ -7787,16 +7785,16 @@
       </c>
       <c r="D359" s="10" t="inlineStr">
         <is>
-          <t>PMP1289326</t>
+          <t>PMP1289327</t>
         </is>
       </c>
       <c r="E359" s="6" t="n">
-        <v>68234331.56</v>
+        <v>2516997.42</v>
       </c>
       <c r="F359" s="10" t="inlineStr"/>
       <c r="G359" s="10" t="inlineStr"/>
       <c r="H359" s="6" t="n">
-        <v>68234331.56</v>
+        <v>2516997.42</v>
       </c>
       <c r="I359" s="11" t="inlineStr"/>
     </row>
@@ -7808,16 +7806,16 @@
       </c>
       <c r="D360" s="10" t="inlineStr">
         <is>
-          <t>PMP1289327</t>
+          <t>PMP1289328</t>
         </is>
       </c>
       <c r="E360" s="6" t="n">
-        <v>2516997.42</v>
+        <v>95451965.2</v>
       </c>
       <c r="F360" s="10" t="inlineStr"/>
       <c r="G360" s="10" t="inlineStr"/>
       <c r="H360" s="6" t="n">
-        <v>2516997.42</v>
+        <v>95451965.2</v>
       </c>
       <c r="I360" s="11" t="inlineStr"/>
     </row>
@@ -7829,16 +7827,16 @@
       </c>
       <c r="D361" s="10" t="inlineStr">
         <is>
-          <t>PMP1289328</t>
+          <t>PMP1289440</t>
         </is>
       </c>
       <c r="E361" s="6" t="n">
-        <v>95451965.2</v>
+        <v>2934219</v>
       </c>
       <c r="F361" s="10" t="inlineStr"/>
       <c r="G361" s="10" t="inlineStr"/>
       <c r="H361" s="6" t="n">
-        <v>95451965.2</v>
+        <v>2934219</v>
       </c>
       <c r="I361" s="11" t="inlineStr"/>
     </row>
@@ -7850,16 +7848,16 @@
       </c>
       <c r="D362" s="10" t="inlineStr">
         <is>
-          <t>PMP1289440</t>
+          <t>PMP1289476</t>
         </is>
       </c>
       <c r="E362" s="6" t="n">
-        <v>2934219</v>
+        <v>7890270.94</v>
       </c>
       <c r="F362" s="10" t="inlineStr"/>
       <c r="G362" s="10" t="inlineStr"/>
       <c r="H362" s="6" t="n">
-        <v>2934219</v>
+        <v>7890270.94</v>
       </c>
       <c r="I362" s="11" t="inlineStr"/>
     </row>
@@ -7871,16 +7869,16 @@
       </c>
       <c r="D363" s="10" t="inlineStr">
         <is>
-          <t>PMP1289476</t>
+          <t>PMP1289505</t>
         </is>
       </c>
       <c r="E363" s="6" t="n">
-        <v>7890270.94</v>
+        <v>1734426.16</v>
       </c>
       <c r="F363" s="10" t="inlineStr"/>
       <c r="G363" s="10" t="inlineStr"/>
       <c r="H363" s="6" t="n">
-        <v>7890270.94</v>
+        <v>1734426.16</v>
       </c>
       <c r="I363" s="11" t="inlineStr"/>
     </row>
@@ -7892,16 +7890,16 @@
       </c>
       <c r="D364" s="10" t="inlineStr">
         <is>
-          <t>PMP1289505</t>
+          <t>PMP1289506</t>
         </is>
       </c>
       <c r="E364" s="6" t="n">
-        <v>1734426.16</v>
+        <v>594994.84</v>
       </c>
       <c r="F364" s="10" t="inlineStr"/>
       <c r="G364" s="10" t="inlineStr"/>
       <c r="H364" s="6" t="n">
-        <v>1734426.16</v>
+        <v>594994.84</v>
       </c>
       <c r="I364" s="11" t="inlineStr"/>
     </row>
@@ -7913,16 +7911,16 @@
       </c>
       <c r="D365" s="10" t="inlineStr">
         <is>
-          <t>PMP1289506</t>
+          <t>PMP1289507</t>
         </is>
       </c>
       <c r="E365" s="6" t="n">
-        <v>594994.84</v>
+        <v>8523029.75</v>
       </c>
       <c r="F365" s="10" t="inlineStr"/>
       <c r="G365" s="10" t="inlineStr"/>
       <c r="H365" s="6" t="n">
-        <v>594994.84</v>
+        <v>8523029.75</v>
       </c>
       <c r="I365" s="11" t="inlineStr"/>
     </row>
@@ -7934,16 +7932,16 @@
       </c>
       <c r="D366" s="10" t="inlineStr">
         <is>
-          <t>PMP1289507</t>
+          <t>PMP1289590</t>
         </is>
       </c>
       <c r="E366" s="6" t="n">
-        <v>8523029.75</v>
+        <v>7403798.08</v>
       </c>
       <c r="F366" s="10" t="inlineStr"/>
       <c r="G366" s="10" t="inlineStr"/>
       <c r="H366" s="6" t="n">
-        <v>8523029.75</v>
+        <v>7403798.08</v>
       </c>
       <c r="I366" s="11" t="inlineStr"/>
     </row>
@@ -7955,39 +7953,51 @@
       </c>
       <c r="D367" s="10" t="inlineStr">
         <is>
-          <t>PMP1289590</t>
+          <t>PMP1289593</t>
         </is>
       </c>
       <c r="E367" s="6" t="n">
-        <v>7403798.08</v>
+        <v>8744137</v>
       </c>
       <c r="F367" s="10" t="inlineStr"/>
       <c r="G367" s="10" t="inlineStr"/>
       <c r="H367" s="6" t="n">
-        <v>7403798.08</v>
+        <v>8744137</v>
       </c>
       <c r="I367" s="11" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="C368" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>Descuentos Clientes</t>
         </is>
       </c>
       <c r="D368" s="10" t="inlineStr">
         <is>
-          <t>PMP1289593</t>
+          <t>DESCUENTO</t>
         </is>
       </c>
       <c r="E368" s="6" t="n">
-        <v>8744137</v>
-      </c>
-      <c r="F368" s="10" t="inlineStr"/>
-      <c r="G368" s="10" t="inlineStr"/>
+        <v>-61299192</v>
+      </c>
+      <c r="F368" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G368" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
+      </c>
       <c r="H368" s="6" t="n">
-        <v>8744137</v>
-      </c>
-      <c r="I368" s="11" t="inlineStr"/>
+        <v>-61299192</v>
+      </c>
+      <c r="I368" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RPL DSCTO  DESCUENTO </t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="C369" s="10" t="inlineStr">
@@ -7997,28 +8007,28 @@
       </c>
       <c r="D369" s="10" t="inlineStr">
         <is>
+          <t>DESCUENTO APERTURA</t>
+        </is>
+      </c>
+      <c r="E369" s="6" t="n">
+        <v>-22852333</v>
+      </c>
+      <c r="F369" s="10" t="inlineStr">
+        <is>
           <t>DESCUENTO</t>
         </is>
       </c>
-      <c r="E369" s="6" t="n">
-        <v>-61299192</v>
-      </c>
-      <c r="F369" s="10" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
       <c r="G369" s="10" t="inlineStr">
         <is>
           <t>987</t>
         </is>
       </c>
       <c r="H369" s="6" t="n">
-        <v>-61299192</v>
+        <v>-22852333</v>
       </c>
       <c r="I369" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RPL DSCTO  DESCUENTO </t>
+          <t xml:space="preserve">DAV DSCTO  DESCUENTO APERTURA </t>
         </is>
       </c>
     </row>
@@ -8030,11 +8040,11 @@
       </c>
       <c r="D370" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO APERTURA</t>
+          <t>DESCUENTO CALENDARI</t>
         </is>
       </c>
       <c r="E370" s="6" t="n">
-        <v>-22852333</v>
+        <v>-2619475738</v>
       </c>
       <c r="F370" s="10" t="inlineStr">
         <is>
@@ -8047,11 +8057,11 @@
         </is>
       </c>
       <c r="H370" s="6" t="n">
-        <v>-22852333</v>
+        <v>-2619475738</v>
       </c>
       <c r="I370" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAV DSCTO  DESCUENTO APERTURA </t>
+          <t xml:space="preserve">DCA DSCTO  DESCUENTO CALENDARI </t>
         </is>
       </c>
     </row>
@@ -8063,11 +8073,11 @@
       </c>
       <c r="D371" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO CALENDARI</t>
+          <t>DESCUENTO COMPRAS</t>
         </is>
       </c>
       <c r="E371" s="6" t="n">
-        <v>-2619475738</v>
+        <v>-1394767</v>
       </c>
       <c r="F371" s="10" t="inlineStr">
         <is>
@@ -8080,11 +8090,11 @@
         </is>
       </c>
       <c r="H371" s="6" t="n">
-        <v>-2619475738</v>
+        <v>-1394767</v>
       </c>
       <c r="I371" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DCA DSCTO  DESCUENTO CALENDARI </t>
+          <t xml:space="preserve">DCC DSCTO  DESCUENTO COMPRAS </t>
         </is>
       </c>
     </row>
@@ -8096,11 +8106,11 @@
       </c>
       <c r="D372" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO COMPRAS</t>
+          <t>DESCUENTO EN PRIMER</t>
         </is>
       </c>
       <c r="E372" s="6" t="n">
-        <v>-1394767</v>
+        <v>-10216531</v>
       </c>
       <c r="F372" s="10" t="inlineStr">
         <is>
@@ -8113,11 +8123,11 @@
         </is>
       </c>
       <c r="H372" s="6" t="n">
-        <v>-1394767</v>
+        <v>-10216531</v>
       </c>
       <c r="I372" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DCC DSCTO  DESCUENTO COMPRAS </t>
+          <t xml:space="preserve">DPC DSCTO  DESCUENTO EN PRIMER </t>
         </is>
       </c>
     </row>
@@ -8129,11 +8139,11 @@
       </c>
       <c r="D373" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO EN PRIMER</t>
+          <t>DEVOLUCIONES</t>
         </is>
       </c>
       <c r="E373" s="6" t="n">
-        <v>-10216531</v>
+        <v>-5587084</v>
       </c>
       <c r="F373" s="10" t="inlineStr">
         <is>
@@ -8146,11 +8156,11 @@
         </is>
       </c>
       <c r="H373" s="6" t="n">
-        <v>-10216531</v>
+        <v>-5587084</v>
       </c>
       <c r="I373" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DPC DSCTO  DESCUENTO EN PRIMER </t>
+          <t xml:space="preserve">DND DSCTO  DEVOLUCIONES </t>
         </is>
       </c>
     </row>
@@ -8162,11 +8172,11 @@
       </c>
       <c r="D374" s="10" t="inlineStr">
         <is>
-          <t>DEVOLUCIONES</t>
+          <t>DSTO COMERCIAL FIJO</t>
         </is>
       </c>
       <c r="E374" s="6" t="n">
-        <v>-5587084</v>
+        <v>-145861342</v>
       </c>
       <c r="F374" s="10" t="inlineStr">
         <is>
@@ -8179,11 +8189,11 @@
         </is>
       </c>
       <c r="H374" s="6" t="n">
-        <v>-5587084</v>
+        <v>-145861342</v>
       </c>
       <c r="I374" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DND DSCTO  DEVOLUCIONES </t>
+          <t xml:space="preserve">DCF DSCTO  DSTO COMERCIAL FIJO </t>
         </is>
       </c>
     </row>
@@ -8195,11 +8205,11 @@
       </c>
       <c r="D375" s="10" t="inlineStr">
         <is>
-          <t>DSTO COMERCIAL FIJO</t>
+          <t>DTO POR ESCALA VOLU</t>
         </is>
       </c>
       <c r="E375" s="6" t="n">
-        <v>-145861342</v>
+        <v>-2210671</v>
       </c>
       <c r="F375" s="10" t="inlineStr">
         <is>
@@ -8212,11 +8222,11 @@
         </is>
       </c>
       <c r="H375" s="6" t="n">
-        <v>-145861342</v>
+        <v>-2210671</v>
       </c>
       <c r="I375" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DCF DSCTO  DSTO COMERCIAL FIJO </t>
+          <t xml:space="preserve">DEC DSCTO  DTO POR ESCALA VOLU </t>
         </is>
       </c>
     </row>
@@ -8232,7 +8242,7 @@
         </is>
       </c>
       <c r="E376" s="6" t="n">
-        <v>-2210671</v>
+        <v>-1327497</v>
       </c>
       <c r="F376" s="10" t="inlineStr">
         <is>
@@ -8245,11 +8255,11 @@
         </is>
       </c>
       <c r="H376" s="6" t="n">
-        <v>-2210671</v>
+        <v>-1327497</v>
       </c>
       <c r="I376" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEC DSCTO  DTO POR ESCALA VOLU </t>
+          <t xml:space="preserve">DEC DSCTO 20251100199283 DTO POR ESCALA VOLU </t>
         </is>
       </c>
     </row>
@@ -8265,7 +8275,7 @@
         </is>
       </c>
       <c r="E377" s="6" t="n">
-        <v>-1327497</v>
+        <v>-896070</v>
       </c>
       <c r="F377" s="10" t="inlineStr">
         <is>
@@ -8278,11 +8288,11 @@
         </is>
       </c>
       <c r="H377" s="6" t="n">
-        <v>-1327497</v>
+        <v>-896070</v>
       </c>
       <c r="I377" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEC DSCTO 20251100199283 DTO POR ESCALA VOLU </t>
+          <t xml:space="preserve">DEC DSCTO 20251200199299 DTO POR ESCALA VOLU </t>
         </is>
       </c>
     </row>
@@ -8298,7 +8308,7 @@
         </is>
       </c>
       <c r="E378" s="6" t="n">
-        <v>-896070</v>
+        <v>-616199</v>
       </c>
       <c r="F378" s="10" t="inlineStr">
         <is>
@@ -8311,11 +8321,11 @@
         </is>
       </c>
       <c r="H378" s="6" t="n">
-        <v>-896070</v>
+        <v>-616199</v>
       </c>
       <c r="I378" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEC DSCTO 20251200199299 DTO POR ESCALA VOLU </t>
+          <t xml:space="preserve">DEC DSCTO 20251200199300 DTO POR ESCALA VOLU </t>
         </is>
       </c>
     </row>
@@ -8331,7 +8341,7 @@
         </is>
       </c>
       <c r="E379" s="6" t="n">
-        <v>-616199</v>
+        <v>-36108</v>
       </c>
       <c r="F379" s="10" t="inlineStr">
         <is>
@@ -8344,11 +8354,11 @@
         </is>
       </c>
       <c r="H379" s="6" t="n">
-        <v>-616199</v>
+        <v>-36108</v>
       </c>
       <c r="I379" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEC DSCTO 20251200199300 DTO POR ESCALA VOLU </t>
+          <t xml:space="preserve">DEC DSCTO 20251200199301 DTO POR ESCALA VOLU </t>
         </is>
       </c>
     </row>
@@ -8364,7 +8374,7 @@
         </is>
       </c>
       <c r="E380" s="6" t="n">
-        <v>-36108</v>
+        <v>-210000</v>
       </c>
       <c r="F380" s="10" t="inlineStr">
         <is>
@@ -8377,11 +8387,11 @@
         </is>
       </c>
       <c r="H380" s="6" t="n">
-        <v>-36108</v>
+        <v>-210000</v>
       </c>
       <c r="I380" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEC DSCTO 20251200199301 DTO POR ESCALA VOLU </t>
+          <t xml:space="preserve">DEC DSCTO 20251200200041 DTO POR ESCALA VOLU </t>
         </is>
       </c>
     </row>
@@ -8397,11 +8407,11 @@
         </is>
       </c>
       <c r="E381" s="6" t="n">
-        <v>-210000</v>
+        <v>-67283120</v>
       </c>
       <c r="F381" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>DROGUE</t>
         </is>
       </c>
       <c r="G381" s="10" t="inlineStr">
@@ -8410,11 +8420,11 @@
         </is>
       </c>
       <c r="H381" s="6" t="n">
-        <v>-210000</v>
+        <v>-67283120</v>
       </c>
       <c r="I381" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEC DSCTO 20251200200041 DTO POR ESCALA VOLU </t>
+          <t>DEC DSCTO  DTO POR ESCALA VOLU DROGUE</t>
         </is>
       </c>
     </row>
@@ -8430,7 +8440,7 @@
         </is>
       </c>
       <c r="E382" s="6" t="n">
-        <v>-67283120</v>
+        <v>-838419</v>
       </c>
       <c r="F382" s="10" t="inlineStr">
         <is>
@@ -8443,11 +8453,11 @@
         </is>
       </c>
       <c r="H382" s="6" t="n">
-        <v>-67283120</v>
+        <v>-838419</v>
       </c>
       <c r="I382" s="11" t="inlineStr">
         <is>
-          <t>DEC DSCTO  DTO POR ESCALA VOLU DROGUE</t>
+          <t>DEC DSCTO 20251100199283 DTO POR ESCALA VOLU DROGUE</t>
         </is>
       </c>
     </row>
@@ -8459,28 +8469,28 @@
       </c>
       <c r="D383" s="10" t="inlineStr">
         <is>
-          <t>DTO POR ESCALA VOLU</t>
+          <t>VPP1 2004529ADM. FIDELIDAD -</t>
         </is>
       </c>
       <c r="E383" s="6" t="n">
-        <v>-838419</v>
+        <v>-57239000</v>
       </c>
       <c r="F383" s="10" t="inlineStr">
         <is>
-          <t>DROGUE</t>
+          <t>FACT PROVEED</t>
         </is>
       </c>
       <c r="G383" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>CSB</t>
         </is>
       </c>
       <c r="H383" s="6" t="n">
-        <v>-838419</v>
+        <v>-57239000</v>
       </c>
       <c r="I383" s="11" t="inlineStr">
         <is>
-          <t>DEC DSCTO 20251100199283 DTO POR ESCALA VOLU DROGUE</t>
+          <t>VPP1 2004529ADM. FIDELIDAD -</t>
         </is>
       </c>
     </row>
@@ -8492,11 +8502,11 @@
       </c>
       <c r="D384" s="10" t="inlineStr">
         <is>
-          <t>VPP1 2004529ADM. FIDELIDAD -</t>
+          <t>VPP1 2004621ADM. FIDELIDAD -</t>
         </is>
       </c>
       <c r="E384" s="6" t="n">
-        <v>-57239000</v>
+        <v>-6426000</v>
       </c>
       <c r="F384" s="10" t="inlineStr">
         <is>
@@ -8509,11 +8519,11 @@
         </is>
       </c>
       <c r="H384" s="6" t="n">
-        <v>-57239000</v>
+        <v>-6426000</v>
       </c>
       <c r="I384" s="11" t="inlineStr">
         <is>
-          <t>VPP1 2004529ADM. FIDELIDAD -</t>
+          <t>VPP1 2004621ADM. FIDELIDAD -</t>
         </is>
       </c>
     </row>
@@ -8525,11 +8535,11 @@
       </c>
       <c r="D385" s="10" t="inlineStr">
         <is>
-          <t>VPP1 2004621ADM. FIDELIDAD -</t>
+          <t>VPP1 2004622ADM. FIDELIDAD -</t>
         </is>
       </c>
       <c r="E385" s="6" t="n">
-        <v>-6426000</v>
+        <v>-41650000</v>
       </c>
       <c r="F385" s="10" t="inlineStr">
         <is>
@@ -8542,11 +8552,11 @@
         </is>
       </c>
       <c r="H385" s="6" t="n">
-        <v>-6426000</v>
+        <v>-41650000</v>
       </c>
       <c r="I385" s="11" t="inlineStr">
         <is>
-          <t>VPP1 2004621ADM. FIDELIDAD -</t>
+          <t>VPP1 2004622ADM. FIDELIDAD -</t>
         </is>
       </c>
     </row>
@@ -8558,11 +8568,11 @@
       </c>
       <c r="D386" s="10" t="inlineStr">
         <is>
-          <t>VPP1 2004622ADM. FIDELIDAD -</t>
+          <t>VPP2 2021716ADM.</t>
         </is>
       </c>
       <c r="E386" s="6" t="n">
-        <v>-41650000</v>
+        <v>-2507098292</v>
       </c>
       <c r="F386" s="10" t="inlineStr">
         <is>
@@ -8575,11 +8585,11 @@
         </is>
       </c>
       <c r="H386" s="6" t="n">
-        <v>-41650000</v>
+        <v>-2507098292</v>
       </c>
       <c r="I386" s="11" t="inlineStr">
         <is>
-          <t>VPP1 2004622ADM. FIDELIDAD -</t>
+          <t>VPP2 2021716ADM.</t>
         </is>
       </c>
     </row>
@@ -8591,11 +8601,11 @@
       </c>
       <c r="D387" s="10" t="inlineStr">
         <is>
-          <t>VPP2 2021716ADM.</t>
+          <t>VPP2 2022342ADM.</t>
         </is>
       </c>
       <c r="E387" s="6" t="n">
-        <v>-2507098292</v>
+        <v>-1075965191</v>
       </c>
       <c r="F387" s="10" t="inlineStr">
         <is>
@@ -8608,44 +8618,44 @@
         </is>
       </c>
       <c r="H387" s="6" t="n">
-        <v>-2507098292</v>
+        <v>-1075965191</v>
       </c>
       <c r="I387" s="11" t="inlineStr">
         <is>
-          <t>VPP2 2021716ADM.</t>
+          <t>VPP2 2022342ADM.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="C388" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Descuento Cliente</t>
         </is>
       </c>
       <c r="D388" s="10" t="inlineStr">
         <is>
-          <t>VPP2 2022342ADM.</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="E388" s="6" t="n">
-        <v>-1075965191</v>
+        <v>-37.26000004360685</v>
       </c>
       <c r="F388" s="10" t="inlineStr">
         <is>
-          <t>FACT PROVEED</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G388" s="10" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>CSR</t>
         </is>
       </c>
       <c r="H388" s="6" t="n">
-        <v>-1075965191</v>
+        <v>-37.26000004360685</v>
       </c>
       <c r="I388" s="11" t="inlineStr">
         <is>
-          <t>VPP2 2022342ADM.</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
@@ -8657,15 +8667,15 @@
       </c>
       <c r="D389" s="10" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
+          <t>PMP1286054</t>
         </is>
       </c>
       <c r="E389" s="6" t="n">
-        <v>-37.26000004360685</v>
+        <v>-864163</v>
       </c>
       <c r="F389" s="10" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
+          <t>Menor Vlr Pagado</t>
         </is>
       </c>
       <c r="G389" s="10" t="inlineStr">
@@ -8674,11 +8684,11 @@
         </is>
       </c>
       <c r="H389" s="6" t="n">
-        <v>-37.26000004360685</v>
+        <v>-864163</v>
       </c>
       <c r="I389" s="11" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
+          <t>Menor Vlr Pagado PMP1286054</t>
         </is>
       </c>
     </row>
@@ -8690,11 +8700,11 @@
       </c>
       <c r="D390" s="10" t="inlineStr">
         <is>
-          <t>PMP1286054</t>
+          <t>PMP1286550</t>
         </is>
       </c>
       <c r="E390" s="6" t="n">
-        <v>-864163</v>
+        <v>-5910046.859999999</v>
       </c>
       <c r="F390" s="10" t="inlineStr">
         <is>
@@ -8707,11 +8717,11 @@
         </is>
       </c>
       <c r="H390" s="6" t="n">
-        <v>-864163</v>
+        <v>-5910046.859999999</v>
       </c>
       <c r="I390" s="11" t="inlineStr">
         <is>
-          <t>Menor Vlr Pagado PMP1286054</t>
+          <t>Menor Vlr Pagado PMP1286550</t>
         </is>
       </c>
     </row>
@@ -8723,61 +8733,61 @@
       </c>
       <c r="D391" s="10" t="inlineStr">
         <is>
-          <t>PMP1286550</t>
+          <t>PMP1286553</t>
         </is>
       </c>
       <c r="E391" s="6" t="n">
-        <v>-5910046.859999999</v>
+        <v>5910047.02</v>
       </c>
       <c r="F391" s="10" t="inlineStr">
         <is>
-          <t>Menor Vlr Pagado</t>
+          <t>Myr Vlr Pagado</t>
         </is>
       </c>
       <c r="G391" s="10" t="inlineStr">
         <is>
-          <t>CSR</t>
+          <t>388</t>
         </is>
       </c>
       <c r="H391" s="6" t="n">
-        <v>-5910046.859999999</v>
+        <v>5910047.02</v>
       </c>
       <c r="I391" s="11" t="inlineStr">
         <is>
-          <t>Menor Vlr Pagado PMP1286550</t>
+          <t>Myr Vlr Pagado PMP1286553</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="C392" s="10" t="inlineStr">
         <is>
-          <t>Descuento Cliente</t>
+          <t>Descuentos Clientes</t>
         </is>
       </c>
       <c r="D392" s="10" t="inlineStr">
         <is>
-          <t>PMP1286553</t>
+          <t>DTO POR ESCALA VOLU</t>
         </is>
       </c>
       <c r="E392" s="6" t="n">
-        <v>5910047.02</v>
+        <v>-163558737</v>
       </c>
       <c r="F392" s="10" t="inlineStr">
         <is>
-          <t>Myr Vlr Pagado</t>
+          <t>PERFUME</t>
         </is>
       </c>
       <c r="G392" s="10" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H392" s="6" t="n">
-        <v>5910047.02</v>
+        <v>-163558737</v>
       </c>
       <c r="I392" s="11" t="inlineStr">
         <is>
-          <t>Myr Vlr Pagado PMP1286553</t>
+          <t>DEC DSCTO  DTO POR ESCALA VOLU PERFUME</t>
         </is>
       </c>
     </row>
@@ -8793,7 +8803,7 @@
         </is>
       </c>
       <c r="E393" s="6" t="n">
-        <v>-163558737</v>
+        <v>-896070</v>
       </c>
       <c r="F393" s="10" t="inlineStr">
         <is>
@@ -8806,11 +8816,11 @@
         </is>
       </c>
       <c r="H393" s="6" t="n">
-        <v>-163558737</v>
+        <v>-896070</v>
       </c>
       <c r="I393" s="11" t="inlineStr">
         <is>
-          <t>DEC DSCTO  DTO POR ESCALA VOLU PERFUME</t>
+          <t>DEC DSCTO 20251200199299 DTO POR ESCALA VOLU PERFUME</t>
         </is>
       </c>
     </row>
@@ -8826,7 +8836,7 @@
         </is>
       </c>
       <c r="E394" s="6" t="n">
-        <v>-896070</v>
+        <v>-762913</v>
       </c>
       <c r="F394" s="10" t="inlineStr">
         <is>
@@ -8839,11 +8849,11 @@
         </is>
       </c>
       <c r="H394" s="6" t="n">
-        <v>-896070</v>
+        <v>-762913</v>
       </c>
       <c r="I394" s="11" t="inlineStr">
         <is>
-          <t>DEC DSCTO 20251200199299 DTO POR ESCALA VOLU PERFUME</t>
+          <t>DEC DSCTO 20251200199300 DTO POR ESCALA VOLU PERFUME</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8869,7 @@
         </is>
       </c>
       <c r="E395" s="6" t="n">
-        <v>-762913</v>
+        <v>-44705</v>
       </c>
       <c r="F395" s="10" t="inlineStr">
         <is>
@@ -8872,11 +8882,11 @@
         </is>
       </c>
       <c r="H395" s="6" t="n">
-        <v>-762913</v>
+        <v>-44705</v>
       </c>
       <c r="I395" s="11" t="inlineStr">
         <is>
-          <t>DEC DSCTO 20251200199300 DTO POR ESCALA VOLU PERFUME</t>
+          <t>DEC DSCTO 20251200199301 DTO POR ESCALA VOLU PERFUME</t>
         </is>
       </c>
     </row>
@@ -8892,7 +8902,7 @@
         </is>
       </c>
       <c r="E396" s="6" t="n">
-        <v>-44705</v>
+        <v>-260000</v>
       </c>
       <c r="F396" s="10" t="inlineStr">
         <is>
@@ -8905,11 +8915,11 @@
         </is>
       </c>
       <c r="H396" s="6" t="n">
-        <v>-44705</v>
+        <v>-260000</v>
       </c>
       <c r="I396" s="11" t="inlineStr">
         <is>
-          <t>DEC DSCTO 20251200199301 DTO POR ESCALA VOLU PERFUME</t>
+          <t>DEC DSCTO 20251200200041 DTO POR ESCALA VOLU PERFUME</t>
         </is>
       </c>
     </row>
@@ -8921,28 +8931,28 @@
       </c>
       <c r="D397" s="10" t="inlineStr">
         <is>
-          <t>DTO POR ESCALA VOLU</t>
+          <t>PMP1282099</t>
         </is>
       </c>
       <c r="E397" s="6" t="n">
-        <v>-260000</v>
+        <v>-307519</v>
       </c>
       <c r="F397" s="10" t="inlineStr">
         <is>
-          <t>PERFUME</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G397" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H397" s="6" t="n">
-        <v>-260000</v>
+        <v>-307519</v>
       </c>
       <c r="I397" s="11" t="inlineStr">
         <is>
-          <t>DEC DSCTO 20251200200041 DTO POR ESCALA VOLU PERFUME</t>
+          <t>Rechazo PMP1282099</t>
         </is>
       </c>
     </row>
@@ -8954,11 +8964,11 @@
       </c>
       <c r="D398" s="10" t="inlineStr">
         <is>
-          <t>PMP1282099</t>
+          <t>PMP1282353</t>
         </is>
       </c>
       <c r="E398" s="6" t="n">
-        <v>-307519</v>
+        <v>-2659670</v>
       </c>
       <c r="F398" s="10" t="inlineStr">
         <is>
@@ -8971,11 +8981,11 @@
         </is>
       </c>
       <c r="H398" s="6" t="n">
-        <v>-307519</v>
+        <v>-2659670</v>
       </c>
       <c r="I398" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1282099</t>
+          <t>Rechazo PMP1282353</t>
         </is>
       </c>
     </row>
@@ -8987,11 +8997,11 @@
       </c>
       <c r="D399" s="10" t="inlineStr">
         <is>
-          <t>PMP1282353</t>
+          <t>PMP1282964</t>
         </is>
       </c>
       <c r="E399" s="6" t="n">
-        <v>-2659670</v>
+        <v>-185365</v>
       </c>
       <c r="F399" s="10" t="inlineStr">
         <is>
@@ -9004,11 +9014,11 @@
         </is>
       </c>
       <c r="H399" s="6" t="n">
-        <v>-2659670</v>
+        <v>-185365</v>
       </c>
       <c r="I399" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1282353</t>
+          <t>Rechazo PMP1282964</t>
         </is>
       </c>
     </row>
@@ -9020,11 +9030,11 @@
       </c>
       <c r="D400" s="10" t="inlineStr">
         <is>
-          <t>PMP1282964</t>
+          <t>PMP1283008</t>
         </is>
       </c>
       <c r="E400" s="6" t="n">
-        <v>-185365</v>
+        <v>-9788</v>
       </c>
       <c r="F400" s="10" t="inlineStr">
         <is>
@@ -9037,11 +9047,11 @@
         </is>
       </c>
       <c r="H400" s="6" t="n">
-        <v>-185365</v>
+        <v>-9788</v>
       </c>
       <c r="I400" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1282964</t>
+          <t>Rechazo PMP1283008</t>
         </is>
       </c>
     </row>
@@ -9053,11 +9063,11 @@
       </c>
       <c r="D401" s="10" t="inlineStr">
         <is>
-          <t>PMP1283008</t>
+          <t>PMP1283012</t>
         </is>
       </c>
       <c r="E401" s="6" t="n">
-        <v>-9788</v>
+        <v>-167913</v>
       </c>
       <c r="F401" s="10" t="inlineStr">
         <is>
@@ -9070,11 +9080,11 @@
         </is>
       </c>
       <c r="H401" s="6" t="n">
-        <v>-9788</v>
+        <v>-167913</v>
       </c>
       <c r="I401" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1283008</t>
+          <t>Rechazo PMP1283012</t>
         </is>
       </c>
     </row>
@@ -9086,11 +9096,11 @@
       </c>
       <c r="D402" s="10" t="inlineStr">
         <is>
-          <t>PMP1283012</t>
+          <t>PMP1283476</t>
         </is>
       </c>
       <c r="E402" s="6" t="n">
-        <v>-167913</v>
+        <v>-836339</v>
       </c>
       <c r="F402" s="10" t="inlineStr">
         <is>
@@ -9103,11 +9113,11 @@
         </is>
       </c>
       <c r="H402" s="6" t="n">
-        <v>-167913</v>
+        <v>-836339</v>
       </c>
       <c r="I402" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1283012</t>
+          <t>Rechazo PMP1283476</t>
         </is>
       </c>
     </row>
@@ -9119,11 +9129,11 @@
       </c>
       <c r="D403" s="10" t="inlineStr">
         <is>
-          <t>PMP1283476</t>
+          <t>PMP1283500</t>
         </is>
       </c>
       <c r="E403" s="6" t="n">
-        <v>-836339</v>
+        <v>-473742856</v>
       </c>
       <c r="F403" s="10" t="inlineStr">
         <is>
@@ -9136,11 +9146,11 @@
         </is>
       </c>
       <c r="H403" s="6" t="n">
-        <v>-836339</v>
+        <v>-473742856</v>
       </c>
       <c r="I403" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1283476</t>
+          <t>Rechazo PMP1283500</t>
         </is>
       </c>
     </row>
@@ -9152,11 +9162,11 @@
       </c>
       <c r="D404" s="10" t="inlineStr">
         <is>
-          <t>PMP1283500</t>
+          <t>PMP1283784</t>
         </is>
       </c>
       <c r="E404" s="6" t="n">
-        <v>-473742856</v>
+        <v>-629893</v>
       </c>
       <c r="F404" s="10" t="inlineStr">
         <is>
@@ -9169,11 +9179,11 @@
         </is>
       </c>
       <c r="H404" s="6" t="n">
-        <v>-473742856</v>
+        <v>-629893</v>
       </c>
       <c r="I404" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1283500</t>
+          <t>Rechazo PMP1283784</t>
         </is>
       </c>
     </row>
@@ -9185,11 +9195,11 @@
       </c>
       <c r="D405" s="10" t="inlineStr">
         <is>
-          <t>PMP1283784</t>
+          <t>PMP1283785</t>
         </is>
       </c>
       <c r="E405" s="6" t="n">
-        <v>-629893</v>
+        <v>-160273</v>
       </c>
       <c r="F405" s="10" t="inlineStr">
         <is>
@@ -9202,11 +9212,11 @@
         </is>
       </c>
       <c r="H405" s="6" t="n">
-        <v>-629893</v>
+        <v>-160273</v>
       </c>
       <c r="I405" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1283784</t>
+          <t>Rechazo PMP1283785</t>
         </is>
       </c>
     </row>
@@ -9218,11 +9228,11 @@
       </c>
       <c r="D406" s="10" t="inlineStr">
         <is>
-          <t>PMP1283785</t>
+          <t>PMP1284114</t>
         </is>
       </c>
       <c r="E406" s="6" t="n">
-        <v>-160273</v>
+        <v>-764103</v>
       </c>
       <c r="F406" s="10" t="inlineStr">
         <is>
@@ -9235,11 +9245,11 @@
         </is>
       </c>
       <c r="H406" s="6" t="n">
-        <v>-160273</v>
+        <v>-764103</v>
       </c>
       <c r="I406" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1283785</t>
+          <t>Rechazo PMP1284114</t>
         </is>
       </c>
     </row>
@@ -9251,11 +9261,11 @@
       </c>
       <c r="D407" s="10" t="inlineStr">
         <is>
-          <t>PMP1284114</t>
+          <t>PMP1284117</t>
         </is>
       </c>
       <c r="E407" s="6" t="n">
-        <v>-764103</v>
+        <v>-177051</v>
       </c>
       <c r="F407" s="10" t="inlineStr">
         <is>
@@ -9268,11 +9278,11 @@
         </is>
       </c>
       <c r="H407" s="6" t="n">
-        <v>-764103</v>
+        <v>-177051</v>
       </c>
       <c r="I407" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284114</t>
+          <t>Rechazo PMP1284117</t>
         </is>
       </c>
     </row>
@@ -9284,11 +9294,11 @@
       </c>
       <c r="D408" s="10" t="inlineStr">
         <is>
-          <t>PMP1284117</t>
+          <t>PMP1284119</t>
         </is>
       </c>
       <c r="E408" s="6" t="n">
-        <v>-177051</v>
+        <v>-644997</v>
       </c>
       <c r="F408" s="10" t="inlineStr">
         <is>
@@ -9301,11 +9311,11 @@
         </is>
       </c>
       <c r="H408" s="6" t="n">
-        <v>-177051</v>
+        <v>-644997</v>
       </c>
       <c r="I408" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284117</t>
+          <t>Rechazo PMP1284119</t>
         </is>
       </c>
     </row>
@@ -9317,11 +9327,11 @@
       </c>
       <c r="D409" s="10" t="inlineStr">
         <is>
-          <t>PMP1284119</t>
+          <t>PMP1284200</t>
         </is>
       </c>
       <c r="E409" s="6" t="n">
-        <v>-644997</v>
+        <v>-175153</v>
       </c>
       <c r="F409" s="10" t="inlineStr">
         <is>
@@ -9334,11 +9344,11 @@
         </is>
       </c>
       <c r="H409" s="6" t="n">
-        <v>-644997</v>
+        <v>-175153</v>
       </c>
       <c r="I409" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284119</t>
+          <t>Rechazo PMP1284200</t>
         </is>
       </c>
     </row>
@@ -9350,11 +9360,11 @@
       </c>
       <c r="D410" s="10" t="inlineStr">
         <is>
-          <t>PMP1284200</t>
+          <t>PMP1284460</t>
         </is>
       </c>
       <c r="E410" s="6" t="n">
-        <v>-175153</v>
+        <v>-167879</v>
       </c>
       <c r="F410" s="10" t="inlineStr">
         <is>
@@ -9367,11 +9377,11 @@
         </is>
       </c>
       <c r="H410" s="6" t="n">
-        <v>-175153</v>
+        <v>-167879</v>
       </c>
       <c r="I410" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284200</t>
+          <t>Rechazo PMP1284460</t>
         </is>
       </c>
     </row>
@@ -9383,11 +9393,11 @@
       </c>
       <c r="D411" s="10" t="inlineStr">
         <is>
-          <t>PMP1284460</t>
+          <t>PMP1284462</t>
         </is>
       </c>
       <c r="E411" s="6" t="n">
-        <v>-167879</v>
+        <v>-322931</v>
       </c>
       <c r="F411" s="10" t="inlineStr">
         <is>
@@ -9400,11 +9410,11 @@
         </is>
       </c>
       <c r="H411" s="6" t="n">
-        <v>-167879</v>
+        <v>-322931</v>
       </c>
       <c r="I411" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284460</t>
+          <t>Rechazo PMP1284462</t>
         </is>
       </c>
     </row>
@@ -9416,11 +9426,11 @@
       </c>
       <c r="D412" s="10" t="inlineStr">
         <is>
-          <t>PMP1284462</t>
+          <t>PMP1284529</t>
         </is>
       </c>
       <c r="E412" s="6" t="n">
-        <v>-322931</v>
+        <v>-276742</v>
       </c>
       <c r="F412" s="10" t="inlineStr">
         <is>
@@ -9433,11 +9443,11 @@
         </is>
       </c>
       <c r="H412" s="6" t="n">
-        <v>-322931</v>
+        <v>-276742</v>
       </c>
       <c r="I412" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284462</t>
+          <t>Rechazo PMP1284529</t>
         </is>
       </c>
     </row>
@@ -9449,11 +9459,11 @@
       </c>
       <c r="D413" s="10" t="inlineStr">
         <is>
-          <t>PMP1284529</t>
+          <t>PMP1284543</t>
         </is>
       </c>
       <c r="E413" s="6" t="n">
-        <v>-276742</v>
+        <v>-3015665</v>
       </c>
       <c r="F413" s="10" t="inlineStr">
         <is>
@@ -9466,11 +9476,11 @@
         </is>
       </c>
       <c r="H413" s="6" t="n">
-        <v>-276742</v>
+        <v>-3015665</v>
       </c>
       <c r="I413" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284529</t>
+          <t>Rechazo PMP1284543</t>
         </is>
       </c>
     </row>
@@ -9482,11 +9492,11 @@
       </c>
       <c r="D414" s="10" t="inlineStr">
         <is>
-          <t>PMP1284543</t>
+          <t>PMP1284546</t>
         </is>
       </c>
       <c r="E414" s="6" t="n">
-        <v>-3015665</v>
+        <v>-135409</v>
       </c>
       <c r="F414" s="10" t="inlineStr">
         <is>
@@ -9499,11 +9509,11 @@
         </is>
       </c>
       <c r="H414" s="6" t="n">
-        <v>-3015665</v>
+        <v>-135409</v>
       </c>
       <c r="I414" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284543</t>
+          <t>Rechazo PMP1284546</t>
         </is>
       </c>
     </row>
@@ -9515,11 +9525,11 @@
       </c>
       <c r="D415" s="10" t="inlineStr">
         <is>
-          <t>PMP1284546</t>
+          <t>PMP1284602</t>
         </is>
       </c>
       <c r="E415" s="6" t="n">
-        <v>-135409</v>
+        <v>-930108</v>
       </c>
       <c r="F415" s="10" t="inlineStr">
         <is>
@@ -9532,11 +9542,11 @@
         </is>
       </c>
       <c r="H415" s="6" t="n">
-        <v>-135409</v>
+        <v>-930108</v>
       </c>
       <c r="I415" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284546</t>
+          <t>Rechazo PMP1284602</t>
         </is>
       </c>
     </row>
@@ -9548,11 +9558,11 @@
       </c>
       <c r="D416" s="10" t="inlineStr">
         <is>
-          <t>PMP1284602</t>
+          <t>PMP1284750</t>
         </is>
       </c>
       <c r="E416" s="6" t="n">
-        <v>-930108</v>
+        <v>-405708</v>
       </c>
       <c r="F416" s="10" t="inlineStr">
         <is>
@@ -9565,11 +9575,11 @@
         </is>
       </c>
       <c r="H416" s="6" t="n">
-        <v>-930108</v>
+        <v>-405708</v>
       </c>
       <c r="I416" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284602</t>
+          <t>Rechazo PMP1284750</t>
         </is>
       </c>
     </row>
@@ -9581,11 +9591,11 @@
       </c>
       <c r="D417" s="10" t="inlineStr">
         <is>
-          <t>PMP1284750</t>
+          <t>PMP1284800</t>
         </is>
       </c>
       <c r="E417" s="6" t="n">
-        <v>-405708</v>
+        <v>-635980</v>
       </c>
       <c r="F417" s="10" t="inlineStr">
         <is>
@@ -9598,11 +9608,11 @@
         </is>
       </c>
       <c r="H417" s="6" t="n">
-        <v>-405708</v>
+        <v>-635980</v>
       </c>
       <c r="I417" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284750</t>
+          <t>Rechazo PMP1284800</t>
         </is>
       </c>
     </row>
@@ -9614,11 +9624,11 @@
       </c>
       <c r="D418" s="10" t="inlineStr">
         <is>
-          <t>PMP1284800</t>
+          <t>PMP1284876</t>
         </is>
       </c>
       <c r="E418" s="6" t="n">
-        <v>-635980</v>
+        <v>-689804</v>
       </c>
       <c r="F418" s="10" t="inlineStr">
         <is>
@@ -9631,11 +9641,11 @@
         </is>
       </c>
       <c r="H418" s="6" t="n">
-        <v>-635980</v>
+        <v>-689804</v>
       </c>
       <c r="I418" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284800</t>
+          <t>Rechazo PMP1284876</t>
         </is>
       </c>
     </row>
@@ -9647,11 +9657,11 @@
       </c>
       <c r="D419" s="10" t="inlineStr">
         <is>
-          <t>PMP1284876</t>
+          <t>PMP1284878</t>
         </is>
       </c>
       <c r="E419" s="6" t="n">
-        <v>-689804</v>
+        <v>-135533</v>
       </c>
       <c r="F419" s="10" t="inlineStr">
         <is>
@@ -9664,11 +9674,11 @@
         </is>
       </c>
       <c r="H419" s="6" t="n">
-        <v>-689804</v>
+        <v>-135533</v>
       </c>
       <c r="I419" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284876</t>
+          <t>Rechazo PMP1284878</t>
         </is>
       </c>
     </row>
@@ -9680,11 +9690,11 @@
       </c>
       <c r="D420" s="10" t="inlineStr">
         <is>
-          <t>PMP1284878</t>
+          <t>PMP1284879</t>
         </is>
       </c>
       <c r="E420" s="6" t="n">
-        <v>-135533</v>
+        <v>-732728</v>
       </c>
       <c r="F420" s="10" t="inlineStr">
         <is>
@@ -9697,11 +9707,11 @@
         </is>
       </c>
       <c r="H420" s="6" t="n">
-        <v>-135533</v>
+        <v>-732728</v>
       </c>
       <c r="I420" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284878</t>
+          <t>Rechazo PMP1284879</t>
         </is>
       </c>
     </row>
@@ -9713,11 +9723,11 @@
       </c>
       <c r="D421" s="10" t="inlineStr">
         <is>
-          <t>PMP1284879</t>
+          <t>PMP1284948</t>
         </is>
       </c>
       <c r="E421" s="6" t="n">
-        <v>-732728</v>
+        <v>-1060968</v>
       </c>
       <c r="F421" s="10" t="inlineStr">
         <is>
@@ -9730,11 +9740,11 @@
         </is>
       </c>
       <c r="H421" s="6" t="n">
-        <v>-732728</v>
+        <v>-1060968</v>
       </c>
       <c r="I421" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284879</t>
+          <t>Rechazo PMP1284948</t>
         </is>
       </c>
     </row>
@@ -9746,11 +9756,11 @@
       </c>
       <c r="D422" s="10" t="inlineStr">
         <is>
-          <t>PMP1284948</t>
+          <t>PMP1284949</t>
         </is>
       </c>
       <c r="E422" s="6" t="n">
-        <v>-1060968</v>
+        <v>-215248</v>
       </c>
       <c r="F422" s="10" t="inlineStr">
         <is>
@@ -9763,11 +9773,11 @@
         </is>
       </c>
       <c r="H422" s="6" t="n">
-        <v>-1060968</v>
+        <v>-215248</v>
       </c>
       <c r="I422" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284948</t>
+          <t>Rechazo PMP1284949</t>
         </is>
       </c>
     </row>
@@ -9779,11 +9789,11 @@
       </c>
       <c r="D423" s="10" t="inlineStr">
         <is>
-          <t>PMP1284949</t>
+          <t>PMP1284950</t>
         </is>
       </c>
       <c r="E423" s="6" t="n">
-        <v>-215248</v>
+        <v>-1297475</v>
       </c>
       <c r="F423" s="10" t="inlineStr">
         <is>
@@ -9796,11 +9806,11 @@
         </is>
       </c>
       <c r="H423" s="6" t="n">
-        <v>-215248</v>
+        <v>-1297475</v>
       </c>
       <c r="I423" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284949</t>
+          <t>Rechazo PMP1284950</t>
         </is>
       </c>
     </row>
@@ -9812,11 +9822,11 @@
       </c>
       <c r="D424" s="10" t="inlineStr">
         <is>
-          <t>PMP1284950</t>
+          <t>PMP1284951</t>
         </is>
       </c>
       <c r="E424" s="6" t="n">
-        <v>-1297475</v>
+        <v>-5702098</v>
       </c>
       <c r="F424" s="10" t="inlineStr">
         <is>
@@ -9829,11 +9839,11 @@
         </is>
       </c>
       <c r="H424" s="6" t="n">
-        <v>-1297475</v>
+        <v>-5702098</v>
       </c>
       <c r="I424" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284950</t>
+          <t>Rechazo PMP1284951</t>
         </is>
       </c>
     </row>
@@ -9845,11 +9855,11 @@
       </c>
       <c r="D425" s="10" t="inlineStr">
         <is>
-          <t>PMP1284951</t>
+          <t>PMP1285048</t>
         </is>
       </c>
       <c r="E425" s="6" t="n">
-        <v>-5702098</v>
+        <v>-221603</v>
       </c>
       <c r="F425" s="10" t="inlineStr">
         <is>
@@ -9862,11 +9872,11 @@
         </is>
       </c>
       <c r="H425" s="6" t="n">
-        <v>-5702098</v>
+        <v>-221603</v>
       </c>
       <c r="I425" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284951</t>
+          <t>Rechazo PMP1285048</t>
         </is>
       </c>
     </row>
@@ -9878,11 +9888,11 @@
       </c>
       <c r="D426" s="10" t="inlineStr">
         <is>
-          <t>PMP1285048</t>
+          <t>PMP1285059</t>
         </is>
       </c>
       <c r="E426" s="6" t="n">
-        <v>-221603</v>
+        <v>-160294</v>
       </c>
       <c r="F426" s="10" t="inlineStr">
         <is>
@@ -9895,11 +9905,11 @@
         </is>
       </c>
       <c r="H426" s="6" t="n">
-        <v>-221603</v>
+        <v>-160294</v>
       </c>
       <c r="I426" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285048</t>
+          <t>Rechazo PMP1285059</t>
         </is>
       </c>
     </row>
@@ -9911,11 +9921,11 @@
       </c>
       <c r="D427" s="10" t="inlineStr">
         <is>
-          <t>PMP1285059</t>
+          <t>PMP1285065</t>
         </is>
       </c>
       <c r="E427" s="6" t="n">
-        <v>-160294</v>
+        <v>-107552</v>
       </c>
       <c r="F427" s="10" t="inlineStr">
         <is>
@@ -9928,11 +9938,11 @@
         </is>
       </c>
       <c r="H427" s="6" t="n">
-        <v>-160294</v>
+        <v>-107552</v>
       </c>
       <c r="I427" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285059</t>
+          <t>Rechazo PMP1285065</t>
         </is>
       </c>
     </row>
@@ -9944,11 +9954,11 @@
       </c>
       <c r="D428" s="10" t="inlineStr">
         <is>
-          <t>PMP1285065</t>
+          <t>PMP1285067</t>
         </is>
       </c>
       <c r="E428" s="6" t="n">
-        <v>-107552</v>
+        <v>-135307</v>
       </c>
       <c r="F428" s="10" t="inlineStr">
         <is>
@@ -9961,11 +9971,11 @@
         </is>
       </c>
       <c r="H428" s="6" t="n">
-        <v>-107552</v>
+        <v>-135307</v>
       </c>
       <c r="I428" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285065</t>
+          <t>Rechazo PMP1285067</t>
         </is>
       </c>
     </row>
@@ -9977,11 +9987,11 @@
       </c>
       <c r="D429" s="10" t="inlineStr">
         <is>
-          <t>PMP1285067</t>
+          <t>PMP1285071</t>
         </is>
       </c>
       <c r="E429" s="6" t="n">
-        <v>-135307</v>
+        <v>-419436</v>
       </c>
       <c r="F429" s="10" t="inlineStr">
         <is>
@@ -9994,11 +10004,11 @@
         </is>
       </c>
       <c r="H429" s="6" t="n">
-        <v>-135307</v>
+        <v>-419436</v>
       </c>
       <c r="I429" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285067</t>
+          <t>Rechazo PMP1285071</t>
         </is>
       </c>
     </row>
@@ -10010,11 +10020,11 @@
       </c>
       <c r="D430" s="10" t="inlineStr">
         <is>
-          <t>PMP1285071</t>
+          <t>PMP1285653</t>
         </is>
       </c>
       <c r="E430" s="6" t="n">
-        <v>-419436</v>
+        <v>-558246</v>
       </c>
       <c r="F430" s="10" t="inlineStr">
         <is>
@@ -10027,11 +10037,11 @@
         </is>
       </c>
       <c r="H430" s="6" t="n">
-        <v>-419436</v>
+        <v>-558246</v>
       </c>
       <c r="I430" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285071</t>
+          <t>Rechazo PMP1285653</t>
         </is>
       </c>
     </row>
@@ -10043,11 +10053,11 @@
       </c>
       <c r="D431" s="10" t="inlineStr">
         <is>
-          <t>PMP1285653</t>
+          <t>PMP1285659</t>
         </is>
       </c>
       <c r="E431" s="6" t="n">
-        <v>-558246</v>
+        <v>-311765</v>
       </c>
       <c r="F431" s="10" t="inlineStr">
         <is>
@@ -10060,11 +10070,11 @@
         </is>
       </c>
       <c r="H431" s="6" t="n">
-        <v>-558246</v>
+        <v>-311765</v>
       </c>
       <c r="I431" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285653</t>
+          <t>Rechazo PMP1285659</t>
         </is>
       </c>
     </row>
@@ -10076,11 +10086,11 @@
       </c>
       <c r="D432" s="10" t="inlineStr">
         <is>
-          <t>PMP1285659</t>
+          <t>PMP1285725</t>
         </is>
       </c>
       <c r="E432" s="6" t="n">
-        <v>-311765</v>
+        <v>-679290</v>
       </c>
       <c r="F432" s="10" t="inlineStr">
         <is>
@@ -10093,11 +10103,11 @@
         </is>
       </c>
       <c r="H432" s="6" t="n">
-        <v>-311765</v>
+        <v>-679290</v>
       </c>
       <c r="I432" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285659</t>
+          <t>Rechazo PMP1285725</t>
         </is>
       </c>
     </row>
@@ -10109,11 +10119,11 @@
       </c>
       <c r="D433" s="10" t="inlineStr">
         <is>
-          <t>PMP1285725</t>
+          <t>PMP1285898</t>
         </is>
       </c>
       <c r="E433" s="6" t="n">
-        <v>-679290</v>
+        <v>-253685</v>
       </c>
       <c r="F433" s="10" t="inlineStr">
         <is>
@@ -10126,11 +10136,11 @@
         </is>
       </c>
       <c r="H433" s="6" t="n">
-        <v>-679290</v>
+        <v>-253685</v>
       </c>
       <c r="I433" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285725</t>
+          <t>Rechazo PMP1285898</t>
         </is>
       </c>
     </row>
@@ -10142,11 +10152,11 @@
       </c>
       <c r="D434" s="10" t="inlineStr">
         <is>
-          <t>PMP1285898</t>
+          <t>PMP1285903</t>
         </is>
       </c>
       <c r="E434" s="6" t="n">
-        <v>-253685</v>
+        <v>-322554</v>
       </c>
       <c r="F434" s="10" t="inlineStr">
         <is>
@@ -10159,11 +10169,11 @@
         </is>
       </c>
       <c r="H434" s="6" t="n">
-        <v>-253685</v>
+        <v>-322554</v>
       </c>
       <c r="I434" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285898</t>
+          <t>Rechazo PMP1285903</t>
         </is>
       </c>
     </row>
@@ -10175,11 +10185,11 @@
       </c>
       <c r="D435" s="10" t="inlineStr">
         <is>
-          <t>PMP1285903</t>
+          <t>PMP1285908</t>
         </is>
       </c>
       <c r="E435" s="6" t="n">
-        <v>-322554</v>
+        <v>-135255</v>
       </c>
       <c r="F435" s="10" t="inlineStr">
         <is>
@@ -10192,11 +10202,11 @@
         </is>
       </c>
       <c r="H435" s="6" t="n">
-        <v>-322554</v>
+        <v>-135255</v>
       </c>
       <c r="I435" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285903</t>
+          <t>Rechazo PMP1285908</t>
         </is>
       </c>
     </row>
@@ -10208,11 +10218,11 @@
       </c>
       <c r="D436" s="10" t="inlineStr">
         <is>
-          <t>PMP1285908</t>
+          <t>PMP1286056</t>
         </is>
       </c>
       <c r="E436" s="6" t="n">
-        <v>-135255</v>
+        <v>-556413</v>
       </c>
       <c r="F436" s="10" t="inlineStr">
         <is>
@@ -10225,11 +10235,11 @@
         </is>
       </c>
       <c r="H436" s="6" t="n">
-        <v>-135255</v>
+        <v>-556413</v>
       </c>
       <c r="I436" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285908</t>
+          <t>Rechazo PMP1286056</t>
         </is>
       </c>
     </row>
@@ -10241,11 +10251,11 @@
       </c>
       <c r="D437" s="10" t="inlineStr">
         <is>
-          <t>PMP1286056</t>
+          <t>PMP1286208</t>
         </is>
       </c>
       <c r="E437" s="6" t="n">
-        <v>-556413</v>
+        <v>-949123</v>
       </c>
       <c r="F437" s="10" t="inlineStr">
         <is>
@@ -10258,11 +10268,11 @@
         </is>
       </c>
       <c r="H437" s="6" t="n">
-        <v>-556413</v>
+        <v>-949123</v>
       </c>
       <c r="I437" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286056</t>
+          <t>Rechazo PMP1286208</t>
         </is>
       </c>
     </row>
@@ -10274,11 +10284,11 @@
       </c>
       <c r="D438" s="10" t="inlineStr">
         <is>
-          <t>PMP1286208</t>
+          <t>PMP1286554</t>
         </is>
       </c>
       <c r="E438" s="6" t="n">
-        <v>-949123</v>
+        <v>-354934</v>
       </c>
       <c r="F438" s="10" t="inlineStr">
         <is>
@@ -10291,11 +10301,11 @@
         </is>
       </c>
       <c r="H438" s="6" t="n">
-        <v>-949123</v>
+        <v>-354934</v>
       </c>
       <c r="I438" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286208</t>
+          <t>Rechazo PMP1286554</t>
         </is>
       </c>
     </row>
@@ -10307,11 +10317,11 @@
       </c>
       <c r="D439" s="10" t="inlineStr">
         <is>
-          <t>PMP1286554</t>
+          <t>PMP1286556</t>
         </is>
       </c>
       <c r="E439" s="6" t="n">
-        <v>-354934</v>
+        <v>-364001</v>
       </c>
       <c r="F439" s="10" t="inlineStr">
         <is>
@@ -10324,11 +10334,11 @@
         </is>
       </c>
       <c r="H439" s="6" t="n">
-        <v>-354934</v>
+        <v>-364001</v>
       </c>
       <c r="I439" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286554</t>
+          <t>Rechazo PMP1286556</t>
         </is>
       </c>
     </row>
@@ -10340,11 +10350,11 @@
       </c>
       <c r="D440" s="10" t="inlineStr">
         <is>
-          <t>PMP1286556</t>
+          <t>PMP1286709</t>
         </is>
       </c>
       <c r="E440" s="6" t="n">
-        <v>-364001</v>
+        <v>-33537478</v>
       </c>
       <c r="F440" s="10" t="inlineStr">
         <is>
@@ -10357,11 +10367,11 @@
         </is>
       </c>
       <c r="H440" s="6" t="n">
-        <v>-364001</v>
+        <v>-33537478</v>
       </c>
       <c r="I440" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286556</t>
+          <t>Rechazo PMP1286709</t>
         </is>
       </c>
     </row>
@@ -10373,11 +10383,11 @@
       </c>
       <c r="D441" s="10" t="inlineStr">
         <is>
-          <t>PMP1286709</t>
+          <t>PMP1286710</t>
         </is>
       </c>
       <c r="E441" s="6" t="n">
-        <v>-33537478</v>
+        <v>-650618</v>
       </c>
       <c r="F441" s="10" t="inlineStr">
         <is>
@@ -10390,11 +10400,11 @@
         </is>
       </c>
       <c r="H441" s="6" t="n">
-        <v>-33537478</v>
+        <v>-650618</v>
       </c>
       <c r="I441" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286709</t>
+          <t>Rechazo PMP1286710</t>
         </is>
       </c>
     </row>
@@ -10406,11 +10416,11 @@
       </c>
       <c r="D442" s="10" t="inlineStr">
         <is>
-          <t>PMP1286710</t>
+          <t>PMP1286711</t>
         </is>
       </c>
       <c r="E442" s="6" t="n">
-        <v>-650618</v>
+        <v>-6920570</v>
       </c>
       <c r="F442" s="10" t="inlineStr">
         <is>
@@ -10423,11 +10433,11 @@
         </is>
       </c>
       <c r="H442" s="6" t="n">
-        <v>-650618</v>
+        <v>-6920570</v>
       </c>
       <c r="I442" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286710</t>
+          <t>Rechazo PMP1286711</t>
         </is>
       </c>
     </row>
@@ -10439,11 +10449,11 @@
       </c>
       <c r="D443" s="10" t="inlineStr">
         <is>
-          <t>PMP1286711</t>
+          <t>PMP1286712</t>
         </is>
       </c>
       <c r="E443" s="6" t="n">
-        <v>-6920570</v>
+        <v>-403395</v>
       </c>
       <c r="F443" s="10" t="inlineStr">
         <is>
@@ -10456,11 +10466,11 @@
         </is>
       </c>
       <c r="H443" s="6" t="n">
-        <v>-6920570</v>
+        <v>-403395</v>
       </c>
       <c r="I443" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286711</t>
+          <t>Rechazo PMP1286712</t>
         </is>
       </c>
     </row>
@@ -10472,11 +10482,11 @@
       </c>
       <c r="D444" s="10" t="inlineStr">
         <is>
-          <t>PMP1286712</t>
+          <t>PMP1286715</t>
         </is>
       </c>
       <c r="E444" s="6" t="n">
-        <v>-403395</v>
+        <v>-4085189</v>
       </c>
       <c r="F444" s="10" t="inlineStr">
         <is>
@@ -10489,11 +10499,11 @@
         </is>
       </c>
       <c r="H444" s="6" t="n">
-        <v>-403395</v>
+        <v>-4085189</v>
       </c>
       <c r="I444" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286712</t>
+          <t>Rechazo PMP1286715</t>
         </is>
       </c>
     </row>
@@ -10505,11 +10515,11 @@
       </c>
       <c r="D445" s="10" t="inlineStr">
         <is>
-          <t>PMP1286715</t>
+          <t>PMP1286716</t>
         </is>
       </c>
       <c r="E445" s="6" t="n">
-        <v>-4085189</v>
+        <v>-822039</v>
       </c>
       <c r="F445" s="10" t="inlineStr">
         <is>
@@ -10522,11 +10532,11 @@
         </is>
       </c>
       <c r="H445" s="6" t="n">
-        <v>-4085189</v>
+        <v>-822039</v>
       </c>
       <c r="I445" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286715</t>
+          <t>Rechazo PMP1286716</t>
         </is>
       </c>
     </row>
@@ -10538,11 +10548,11 @@
       </c>
       <c r="D446" s="10" t="inlineStr">
         <is>
-          <t>PMP1286716</t>
+          <t>PMP1287257</t>
         </is>
       </c>
       <c r="E446" s="6" t="n">
-        <v>-822039</v>
+        <v>-156625</v>
       </c>
       <c r="F446" s="10" t="inlineStr">
         <is>
@@ -10555,11 +10565,11 @@
         </is>
       </c>
       <c r="H446" s="6" t="n">
-        <v>-822039</v>
+        <v>-156625</v>
       </c>
       <c r="I446" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286716</t>
+          <t>Rechazo PMP1287257</t>
         </is>
       </c>
     </row>
@@ -10571,11 +10581,11 @@
       </c>
       <c r="D447" s="10" t="inlineStr">
         <is>
-          <t>PMP1287257</t>
+          <t>PMP1287321</t>
         </is>
       </c>
       <c r="E447" s="6" t="n">
-        <v>-156625</v>
+        <v>-182163</v>
       </c>
       <c r="F447" s="10" t="inlineStr">
         <is>
@@ -10588,11 +10598,11 @@
         </is>
       </c>
       <c r="H447" s="6" t="n">
-        <v>-156625</v>
+        <v>-182163</v>
       </c>
       <c r="I447" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287257</t>
+          <t>Rechazo PMP1287321</t>
         </is>
       </c>
     </row>
@@ -10604,11 +10614,11 @@
       </c>
       <c r="D448" s="10" t="inlineStr">
         <is>
-          <t>PMP1287321</t>
+          <t>PMP1287325</t>
         </is>
       </c>
       <c r="E448" s="6" t="n">
-        <v>-182163</v>
+        <v>-118625</v>
       </c>
       <c r="F448" s="10" t="inlineStr">
         <is>
@@ -10621,11 +10631,11 @@
         </is>
       </c>
       <c r="H448" s="6" t="n">
-        <v>-182163</v>
+        <v>-118625</v>
       </c>
       <c r="I448" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287321</t>
+          <t>Rechazo PMP1287325</t>
         </is>
       </c>
     </row>
@@ -10637,11 +10647,11 @@
       </c>
       <c r="D449" s="10" t="inlineStr">
         <is>
-          <t>PMP1287325</t>
+          <t>PMP1287335</t>
         </is>
       </c>
       <c r="E449" s="6" t="n">
-        <v>-118625</v>
+        <v>-128620</v>
       </c>
       <c r="F449" s="10" t="inlineStr">
         <is>
@@ -10654,11 +10664,11 @@
         </is>
       </c>
       <c r="H449" s="6" t="n">
-        <v>-118625</v>
+        <v>-128620</v>
       </c>
       <c r="I449" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287325</t>
+          <t>Rechazo PMP1287335</t>
         </is>
       </c>
     </row>
@@ -10670,11 +10680,11 @@
       </c>
       <c r="D450" s="10" t="inlineStr">
         <is>
-          <t>PMP1287335</t>
+          <t>PMP1287379</t>
         </is>
       </c>
       <c r="E450" s="6" t="n">
-        <v>-128620</v>
+        <v>-271757</v>
       </c>
       <c r="F450" s="10" t="inlineStr">
         <is>
@@ -10687,11 +10697,11 @@
         </is>
       </c>
       <c r="H450" s="6" t="n">
-        <v>-128620</v>
+        <v>-271757</v>
       </c>
       <c r="I450" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287335</t>
+          <t>Rechazo PMP1287379</t>
         </is>
       </c>
     </row>
@@ -10703,11 +10713,11 @@
       </c>
       <c r="D451" s="10" t="inlineStr">
         <is>
-          <t>PMP1287379</t>
+          <t>PMP1287385</t>
         </is>
       </c>
       <c r="E451" s="6" t="n">
-        <v>-271757</v>
+        <v>-214996</v>
       </c>
       <c r="F451" s="10" t="inlineStr">
         <is>
@@ -10720,11 +10730,11 @@
         </is>
       </c>
       <c r="H451" s="6" t="n">
-        <v>-271757</v>
+        <v>-214996</v>
       </c>
       <c r="I451" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287379</t>
+          <t>Rechazo PMP1287385</t>
         </is>
       </c>
     </row>
@@ -10736,11 +10746,11 @@
       </c>
       <c r="D452" s="10" t="inlineStr">
         <is>
-          <t>PMP1287385</t>
+          <t>PMP1287386</t>
         </is>
       </c>
       <c r="E452" s="6" t="n">
-        <v>-214996</v>
+        <v>-267680</v>
       </c>
       <c r="F452" s="10" t="inlineStr">
         <is>
@@ -10753,11 +10763,11 @@
         </is>
       </c>
       <c r="H452" s="6" t="n">
-        <v>-214996</v>
+        <v>-267680</v>
       </c>
       <c r="I452" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287385</t>
+          <t>Rechazo PMP1287386</t>
         </is>
       </c>
     </row>
@@ -10769,11 +10779,11 @@
       </c>
       <c r="D453" s="10" t="inlineStr">
         <is>
-          <t>PMP1287386</t>
+          <t>PMP1287574</t>
         </is>
       </c>
       <c r="E453" s="6" t="n">
-        <v>-267680</v>
+        <v>-11940004</v>
       </c>
       <c r="F453" s="10" t="inlineStr">
         <is>
@@ -10786,11 +10796,11 @@
         </is>
       </c>
       <c r="H453" s="6" t="n">
-        <v>-267680</v>
+        <v>-11940004</v>
       </c>
       <c r="I453" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287386</t>
+          <t>Rechazo PMP1287574</t>
         </is>
       </c>
     </row>
@@ -10802,11 +10812,11 @@
       </c>
       <c r="D454" s="10" t="inlineStr">
         <is>
-          <t>PMP1287574</t>
+          <t>PMP1287736</t>
         </is>
       </c>
       <c r="E454" s="6" t="n">
-        <v>-11940004</v>
+        <v>-93440</v>
       </c>
       <c r="F454" s="10" t="inlineStr">
         <is>
@@ -10819,11 +10829,11 @@
         </is>
       </c>
       <c r="H454" s="6" t="n">
-        <v>-11940004</v>
+        <v>-93440</v>
       </c>
       <c r="I454" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287574</t>
+          <t>Rechazo PMP1287736</t>
         </is>
       </c>
     </row>
@@ -10835,11 +10845,11 @@
       </c>
       <c r="D455" s="10" t="inlineStr">
         <is>
-          <t>PMP1287736</t>
+          <t>PMP128777746</t>
         </is>
       </c>
       <c r="E455" s="6" t="n">
-        <v>-93440</v>
+        <v>-322500</v>
       </c>
       <c r="F455" s="10" t="inlineStr">
         <is>
@@ -10852,11 +10862,11 @@
         </is>
       </c>
       <c r="H455" s="6" t="n">
-        <v>-93440</v>
+        <v>-322500</v>
       </c>
       <c r="I455" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287736</t>
+          <t>Rechazo PMP128777746</t>
         </is>
       </c>
     </row>
@@ -10868,11 +10878,11 @@
       </c>
       <c r="D456" s="10" t="inlineStr">
         <is>
-          <t>PMP128777746</t>
+          <t>PMP1287829</t>
         </is>
       </c>
       <c r="E456" s="6" t="n">
-        <v>-322500</v>
+        <v>-290823</v>
       </c>
       <c r="F456" s="10" t="inlineStr">
         <is>
@@ -10885,11 +10895,11 @@
         </is>
       </c>
       <c r="H456" s="6" t="n">
-        <v>-322500</v>
+        <v>-290823</v>
       </c>
       <c r="I456" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP128777746</t>
+          <t>Rechazo PMP1287829</t>
         </is>
       </c>
     </row>
@@ -10901,11 +10911,11 @@
       </c>
       <c r="D457" s="10" t="inlineStr">
         <is>
-          <t>PMP1287829</t>
+          <t>PMP1287903</t>
         </is>
       </c>
       <c r="E457" s="6" t="n">
-        <v>-290823</v>
+        <v>-128514</v>
       </c>
       <c r="F457" s="10" t="inlineStr">
         <is>
@@ -10918,11 +10928,11 @@
         </is>
       </c>
       <c r="H457" s="6" t="n">
-        <v>-290823</v>
+        <v>-128514</v>
       </c>
       <c r="I457" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287829</t>
+          <t>Rechazo PMP1287903</t>
         </is>
       </c>
     </row>
@@ -10934,11 +10944,11 @@
       </c>
       <c r="D458" s="10" t="inlineStr">
         <is>
-          <t>PMP1287903</t>
+          <t>PMP1287904</t>
         </is>
       </c>
       <c r="E458" s="6" t="n">
-        <v>-128514</v>
+        <v>-80064</v>
       </c>
       <c r="F458" s="10" t="inlineStr">
         <is>
@@ -10951,11 +10961,11 @@
         </is>
       </c>
       <c r="H458" s="6" t="n">
-        <v>-128514</v>
+        <v>-80064</v>
       </c>
       <c r="I458" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287903</t>
+          <t>Rechazo PMP1287904</t>
         </is>
       </c>
     </row>
@@ -10967,11 +10977,11 @@
       </c>
       <c r="D459" s="10" t="inlineStr">
         <is>
-          <t>PMP1287904</t>
+          <t>PMP1287920</t>
         </is>
       </c>
       <c r="E459" s="6" t="n">
-        <v>-80064</v>
+        <v>-582605</v>
       </c>
       <c r="F459" s="10" t="inlineStr">
         <is>
@@ -10984,11 +10994,11 @@
         </is>
       </c>
       <c r="H459" s="6" t="n">
-        <v>-80064</v>
+        <v>-582605</v>
       </c>
       <c r="I459" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287904</t>
+          <t>Rechazo PMP1287920</t>
         </is>
       </c>
     </row>
@@ -11000,11 +11010,11 @@
       </c>
       <c r="D460" s="10" t="inlineStr">
         <is>
-          <t>PMP1287920</t>
+          <t>PMP1287921</t>
         </is>
       </c>
       <c r="E460" s="6" t="n">
-        <v>-582605</v>
+        <v>-124374</v>
       </c>
       <c r="F460" s="10" t="inlineStr">
         <is>
@@ -11017,11 +11027,11 @@
         </is>
       </c>
       <c r="H460" s="6" t="n">
-        <v>-582605</v>
+        <v>-124374</v>
       </c>
       <c r="I460" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287920</t>
+          <t>Rechazo PMP1287921</t>
         </is>
       </c>
     </row>
@@ -11033,11 +11043,11 @@
       </c>
       <c r="D461" s="10" t="inlineStr">
         <is>
-          <t>PMP1287921</t>
+          <t>PMP1287928</t>
         </is>
       </c>
       <c r="E461" s="6" t="n">
-        <v>-124374</v>
+        <v>-246230</v>
       </c>
       <c r="F461" s="10" t="inlineStr">
         <is>
@@ -11050,11 +11060,11 @@
         </is>
       </c>
       <c r="H461" s="6" t="n">
-        <v>-124374</v>
+        <v>-246230</v>
       </c>
       <c r="I461" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287921</t>
+          <t>Rechazo PMP1287928</t>
         </is>
       </c>
     </row>
@@ -11066,11 +11076,11 @@
       </c>
       <c r="D462" s="10" t="inlineStr">
         <is>
-          <t>PMP1287928</t>
+          <t>PMP1287930</t>
         </is>
       </c>
       <c r="E462" s="6" t="n">
-        <v>-246230</v>
+        <v>-91079</v>
       </c>
       <c r="F462" s="10" t="inlineStr">
         <is>
@@ -11083,11 +11093,11 @@
         </is>
       </c>
       <c r="H462" s="6" t="n">
-        <v>-246230</v>
+        <v>-91079</v>
       </c>
       <c r="I462" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287928</t>
+          <t>Rechazo PMP1287930</t>
         </is>
       </c>
     </row>
@@ -11099,11 +11109,11 @@
       </c>
       <c r="D463" s="10" t="inlineStr">
         <is>
-          <t>PMP1287930</t>
+          <t>PMP1287931</t>
         </is>
       </c>
       <c r="E463" s="6" t="n">
-        <v>-91079</v>
+        <v>-215025</v>
       </c>
       <c r="F463" s="10" t="inlineStr">
         <is>
@@ -11116,11 +11126,11 @@
         </is>
       </c>
       <c r="H463" s="6" t="n">
-        <v>-91079</v>
+        <v>-215025</v>
       </c>
       <c r="I463" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287930</t>
+          <t>Rechazo PMP1287931</t>
         </is>
       </c>
     </row>
@@ -11132,11 +11142,11 @@
       </c>
       <c r="D464" s="10" t="inlineStr">
         <is>
-          <t>PMP1287931</t>
+          <t>PMP1287948</t>
         </is>
       </c>
       <c r="E464" s="6" t="n">
-        <v>-215025</v>
+        <v>-354871</v>
       </c>
       <c r="F464" s="10" t="inlineStr">
         <is>
@@ -11149,11 +11159,11 @@
         </is>
       </c>
       <c r="H464" s="6" t="n">
-        <v>-215025</v>
+        <v>-354871</v>
       </c>
       <c r="I464" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287931</t>
+          <t>Rechazo PMP1287948</t>
         </is>
       </c>
     </row>
@@ -11165,11 +11175,11 @@
       </c>
       <c r="D465" s="10" t="inlineStr">
         <is>
-          <t>PMP1287948</t>
+          <t>PMP1287949</t>
         </is>
       </c>
       <c r="E465" s="6" t="n">
-        <v>-354871</v>
+        <v>-410669</v>
       </c>
       <c r="F465" s="10" t="inlineStr">
         <is>
@@ -11182,11 +11192,11 @@
         </is>
       </c>
       <c r="H465" s="6" t="n">
-        <v>-354871</v>
+        <v>-410669</v>
       </c>
       <c r="I465" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287948</t>
+          <t>Rechazo PMP1287949</t>
         </is>
       </c>
     </row>
@@ -11198,11 +11208,11 @@
       </c>
       <c r="D466" s="10" t="inlineStr">
         <is>
-          <t>PMP1287949</t>
+          <t>PMP1287951</t>
         </is>
       </c>
       <c r="E466" s="6" t="n">
-        <v>-410669</v>
+        <v>-29456389</v>
       </c>
       <c r="F466" s="10" t="inlineStr">
         <is>
@@ -11215,11 +11225,11 @@
         </is>
       </c>
       <c r="H466" s="6" t="n">
-        <v>-410669</v>
+        <v>-29456389</v>
       </c>
       <c r="I466" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287949</t>
+          <t>Rechazo PMP1287951</t>
         </is>
       </c>
     </row>
@@ -11231,11 +11241,11 @@
       </c>
       <c r="D467" s="10" t="inlineStr">
         <is>
-          <t>PMP1287951</t>
+          <t>PMP1287957</t>
         </is>
       </c>
       <c r="E467" s="6" t="n">
-        <v>-29456389</v>
+        <v>-107492</v>
       </c>
       <c r="F467" s="10" t="inlineStr">
         <is>
@@ -11248,11 +11258,11 @@
         </is>
       </c>
       <c r="H467" s="6" t="n">
-        <v>-29456389</v>
+        <v>-107492</v>
       </c>
       <c r="I467" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287951</t>
+          <t>Rechazo PMP1287957</t>
         </is>
       </c>
     </row>
@@ -11264,11 +11274,11 @@
       </c>
       <c r="D468" s="10" t="inlineStr">
         <is>
-          <t>PMP1287957</t>
+          <t>PMP1288418</t>
         </is>
       </c>
       <c r="E468" s="6" t="n">
-        <v>-107492</v>
+        <v>-2183651</v>
       </c>
       <c r="F468" s="10" t="inlineStr">
         <is>
@@ -11281,11 +11291,11 @@
         </is>
       </c>
       <c r="H468" s="6" t="n">
-        <v>-107492</v>
+        <v>-2183651</v>
       </c>
       <c r="I468" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287957</t>
+          <t>Rechazo PMP1288418</t>
         </is>
       </c>
     </row>
@@ -11297,11 +11307,11 @@
       </c>
       <c r="D469" s="10" t="inlineStr">
         <is>
-          <t>PMP1288418</t>
+          <t>PMP1288731</t>
         </is>
       </c>
       <c r="E469" s="6" t="n">
-        <v>-2183651</v>
+        <v>-160222</v>
       </c>
       <c r="F469" s="10" t="inlineStr">
         <is>
@@ -11314,11 +11324,11 @@
         </is>
       </c>
       <c r="H469" s="6" t="n">
-        <v>-2183651</v>
+        <v>-160222</v>
       </c>
       <c r="I469" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288418</t>
+          <t>Rechazo PMP1288731</t>
         </is>
       </c>
     </row>
@@ -11330,11 +11340,11 @@
       </c>
       <c r="D470" s="10" t="inlineStr">
         <is>
-          <t>PMP1288731</t>
+          <t>PMP1288919</t>
         </is>
       </c>
       <c r="E470" s="6" t="n">
-        <v>-160222</v>
+        <v>-9852</v>
       </c>
       <c r="F470" s="10" t="inlineStr">
         <is>
@@ -11347,11 +11357,11 @@
         </is>
       </c>
       <c r="H470" s="6" t="n">
-        <v>-160222</v>
+        <v>-9852</v>
       </c>
       <c r="I470" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288731</t>
+          <t>Rechazo PMP1288919</t>
         </is>
       </c>
     </row>
@@ -11363,11 +11373,11 @@
       </c>
       <c r="D471" s="10" t="inlineStr">
         <is>
-          <t>PMP1288919</t>
+          <t>PMP1288926</t>
         </is>
       </c>
       <c r="E471" s="6" t="n">
-        <v>-9852</v>
+        <v>-322749</v>
       </c>
       <c r="F471" s="10" t="inlineStr">
         <is>
@@ -11380,11 +11390,11 @@
         </is>
       </c>
       <c r="H471" s="6" t="n">
-        <v>-9852</v>
+        <v>-322749</v>
       </c>
       <c r="I471" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288919</t>
+          <t>Rechazo PMP1288926</t>
         </is>
       </c>
     </row>
@@ -11396,11 +11406,11 @@
       </c>
       <c r="D472" s="10" t="inlineStr">
         <is>
-          <t>PMP1288926</t>
+          <t>PMP1288987</t>
         </is>
       </c>
       <c r="E472" s="6" t="n">
-        <v>-322749</v>
+        <v>-1106307</v>
       </c>
       <c r="F472" s="10" t="inlineStr">
         <is>
@@ -11413,11 +11423,11 @@
         </is>
       </c>
       <c r="H472" s="6" t="n">
-        <v>-322749</v>
+        <v>-1106307</v>
       </c>
       <c r="I472" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288926</t>
+          <t>Rechazo PMP1288987</t>
         </is>
       </c>
     </row>
@@ -11429,11 +11439,11 @@
       </c>
       <c r="D473" s="10" t="inlineStr">
         <is>
-          <t>PMP1288987</t>
+          <t>PMP1288988</t>
         </is>
       </c>
       <c r="E473" s="6" t="n">
-        <v>-1106307</v>
+        <v>-33894</v>
       </c>
       <c r="F473" s="10" t="inlineStr">
         <is>
@@ -11446,11 +11456,11 @@
         </is>
       </c>
       <c r="H473" s="6" t="n">
-        <v>-1106307</v>
+        <v>-33894</v>
       </c>
       <c r="I473" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288987</t>
+          <t>Rechazo PMP1288988</t>
         </is>
       </c>
     </row>
@@ -11462,11 +11472,11 @@
       </c>
       <c r="D474" s="10" t="inlineStr">
         <is>
-          <t>PMP1288988</t>
+          <t>PMP1288989</t>
         </is>
       </c>
       <c r="E474" s="6" t="n">
-        <v>-33894</v>
+        <v>-2259163</v>
       </c>
       <c r="F474" s="10" t="inlineStr">
         <is>
@@ -11479,11 +11489,11 @@
         </is>
       </c>
       <c r="H474" s="6" t="n">
-        <v>-33894</v>
+        <v>-2259163</v>
       </c>
       <c r="I474" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288988</t>
+          <t>Rechazo PMP1288989</t>
         </is>
       </c>
     </row>
@@ -11495,11 +11505,11 @@
       </c>
       <c r="D475" s="10" t="inlineStr">
         <is>
-          <t>PMP1288989</t>
+          <t>PMP1289251</t>
         </is>
       </c>
       <c r="E475" s="6" t="n">
-        <v>-2259163</v>
+        <v>-200703</v>
       </c>
       <c r="F475" s="10" t="inlineStr">
         <is>
@@ -11512,11 +11522,11 @@
         </is>
       </c>
       <c r="H475" s="6" t="n">
-        <v>-2259163</v>
+        <v>-200703</v>
       </c>
       <c r="I475" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288989</t>
+          <t>Rechazo PMP1289251</t>
         </is>
       </c>
     </row>
@@ -11528,11 +11538,11 @@
       </c>
       <c r="D476" s="10" t="inlineStr">
         <is>
-          <t>PMP1289251</t>
+          <t>PMP1289253</t>
         </is>
       </c>
       <c r="E476" s="6" t="n">
-        <v>-200703</v>
+        <v>-2482097</v>
       </c>
       <c r="F476" s="10" t="inlineStr">
         <is>
@@ -11545,11 +11555,11 @@
         </is>
       </c>
       <c r="H476" s="6" t="n">
-        <v>-200703</v>
+        <v>-2482097</v>
       </c>
       <c r="I476" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1289251</t>
+          <t>Rechazo PMP1289253</t>
         </is>
       </c>
     </row>
@@ -11561,11 +11571,11 @@
       </c>
       <c r="D477" s="10" t="inlineStr">
         <is>
-          <t>PMP1289253</t>
+          <t>PMP1289324</t>
         </is>
       </c>
       <c r="E477" s="6" t="n">
-        <v>-2482097</v>
+        <v>-532656</v>
       </c>
       <c r="F477" s="10" t="inlineStr">
         <is>
@@ -11578,11 +11588,11 @@
         </is>
       </c>
       <c r="H477" s="6" t="n">
-        <v>-2482097</v>
+        <v>-532656</v>
       </c>
       <c r="I477" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1289253</t>
+          <t>Rechazo PMP1289324</t>
         </is>
       </c>
     </row>
@@ -11594,11 +11604,11 @@
       </c>
       <c r="D478" s="10" t="inlineStr">
         <is>
-          <t>PMP1289324</t>
+          <t>PMP1289326</t>
         </is>
       </c>
       <c r="E478" s="6" t="n">
-        <v>-532656</v>
+        <v>-523796</v>
       </c>
       <c r="F478" s="10" t="inlineStr">
         <is>
@@ -11611,11 +11621,11 @@
         </is>
       </c>
       <c r="H478" s="6" t="n">
-        <v>-532656</v>
+        <v>-523796</v>
       </c>
       <c r="I478" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1289324</t>
+          <t>Rechazo PMP1289326</t>
         </is>
       </c>
     </row>
@@ -11627,11 +11637,11 @@
       </c>
       <c r="D479" s="10" t="inlineStr">
         <is>
-          <t>PMP1289326</t>
+          <t>PMP1289328</t>
         </is>
       </c>
       <c r="E479" s="6" t="n">
-        <v>-523796</v>
+        <v>-303757</v>
       </c>
       <c r="F479" s="10" t="inlineStr">
         <is>
@@ -11644,11 +11654,11 @@
         </is>
       </c>
       <c r="H479" s="6" t="n">
-        <v>-523796</v>
+        <v>-303757</v>
       </c>
       <c r="I479" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1289326</t>
+          <t>Rechazo PMP1289328</t>
         </is>
       </c>
     </row>
@@ -11660,11 +11670,11 @@
       </c>
       <c r="D480" s="10" t="inlineStr">
         <is>
-          <t>PMP1289328</t>
+          <t>PMP1289507</t>
         </is>
       </c>
       <c r="E480" s="6" t="n">
-        <v>-303757</v>
+        <v>-160184</v>
       </c>
       <c r="F480" s="10" t="inlineStr">
         <is>
@@ -11677,11 +11687,11 @@
         </is>
       </c>
       <c r="H480" s="6" t="n">
-        <v>-303757</v>
+        <v>-160184</v>
       </c>
       <c r="I480" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1289328</t>
+          <t>Rechazo PMP1289507</t>
         </is>
       </c>
     </row>
@@ -11693,59 +11703,26 @@
       </c>
       <c r="D481" s="10" t="inlineStr">
         <is>
-          <t>PMP1289507</t>
+          <t>Costo de Transferen</t>
         </is>
       </c>
       <c r="E481" s="6" t="n">
-        <v>-160184</v>
+        <v>-3000</v>
       </c>
       <c r="F481" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>Costo de Transferen</t>
         </is>
       </c>
       <c r="G481" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>WOB</t>
         </is>
       </c>
       <c r="H481" s="6" t="n">
-        <v>-160184</v>
+        <v>-3000</v>
       </c>
       <c r="I481" s="11" t="inlineStr">
-        <is>
-          <t>Rechazo PMP1289507</t>
-        </is>
-      </c>
-    </row>
-    <row r="482">
-      <c r="C482" s="10" t="inlineStr">
-        <is>
-          <t>Descuentos Clientes</t>
-        </is>
-      </c>
-      <c r="D482" s="10" t="inlineStr">
-        <is>
-          <t>Costo de Transferen</t>
-        </is>
-      </c>
-      <c r="E482" s="6" t="n">
-        <v>-3000</v>
-      </c>
-      <c r="F482" s="10" t="inlineStr">
-        <is>
-          <t>Costo de Transferen</t>
-        </is>
-      </c>
-      <c r="G482" s="10" t="inlineStr">
-        <is>
-          <t>WOB</t>
-        </is>
-      </c>
-      <c r="H482" s="6" t="n">
-        <v>-3000</v>
-      </c>
-      <c r="I482" s="11" t="inlineStr">
         <is>
           <t>MENORES VALORES</t>
         </is>

--- a/Pruebas/Archivos/Template/Colombia/Template_HRC_Cenco.xlsx
+++ b/Pruebas/Archivos/Template/Colombia/Template_HRC_Cenco.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I481"/>
+  <dimension ref="A1:I488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -583,7 +583,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>26/11/2025</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -7974,28 +7974,28 @@
       </c>
       <c r="D368" s="10" t="inlineStr">
         <is>
+          <t>DTO POR ESCALA VOLU</t>
+        </is>
+      </c>
+      <c r="E368" s="6" t="n">
+        <v>-2187232</v>
+      </c>
+      <c r="F368" s="10" t="inlineStr">
+        <is>
           <t>DESCUENTO</t>
         </is>
       </c>
-      <c r="E368" s="6" t="n">
-        <v>-61299192</v>
-      </c>
-      <c r="F368" s="10" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
       <c r="G368" s="10" t="inlineStr">
         <is>
           <t>987</t>
         </is>
       </c>
       <c r="H368" s="6" t="n">
-        <v>-61299192</v>
+        <v>-2187232</v>
       </c>
       <c r="I368" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RPL DSCTO  DESCUENTO </t>
+          <t xml:space="preserve">DEC DSCTO  DTO POR ESCALA VOLU </t>
         </is>
       </c>
     </row>
@@ -8007,11 +8007,11 @@
       </c>
       <c r="D369" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO APERTURA</t>
+          <t>DTO POR ESCALA VOLU</t>
         </is>
       </c>
       <c r="E369" s="6" t="n">
-        <v>-22852333</v>
+        <v>-1327497</v>
       </c>
       <c r="F369" s="10" t="inlineStr">
         <is>
@@ -8024,11 +8024,11 @@
         </is>
       </c>
       <c r="H369" s="6" t="n">
-        <v>-22852333</v>
+        <v>-1327497</v>
       </c>
       <c r="I369" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAV DSCTO  DESCUENTO APERTURA </t>
+          <t xml:space="preserve">DEC DSCTO 20251100199283 DTO POR ESCALA VOLU </t>
         </is>
       </c>
     </row>
@@ -8040,11 +8040,11 @@
       </c>
       <c r="D370" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO CALENDARI</t>
+          <t>DTO POR ESCALA VOLU</t>
         </is>
       </c>
       <c r="E370" s="6" t="n">
-        <v>-2619475738</v>
+        <v>-896070</v>
       </c>
       <c r="F370" s="10" t="inlineStr">
         <is>
@@ -8057,11 +8057,11 @@
         </is>
       </c>
       <c r="H370" s="6" t="n">
-        <v>-2619475738</v>
+        <v>-896070</v>
       </c>
       <c r="I370" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DCA DSCTO  DESCUENTO CALENDARI </t>
+          <t xml:space="preserve">DEC DSCTO 20251200199299 DTO POR ESCALA VOLU </t>
         </is>
       </c>
     </row>
@@ -8073,11 +8073,11 @@
       </c>
       <c r="D371" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO COMPRAS</t>
+          <t>DTO POR ESCALA VOLU</t>
         </is>
       </c>
       <c r="E371" s="6" t="n">
-        <v>-1394767</v>
+        <v>-616199</v>
       </c>
       <c r="F371" s="10" t="inlineStr">
         <is>
@@ -8090,11 +8090,11 @@
         </is>
       </c>
       <c r="H371" s="6" t="n">
-        <v>-1394767</v>
+        <v>-616199</v>
       </c>
       <c r="I371" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DCC DSCTO  DESCUENTO COMPRAS </t>
+          <t xml:space="preserve">DEC DSCTO 20251200199300 DTO POR ESCALA VOLU </t>
         </is>
       </c>
     </row>
@@ -8106,11 +8106,11 @@
       </c>
       <c r="D372" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO EN PRIMER</t>
+          <t>DTO POR ESCALA VOLU</t>
         </is>
       </c>
       <c r="E372" s="6" t="n">
-        <v>-10216531</v>
+        <v>-36108</v>
       </c>
       <c r="F372" s="10" t="inlineStr">
         <is>
@@ -8123,11 +8123,11 @@
         </is>
       </c>
       <c r="H372" s="6" t="n">
-        <v>-10216531</v>
+        <v>-36108</v>
       </c>
       <c r="I372" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DPC DSCTO  DESCUENTO EN PRIMER </t>
+          <t xml:space="preserve">DEC DSCTO 20251200199301 DTO POR ESCALA VOLU </t>
         </is>
       </c>
     </row>
@@ -8139,11 +8139,11 @@
       </c>
       <c r="D373" s="10" t="inlineStr">
         <is>
-          <t>DEVOLUCIONES</t>
+          <t>DTO POR ESCALA VOLU</t>
         </is>
       </c>
       <c r="E373" s="6" t="n">
-        <v>-5587084</v>
+        <v>-210000</v>
       </c>
       <c r="F373" s="10" t="inlineStr">
         <is>
@@ -8156,11 +8156,11 @@
         </is>
       </c>
       <c r="H373" s="6" t="n">
-        <v>-5587084</v>
+        <v>-210000</v>
       </c>
       <c r="I373" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DND DSCTO  DEVOLUCIONES </t>
+          <t xml:space="preserve">DEC DSCTO 20251200200041 DTO POR ESCALA VOLU </t>
         </is>
       </c>
     </row>
@@ -8172,15 +8172,15 @@
       </c>
       <c r="D374" s="10" t="inlineStr">
         <is>
-          <t>DSTO COMERCIAL FIJO</t>
+          <t>DESCUENTO APERTURA</t>
         </is>
       </c>
       <c r="E374" s="6" t="n">
-        <v>-145861342</v>
+        <v>-8594192</v>
       </c>
       <c r="F374" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>DROGUE</t>
         </is>
       </c>
       <c r="G374" s="10" t="inlineStr">
@@ -8189,11 +8189,11 @@
         </is>
       </c>
       <c r="H374" s="6" t="n">
-        <v>-145861342</v>
+        <v>-8594192</v>
       </c>
       <c r="I374" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DCF DSCTO  DSTO COMERCIAL FIJO </t>
+          <t>DAV DSCTO  DESCUENTO APERTURA DROGUE</t>
         </is>
       </c>
     </row>
@@ -8205,15 +8205,15 @@
       </c>
       <c r="D375" s="10" t="inlineStr">
         <is>
-          <t>DTO POR ESCALA VOLU</t>
+          <t>DESCUENTO CALENDARI</t>
         </is>
       </c>
       <c r="E375" s="6" t="n">
-        <v>-2210671</v>
+        <v>-817508590</v>
       </c>
       <c r="F375" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>DROGUE</t>
         </is>
       </c>
       <c r="G375" s="10" t="inlineStr">
@@ -8222,11 +8222,11 @@
         </is>
       </c>
       <c r="H375" s="6" t="n">
-        <v>-2210671</v>
+        <v>-817508590</v>
       </c>
       <c r="I375" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEC DSCTO  DTO POR ESCALA VOLU </t>
+          <t>DCA DSCTO  DESCUENTO CALENDARI DROGUE</t>
         </is>
       </c>
     </row>
@@ -8238,15 +8238,15 @@
       </c>
       <c r="D376" s="10" t="inlineStr">
         <is>
-          <t>DTO POR ESCALA VOLU</t>
+          <t>DEVOLUCIONES</t>
         </is>
       </c>
       <c r="E376" s="6" t="n">
-        <v>-1327497</v>
+        <v>-3512351</v>
       </c>
       <c r="F376" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>DROGUE</t>
         </is>
       </c>
       <c r="G376" s="10" t="inlineStr">
@@ -8255,11 +8255,11 @@
         </is>
       </c>
       <c r="H376" s="6" t="n">
-        <v>-1327497</v>
+        <v>-3512351</v>
       </c>
       <c r="I376" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEC DSCTO 20251100199283 DTO POR ESCALA VOLU </t>
+          <t>DND DSCTO  DEVOLUCIONES DROGUE</t>
         </is>
       </c>
     </row>
@@ -8271,15 +8271,15 @@
       </c>
       <c r="D377" s="10" t="inlineStr">
         <is>
-          <t>DTO POR ESCALA VOLU</t>
+          <t>DSTO COMERCIAL FIJO</t>
         </is>
       </c>
       <c r="E377" s="6" t="n">
-        <v>-896070</v>
+        <v>-48283208</v>
       </c>
       <c r="F377" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>DROGUE</t>
         </is>
       </c>
       <c r="G377" s="10" t="inlineStr">
@@ -8288,11 +8288,11 @@
         </is>
       </c>
       <c r="H377" s="6" t="n">
-        <v>-896070</v>
+        <v>-48283208</v>
       </c>
       <c r="I377" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEC DSCTO 20251200199299 DTO POR ESCALA VOLU </t>
+          <t>DCF DSCTO  DSTO COMERCIAL FIJO DROGUE</t>
         </is>
       </c>
     </row>
@@ -8308,11 +8308,11 @@
         </is>
       </c>
       <c r="E378" s="6" t="n">
-        <v>-616199</v>
+        <v>-67283120</v>
       </c>
       <c r="F378" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>DROGUE</t>
         </is>
       </c>
       <c r="G378" s="10" t="inlineStr">
@@ -8321,11 +8321,11 @@
         </is>
       </c>
       <c r="H378" s="6" t="n">
-        <v>-616199</v>
+        <v>-67283120</v>
       </c>
       <c r="I378" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEC DSCTO 20251200199300 DTO POR ESCALA VOLU </t>
+          <t>DEC DSCTO  DTO POR ESCALA VOLU DROGUE</t>
         </is>
       </c>
     </row>
@@ -8341,11 +8341,11 @@
         </is>
       </c>
       <c r="E379" s="6" t="n">
-        <v>-36108</v>
+        <v>-838419</v>
       </c>
       <c r="F379" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>DROGUE</t>
         </is>
       </c>
       <c r="G379" s="10" t="inlineStr">
@@ -8354,11 +8354,11 @@
         </is>
       </c>
       <c r="H379" s="6" t="n">
-        <v>-36108</v>
+        <v>-838419</v>
       </c>
       <c r="I379" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEC DSCTO 20251200199301 DTO POR ESCALA VOLU </t>
+          <t>DEC DSCTO 20251100199283 DTO POR ESCALA VOLU DROGUE</t>
         </is>
       </c>
     </row>
@@ -8370,28 +8370,28 @@
       </c>
       <c r="D380" s="10" t="inlineStr">
         <is>
-          <t>DTO POR ESCALA VOLU</t>
+          <t>VPP1 2004529ADM. FIDELIDAD -</t>
         </is>
       </c>
       <c r="E380" s="6" t="n">
-        <v>-210000</v>
+        <v>-57239000</v>
       </c>
       <c r="F380" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>FACT PROVEED</t>
         </is>
       </c>
       <c r="G380" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>CSB</t>
         </is>
       </c>
       <c r="H380" s="6" t="n">
-        <v>-210000</v>
+        <v>-57239000</v>
       </c>
       <c r="I380" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEC DSCTO 20251200200041 DTO POR ESCALA VOLU </t>
+          <t>VPP1 2004529ADM. FIDELIDAD -</t>
         </is>
       </c>
     </row>
@@ -8403,28 +8403,28 @@
       </c>
       <c r="D381" s="10" t="inlineStr">
         <is>
-          <t>DTO POR ESCALA VOLU</t>
+          <t>VPP1 2004621ADM. FIDELIDAD -</t>
         </is>
       </c>
       <c r="E381" s="6" t="n">
-        <v>-67283120</v>
+        <v>-6426000</v>
       </c>
       <c r="F381" s="10" t="inlineStr">
         <is>
-          <t>DROGUE</t>
+          <t>FACT PROVEED</t>
         </is>
       </c>
       <c r="G381" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>CSB</t>
         </is>
       </c>
       <c r="H381" s="6" t="n">
-        <v>-67283120</v>
+        <v>-6426000</v>
       </c>
       <c r="I381" s="11" t="inlineStr">
         <is>
-          <t>DEC DSCTO  DTO POR ESCALA VOLU DROGUE</t>
+          <t>VPP1 2004621ADM. FIDELIDAD -</t>
         </is>
       </c>
     </row>
@@ -8436,28 +8436,28 @@
       </c>
       <c r="D382" s="10" t="inlineStr">
         <is>
-          <t>DTO POR ESCALA VOLU</t>
+          <t>VPP1 2004622ADM. FIDELIDAD -</t>
         </is>
       </c>
       <c r="E382" s="6" t="n">
-        <v>-838419</v>
+        <v>-41650000</v>
       </c>
       <c r="F382" s="10" t="inlineStr">
         <is>
-          <t>DROGUE</t>
+          <t>FACT PROVEED</t>
         </is>
       </c>
       <c r="G382" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>CSB</t>
         </is>
       </c>
       <c r="H382" s="6" t="n">
-        <v>-838419</v>
+        <v>-41650000</v>
       </c>
       <c r="I382" s="11" t="inlineStr">
         <is>
-          <t>DEC DSCTO 20251100199283 DTO POR ESCALA VOLU DROGUE</t>
+          <t>VPP1 2004622ADM. FIDELIDAD -</t>
         </is>
       </c>
     </row>
@@ -8469,11 +8469,11 @@
       </c>
       <c r="D383" s="10" t="inlineStr">
         <is>
-          <t>VPP1 2004529ADM. FIDELIDAD -</t>
+          <t>VPP2 2021716ADM.</t>
         </is>
       </c>
       <c r="E383" s="6" t="n">
-        <v>-57239000</v>
+        <v>-2507098292</v>
       </c>
       <c r="F383" s="10" t="inlineStr">
         <is>
@@ -8486,11 +8486,11 @@
         </is>
       </c>
       <c r="H383" s="6" t="n">
-        <v>-57239000</v>
+        <v>-2507098292</v>
       </c>
       <c r="I383" s="11" t="inlineStr">
         <is>
-          <t>VPP1 2004529ADM. FIDELIDAD -</t>
+          <t>VPP2 2021716ADM.</t>
         </is>
       </c>
     </row>
@@ -8502,11 +8502,11 @@
       </c>
       <c r="D384" s="10" t="inlineStr">
         <is>
-          <t>VPP1 2004621ADM. FIDELIDAD -</t>
+          <t>VPP2 2022342ADM.</t>
         </is>
       </c>
       <c r="E384" s="6" t="n">
-        <v>-6426000</v>
+        <v>-1075965191</v>
       </c>
       <c r="F384" s="10" t="inlineStr">
         <is>
@@ -8519,110 +8519,110 @@
         </is>
       </c>
       <c r="H384" s="6" t="n">
-        <v>-6426000</v>
+        <v>-1075965191</v>
       </c>
       <c r="I384" s="11" t="inlineStr">
         <is>
-          <t>VPP1 2004621ADM. FIDELIDAD -</t>
+          <t>VPP2 2022342ADM.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="C385" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Descuento Cliente</t>
         </is>
       </c>
       <c r="D385" s="10" t="inlineStr">
         <is>
-          <t>VPP1 2004622ADM. FIDELIDAD -</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="E385" s="6" t="n">
-        <v>-41650000</v>
+        <v>-37.26000004360685</v>
       </c>
       <c r="F385" s="10" t="inlineStr">
         <is>
-          <t>FACT PROVEED</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G385" s="10" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>CSR</t>
         </is>
       </c>
       <c r="H385" s="6" t="n">
-        <v>-41650000</v>
+        <v>-37.26000004360685</v>
       </c>
       <c r="I385" s="11" t="inlineStr">
         <is>
-          <t>VPP1 2004622ADM. FIDELIDAD -</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="C386" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Descuento Cliente</t>
         </is>
       </c>
       <c r="D386" s="10" t="inlineStr">
         <is>
-          <t>VPP2 2021716ADM.</t>
+          <t>PMP1286054</t>
         </is>
       </c>
       <c r="E386" s="6" t="n">
-        <v>-2507098292</v>
+        <v>-864163</v>
       </c>
       <c r="F386" s="10" t="inlineStr">
         <is>
-          <t>FACT PROVEED</t>
+          <t>Menor Vlr Pagado</t>
         </is>
       </c>
       <c r="G386" s="10" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>CSR</t>
         </is>
       </c>
       <c r="H386" s="6" t="n">
-        <v>-2507098292</v>
+        <v>-864163</v>
       </c>
       <c r="I386" s="11" t="inlineStr">
         <is>
-          <t>VPP2 2021716ADM.</t>
+          <t>Menor Vlr Pagado PMP1286054</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="C387" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Descuento Cliente</t>
         </is>
       </c>
       <c r="D387" s="10" t="inlineStr">
         <is>
-          <t>VPP2 2022342ADM.</t>
+          <t>PMP1286550</t>
         </is>
       </c>
       <c r="E387" s="6" t="n">
-        <v>-1075965191</v>
+        <v>-5910046.859999999</v>
       </c>
       <c r="F387" s="10" t="inlineStr">
         <is>
-          <t>FACT PROVEED</t>
+          <t>Menor Vlr Pagado</t>
         </is>
       </c>
       <c r="G387" s="10" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>CSR</t>
         </is>
       </c>
       <c r="H387" s="6" t="n">
-        <v>-1075965191</v>
+        <v>-5910046.859999999</v>
       </c>
       <c r="I387" s="11" t="inlineStr">
         <is>
-          <t>VPP2 2022342ADM.</t>
+          <t>Menor Vlr Pagado PMP1286550</t>
         </is>
       </c>
     </row>
@@ -8634,127 +8634,127 @@
       </c>
       <c r="D388" s="10" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
+          <t>PMP1286553</t>
         </is>
       </c>
       <c r="E388" s="6" t="n">
-        <v>-37.26000004360685</v>
+        <v>5910047.02</v>
       </c>
       <c r="F388" s="10" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
+          <t>Myr Vlr Pagado</t>
         </is>
       </c>
       <c r="G388" s="10" t="inlineStr">
         <is>
-          <t>CSR</t>
+          <t>388</t>
         </is>
       </c>
       <c r="H388" s="6" t="n">
-        <v>-37.26000004360685</v>
+        <v>5910047.02</v>
       </c>
       <c r="I388" s="11" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
+          <t>Myr Vlr Pagado PMP1286553</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="C389" s="10" t="inlineStr">
         <is>
-          <t>Descuento Cliente</t>
+          <t>Descuentos Clientes</t>
         </is>
       </c>
       <c r="D389" s="10" t="inlineStr">
         <is>
-          <t>PMP1286054</t>
+          <t>DESCUENTO APERTURA</t>
         </is>
       </c>
       <c r="E389" s="6" t="n">
-        <v>-864163</v>
+        <v>-14258141</v>
       </c>
       <c r="F389" s="10" t="inlineStr">
         <is>
-          <t>Menor Vlr Pagado</t>
+          <t>PERFUME</t>
         </is>
       </c>
       <c r="G389" s="10" t="inlineStr">
         <is>
-          <t>CSR</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H389" s="6" t="n">
-        <v>-864163</v>
+        <v>-14258141</v>
       </c>
       <c r="I389" s="11" t="inlineStr">
         <is>
-          <t>Menor Vlr Pagado PMP1286054</t>
+          <t>DAV DSCTO  DESCUENTO APERTURA PERFUME</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="C390" s="10" t="inlineStr">
         <is>
-          <t>Descuento Cliente</t>
+          <t>Descuentos Clientes</t>
         </is>
       </c>
       <c r="D390" s="10" t="inlineStr">
         <is>
-          <t>PMP1286550</t>
+          <t>DESCUENTO CALENDARI</t>
         </is>
       </c>
       <c r="E390" s="6" t="n">
-        <v>-5910046.859999999</v>
+        <v>-1758901158</v>
       </c>
       <c r="F390" s="10" t="inlineStr">
         <is>
-          <t>Menor Vlr Pagado</t>
+          <t>PERFUME</t>
         </is>
       </c>
       <c r="G390" s="10" t="inlineStr">
         <is>
-          <t>CSR</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H390" s="6" t="n">
-        <v>-5910046.859999999</v>
+        <v>-1758901158</v>
       </c>
       <c r="I390" s="11" t="inlineStr">
         <is>
-          <t>Menor Vlr Pagado PMP1286550</t>
+          <t>DCA DSCTO  DESCUENTO CALENDARI PERFUME</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="C391" s="10" t="inlineStr">
         <is>
-          <t>Descuento Cliente</t>
+          <t>Descuentos Clientes</t>
         </is>
       </c>
       <c r="D391" s="10" t="inlineStr">
         <is>
-          <t>PMP1286553</t>
+          <t>DEVOLUCIONES</t>
         </is>
       </c>
       <c r="E391" s="6" t="n">
-        <v>5910047.02</v>
+        <v>-2074733</v>
       </c>
       <c r="F391" s="10" t="inlineStr">
         <is>
-          <t>Myr Vlr Pagado</t>
+          <t>PERFUME</t>
         </is>
       </c>
       <c r="G391" s="10" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H391" s="6" t="n">
-        <v>5910047.02</v>
+        <v>-2074733</v>
       </c>
       <c r="I391" s="11" t="inlineStr">
         <is>
-          <t>Myr Vlr Pagado PMP1286553</t>
+          <t>DND DSCTO  DEVOLUCIONES PERFUME</t>
         </is>
       </c>
     </row>
@@ -8766,11 +8766,11 @@
       </c>
       <c r="D392" s="10" t="inlineStr">
         <is>
-          <t>DTO POR ESCALA VOLU</t>
+          <t>DSTO COMERCIAL FIJO</t>
         </is>
       </c>
       <c r="E392" s="6" t="n">
-        <v>-163558737</v>
+        <v>-76656631</v>
       </c>
       <c r="F392" s="10" t="inlineStr">
         <is>
@@ -8783,11 +8783,11 @@
         </is>
       </c>
       <c r="H392" s="6" t="n">
-        <v>-163558737</v>
+        <v>-76656631</v>
       </c>
       <c r="I392" s="11" t="inlineStr">
         <is>
-          <t>DEC DSCTO  DTO POR ESCALA VOLU PERFUME</t>
+          <t>DCF DSCTO  DSTO COMERCIAL FIJO PERFUME</t>
         </is>
       </c>
     </row>
@@ -8803,7 +8803,7 @@
         </is>
       </c>
       <c r="E393" s="6" t="n">
-        <v>-896070</v>
+        <v>-163582176</v>
       </c>
       <c r="F393" s="10" t="inlineStr">
         <is>
@@ -8816,11 +8816,11 @@
         </is>
       </c>
       <c r="H393" s="6" t="n">
-        <v>-896070</v>
+        <v>-163582176</v>
       </c>
       <c r="I393" s="11" t="inlineStr">
         <is>
-          <t>DEC DSCTO 20251200199299 DTO POR ESCALA VOLU PERFUME</t>
+          <t>DEC DSCTO  DTO POR ESCALA VOLU PERFUME</t>
         </is>
       </c>
     </row>
@@ -8836,7 +8836,7 @@
         </is>
       </c>
       <c r="E394" s="6" t="n">
-        <v>-762913</v>
+        <v>-896070</v>
       </c>
       <c r="F394" s="10" t="inlineStr">
         <is>
@@ -8849,11 +8849,11 @@
         </is>
       </c>
       <c r="H394" s="6" t="n">
-        <v>-762913</v>
+        <v>-896070</v>
       </c>
       <c r="I394" s="11" t="inlineStr">
         <is>
-          <t>DEC DSCTO 20251200199300 DTO POR ESCALA VOLU PERFUME</t>
+          <t>DEC DSCTO 20251200199299 DTO POR ESCALA VOLU PERFUME</t>
         </is>
       </c>
     </row>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="E395" s="6" t="n">
-        <v>-44705</v>
+        <v>-762913</v>
       </c>
       <c r="F395" s="10" t="inlineStr">
         <is>
@@ -8882,11 +8882,11 @@
         </is>
       </c>
       <c r="H395" s="6" t="n">
-        <v>-44705</v>
+        <v>-762913</v>
       </c>
       <c r="I395" s="11" t="inlineStr">
         <is>
-          <t>DEC DSCTO 20251200199301 DTO POR ESCALA VOLU PERFUME</t>
+          <t>DEC DSCTO 20251200199300 DTO POR ESCALA VOLU PERFUME</t>
         </is>
       </c>
     </row>
@@ -8902,7 +8902,7 @@
         </is>
       </c>
       <c r="E396" s="6" t="n">
-        <v>-260000</v>
+        <v>-44705</v>
       </c>
       <c r="F396" s="10" t="inlineStr">
         <is>
@@ -8915,11 +8915,11 @@
         </is>
       </c>
       <c r="H396" s="6" t="n">
-        <v>-260000</v>
+        <v>-44705</v>
       </c>
       <c r="I396" s="11" t="inlineStr">
         <is>
-          <t>DEC DSCTO 20251200200041 DTO POR ESCALA VOLU PERFUME</t>
+          <t>DEC DSCTO 20251200199301 DTO POR ESCALA VOLU PERFUME</t>
         </is>
       </c>
     </row>
@@ -8931,28 +8931,28 @@
       </c>
       <c r="D397" s="10" t="inlineStr">
         <is>
-          <t>PMP1282099</t>
+          <t>DTO POR ESCALA VOLU</t>
         </is>
       </c>
       <c r="E397" s="6" t="n">
-        <v>-307519</v>
+        <v>-260000</v>
       </c>
       <c r="F397" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PERFUME</t>
         </is>
       </c>
       <c r="G397" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H397" s="6" t="n">
-        <v>-307519</v>
+        <v>-260000</v>
       </c>
       <c r="I397" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1282099</t>
+          <t>DEC DSCTO 20251200200041 DTO POR ESCALA VOLU PERFUME</t>
         </is>
       </c>
     </row>
@@ -8964,28 +8964,28 @@
       </c>
       <c r="D398" s="10" t="inlineStr">
         <is>
-          <t>PMP1282353</t>
+          <t>DESCUENTO CALENDARI</t>
         </is>
       </c>
       <c r="E398" s="6" t="n">
-        <v>-2659670</v>
+        <v>-13427534</v>
       </c>
       <c r="F398" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PLATOS</t>
         </is>
       </c>
       <c r="G398" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H398" s="6" t="n">
-        <v>-2659670</v>
+        <v>-13427534</v>
       </c>
       <c r="I398" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1282353</t>
+          <t>DCA DSCTO  DESCUENTO CALENDARI PLATOS</t>
         </is>
       </c>
     </row>
@@ -8997,28 +8997,28 @@
       </c>
       <c r="D399" s="10" t="inlineStr">
         <is>
-          <t>PMP1282964</t>
+          <t>DESCUENTO COMPRAS</t>
         </is>
       </c>
       <c r="E399" s="6" t="n">
-        <v>-185365</v>
+        <v>-1394767</v>
       </c>
       <c r="F399" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PLATOS</t>
         </is>
       </c>
       <c r="G399" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H399" s="6" t="n">
-        <v>-185365</v>
+        <v>-1394767</v>
       </c>
       <c r="I399" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1282964</t>
+          <t>DCC DSCTO  DESCUENTO COMPRAS PLATOS</t>
         </is>
       </c>
     </row>
@@ -9030,28 +9030,28 @@
       </c>
       <c r="D400" s="10" t="inlineStr">
         <is>
-          <t>PMP1283008</t>
+          <t>DSTO COMERCIAL FIJO</t>
         </is>
       </c>
       <c r="E400" s="6" t="n">
-        <v>-9788</v>
+        <v>-20921503</v>
       </c>
       <c r="F400" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PLATOS</t>
         </is>
       </c>
       <c r="G400" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H400" s="6" t="n">
-        <v>-9788</v>
+        <v>-20921503</v>
       </c>
       <c r="I400" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1283008</t>
+          <t>DCF DSCTO  DSTO COMERCIAL FIJO PLATOS</t>
         </is>
       </c>
     </row>
@@ -9063,28 +9063,28 @@
       </c>
       <c r="D401" s="10" t="inlineStr">
         <is>
-          <t>PMP1283012</t>
+          <t>DESCUENTO</t>
         </is>
       </c>
       <c r="E401" s="6" t="n">
-        <v>-167913</v>
+        <v>-61299192</v>
       </c>
       <c r="F401" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>RANCHO</t>
         </is>
       </c>
       <c r="G401" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H401" s="6" t="n">
-        <v>-167913</v>
+        <v>-61299192</v>
       </c>
       <c r="I401" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1283012</t>
+          <t>RPL DSCTO  DESCUENTO RANCHO</t>
         </is>
       </c>
     </row>
@@ -9096,28 +9096,28 @@
       </c>
       <c r="D402" s="10" t="inlineStr">
         <is>
-          <t>PMP1283476</t>
+          <t>DESCUENTO CALENDARI</t>
         </is>
       </c>
       <c r="E402" s="6" t="n">
-        <v>-836339</v>
+        <v>-29638456</v>
       </c>
       <c r="F402" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>RANCHO</t>
         </is>
       </c>
       <c r="G402" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H402" s="6" t="n">
-        <v>-836339</v>
+        <v>-29638456</v>
       </c>
       <c r="I402" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1283476</t>
+          <t>DCA DSCTO  DESCUENTO CALENDARI RANCHO</t>
         </is>
       </c>
     </row>
@@ -9129,28 +9129,28 @@
       </c>
       <c r="D403" s="10" t="inlineStr">
         <is>
-          <t>PMP1283500</t>
+          <t>DESCUENTO EN PRIMER</t>
         </is>
       </c>
       <c r="E403" s="6" t="n">
-        <v>-473742856</v>
+        <v>-10216531</v>
       </c>
       <c r="F403" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>RANCHO</t>
         </is>
       </c>
       <c r="G403" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H403" s="6" t="n">
-        <v>-473742856</v>
+        <v>-10216531</v>
       </c>
       <c r="I403" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1283500</t>
+          <t>DPC DSCTO  DESCUENTO EN PRIMER RANCHO</t>
         </is>
       </c>
     </row>
@@ -9162,11 +9162,11 @@
       </c>
       <c r="D404" s="10" t="inlineStr">
         <is>
-          <t>PMP1283784</t>
+          <t>PMP1282099</t>
         </is>
       </c>
       <c r="E404" s="6" t="n">
-        <v>-629893</v>
+        <v>-307519</v>
       </c>
       <c r="F404" s="10" t="inlineStr">
         <is>
@@ -9179,11 +9179,11 @@
         </is>
       </c>
       <c r="H404" s="6" t="n">
-        <v>-629893</v>
+        <v>-307519</v>
       </c>
       <c r="I404" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1283784</t>
+          <t>Rechazo PMP1282099</t>
         </is>
       </c>
     </row>
@@ -9195,11 +9195,11 @@
       </c>
       <c r="D405" s="10" t="inlineStr">
         <is>
-          <t>PMP1283785</t>
+          <t>PMP1282353</t>
         </is>
       </c>
       <c r="E405" s="6" t="n">
-        <v>-160273</v>
+        <v>-2659670</v>
       </c>
       <c r="F405" s="10" t="inlineStr">
         <is>
@@ -9212,11 +9212,11 @@
         </is>
       </c>
       <c r="H405" s="6" t="n">
-        <v>-160273</v>
+        <v>-2659670</v>
       </c>
       <c r="I405" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1283785</t>
+          <t>Rechazo PMP1282353</t>
         </is>
       </c>
     </row>
@@ -9228,11 +9228,11 @@
       </c>
       <c r="D406" s="10" t="inlineStr">
         <is>
-          <t>PMP1284114</t>
+          <t>PMP1282964</t>
         </is>
       </c>
       <c r="E406" s="6" t="n">
-        <v>-764103</v>
+        <v>-185365</v>
       </c>
       <c r="F406" s="10" t="inlineStr">
         <is>
@@ -9245,11 +9245,11 @@
         </is>
       </c>
       <c r="H406" s="6" t="n">
-        <v>-764103</v>
+        <v>-185365</v>
       </c>
       <c r="I406" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284114</t>
+          <t>Rechazo PMP1282964</t>
         </is>
       </c>
     </row>
@@ -9261,11 +9261,11 @@
       </c>
       <c r="D407" s="10" t="inlineStr">
         <is>
-          <t>PMP1284117</t>
+          <t>PMP1283008</t>
         </is>
       </c>
       <c r="E407" s="6" t="n">
-        <v>-177051</v>
+        <v>-9788</v>
       </c>
       <c r="F407" s="10" t="inlineStr">
         <is>
@@ -9278,11 +9278,11 @@
         </is>
       </c>
       <c r="H407" s="6" t="n">
-        <v>-177051</v>
+        <v>-9788</v>
       </c>
       <c r="I407" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284117</t>
+          <t>Rechazo PMP1283008</t>
         </is>
       </c>
     </row>
@@ -9294,11 +9294,11 @@
       </c>
       <c r="D408" s="10" t="inlineStr">
         <is>
-          <t>PMP1284119</t>
+          <t>PMP1283012</t>
         </is>
       </c>
       <c r="E408" s="6" t="n">
-        <v>-644997</v>
+        <v>-167913</v>
       </c>
       <c r="F408" s="10" t="inlineStr">
         <is>
@@ -9311,11 +9311,11 @@
         </is>
       </c>
       <c r="H408" s="6" t="n">
-        <v>-644997</v>
+        <v>-167913</v>
       </c>
       <c r="I408" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284119</t>
+          <t>Rechazo PMP1283012</t>
         </is>
       </c>
     </row>
@@ -9327,11 +9327,11 @@
       </c>
       <c r="D409" s="10" t="inlineStr">
         <is>
-          <t>PMP1284200</t>
+          <t>PMP1283476</t>
         </is>
       </c>
       <c r="E409" s="6" t="n">
-        <v>-175153</v>
+        <v>-836339</v>
       </c>
       <c r="F409" s="10" t="inlineStr">
         <is>
@@ -9344,11 +9344,11 @@
         </is>
       </c>
       <c r="H409" s="6" t="n">
-        <v>-175153</v>
+        <v>-836339</v>
       </c>
       <c r="I409" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284200</t>
+          <t>Rechazo PMP1283476</t>
         </is>
       </c>
     </row>
@@ -9360,11 +9360,11 @@
       </c>
       <c r="D410" s="10" t="inlineStr">
         <is>
-          <t>PMP1284460</t>
+          <t>PMP1283500</t>
         </is>
       </c>
       <c r="E410" s="6" t="n">
-        <v>-167879</v>
+        <v>-473742856</v>
       </c>
       <c r="F410" s="10" t="inlineStr">
         <is>
@@ -9377,11 +9377,11 @@
         </is>
       </c>
       <c r="H410" s="6" t="n">
-        <v>-167879</v>
+        <v>-473742856</v>
       </c>
       <c r="I410" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284460</t>
+          <t>Rechazo PMP1283500</t>
         </is>
       </c>
     </row>
@@ -9393,11 +9393,11 @@
       </c>
       <c r="D411" s="10" t="inlineStr">
         <is>
-          <t>PMP1284462</t>
+          <t>PMP1283784</t>
         </is>
       </c>
       <c r="E411" s="6" t="n">
-        <v>-322931</v>
+        <v>-629893</v>
       </c>
       <c r="F411" s="10" t="inlineStr">
         <is>
@@ -9410,11 +9410,11 @@
         </is>
       </c>
       <c r="H411" s="6" t="n">
-        <v>-322931</v>
+        <v>-629893</v>
       </c>
       <c r="I411" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284462</t>
+          <t>Rechazo PMP1283784</t>
         </is>
       </c>
     </row>
@@ -9426,11 +9426,11 @@
       </c>
       <c r="D412" s="10" t="inlineStr">
         <is>
-          <t>PMP1284529</t>
+          <t>PMP1283785</t>
         </is>
       </c>
       <c r="E412" s="6" t="n">
-        <v>-276742</v>
+        <v>-160273</v>
       </c>
       <c r="F412" s="10" t="inlineStr">
         <is>
@@ -9443,11 +9443,11 @@
         </is>
       </c>
       <c r="H412" s="6" t="n">
-        <v>-276742</v>
+        <v>-160273</v>
       </c>
       <c r="I412" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284529</t>
+          <t>Rechazo PMP1283785</t>
         </is>
       </c>
     </row>
@@ -9459,11 +9459,11 @@
       </c>
       <c r="D413" s="10" t="inlineStr">
         <is>
-          <t>PMP1284543</t>
+          <t>PMP1284114</t>
         </is>
       </c>
       <c r="E413" s="6" t="n">
-        <v>-3015665</v>
+        <v>-764103</v>
       </c>
       <c r="F413" s="10" t="inlineStr">
         <is>
@@ -9476,11 +9476,11 @@
         </is>
       </c>
       <c r="H413" s="6" t="n">
-        <v>-3015665</v>
+        <v>-764103</v>
       </c>
       <c r="I413" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284543</t>
+          <t>Rechazo PMP1284114</t>
         </is>
       </c>
     </row>
@@ -9492,11 +9492,11 @@
       </c>
       <c r="D414" s="10" t="inlineStr">
         <is>
-          <t>PMP1284546</t>
+          <t>PMP1284117</t>
         </is>
       </c>
       <c r="E414" s="6" t="n">
-        <v>-135409</v>
+        <v>-177051</v>
       </c>
       <c r="F414" s="10" t="inlineStr">
         <is>
@@ -9509,11 +9509,11 @@
         </is>
       </c>
       <c r="H414" s="6" t="n">
-        <v>-135409</v>
+        <v>-177051</v>
       </c>
       <c r="I414" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284546</t>
+          <t>Rechazo PMP1284117</t>
         </is>
       </c>
     </row>
@@ -9525,11 +9525,11 @@
       </c>
       <c r="D415" s="10" t="inlineStr">
         <is>
-          <t>PMP1284602</t>
+          <t>PMP1284119</t>
         </is>
       </c>
       <c r="E415" s="6" t="n">
-        <v>-930108</v>
+        <v>-644997</v>
       </c>
       <c r="F415" s="10" t="inlineStr">
         <is>
@@ -9542,11 +9542,11 @@
         </is>
       </c>
       <c r="H415" s="6" t="n">
-        <v>-930108</v>
+        <v>-644997</v>
       </c>
       <c r="I415" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284602</t>
+          <t>Rechazo PMP1284119</t>
         </is>
       </c>
     </row>
@@ -9558,11 +9558,11 @@
       </c>
       <c r="D416" s="10" t="inlineStr">
         <is>
-          <t>PMP1284750</t>
+          <t>PMP1284200</t>
         </is>
       </c>
       <c r="E416" s="6" t="n">
-        <v>-405708</v>
+        <v>-175153</v>
       </c>
       <c r="F416" s="10" t="inlineStr">
         <is>
@@ -9575,11 +9575,11 @@
         </is>
       </c>
       <c r="H416" s="6" t="n">
-        <v>-405708</v>
+        <v>-175153</v>
       </c>
       <c r="I416" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284750</t>
+          <t>Rechazo PMP1284200</t>
         </is>
       </c>
     </row>
@@ -9591,11 +9591,11 @@
       </c>
       <c r="D417" s="10" t="inlineStr">
         <is>
-          <t>PMP1284800</t>
+          <t>PMP1284460</t>
         </is>
       </c>
       <c r="E417" s="6" t="n">
-        <v>-635980</v>
+        <v>-167879</v>
       </c>
       <c r="F417" s="10" t="inlineStr">
         <is>
@@ -9608,11 +9608,11 @@
         </is>
       </c>
       <c r="H417" s="6" t="n">
-        <v>-635980</v>
+        <v>-167879</v>
       </c>
       <c r="I417" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284800</t>
+          <t>Rechazo PMP1284460</t>
         </is>
       </c>
     </row>
@@ -9624,11 +9624,11 @@
       </c>
       <c r="D418" s="10" t="inlineStr">
         <is>
-          <t>PMP1284876</t>
+          <t>PMP1284462</t>
         </is>
       </c>
       <c r="E418" s="6" t="n">
-        <v>-689804</v>
+        <v>-322931</v>
       </c>
       <c r="F418" s="10" t="inlineStr">
         <is>
@@ -9641,11 +9641,11 @@
         </is>
       </c>
       <c r="H418" s="6" t="n">
-        <v>-689804</v>
+        <v>-322931</v>
       </c>
       <c r="I418" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284876</t>
+          <t>Rechazo PMP1284462</t>
         </is>
       </c>
     </row>
@@ -9657,11 +9657,11 @@
       </c>
       <c r="D419" s="10" t="inlineStr">
         <is>
-          <t>PMP1284878</t>
+          <t>PMP1284529</t>
         </is>
       </c>
       <c r="E419" s="6" t="n">
-        <v>-135533</v>
+        <v>-276742</v>
       </c>
       <c r="F419" s="10" t="inlineStr">
         <is>
@@ -9674,11 +9674,11 @@
         </is>
       </c>
       <c r="H419" s="6" t="n">
-        <v>-135533</v>
+        <v>-276742</v>
       </c>
       <c r="I419" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284878</t>
+          <t>Rechazo PMP1284529</t>
         </is>
       </c>
     </row>
@@ -9690,11 +9690,11 @@
       </c>
       <c r="D420" s="10" t="inlineStr">
         <is>
-          <t>PMP1284879</t>
+          <t>PMP1284543</t>
         </is>
       </c>
       <c r="E420" s="6" t="n">
-        <v>-732728</v>
+        <v>-3015665</v>
       </c>
       <c r="F420" s="10" t="inlineStr">
         <is>
@@ -9707,11 +9707,11 @@
         </is>
       </c>
       <c r="H420" s="6" t="n">
-        <v>-732728</v>
+        <v>-3015665</v>
       </c>
       <c r="I420" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284879</t>
+          <t>Rechazo PMP1284543</t>
         </is>
       </c>
     </row>
@@ -9723,11 +9723,11 @@
       </c>
       <c r="D421" s="10" t="inlineStr">
         <is>
-          <t>PMP1284948</t>
+          <t>PMP1284546</t>
         </is>
       </c>
       <c r="E421" s="6" t="n">
-        <v>-1060968</v>
+        <v>-135409</v>
       </c>
       <c r="F421" s="10" t="inlineStr">
         <is>
@@ -9740,11 +9740,11 @@
         </is>
       </c>
       <c r="H421" s="6" t="n">
-        <v>-1060968</v>
+        <v>-135409</v>
       </c>
       <c r="I421" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284948</t>
+          <t>Rechazo PMP1284546</t>
         </is>
       </c>
     </row>
@@ -9756,11 +9756,11 @@
       </c>
       <c r="D422" s="10" t="inlineStr">
         <is>
-          <t>PMP1284949</t>
+          <t>PMP1284602</t>
         </is>
       </c>
       <c r="E422" s="6" t="n">
-        <v>-215248</v>
+        <v>-930108</v>
       </c>
       <c r="F422" s="10" t="inlineStr">
         <is>
@@ -9773,11 +9773,11 @@
         </is>
       </c>
       <c r="H422" s="6" t="n">
-        <v>-215248</v>
+        <v>-930108</v>
       </c>
       <c r="I422" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284949</t>
+          <t>Rechazo PMP1284602</t>
         </is>
       </c>
     </row>
@@ -9789,11 +9789,11 @@
       </c>
       <c r="D423" s="10" t="inlineStr">
         <is>
-          <t>PMP1284950</t>
+          <t>PMP1284750</t>
         </is>
       </c>
       <c r="E423" s="6" t="n">
-        <v>-1297475</v>
+        <v>-405708</v>
       </c>
       <c r="F423" s="10" t="inlineStr">
         <is>
@@ -9806,11 +9806,11 @@
         </is>
       </c>
       <c r="H423" s="6" t="n">
-        <v>-1297475</v>
+        <v>-405708</v>
       </c>
       <c r="I423" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284950</t>
+          <t>Rechazo PMP1284750</t>
         </is>
       </c>
     </row>
@@ -9822,11 +9822,11 @@
       </c>
       <c r="D424" s="10" t="inlineStr">
         <is>
-          <t>PMP1284951</t>
+          <t>PMP1284800</t>
         </is>
       </c>
       <c r="E424" s="6" t="n">
-        <v>-5702098</v>
+        <v>-635980</v>
       </c>
       <c r="F424" s="10" t="inlineStr">
         <is>
@@ -9839,11 +9839,11 @@
         </is>
       </c>
       <c r="H424" s="6" t="n">
-        <v>-5702098</v>
+        <v>-635980</v>
       </c>
       <c r="I424" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284951</t>
+          <t>Rechazo PMP1284800</t>
         </is>
       </c>
     </row>
@@ -9855,11 +9855,11 @@
       </c>
       <c r="D425" s="10" t="inlineStr">
         <is>
-          <t>PMP1285048</t>
+          <t>PMP1284876</t>
         </is>
       </c>
       <c r="E425" s="6" t="n">
-        <v>-221603</v>
+        <v>-689804</v>
       </c>
       <c r="F425" s="10" t="inlineStr">
         <is>
@@ -9872,11 +9872,11 @@
         </is>
       </c>
       <c r="H425" s="6" t="n">
-        <v>-221603</v>
+        <v>-689804</v>
       </c>
       <c r="I425" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285048</t>
+          <t>Rechazo PMP1284876</t>
         </is>
       </c>
     </row>
@@ -9888,11 +9888,11 @@
       </c>
       <c r="D426" s="10" t="inlineStr">
         <is>
-          <t>PMP1285059</t>
+          <t>PMP1284878</t>
         </is>
       </c>
       <c r="E426" s="6" t="n">
-        <v>-160294</v>
+        <v>-135533</v>
       </c>
       <c r="F426" s="10" t="inlineStr">
         <is>
@@ -9905,11 +9905,11 @@
         </is>
       </c>
       <c r="H426" s="6" t="n">
-        <v>-160294</v>
+        <v>-135533</v>
       </c>
       <c r="I426" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285059</t>
+          <t>Rechazo PMP1284878</t>
         </is>
       </c>
     </row>
@@ -9921,11 +9921,11 @@
       </c>
       <c r="D427" s="10" t="inlineStr">
         <is>
-          <t>PMP1285065</t>
+          <t>PMP1284879</t>
         </is>
       </c>
       <c r="E427" s="6" t="n">
-        <v>-107552</v>
+        <v>-732728</v>
       </c>
       <c r="F427" s="10" t="inlineStr">
         <is>
@@ -9938,11 +9938,11 @@
         </is>
       </c>
       <c r="H427" s="6" t="n">
-        <v>-107552</v>
+        <v>-732728</v>
       </c>
       <c r="I427" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285065</t>
+          <t>Rechazo PMP1284879</t>
         </is>
       </c>
     </row>
@@ -9954,11 +9954,11 @@
       </c>
       <c r="D428" s="10" t="inlineStr">
         <is>
-          <t>PMP1285067</t>
+          <t>PMP1284948</t>
         </is>
       </c>
       <c r="E428" s="6" t="n">
-        <v>-135307</v>
+        <v>-1060968</v>
       </c>
       <c r="F428" s="10" t="inlineStr">
         <is>
@@ -9971,11 +9971,11 @@
         </is>
       </c>
       <c r="H428" s="6" t="n">
-        <v>-135307</v>
+        <v>-1060968</v>
       </c>
       <c r="I428" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285067</t>
+          <t>Rechazo PMP1284948</t>
         </is>
       </c>
     </row>
@@ -9987,11 +9987,11 @@
       </c>
       <c r="D429" s="10" t="inlineStr">
         <is>
-          <t>PMP1285071</t>
+          <t>PMP1284949</t>
         </is>
       </c>
       <c r="E429" s="6" t="n">
-        <v>-419436</v>
+        <v>-215248</v>
       </c>
       <c r="F429" s="10" t="inlineStr">
         <is>
@@ -10004,11 +10004,11 @@
         </is>
       </c>
       <c r="H429" s="6" t="n">
-        <v>-419436</v>
+        <v>-215248</v>
       </c>
       <c r="I429" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285071</t>
+          <t>Rechazo PMP1284949</t>
         </is>
       </c>
     </row>
@@ -10020,11 +10020,11 @@
       </c>
       <c r="D430" s="10" t="inlineStr">
         <is>
-          <t>PMP1285653</t>
+          <t>PMP1284950</t>
         </is>
       </c>
       <c r="E430" s="6" t="n">
-        <v>-558246</v>
+        <v>-1297475</v>
       </c>
       <c r="F430" s="10" t="inlineStr">
         <is>
@@ -10037,11 +10037,11 @@
         </is>
       </c>
       <c r="H430" s="6" t="n">
-        <v>-558246</v>
+        <v>-1297475</v>
       </c>
       <c r="I430" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285653</t>
+          <t>Rechazo PMP1284950</t>
         </is>
       </c>
     </row>
@@ -10053,11 +10053,11 @@
       </c>
       <c r="D431" s="10" t="inlineStr">
         <is>
-          <t>PMP1285659</t>
+          <t>PMP1284951</t>
         </is>
       </c>
       <c r="E431" s="6" t="n">
-        <v>-311765</v>
+        <v>-5702098</v>
       </c>
       <c r="F431" s="10" t="inlineStr">
         <is>
@@ -10070,11 +10070,11 @@
         </is>
       </c>
       <c r="H431" s="6" t="n">
-        <v>-311765</v>
+        <v>-5702098</v>
       </c>
       <c r="I431" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285659</t>
+          <t>Rechazo PMP1284951</t>
         </is>
       </c>
     </row>
@@ -10086,11 +10086,11 @@
       </c>
       <c r="D432" s="10" t="inlineStr">
         <is>
-          <t>PMP1285725</t>
+          <t>PMP1285048</t>
         </is>
       </c>
       <c r="E432" s="6" t="n">
-        <v>-679290</v>
+        <v>-221603</v>
       </c>
       <c r="F432" s="10" t="inlineStr">
         <is>
@@ -10103,11 +10103,11 @@
         </is>
       </c>
       <c r="H432" s="6" t="n">
-        <v>-679290</v>
+        <v>-221603</v>
       </c>
       <c r="I432" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285725</t>
+          <t>Rechazo PMP1285048</t>
         </is>
       </c>
     </row>
@@ -10119,11 +10119,11 @@
       </c>
       <c r="D433" s="10" t="inlineStr">
         <is>
-          <t>PMP1285898</t>
+          <t>PMP1285059</t>
         </is>
       </c>
       <c r="E433" s="6" t="n">
-        <v>-253685</v>
+        <v>-160294</v>
       </c>
       <c r="F433" s="10" t="inlineStr">
         <is>
@@ -10136,11 +10136,11 @@
         </is>
       </c>
       <c r="H433" s="6" t="n">
-        <v>-253685</v>
+        <v>-160294</v>
       </c>
       <c r="I433" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285898</t>
+          <t>Rechazo PMP1285059</t>
         </is>
       </c>
     </row>
@@ -10152,11 +10152,11 @@
       </c>
       <c r="D434" s="10" t="inlineStr">
         <is>
-          <t>PMP1285903</t>
+          <t>PMP1285065</t>
         </is>
       </c>
       <c r="E434" s="6" t="n">
-        <v>-322554</v>
+        <v>-107552</v>
       </c>
       <c r="F434" s="10" t="inlineStr">
         <is>
@@ -10169,11 +10169,11 @@
         </is>
       </c>
       <c r="H434" s="6" t="n">
-        <v>-322554</v>
+        <v>-107552</v>
       </c>
       <c r="I434" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285903</t>
+          <t>Rechazo PMP1285065</t>
         </is>
       </c>
     </row>
@@ -10185,11 +10185,11 @@
       </c>
       <c r="D435" s="10" t="inlineStr">
         <is>
-          <t>PMP1285908</t>
+          <t>PMP1285067</t>
         </is>
       </c>
       <c r="E435" s="6" t="n">
-        <v>-135255</v>
+        <v>-135307</v>
       </c>
       <c r="F435" s="10" t="inlineStr">
         <is>
@@ -10202,11 +10202,11 @@
         </is>
       </c>
       <c r="H435" s="6" t="n">
-        <v>-135255</v>
+        <v>-135307</v>
       </c>
       <c r="I435" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285908</t>
+          <t>Rechazo PMP1285067</t>
         </is>
       </c>
     </row>
@@ -10218,11 +10218,11 @@
       </c>
       <c r="D436" s="10" t="inlineStr">
         <is>
-          <t>PMP1286056</t>
+          <t>PMP1285071</t>
         </is>
       </c>
       <c r="E436" s="6" t="n">
-        <v>-556413</v>
+        <v>-419436</v>
       </c>
       <c r="F436" s="10" t="inlineStr">
         <is>
@@ -10235,11 +10235,11 @@
         </is>
       </c>
       <c r="H436" s="6" t="n">
-        <v>-556413</v>
+        <v>-419436</v>
       </c>
       <c r="I436" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286056</t>
+          <t>Rechazo PMP1285071</t>
         </is>
       </c>
     </row>
@@ -10251,11 +10251,11 @@
       </c>
       <c r="D437" s="10" t="inlineStr">
         <is>
-          <t>PMP1286208</t>
+          <t>PMP1285653</t>
         </is>
       </c>
       <c r="E437" s="6" t="n">
-        <v>-949123</v>
+        <v>-558246</v>
       </c>
       <c r="F437" s="10" t="inlineStr">
         <is>
@@ -10268,11 +10268,11 @@
         </is>
       </c>
       <c r="H437" s="6" t="n">
-        <v>-949123</v>
+        <v>-558246</v>
       </c>
       <c r="I437" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286208</t>
+          <t>Rechazo PMP1285653</t>
         </is>
       </c>
     </row>
@@ -10284,11 +10284,11 @@
       </c>
       <c r="D438" s="10" t="inlineStr">
         <is>
-          <t>PMP1286554</t>
+          <t>PMP1285659</t>
         </is>
       </c>
       <c r="E438" s="6" t="n">
-        <v>-354934</v>
+        <v>-311765</v>
       </c>
       <c r="F438" s="10" t="inlineStr">
         <is>
@@ -10301,11 +10301,11 @@
         </is>
       </c>
       <c r="H438" s="6" t="n">
-        <v>-354934</v>
+        <v>-311765</v>
       </c>
       <c r="I438" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286554</t>
+          <t>Rechazo PMP1285659</t>
         </is>
       </c>
     </row>
@@ -10317,11 +10317,11 @@
       </c>
       <c r="D439" s="10" t="inlineStr">
         <is>
-          <t>PMP1286556</t>
+          <t>PMP1285725</t>
         </is>
       </c>
       <c r="E439" s="6" t="n">
-        <v>-364001</v>
+        <v>-679290</v>
       </c>
       <c r="F439" s="10" t="inlineStr">
         <is>
@@ -10334,11 +10334,11 @@
         </is>
       </c>
       <c r="H439" s="6" t="n">
-        <v>-364001</v>
+        <v>-679290</v>
       </c>
       <c r="I439" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286556</t>
+          <t>Rechazo PMP1285725</t>
         </is>
       </c>
     </row>
@@ -10350,11 +10350,11 @@
       </c>
       <c r="D440" s="10" t="inlineStr">
         <is>
-          <t>PMP1286709</t>
+          <t>PMP1285898</t>
         </is>
       </c>
       <c r="E440" s="6" t="n">
-        <v>-33537478</v>
+        <v>-253685</v>
       </c>
       <c r="F440" s="10" t="inlineStr">
         <is>
@@ -10367,11 +10367,11 @@
         </is>
       </c>
       <c r="H440" s="6" t="n">
-        <v>-33537478</v>
+        <v>-253685</v>
       </c>
       <c r="I440" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286709</t>
+          <t>Rechazo PMP1285898</t>
         </is>
       </c>
     </row>
@@ -10383,11 +10383,11 @@
       </c>
       <c r="D441" s="10" t="inlineStr">
         <is>
-          <t>PMP1286710</t>
+          <t>PMP1285903</t>
         </is>
       </c>
       <c r="E441" s="6" t="n">
-        <v>-650618</v>
+        <v>-322554</v>
       </c>
       <c r="F441" s="10" t="inlineStr">
         <is>
@@ -10400,11 +10400,11 @@
         </is>
       </c>
       <c r="H441" s="6" t="n">
-        <v>-650618</v>
+        <v>-322554</v>
       </c>
       <c r="I441" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286710</t>
+          <t>Rechazo PMP1285903</t>
         </is>
       </c>
     </row>
@@ -10416,11 +10416,11 @@
       </c>
       <c r="D442" s="10" t="inlineStr">
         <is>
-          <t>PMP1286711</t>
+          <t>PMP1285908</t>
         </is>
       </c>
       <c r="E442" s="6" t="n">
-        <v>-6920570</v>
+        <v>-135255</v>
       </c>
       <c r="F442" s="10" t="inlineStr">
         <is>
@@ -10433,11 +10433,11 @@
         </is>
       </c>
       <c r="H442" s="6" t="n">
-        <v>-6920570</v>
+        <v>-135255</v>
       </c>
       <c r="I442" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286711</t>
+          <t>Rechazo PMP1285908</t>
         </is>
       </c>
     </row>
@@ -10449,11 +10449,11 @@
       </c>
       <c r="D443" s="10" t="inlineStr">
         <is>
-          <t>PMP1286712</t>
+          <t>PMP1286056</t>
         </is>
       </c>
       <c r="E443" s="6" t="n">
-        <v>-403395</v>
+        <v>-556413</v>
       </c>
       <c r="F443" s="10" t="inlineStr">
         <is>
@@ -10466,11 +10466,11 @@
         </is>
       </c>
       <c r="H443" s="6" t="n">
-        <v>-403395</v>
+        <v>-556413</v>
       </c>
       <c r="I443" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286712</t>
+          <t>Rechazo PMP1286056</t>
         </is>
       </c>
     </row>
@@ -10482,11 +10482,11 @@
       </c>
       <c r="D444" s="10" t="inlineStr">
         <is>
-          <t>PMP1286715</t>
+          <t>PMP1286208</t>
         </is>
       </c>
       <c r="E444" s="6" t="n">
-        <v>-4085189</v>
+        <v>-949123</v>
       </c>
       <c r="F444" s="10" t="inlineStr">
         <is>
@@ -10499,11 +10499,11 @@
         </is>
       </c>
       <c r="H444" s="6" t="n">
-        <v>-4085189</v>
+        <v>-949123</v>
       </c>
       <c r="I444" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286715</t>
+          <t>Rechazo PMP1286208</t>
         </is>
       </c>
     </row>
@@ -10515,11 +10515,11 @@
       </c>
       <c r="D445" s="10" t="inlineStr">
         <is>
-          <t>PMP1286716</t>
+          <t>PMP1286554</t>
         </is>
       </c>
       <c r="E445" s="6" t="n">
-        <v>-822039</v>
+        <v>-354934</v>
       </c>
       <c r="F445" s="10" t="inlineStr">
         <is>
@@ -10532,11 +10532,11 @@
         </is>
       </c>
       <c r="H445" s="6" t="n">
-        <v>-822039</v>
+        <v>-354934</v>
       </c>
       <c r="I445" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286716</t>
+          <t>Rechazo PMP1286554</t>
         </is>
       </c>
     </row>
@@ -10548,11 +10548,11 @@
       </c>
       <c r="D446" s="10" t="inlineStr">
         <is>
-          <t>PMP1287257</t>
+          <t>PMP1286556</t>
         </is>
       </c>
       <c r="E446" s="6" t="n">
-        <v>-156625</v>
+        <v>-364001</v>
       </c>
       <c r="F446" s="10" t="inlineStr">
         <is>
@@ -10565,11 +10565,11 @@
         </is>
       </c>
       <c r="H446" s="6" t="n">
-        <v>-156625</v>
+        <v>-364001</v>
       </c>
       <c r="I446" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287257</t>
+          <t>Rechazo PMP1286556</t>
         </is>
       </c>
     </row>
@@ -10581,11 +10581,11 @@
       </c>
       <c r="D447" s="10" t="inlineStr">
         <is>
-          <t>PMP1287321</t>
+          <t>PMP1286709</t>
         </is>
       </c>
       <c r="E447" s="6" t="n">
-        <v>-182163</v>
+        <v>-33537478</v>
       </c>
       <c r="F447" s="10" t="inlineStr">
         <is>
@@ -10598,11 +10598,11 @@
         </is>
       </c>
       <c r="H447" s="6" t="n">
-        <v>-182163</v>
+        <v>-33537478</v>
       </c>
       <c r="I447" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287321</t>
+          <t>Rechazo PMP1286709</t>
         </is>
       </c>
     </row>
@@ -10614,11 +10614,11 @@
       </c>
       <c r="D448" s="10" t="inlineStr">
         <is>
-          <t>PMP1287325</t>
+          <t>PMP1286710</t>
         </is>
       </c>
       <c r="E448" s="6" t="n">
-        <v>-118625</v>
+        <v>-650618</v>
       </c>
       <c r="F448" s="10" t="inlineStr">
         <is>
@@ -10631,11 +10631,11 @@
         </is>
       </c>
       <c r="H448" s="6" t="n">
-        <v>-118625</v>
+        <v>-650618</v>
       </c>
       <c r="I448" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287325</t>
+          <t>Rechazo PMP1286710</t>
         </is>
       </c>
     </row>
@@ -10647,11 +10647,11 @@
       </c>
       <c r="D449" s="10" t="inlineStr">
         <is>
-          <t>PMP1287335</t>
+          <t>PMP1286711</t>
         </is>
       </c>
       <c r="E449" s="6" t="n">
-        <v>-128620</v>
+        <v>-6920570</v>
       </c>
       <c r="F449" s="10" t="inlineStr">
         <is>
@@ -10664,11 +10664,11 @@
         </is>
       </c>
       <c r="H449" s="6" t="n">
-        <v>-128620</v>
+        <v>-6920570</v>
       </c>
       <c r="I449" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287335</t>
+          <t>Rechazo PMP1286711</t>
         </is>
       </c>
     </row>
@@ -10680,11 +10680,11 @@
       </c>
       <c r="D450" s="10" t="inlineStr">
         <is>
-          <t>PMP1287379</t>
+          <t>PMP1286712</t>
         </is>
       </c>
       <c r="E450" s="6" t="n">
-        <v>-271757</v>
+        <v>-403395</v>
       </c>
       <c r="F450" s="10" t="inlineStr">
         <is>
@@ -10697,11 +10697,11 @@
         </is>
       </c>
       <c r="H450" s="6" t="n">
-        <v>-271757</v>
+        <v>-403395</v>
       </c>
       <c r="I450" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287379</t>
+          <t>Rechazo PMP1286712</t>
         </is>
       </c>
     </row>
@@ -10713,11 +10713,11 @@
       </c>
       <c r="D451" s="10" t="inlineStr">
         <is>
-          <t>PMP1287385</t>
+          <t>PMP1286715</t>
         </is>
       </c>
       <c r="E451" s="6" t="n">
-        <v>-214996</v>
+        <v>-4085189</v>
       </c>
       <c r="F451" s="10" t="inlineStr">
         <is>
@@ -10730,11 +10730,11 @@
         </is>
       </c>
       <c r="H451" s="6" t="n">
-        <v>-214996</v>
+        <v>-4085189</v>
       </c>
       <c r="I451" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287385</t>
+          <t>Rechazo PMP1286715</t>
         </is>
       </c>
     </row>
@@ -10746,11 +10746,11 @@
       </c>
       <c r="D452" s="10" t="inlineStr">
         <is>
-          <t>PMP1287386</t>
+          <t>PMP1286716</t>
         </is>
       </c>
       <c r="E452" s="6" t="n">
-        <v>-267680</v>
+        <v>-822039</v>
       </c>
       <c r="F452" s="10" t="inlineStr">
         <is>
@@ -10763,11 +10763,11 @@
         </is>
       </c>
       <c r="H452" s="6" t="n">
-        <v>-267680</v>
+        <v>-822039</v>
       </c>
       <c r="I452" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287386</t>
+          <t>Rechazo PMP1286716</t>
         </is>
       </c>
     </row>
@@ -10779,11 +10779,11 @@
       </c>
       <c r="D453" s="10" t="inlineStr">
         <is>
-          <t>PMP1287574</t>
+          <t>PMP1287257</t>
         </is>
       </c>
       <c r="E453" s="6" t="n">
-        <v>-11940004</v>
+        <v>-156625</v>
       </c>
       <c r="F453" s="10" t="inlineStr">
         <is>
@@ -10796,11 +10796,11 @@
         </is>
       </c>
       <c r="H453" s="6" t="n">
-        <v>-11940004</v>
+        <v>-156625</v>
       </c>
       <c r="I453" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287574</t>
+          <t>Rechazo PMP1287257</t>
         </is>
       </c>
     </row>
@@ -10812,11 +10812,11 @@
       </c>
       <c r="D454" s="10" t="inlineStr">
         <is>
-          <t>PMP1287736</t>
+          <t>PMP1287321</t>
         </is>
       </c>
       <c r="E454" s="6" t="n">
-        <v>-93440</v>
+        <v>-182163</v>
       </c>
       <c r="F454" s="10" t="inlineStr">
         <is>
@@ -10829,11 +10829,11 @@
         </is>
       </c>
       <c r="H454" s="6" t="n">
-        <v>-93440</v>
+        <v>-182163</v>
       </c>
       <c r="I454" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287736</t>
+          <t>Rechazo PMP1287321</t>
         </is>
       </c>
     </row>
@@ -10845,11 +10845,11 @@
       </c>
       <c r="D455" s="10" t="inlineStr">
         <is>
-          <t>PMP128777746</t>
+          <t>PMP1287325</t>
         </is>
       </c>
       <c r="E455" s="6" t="n">
-        <v>-322500</v>
+        <v>-118625</v>
       </c>
       <c r="F455" s="10" t="inlineStr">
         <is>
@@ -10862,11 +10862,11 @@
         </is>
       </c>
       <c r="H455" s="6" t="n">
-        <v>-322500</v>
+        <v>-118625</v>
       </c>
       <c r="I455" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP128777746</t>
+          <t>Rechazo PMP1287325</t>
         </is>
       </c>
     </row>
@@ -10878,11 +10878,11 @@
       </c>
       <c r="D456" s="10" t="inlineStr">
         <is>
-          <t>PMP1287829</t>
+          <t>PMP1287335</t>
         </is>
       </c>
       <c r="E456" s="6" t="n">
-        <v>-290823</v>
+        <v>-128620</v>
       </c>
       <c r="F456" s="10" t="inlineStr">
         <is>
@@ -10895,11 +10895,11 @@
         </is>
       </c>
       <c r="H456" s="6" t="n">
-        <v>-290823</v>
+        <v>-128620</v>
       </c>
       <c r="I456" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287829</t>
+          <t>Rechazo PMP1287335</t>
         </is>
       </c>
     </row>
@@ -10911,11 +10911,11 @@
       </c>
       <c r="D457" s="10" t="inlineStr">
         <is>
-          <t>PMP1287903</t>
+          <t>PMP1287379</t>
         </is>
       </c>
       <c r="E457" s="6" t="n">
-        <v>-128514</v>
+        <v>-271757</v>
       </c>
       <c r="F457" s="10" t="inlineStr">
         <is>
@@ -10928,11 +10928,11 @@
         </is>
       </c>
       <c r="H457" s="6" t="n">
-        <v>-128514</v>
+        <v>-271757</v>
       </c>
       <c r="I457" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287903</t>
+          <t>Rechazo PMP1287379</t>
         </is>
       </c>
     </row>
@@ -10944,11 +10944,11 @@
       </c>
       <c r="D458" s="10" t="inlineStr">
         <is>
-          <t>PMP1287904</t>
+          <t>PMP1287385</t>
         </is>
       </c>
       <c r="E458" s="6" t="n">
-        <v>-80064</v>
+        <v>-214996</v>
       </c>
       <c r="F458" s="10" t="inlineStr">
         <is>
@@ -10961,11 +10961,11 @@
         </is>
       </c>
       <c r="H458" s="6" t="n">
-        <v>-80064</v>
+        <v>-214996</v>
       </c>
       <c r="I458" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287904</t>
+          <t>Rechazo PMP1287385</t>
         </is>
       </c>
     </row>
@@ -10977,11 +10977,11 @@
       </c>
       <c r="D459" s="10" t="inlineStr">
         <is>
-          <t>PMP1287920</t>
+          <t>PMP1287386</t>
         </is>
       </c>
       <c r="E459" s="6" t="n">
-        <v>-582605</v>
+        <v>-267680</v>
       </c>
       <c r="F459" s="10" t="inlineStr">
         <is>
@@ -10994,11 +10994,11 @@
         </is>
       </c>
       <c r="H459" s="6" t="n">
-        <v>-582605</v>
+        <v>-267680</v>
       </c>
       <c r="I459" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287920</t>
+          <t>Rechazo PMP1287386</t>
         </is>
       </c>
     </row>
@@ -11010,11 +11010,11 @@
       </c>
       <c r="D460" s="10" t="inlineStr">
         <is>
-          <t>PMP1287921</t>
+          <t>PMP1287574</t>
         </is>
       </c>
       <c r="E460" s="6" t="n">
-        <v>-124374</v>
+        <v>-11940004</v>
       </c>
       <c r="F460" s="10" t="inlineStr">
         <is>
@@ -11027,11 +11027,11 @@
         </is>
       </c>
       <c r="H460" s="6" t="n">
-        <v>-124374</v>
+        <v>-11940004</v>
       </c>
       <c r="I460" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287921</t>
+          <t>Rechazo PMP1287574</t>
         </is>
       </c>
     </row>
@@ -11043,11 +11043,11 @@
       </c>
       <c r="D461" s="10" t="inlineStr">
         <is>
-          <t>PMP1287928</t>
+          <t>PMP1287736</t>
         </is>
       </c>
       <c r="E461" s="6" t="n">
-        <v>-246230</v>
+        <v>-93440</v>
       </c>
       <c r="F461" s="10" t="inlineStr">
         <is>
@@ -11060,11 +11060,11 @@
         </is>
       </c>
       <c r="H461" s="6" t="n">
-        <v>-246230</v>
+        <v>-93440</v>
       </c>
       <c r="I461" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287928</t>
+          <t>Rechazo PMP1287736</t>
         </is>
       </c>
     </row>
@@ -11076,11 +11076,11 @@
       </c>
       <c r="D462" s="10" t="inlineStr">
         <is>
-          <t>PMP1287930</t>
+          <t>PMP128777746</t>
         </is>
       </c>
       <c r="E462" s="6" t="n">
-        <v>-91079</v>
+        <v>-322500</v>
       </c>
       <c r="F462" s="10" t="inlineStr">
         <is>
@@ -11093,11 +11093,11 @@
         </is>
       </c>
       <c r="H462" s="6" t="n">
-        <v>-91079</v>
+        <v>-322500</v>
       </c>
       <c r="I462" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287930</t>
+          <t>Rechazo PMP128777746</t>
         </is>
       </c>
     </row>
@@ -11109,11 +11109,11 @@
       </c>
       <c r="D463" s="10" t="inlineStr">
         <is>
-          <t>PMP1287931</t>
+          <t>PMP1287829</t>
         </is>
       </c>
       <c r="E463" s="6" t="n">
-        <v>-215025</v>
+        <v>-290823</v>
       </c>
       <c r="F463" s="10" t="inlineStr">
         <is>
@@ -11126,11 +11126,11 @@
         </is>
       </c>
       <c r="H463" s="6" t="n">
-        <v>-215025</v>
+        <v>-290823</v>
       </c>
       <c r="I463" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287931</t>
+          <t>Rechazo PMP1287829</t>
         </is>
       </c>
     </row>
@@ -11142,11 +11142,11 @@
       </c>
       <c r="D464" s="10" t="inlineStr">
         <is>
-          <t>PMP1287948</t>
+          <t>PMP1287903</t>
         </is>
       </c>
       <c r="E464" s="6" t="n">
-        <v>-354871</v>
+        <v>-128514</v>
       </c>
       <c r="F464" s="10" t="inlineStr">
         <is>
@@ -11159,11 +11159,11 @@
         </is>
       </c>
       <c r="H464" s="6" t="n">
-        <v>-354871</v>
+        <v>-128514</v>
       </c>
       <c r="I464" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287948</t>
+          <t>Rechazo PMP1287903</t>
         </is>
       </c>
     </row>
@@ -11175,11 +11175,11 @@
       </c>
       <c r="D465" s="10" t="inlineStr">
         <is>
-          <t>PMP1287949</t>
+          <t>PMP1287904</t>
         </is>
       </c>
       <c r="E465" s="6" t="n">
-        <v>-410669</v>
+        <v>-80064</v>
       </c>
       <c r="F465" s="10" t="inlineStr">
         <is>
@@ -11192,11 +11192,11 @@
         </is>
       </c>
       <c r="H465" s="6" t="n">
-        <v>-410669</v>
+        <v>-80064</v>
       </c>
       <c r="I465" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287949</t>
+          <t>Rechazo PMP1287904</t>
         </is>
       </c>
     </row>
@@ -11208,11 +11208,11 @@
       </c>
       <c r="D466" s="10" t="inlineStr">
         <is>
-          <t>PMP1287951</t>
+          <t>PMP1287920</t>
         </is>
       </c>
       <c r="E466" s="6" t="n">
-        <v>-29456389</v>
+        <v>-582605</v>
       </c>
       <c r="F466" s="10" t="inlineStr">
         <is>
@@ -11225,11 +11225,11 @@
         </is>
       </c>
       <c r="H466" s="6" t="n">
-        <v>-29456389</v>
+        <v>-582605</v>
       </c>
       <c r="I466" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287951</t>
+          <t>Rechazo PMP1287920</t>
         </is>
       </c>
     </row>
@@ -11241,11 +11241,11 @@
       </c>
       <c r="D467" s="10" t="inlineStr">
         <is>
-          <t>PMP1287957</t>
+          <t>PMP1287921</t>
         </is>
       </c>
       <c r="E467" s="6" t="n">
-        <v>-107492</v>
+        <v>-124374</v>
       </c>
       <c r="F467" s="10" t="inlineStr">
         <is>
@@ -11258,11 +11258,11 @@
         </is>
       </c>
       <c r="H467" s="6" t="n">
-        <v>-107492</v>
+        <v>-124374</v>
       </c>
       <c r="I467" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287957</t>
+          <t>Rechazo PMP1287921</t>
         </is>
       </c>
     </row>
@@ -11274,11 +11274,11 @@
       </c>
       <c r="D468" s="10" t="inlineStr">
         <is>
-          <t>PMP1288418</t>
+          <t>PMP1287928</t>
         </is>
       </c>
       <c r="E468" s="6" t="n">
-        <v>-2183651</v>
+        <v>-246230</v>
       </c>
       <c r="F468" s="10" t="inlineStr">
         <is>
@@ -11291,11 +11291,11 @@
         </is>
       </c>
       <c r="H468" s="6" t="n">
-        <v>-2183651</v>
+        <v>-246230</v>
       </c>
       <c r="I468" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288418</t>
+          <t>Rechazo PMP1287928</t>
         </is>
       </c>
     </row>
@@ -11307,11 +11307,11 @@
       </c>
       <c r="D469" s="10" t="inlineStr">
         <is>
-          <t>PMP1288731</t>
+          <t>PMP1287930</t>
         </is>
       </c>
       <c r="E469" s="6" t="n">
-        <v>-160222</v>
+        <v>-91079</v>
       </c>
       <c r="F469" s="10" t="inlineStr">
         <is>
@@ -11324,11 +11324,11 @@
         </is>
       </c>
       <c r="H469" s="6" t="n">
-        <v>-160222</v>
+        <v>-91079</v>
       </c>
       <c r="I469" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288731</t>
+          <t>Rechazo PMP1287930</t>
         </is>
       </c>
     </row>
@@ -11340,11 +11340,11 @@
       </c>
       <c r="D470" s="10" t="inlineStr">
         <is>
-          <t>PMP1288919</t>
+          <t>PMP1287931</t>
         </is>
       </c>
       <c r="E470" s="6" t="n">
-        <v>-9852</v>
+        <v>-215025</v>
       </c>
       <c r="F470" s="10" t="inlineStr">
         <is>
@@ -11357,11 +11357,11 @@
         </is>
       </c>
       <c r="H470" s="6" t="n">
-        <v>-9852</v>
+        <v>-215025</v>
       </c>
       <c r="I470" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288919</t>
+          <t>Rechazo PMP1287931</t>
         </is>
       </c>
     </row>
@@ -11373,11 +11373,11 @@
       </c>
       <c r="D471" s="10" t="inlineStr">
         <is>
-          <t>PMP1288926</t>
+          <t>PMP1287948</t>
         </is>
       </c>
       <c r="E471" s="6" t="n">
-        <v>-322749</v>
+        <v>-354871</v>
       </c>
       <c r="F471" s="10" t="inlineStr">
         <is>
@@ -11390,11 +11390,11 @@
         </is>
       </c>
       <c r="H471" s="6" t="n">
-        <v>-322749</v>
+        <v>-354871</v>
       </c>
       <c r="I471" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288926</t>
+          <t>Rechazo PMP1287948</t>
         </is>
       </c>
     </row>
@@ -11406,11 +11406,11 @@
       </c>
       <c r="D472" s="10" t="inlineStr">
         <is>
-          <t>PMP1288987</t>
+          <t>PMP1287949</t>
         </is>
       </c>
       <c r="E472" s="6" t="n">
-        <v>-1106307</v>
+        <v>-410669</v>
       </c>
       <c r="F472" s="10" t="inlineStr">
         <is>
@@ -11423,11 +11423,11 @@
         </is>
       </c>
       <c r="H472" s="6" t="n">
-        <v>-1106307</v>
+        <v>-410669</v>
       </c>
       <c r="I472" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288987</t>
+          <t>Rechazo PMP1287949</t>
         </is>
       </c>
     </row>
@@ -11439,11 +11439,11 @@
       </c>
       <c r="D473" s="10" t="inlineStr">
         <is>
-          <t>PMP1288988</t>
+          <t>PMP1287951</t>
         </is>
       </c>
       <c r="E473" s="6" t="n">
-        <v>-33894</v>
+        <v>-29456389</v>
       </c>
       <c r="F473" s="10" t="inlineStr">
         <is>
@@ -11456,11 +11456,11 @@
         </is>
       </c>
       <c r="H473" s="6" t="n">
-        <v>-33894</v>
+        <v>-29456389</v>
       </c>
       <c r="I473" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288988</t>
+          <t>Rechazo PMP1287951</t>
         </is>
       </c>
     </row>
@@ -11472,11 +11472,11 @@
       </c>
       <c r="D474" s="10" t="inlineStr">
         <is>
-          <t>PMP1288989</t>
+          <t>PMP1287957</t>
         </is>
       </c>
       <c r="E474" s="6" t="n">
-        <v>-2259163</v>
+        <v>-107492</v>
       </c>
       <c r="F474" s="10" t="inlineStr">
         <is>
@@ -11489,11 +11489,11 @@
         </is>
       </c>
       <c r="H474" s="6" t="n">
-        <v>-2259163</v>
+        <v>-107492</v>
       </c>
       <c r="I474" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288989</t>
+          <t>Rechazo PMP1287957</t>
         </is>
       </c>
     </row>
@@ -11505,11 +11505,11 @@
       </c>
       <c r="D475" s="10" t="inlineStr">
         <is>
-          <t>PMP1289251</t>
+          <t>PMP1288418</t>
         </is>
       </c>
       <c r="E475" s="6" t="n">
-        <v>-200703</v>
+        <v>-2183651</v>
       </c>
       <c r="F475" s="10" t="inlineStr">
         <is>
@@ -11522,11 +11522,11 @@
         </is>
       </c>
       <c r="H475" s="6" t="n">
-        <v>-200703</v>
+        <v>-2183651</v>
       </c>
       <c r="I475" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1289251</t>
+          <t>Rechazo PMP1288418</t>
         </is>
       </c>
     </row>
@@ -11538,11 +11538,11 @@
       </c>
       <c r="D476" s="10" t="inlineStr">
         <is>
-          <t>PMP1289253</t>
+          <t>PMP1288731</t>
         </is>
       </c>
       <c r="E476" s="6" t="n">
-        <v>-2482097</v>
+        <v>-160222</v>
       </c>
       <c r="F476" s="10" t="inlineStr">
         <is>
@@ -11555,11 +11555,11 @@
         </is>
       </c>
       <c r="H476" s="6" t="n">
-        <v>-2482097</v>
+        <v>-160222</v>
       </c>
       <c r="I476" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1289253</t>
+          <t>Rechazo PMP1288731</t>
         </is>
       </c>
     </row>
@@ -11571,11 +11571,11 @@
       </c>
       <c r="D477" s="10" t="inlineStr">
         <is>
-          <t>PMP1289324</t>
+          <t>PMP1288919</t>
         </is>
       </c>
       <c r="E477" s="6" t="n">
-        <v>-532656</v>
+        <v>-9852</v>
       </c>
       <c r="F477" s="10" t="inlineStr">
         <is>
@@ -11588,11 +11588,11 @@
         </is>
       </c>
       <c r="H477" s="6" t="n">
-        <v>-532656</v>
+        <v>-9852</v>
       </c>
       <c r="I477" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1289324</t>
+          <t>Rechazo PMP1288919</t>
         </is>
       </c>
     </row>
@@ -11604,11 +11604,11 @@
       </c>
       <c r="D478" s="10" t="inlineStr">
         <is>
-          <t>PMP1289326</t>
+          <t>PMP1288926</t>
         </is>
       </c>
       <c r="E478" s="6" t="n">
-        <v>-523796</v>
+        <v>-322749</v>
       </c>
       <c r="F478" s="10" t="inlineStr">
         <is>
@@ -11621,11 +11621,11 @@
         </is>
       </c>
       <c r="H478" s="6" t="n">
-        <v>-523796</v>
+        <v>-322749</v>
       </c>
       <c r="I478" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1289326</t>
+          <t>Rechazo PMP1288926</t>
         </is>
       </c>
     </row>
@@ -11637,11 +11637,11 @@
       </c>
       <c r="D479" s="10" t="inlineStr">
         <is>
-          <t>PMP1289328</t>
+          <t>PMP1288987</t>
         </is>
       </c>
       <c r="E479" s="6" t="n">
-        <v>-303757</v>
+        <v>-1106307</v>
       </c>
       <c r="F479" s="10" t="inlineStr">
         <is>
@@ -11654,11 +11654,11 @@
         </is>
       </c>
       <c r="H479" s="6" t="n">
-        <v>-303757</v>
+        <v>-1106307</v>
       </c>
       <c r="I479" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1289328</t>
+          <t>Rechazo PMP1288987</t>
         </is>
       </c>
     </row>
@@ -11670,11 +11670,11 @@
       </c>
       <c r="D480" s="10" t="inlineStr">
         <is>
-          <t>PMP1289507</t>
+          <t>PMP1288988</t>
         </is>
       </c>
       <c r="E480" s="6" t="n">
-        <v>-160184</v>
+        <v>-33894</v>
       </c>
       <c r="F480" s="10" t="inlineStr">
         <is>
@@ -11687,11 +11687,11 @@
         </is>
       </c>
       <c r="H480" s="6" t="n">
-        <v>-160184</v>
+        <v>-33894</v>
       </c>
       <c r="I480" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1289507</t>
+          <t>Rechazo PMP1288988</t>
         </is>
       </c>
     </row>
@@ -11703,26 +11703,257 @@
       </c>
       <c r="D481" s="10" t="inlineStr">
         <is>
+          <t>PMP1288989</t>
+        </is>
+      </c>
+      <c r="E481" s="6" t="n">
+        <v>-2259163</v>
+      </c>
+      <c r="F481" s="10" t="inlineStr">
+        <is>
+          <t>Rechazo</t>
+        </is>
+      </c>
+      <c r="G481" s="10" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="H481" s="6" t="n">
+        <v>-2259163</v>
+      </c>
+      <c r="I481" s="11" t="inlineStr">
+        <is>
+          <t>Rechazo PMP1288989</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="C482" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Clientes</t>
+        </is>
+      </c>
+      <c r="D482" s="10" t="inlineStr">
+        <is>
+          <t>PMP1289251</t>
+        </is>
+      </c>
+      <c r="E482" s="6" t="n">
+        <v>-200703</v>
+      </c>
+      <c r="F482" s="10" t="inlineStr">
+        <is>
+          <t>Rechazo</t>
+        </is>
+      </c>
+      <c r="G482" s="10" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="H482" s="6" t="n">
+        <v>-200703</v>
+      </c>
+      <c r="I482" s="11" t="inlineStr">
+        <is>
+          <t>Rechazo PMP1289251</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="C483" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Clientes</t>
+        </is>
+      </c>
+      <c r="D483" s="10" t="inlineStr">
+        <is>
+          <t>PMP1289253</t>
+        </is>
+      </c>
+      <c r="E483" s="6" t="n">
+        <v>-2482097</v>
+      </c>
+      <c r="F483" s="10" t="inlineStr">
+        <is>
+          <t>Rechazo</t>
+        </is>
+      </c>
+      <c r="G483" s="10" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="H483" s="6" t="n">
+        <v>-2482097</v>
+      </c>
+      <c r="I483" s="11" t="inlineStr">
+        <is>
+          <t>Rechazo PMP1289253</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="C484" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Clientes</t>
+        </is>
+      </c>
+      <c r="D484" s="10" t="inlineStr">
+        <is>
+          <t>PMP1289324</t>
+        </is>
+      </c>
+      <c r="E484" s="6" t="n">
+        <v>-532656</v>
+      </c>
+      <c r="F484" s="10" t="inlineStr">
+        <is>
+          <t>Rechazo</t>
+        </is>
+      </c>
+      <c r="G484" s="10" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="H484" s="6" t="n">
+        <v>-532656</v>
+      </c>
+      <c r="I484" s="11" t="inlineStr">
+        <is>
+          <t>Rechazo PMP1289324</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="C485" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Clientes</t>
+        </is>
+      </c>
+      <c r="D485" s="10" t="inlineStr">
+        <is>
+          <t>PMP1289326</t>
+        </is>
+      </c>
+      <c r="E485" s="6" t="n">
+        <v>-523796</v>
+      </c>
+      <c r="F485" s="10" t="inlineStr">
+        <is>
+          <t>Rechazo</t>
+        </is>
+      </c>
+      <c r="G485" s="10" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="H485" s="6" t="n">
+        <v>-523796</v>
+      </c>
+      <c r="I485" s="11" t="inlineStr">
+        <is>
+          <t>Rechazo PMP1289326</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="C486" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Clientes</t>
+        </is>
+      </c>
+      <c r="D486" s="10" t="inlineStr">
+        <is>
+          <t>PMP1289328</t>
+        </is>
+      </c>
+      <c r="E486" s="6" t="n">
+        <v>-303757</v>
+      </c>
+      <c r="F486" s="10" t="inlineStr">
+        <is>
+          <t>Rechazo</t>
+        </is>
+      </c>
+      <c r="G486" s="10" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="H486" s="6" t="n">
+        <v>-303757</v>
+      </c>
+      <c r="I486" s="11" t="inlineStr">
+        <is>
+          <t>Rechazo PMP1289328</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="C487" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Clientes</t>
+        </is>
+      </c>
+      <c r="D487" s="10" t="inlineStr">
+        <is>
+          <t>PMP1289507</t>
+        </is>
+      </c>
+      <c r="E487" s="6" t="n">
+        <v>-160184</v>
+      </c>
+      <c r="F487" s="10" t="inlineStr">
+        <is>
+          <t>Rechazo</t>
+        </is>
+      </c>
+      <c r="G487" s="10" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="H487" s="6" t="n">
+        <v>-160184</v>
+      </c>
+      <c r="I487" s="11" t="inlineStr">
+        <is>
+          <t>Rechazo PMP1289507</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="C488" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Clientes</t>
+        </is>
+      </c>
+      <c r="D488" s="10" t="inlineStr">
+        <is>
           <t>Costo de Transferen</t>
         </is>
       </c>
-      <c r="E481" s="6" t="n">
+      <c r="E488" s="6" t="n">
         <v>-3000</v>
       </c>
-      <c r="F481" s="10" t="inlineStr">
+      <c r="F488" s="10" t="inlineStr">
         <is>
           <t>Costo de Transferen</t>
         </is>
       </c>
-      <c r="G481" s="10" t="inlineStr">
+      <c r="G488" s="10" t="inlineStr">
         <is>
           <t>WOB</t>
         </is>
       </c>
-      <c r="H481" s="6" t="n">
+      <c r="H488" s="6" t="n">
         <v>-3000</v>
       </c>
-      <c r="I481" s="11" t="inlineStr">
+      <c r="I488" s="11" t="inlineStr">
         <is>
           <t>MENORES VALORES</t>
         </is>

--- a/Pruebas/Archivos/Template/Colombia/Template_HRC_Cenco.xlsx
+++ b/Pruebas/Archivos/Template/Colombia/Template_HRC_Cenco.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I482"/>
+  <dimension ref="A1:I483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -7969,33 +7969,29 @@
     <row r="368">
       <c r="C368" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Nota de Crédito</t>
         </is>
       </c>
       <c r="D368" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO APERTURA</t>
+          <t>1200016485</t>
         </is>
       </c>
       <c r="E368" s="6" t="n">
-        <v>-8594192</v>
+        <v>-4509059502</v>
       </c>
       <c r="F368" s="10" t="inlineStr">
         <is>
-          <t>DROGUE</t>
-        </is>
-      </c>
-      <c r="G368" s="10" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+          <t>NRO</t>
+        </is>
+      </c>
+      <c r="G368" s="10" t="inlineStr"/>
       <c r="H368" s="6" t="n">
-        <v>-8594192</v>
+        <v>-4509059502</v>
       </c>
       <c r="I368" s="11" t="inlineStr">
         <is>
-          <t>DAV DSCTO  DESCUENTO APERTURA DROGUE</t>
+          <t>favor del cliente sin aplicar por falta de soporte</t>
         </is>
       </c>
     </row>
@@ -8007,11 +8003,11 @@
       </c>
       <c r="D369" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO CALENDARI</t>
+          <t>DESCUENTO APERTURA</t>
         </is>
       </c>
       <c r="E369" s="6" t="n">
-        <v>-817508590</v>
+        <v>-8594192</v>
       </c>
       <c r="F369" s="10" t="inlineStr">
         <is>
@@ -8024,11 +8020,11 @@
         </is>
       </c>
       <c r="H369" s="6" t="n">
-        <v>-817508590</v>
+        <v>-8594192</v>
       </c>
       <c r="I369" s="11" t="inlineStr">
         <is>
-          <t>DCA DSCTO  DESCUENTO CALENDARI DROGUE</t>
+          <t>DAV DSCTO  DESCUENTO APERTURA DROGUE</t>
         </is>
       </c>
     </row>
@@ -8040,11 +8036,11 @@
       </c>
       <c r="D370" s="10" t="inlineStr">
         <is>
-          <t>DEVOLUCIONES</t>
+          <t>DESCUENTO CALENDARI</t>
         </is>
       </c>
       <c r="E370" s="6" t="n">
-        <v>-3512351</v>
+        <v>-817508590</v>
       </c>
       <c r="F370" s="10" t="inlineStr">
         <is>
@@ -8057,11 +8053,11 @@
         </is>
       </c>
       <c r="H370" s="6" t="n">
-        <v>-3512351</v>
+        <v>-817508590</v>
       </c>
       <c r="I370" s="11" t="inlineStr">
         <is>
-          <t>DND DSCTO  DEVOLUCIONES DROGUE</t>
+          <t>DCA DSCTO  DESCUENTO CALENDARI DROGUE</t>
         </is>
       </c>
     </row>
@@ -8073,11 +8069,11 @@
       </c>
       <c r="D371" s="10" t="inlineStr">
         <is>
-          <t>DSTO COMERCIAL FIJO</t>
+          <t>DEVOLUCIONES</t>
         </is>
       </c>
       <c r="E371" s="6" t="n">
-        <v>-48283208</v>
+        <v>-3512351</v>
       </c>
       <c r="F371" s="10" t="inlineStr">
         <is>
@@ -8090,11 +8086,11 @@
         </is>
       </c>
       <c r="H371" s="6" t="n">
-        <v>-48283208</v>
+        <v>-3512351</v>
       </c>
       <c r="I371" s="11" t="inlineStr">
         <is>
-          <t>DCF DSCTO  DSTO COMERCIAL FIJO DROGUE</t>
+          <t>DND DSCTO  DEVOLUCIONES DROGUE</t>
         </is>
       </c>
     </row>
@@ -8106,11 +8102,11 @@
       </c>
       <c r="D372" s="10" t="inlineStr">
         <is>
-          <t>DTO POR ESCALA VOLU</t>
+          <t>DSTO COMERCIAL FIJO</t>
         </is>
       </c>
       <c r="E372" s="6" t="n">
-        <v>-67702329</v>
+        <v>-48283208</v>
       </c>
       <c r="F372" s="10" t="inlineStr">
         <is>
@@ -8123,11 +8119,11 @@
         </is>
       </c>
       <c r="H372" s="6" t="n">
-        <v>-67702329</v>
+        <v>-48283208</v>
       </c>
       <c r="I372" s="11" t="inlineStr">
         <is>
-          <t>DEC DSCTO  DTO POR ESCALA VOLU DROGUE</t>
+          <t>DCF DSCTO  DSTO COMERCIAL FIJO DROGUE</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8139,7 @@
         </is>
       </c>
       <c r="E373" s="6" t="n">
-        <v>-2165916</v>
+        <v>-67702329</v>
       </c>
       <c r="F373" s="10" t="inlineStr">
         <is>
@@ -8156,11 +8152,11 @@
         </is>
       </c>
       <c r="H373" s="6" t="n">
-        <v>-2165916</v>
+        <v>-67702329</v>
       </c>
       <c r="I373" s="11" t="inlineStr">
         <is>
-          <t>DEC DSCTO 20251100199283 DTO POR ESCALA VOLU DROGUE</t>
+          <t>DEC DSCTO  DTO POR ESCALA VOLU DROGUE</t>
         </is>
       </c>
     </row>
@@ -8172,28 +8168,28 @@
       </c>
       <c r="D374" s="10" t="inlineStr">
         <is>
-          <t>VPP1 2004529ADM. FIDELIDAD -</t>
+          <t>DTO POR ESCALA VOLU</t>
         </is>
       </c>
       <c r="E374" s="6" t="n">
-        <v>-57239000</v>
+        <v>-2165916</v>
       </c>
       <c r="F374" s="10" t="inlineStr">
         <is>
-          <t>FACT PROVEED</t>
+          <t>DROGUE</t>
         </is>
       </c>
       <c r="G374" s="10" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H374" s="6" t="n">
-        <v>-57239000</v>
+        <v>-2165916</v>
       </c>
       <c r="I374" s="11" t="inlineStr">
         <is>
-          <t>VPP1 2004529ADM. FIDELIDAD -</t>
+          <t>DEC DSCTO 20251100199283 DTO POR ESCALA VOLU DROGUE</t>
         </is>
       </c>
     </row>
@@ -8205,11 +8201,11 @@
       </c>
       <c r="D375" s="10" t="inlineStr">
         <is>
-          <t>VPP1 2004621ADM. FIDELIDAD -</t>
+          <t>VPP1 2004529ADM. FIDELIDAD -</t>
         </is>
       </c>
       <c r="E375" s="6" t="n">
-        <v>-6426000</v>
+        <v>-57239000</v>
       </c>
       <c r="F375" s="10" t="inlineStr">
         <is>
@@ -8222,11 +8218,11 @@
         </is>
       </c>
       <c r="H375" s="6" t="n">
-        <v>-6426000</v>
+        <v>-57239000</v>
       </c>
       <c r="I375" s="11" t="inlineStr">
         <is>
-          <t>VPP1 2004621ADM. FIDELIDAD -</t>
+          <t>VPP1 2004529ADM. FIDELIDAD -</t>
         </is>
       </c>
     </row>
@@ -8238,11 +8234,11 @@
       </c>
       <c r="D376" s="10" t="inlineStr">
         <is>
-          <t>VPP1 2004622ADM. FIDELIDAD -</t>
+          <t>VPP1 2004621ADM. FIDELIDAD -</t>
         </is>
       </c>
       <c r="E376" s="6" t="n">
-        <v>-41650000</v>
+        <v>-6426000</v>
       </c>
       <c r="F376" s="10" t="inlineStr">
         <is>
@@ -8255,11 +8251,11 @@
         </is>
       </c>
       <c r="H376" s="6" t="n">
-        <v>-41650000</v>
+        <v>-6426000</v>
       </c>
       <c r="I376" s="11" t="inlineStr">
         <is>
-          <t>VPP1 2004622ADM. FIDELIDAD -</t>
+          <t>VPP1 2004621ADM. FIDELIDAD -</t>
         </is>
       </c>
     </row>
@@ -8271,11 +8267,11 @@
       </c>
       <c r="D377" s="10" t="inlineStr">
         <is>
-          <t>VPP2 2021716ADM.</t>
+          <t>VPP1 2004622ADM. FIDELIDAD -</t>
         </is>
       </c>
       <c r="E377" s="6" t="n">
-        <v>-2507098292</v>
+        <v>-41650000</v>
       </c>
       <c r="F377" s="10" t="inlineStr">
         <is>
@@ -8288,11 +8284,11 @@
         </is>
       </c>
       <c r="H377" s="6" t="n">
-        <v>-2507098292</v>
+        <v>-41650000</v>
       </c>
       <c r="I377" s="11" t="inlineStr">
         <is>
-          <t>VPP2 2021716ADM.</t>
+          <t>VPP1 2004622ADM. FIDELIDAD -</t>
         </is>
       </c>
     </row>
@@ -8304,11 +8300,11 @@
       </c>
       <c r="D378" s="10" t="inlineStr">
         <is>
-          <t>VPP2 2022342ADM.</t>
+          <t>VPP2 2021716ADM.</t>
         </is>
       </c>
       <c r="E378" s="6" t="n">
-        <v>-1075965191</v>
+        <v>-2507098292</v>
       </c>
       <c r="F378" s="10" t="inlineStr">
         <is>
@@ -8321,44 +8317,44 @@
         </is>
       </c>
       <c r="H378" s="6" t="n">
-        <v>-1075965191</v>
+        <v>-2507098292</v>
       </c>
       <c r="I378" s="11" t="inlineStr">
         <is>
-          <t>VPP2 2022342ADM.</t>
+          <t>VPP2 2021716ADM.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="C379" s="10" t="inlineStr">
         <is>
-          <t>Descuento Cliente</t>
+          <t>Descuentos Clientes</t>
         </is>
       </c>
       <c r="D379" s="10" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
+          <t>VPP2 2022342ADM.</t>
         </is>
       </c>
       <c r="E379" s="6" t="n">
-        <v>-37.26000004360685</v>
+        <v>-1075965191</v>
       </c>
       <c r="F379" s="10" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
+          <t>FACT PROVEED</t>
         </is>
       </c>
       <c r="G379" s="10" t="inlineStr">
         <is>
-          <t>CSR</t>
+          <t>CSB</t>
         </is>
       </c>
       <c r="H379" s="6" t="n">
-        <v>-37.26000004360685</v>
+        <v>-1075965191</v>
       </c>
       <c r="I379" s="11" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
+          <t>VPP2 2022342ADM.</t>
         </is>
       </c>
     </row>
@@ -8370,15 +8366,15 @@
       </c>
       <c r="D380" s="10" t="inlineStr">
         <is>
-          <t>PMP1286054</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="E380" s="6" t="n">
-        <v>-864163</v>
+        <v>-37.26000004360685</v>
       </c>
       <c r="F380" s="10" t="inlineStr">
         <is>
-          <t>Menor Vlr Pagado</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G380" s="10" t="inlineStr">
@@ -8387,11 +8383,11 @@
         </is>
       </c>
       <c r="H380" s="6" t="n">
-        <v>-864163</v>
+        <v>-37.26000004360685</v>
       </c>
       <c r="I380" s="11" t="inlineStr">
         <is>
-          <t>Menor Vlr Pagado PMP1286054</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
@@ -8403,11 +8399,11 @@
       </c>
       <c r="D381" s="10" t="inlineStr">
         <is>
-          <t>PMP1286550</t>
+          <t>PMP1286054</t>
         </is>
       </c>
       <c r="E381" s="6" t="n">
-        <v>-5910046.859999999</v>
+        <v>-864163</v>
       </c>
       <c r="F381" s="10" t="inlineStr">
         <is>
@@ -8420,11 +8416,11 @@
         </is>
       </c>
       <c r="H381" s="6" t="n">
-        <v>-5910046.859999999</v>
+        <v>-864163</v>
       </c>
       <c r="I381" s="11" t="inlineStr">
         <is>
-          <t>Menor Vlr Pagado PMP1286550</t>
+          <t>Menor Vlr Pagado PMP1286054</t>
         </is>
       </c>
     </row>
@@ -8436,61 +8432,61 @@
       </c>
       <c r="D382" s="10" t="inlineStr">
         <is>
-          <t>PMP1286553</t>
+          <t>PMP1286550</t>
         </is>
       </c>
       <c r="E382" s="6" t="n">
-        <v>5910047.02</v>
+        <v>-5910046.859999999</v>
       </c>
       <c r="F382" s="10" t="inlineStr">
         <is>
-          <t>Myr Vlr Pagado</t>
+          <t>Menor Vlr Pagado</t>
         </is>
       </c>
       <c r="G382" s="10" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>CSR</t>
         </is>
       </c>
       <c r="H382" s="6" t="n">
-        <v>5910047.02</v>
+        <v>-5910046.859999999</v>
       </c>
       <c r="I382" s="11" t="inlineStr">
         <is>
-          <t>Myr Vlr Pagado PMP1286553</t>
+          <t>Menor Vlr Pagado PMP1286550</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="C383" s="10" t="inlineStr">
         <is>
-          <t>Descuentos Clientes</t>
+          <t>Descuento Cliente</t>
         </is>
       </c>
       <c r="D383" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO APERTURA</t>
+          <t>PMP1286553</t>
         </is>
       </c>
       <c r="E383" s="6" t="n">
-        <v>-14258141</v>
+        <v>5910047.02</v>
       </c>
       <c r="F383" s="10" t="inlineStr">
         <is>
-          <t>PERFUME</t>
+          <t>Myr Vlr Pagado</t>
         </is>
       </c>
       <c r="G383" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>388</t>
         </is>
       </c>
       <c r="H383" s="6" t="n">
-        <v>-14258141</v>
+        <v>5910047.02</v>
       </c>
       <c r="I383" s="11" t="inlineStr">
         <is>
-          <t>DAV DSCTO  DESCUENTO APERTURA PERFUME</t>
+          <t>Myr Vlr Pagado PMP1286553</t>
         </is>
       </c>
     </row>
@@ -8502,11 +8498,11 @@
       </c>
       <c r="D384" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO CALENDARI</t>
+          <t>DESCUENTO APERTURA</t>
         </is>
       </c>
       <c r="E384" s="6" t="n">
-        <v>-1758901158</v>
+        <v>-14258141</v>
       </c>
       <c r="F384" s="10" t="inlineStr">
         <is>
@@ -8519,11 +8515,11 @@
         </is>
       </c>
       <c r="H384" s="6" t="n">
-        <v>-1758901158</v>
+        <v>-14258141</v>
       </c>
       <c r="I384" s="11" t="inlineStr">
         <is>
-          <t>DCA DSCTO  DESCUENTO CALENDARI PERFUME</t>
+          <t>DAV DSCTO  DESCUENTO APERTURA PERFUME</t>
         </is>
       </c>
     </row>
@@ -8535,11 +8531,11 @@
       </c>
       <c r="D385" s="10" t="inlineStr">
         <is>
-          <t>DEVOLUCIONES</t>
+          <t>DESCUENTO CALENDARI</t>
         </is>
       </c>
       <c r="E385" s="6" t="n">
-        <v>-2074733</v>
+        <v>-1758901158</v>
       </c>
       <c r="F385" s="10" t="inlineStr">
         <is>
@@ -8552,11 +8548,11 @@
         </is>
       </c>
       <c r="H385" s="6" t="n">
-        <v>-2074733</v>
+        <v>-1758901158</v>
       </c>
       <c r="I385" s="11" t="inlineStr">
         <is>
-          <t>DND DSCTO  DEVOLUCIONES PERFUME</t>
+          <t>DCA DSCTO  DESCUENTO CALENDARI PERFUME</t>
         </is>
       </c>
     </row>
@@ -8568,11 +8564,11 @@
       </c>
       <c r="D386" s="10" t="inlineStr">
         <is>
-          <t>DSTO COMERCIAL FIJO</t>
+          <t>DEVOLUCIONES</t>
         </is>
       </c>
       <c r="E386" s="6" t="n">
-        <v>-76656631</v>
+        <v>-2074733</v>
       </c>
       <c r="F386" s="10" t="inlineStr">
         <is>
@@ -8585,11 +8581,11 @@
         </is>
       </c>
       <c r="H386" s="6" t="n">
-        <v>-76656631</v>
+        <v>-2074733</v>
       </c>
       <c r="I386" s="11" t="inlineStr">
         <is>
-          <t>DCF DSCTO  DSTO COMERCIAL FIJO PERFUME</t>
+          <t>DND DSCTO  DEVOLUCIONES PERFUME</t>
         </is>
       </c>
     </row>
@@ -8601,11 +8597,11 @@
       </c>
       <c r="D387" s="10" t="inlineStr">
         <is>
-          <t>DTO POR ESCALA VOLU</t>
+          <t>DSTO COMERCIAL FIJO</t>
         </is>
       </c>
       <c r="E387" s="6" t="n">
-        <v>-165350199</v>
+        <v>-76656631</v>
       </c>
       <c r="F387" s="10" t="inlineStr">
         <is>
@@ -8618,11 +8614,11 @@
         </is>
       </c>
       <c r="H387" s="6" t="n">
-        <v>-165350199</v>
+        <v>-76656631</v>
       </c>
       <c r="I387" s="11" t="inlineStr">
         <is>
-          <t>DEC DSCTO  DTO POR ESCALA VOLU PERFUME</t>
+          <t>DCF DSCTO  DSTO COMERCIAL FIJO PERFUME</t>
         </is>
       </c>
     </row>
@@ -8638,7 +8634,7 @@
         </is>
       </c>
       <c r="E388" s="6" t="n">
-        <v>-1792140</v>
+        <v>-165350199</v>
       </c>
       <c r="F388" s="10" t="inlineStr">
         <is>
@@ -8651,11 +8647,11 @@
         </is>
       </c>
       <c r="H388" s="6" t="n">
-        <v>-1792140</v>
+        <v>-165350199</v>
       </c>
       <c r="I388" s="11" t="inlineStr">
         <is>
-          <t>DEC DSCTO 20251200199299 DTO POR ESCALA VOLU PERFUME</t>
+          <t>DEC DSCTO  DTO POR ESCALA VOLU PERFUME</t>
         </is>
       </c>
     </row>
@@ -8671,7 +8667,7 @@
         </is>
       </c>
       <c r="E389" s="6" t="n">
-        <v>-1379112</v>
+        <v>-1792140</v>
       </c>
       <c r="F389" s="10" t="inlineStr">
         <is>
@@ -8684,11 +8680,11 @@
         </is>
       </c>
       <c r="H389" s="6" t="n">
-        <v>-1379112</v>
+        <v>-1792140</v>
       </c>
       <c r="I389" s="11" t="inlineStr">
         <is>
-          <t>DEC DSCTO 20251200199300 DTO POR ESCALA VOLU PERFUME</t>
+          <t>DEC DSCTO 20251200199299 DTO POR ESCALA VOLU PERFUME</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8700,7 @@
         </is>
       </c>
       <c r="E390" s="6" t="n">
-        <v>-80813</v>
+        <v>-1379112</v>
       </c>
       <c r="F390" s="10" t="inlineStr">
         <is>
@@ -8717,11 +8713,11 @@
         </is>
       </c>
       <c r="H390" s="6" t="n">
-        <v>-80813</v>
+        <v>-1379112</v>
       </c>
       <c r="I390" s="11" t="inlineStr">
         <is>
-          <t>DEC DSCTO 20251200199301 DTO POR ESCALA VOLU PERFUME</t>
+          <t>DEC DSCTO 20251200199300 DTO POR ESCALA VOLU PERFUME</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8733,7 @@
         </is>
       </c>
       <c r="E391" s="6" t="n">
-        <v>-470000</v>
+        <v>-80813</v>
       </c>
       <c r="F391" s="10" t="inlineStr">
         <is>
@@ -8750,11 +8746,11 @@
         </is>
       </c>
       <c r="H391" s="6" t="n">
-        <v>-470000</v>
+        <v>-80813</v>
       </c>
       <c r="I391" s="11" t="inlineStr">
         <is>
-          <t>DEC DSCTO 20251200200041 DTO POR ESCALA VOLU PERFUME</t>
+          <t>DEC DSCTO 20251200199301 DTO POR ESCALA VOLU PERFUME</t>
         </is>
       </c>
     </row>
@@ -8766,15 +8762,15 @@
       </c>
       <c r="D392" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO CALENDARI</t>
+          <t>DTO POR ESCALA VOLU</t>
         </is>
       </c>
       <c r="E392" s="6" t="n">
-        <v>-13427534</v>
+        <v>-470000</v>
       </c>
       <c r="F392" s="10" t="inlineStr">
         <is>
-          <t>PLATOS</t>
+          <t>PERFUME</t>
         </is>
       </c>
       <c r="G392" s="10" t="inlineStr">
@@ -8783,11 +8779,11 @@
         </is>
       </c>
       <c r="H392" s="6" t="n">
-        <v>-13427534</v>
+        <v>-470000</v>
       </c>
       <c r="I392" s="11" t="inlineStr">
         <is>
-          <t>DCA DSCTO  DESCUENTO CALENDARI PLATOS</t>
+          <t>DEC DSCTO 20251200200041 DTO POR ESCALA VOLU PERFUME</t>
         </is>
       </c>
     </row>
@@ -8799,11 +8795,11 @@
       </c>
       <c r="D393" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO COMPRAS</t>
+          <t>DESCUENTO CALENDARI</t>
         </is>
       </c>
       <c r="E393" s="6" t="n">
-        <v>-1394767</v>
+        <v>-13427534</v>
       </c>
       <c r="F393" s="10" t="inlineStr">
         <is>
@@ -8816,11 +8812,11 @@
         </is>
       </c>
       <c r="H393" s="6" t="n">
-        <v>-1394767</v>
+        <v>-13427534</v>
       </c>
       <c r="I393" s="11" t="inlineStr">
         <is>
-          <t>DCC DSCTO  DESCUENTO COMPRAS PLATOS</t>
+          <t>DCA DSCTO  DESCUENTO CALENDARI PLATOS</t>
         </is>
       </c>
     </row>
@@ -8832,11 +8828,11 @@
       </c>
       <c r="D394" s="10" t="inlineStr">
         <is>
-          <t>DSTO COMERCIAL FIJO</t>
+          <t>DESCUENTO COMPRAS</t>
         </is>
       </c>
       <c r="E394" s="6" t="n">
-        <v>-20921503</v>
+        <v>-1394767</v>
       </c>
       <c r="F394" s="10" t="inlineStr">
         <is>
@@ -8849,11 +8845,11 @@
         </is>
       </c>
       <c r="H394" s="6" t="n">
-        <v>-20921503</v>
+        <v>-1394767</v>
       </c>
       <c r="I394" s="11" t="inlineStr">
         <is>
-          <t>DCF DSCTO  DSTO COMERCIAL FIJO PLATOS</t>
+          <t>DCC DSCTO  DESCUENTO COMPRAS PLATOS</t>
         </is>
       </c>
     </row>
@@ -8865,15 +8861,15 @@
       </c>
       <c r="D395" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>DSTO COMERCIAL FIJO</t>
         </is>
       </c>
       <c r="E395" s="6" t="n">
-        <v>-61299192</v>
+        <v>-20921503</v>
       </c>
       <c r="F395" s="10" t="inlineStr">
         <is>
-          <t>RANCHO</t>
+          <t>PLATOS</t>
         </is>
       </c>
       <c r="G395" s="10" t="inlineStr">
@@ -8882,11 +8878,11 @@
         </is>
       </c>
       <c r="H395" s="6" t="n">
-        <v>-61299192</v>
+        <v>-20921503</v>
       </c>
       <c r="I395" s="11" t="inlineStr">
         <is>
-          <t>RPL DSCTO  DESCUENTO RANCHO</t>
+          <t>DCF DSCTO  DSTO COMERCIAL FIJO PLATOS</t>
         </is>
       </c>
     </row>
@@ -8898,11 +8894,11 @@
       </c>
       <c r="D396" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO CALENDARI</t>
+          <t>DESCUENTO</t>
         </is>
       </c>
       <c r="E396" s="6" t="n">
-        <v>-29638456</v>
+        <v>-61299192</v>
       </c>
       <c r="F396" s="10" t="inlineStr">
         <is>
@@ -8915,11 +8911,11 @@
         </is>
       </c>
       <c r="H396" s="6" t="n">
-        <v>-29638456</v>
+        <v>-61299192</v>
       </c>
       <c r="I396" s="11" t="inlineStr">
         <is>
-          <t>DCA DSCTO  DESCUENTO CALENDARI RANCHO</t>
+          <t>RPL DSCTO  DESCUENTO RANCHO</t>
         </is>
       </c>
     </row>
@@ -8931,11 +8927,11 @@
       </c>
       <c r="D397" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO EN PRIMER</t>
+          <t>DESCUENTO CALENDARI</t>
         </is>
       </c>
       <c r="E397" s="6" t="n">
-        <v>-10216531</v>
+        <v>-29638456</v>
       </c>
       <c r="F397" s="10" t="inlineStr">
         <is>
@@ -8948,11 +8944,11 @@
         </is>
       </c>
       <c r="H397" s="6" t="n">
-        <v>-10216531</v>
+        <v>-29638456</v>
       </c>
       <c r="I397" s="11" t="inlineStr">
         <is>
-          <t>DPC DSCTO  DESCUENTO EN PRIMER RANCHO</t>
+          <t>DCA DSCTO  DESCUENTO CALENDARI RANCHO</t>
         </is>
       </c>
     </row>
@@ -8964,28 +8960,28 @@
       </c>
       <c r="D398" s="10" t="inlineStr">
         <is>
-          <t>PMP1282099</t>
+          <t>DESCUENTO EN PRIMER</t>
         </is>
       </c>
       <c r="E398" s="6" t="n">
-        <v>-307519</v>
+        <v>-10216531</v>
       </c>
       <c r="F398" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>RANCHO</t>
         </is>
       </c>
       <c r="G398" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H398" s="6" t="n">
-        <v>-307519</v>
+        <v>-10216531</v>
       </c>
       <c r="I398" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1282099</t>
+          <t>DPC DSCTO  DESCUENTO EN PRIMER RANCHO</t>
         </is>
       </c>
     </row>
@@ -8997,11 +8993,11 @@
       </c>
       <c r="D399" s="10" t="inlineStr">
         <is>
-          <t>PMP1282353</t>
+          <t>PMP1282099</t>
         </is>
       </c>
       <c r="E399" s="6" t="n">
-        <v>-2659670</v>
+        <v>-307519</v>
       </c>
       <c r="F399" s="10" t="inlineStr">
         <is>
@@ -9014,11 +9010,11 @@
         </is>
       </c>
       <c r="H399" s="6" t="n">
-        <v>-2659670</v>
+        <v>-307519</v>
       </c>
       <c r="I399" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1282353</t>
+          <t>Rechazo PMP1282099</t>
         </is>
       </c>
     </row>
@@ -9030,11 +9026,11 @@
       </c>
       <c r="D400" s="10" t="inlineStr">
         <is>
-          <t>PMP1282964</t>
+          <t>PMP1282353</t>
         </is>
       </c>
       <c r="E400" s="6" t="n">
-        <v>-185365</v>
+        <v>-2659670</v>
       </c>
       <c r="F400" s="10" t="inlineStr">
         <is>
@@ -9047,11 +9043,11 @@
         </is>
       </c>
       <c r="H400" s="6" t="n">
-        <v>-185365</v>
+        <v>-2659670</v>
       </c>
       <c r="I400" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1282964</t>
+          <t>Rechazo PMP1282353</t>
         </is>
       </c>
     </row>
@@ -9063,11 +9059,11 @@
       </c>
       <c r="D401" s="10" t="inlineStr">
         <is>
-          <t>PMP1283008</t>
+          <t>PMP1282964</t>
         </is>
       </c>
       <c r="E401" s="6" t="n">
-        <v>-9788</v>
+        <v>-185365</v>
       </c>
       <c r="F401" s="10" t="inlineStr">
         <is>
@@ -9080,11 +9076,11 @@
         </is>
       </c>
       <c r="H401" s="6" t="n">
-        <v>-9788</v>
+        <v>-185365</v>
       </c>
       <c r="I401" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1283008</t>
+          <t>Rechazo PMP1282964</t>
         </is>
       </c>
     </row>
@@ -9096,11 +9092,11 @@
       </c>
       <c r="D402" s="10" t="inlineStr">
         <is>
-          <t>PMP1283012</t>
+          <t>PMP1283008</t>
         </is>
       </c>
       <c r="E402" s="6" t="n">
-        <v>-167913</v>
+        <v>-9788</v>
       </c>
       <c r="F402" s="10" t="inlineStr">
         <is>
@@ -9113,11 +9109,11 @@
         </is>
       </c>
       <c r="H402" s="6" t="n">
-        <v>-167913</v>
+        <v>-9788</v>
       </c>
       <c r="I402" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1283012</t>
+          <t>Rechazo PMP1283008</t>
         </is>
       </c>
     </row>
@@ -9129,11 +9125,11 @@
       </c>
       <c r="D403" s="10" t="inlineStr">
         <is>
-          <t>PMP1283476</t>
+          <t>PMP1283012</t>
         </is>
       </c>
       <c r="E403" s="6" t="n">
-        <v>-836339</v>
+        <v>-167913</v>
       </c>
       <c r="F403" s="10" t="inlineStr">
         <is>
@@ -9146,11 +9142,11 @@
         </is>
       </c>
       <c r="H403" s="6" t="n">
-        <v>-836339</v>
+        <v>-167913</v>
       </c>
       <c r="I403" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1283476</t>
+          <t>Rechazo PMP1283012</t>
         </is>
       </c>
     </row>
@@ -9162,11 +9158,11 @@
       </c>
       <c r="D404" s="10" t="inlineStr">
         <is>
-          <t>PMP1283500</t>
+          <t>PMP1283476</t>
         </is>
       </c>
       <c r="E404" s="6" t="n">
-        <v>-473742856</v>
+        <v>-836339</v>
       </c>
       <c r="F404" s="10" t="inlineStr">
         <is>
@@ -9179,11 +9175,11 @@
         </is>
       </c>
       <c r="H404" s="6" t="n">
-        <v>-473742856</v>
+        <v>-836339</v>
       </c>
       <c r="I404" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1283500</t>
+          <t>Rechazo PMP1283476</t>
         </is>
       </c>
     </row>
@@ -9195,11 +9191,11 @@
       </c>
       <c r="D405" s="10" t="inlineStr">
         <is>
-          <t>PMP1283784</t>
+          <t>PMP1283500</t>
         </is>
       </c>
       <c r="E405" s="6" t="n">
-        <v>-629893</v>
+        <v>-473742856</v>
       </c>
       <c r="F405" s="10" t="inlineStr">
         <is>
@@ -9212,11 +9208,11 @@
         </is>
       </c>
       <c r="H405" s="6" t="n">
-        <v>-629893</v>
+        <v>-473742856</v>
       </c>
       <c r="I405" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1283784</t>
+          <t>Rechazo PMP1283500</t>
         </is>
       </c>
     </row>
@@ -9228,11 +9224,11 @@
       </c>
       <c r="D406" s="10" t="inlineStr">
         <is>
-          <t>PMP1283785</t>
+          <t>PMP1283784</t>
         </is>
       </c>
       <c r="E406" s="6" t="n">
-        <v>-160273</v>
+        <v>-629893</v>
       </c>
       <c r="F406" s="10" t="inlineStr">
         <is>
@@ -9245,11 +9241,11 @@
         </is>
       </c>
       <c r="H406" s="6" t="n">
-        <v>-160273</v>
+        <v>-629893</v>
       </c>
       <c r="I406" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1283785</t>
+          <t>Rechazo PMP1283784</t>
         </is>
       </c>
     </row>
@@ -9261,11 +9257,11 @@
       </c>
       <c r="D407" s="10" t="inlineStr">
         <is>
-          <t>PMP1284114</t>
+          <t>PMP1283785</t>
         </is>
       </c>
       <c r="E407" s="6" t="n">
-        <v>-764103</v>
+        <v>-160273</v>
       </c>
       <c r="F407" s="10" t="inlineStr">
         <is>
@@ -9278,11 +9274,11 @@
         </is>
       </c>
       <c r="H407" s="6" t="n">
-        <v>-764103</v>
+        <v>-160273</v>
       </c>
       <c r="I407" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284114</t>
+          <t>Rechazo PMP1283785</t>
         </is>
       </c>
     </row>
@@ -9294,11 +9290,11 @@
       </c>
       <c r="D408" s="10" t="inlineStr">
         <is>
-          <t>PMP1284117</t>
+          <t>PMP1284114</t>
         </is>
       </c>
       <c r="E408" s="6" t="n">
-        <v>-177051</v>
+        <v>-764103</v>
       </c>
       <c r="F408" s="10" t="inlineStr">
         <is>
@@ -9311,11 +9307,11 @@
         </is>
       </c>
       <c r="H408" s="6" t="n">
-        <v>-177051</v>
+        <v>-764103</v>
       </c>
       <c r="I408" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284117</t>
+          <t>Rechazo PMP1284114</t>
         </is>
       </c>
     </row>
@@ -9327,11 +9323,11 @@
       </c>
       <c r="D409" s="10" t="inlineStr">
         <is>
-          <t>PMP1284119</t>
+          <t>PMP1284117</t>
         </is>
       </c>
       <c r="E409" s="6" t="n">
-        <v>-644997</v>
+        <v>-177051</v>
       </c>
       <c r="F409" s="10" t="inlineStr">
         <is>
@@ -9344,11 +9340,11 @@
         </is>
       </c>
       <c r="H409" s="6" t="n">
-        <v>-644997</v>
+        <v>-177051</v>
       </c>
       <c r="I409" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284119</t>
+          <t>Rechazo PMP1284117</t>
         </is>
       </c>
     </row>
@@ -9360,11 +9356,11 @@
       </c>
       <c r="D410" s="10" t="inlineStr">
         <is>
-          <t>PMP1284200</t>
+          <t>PMP1284119</t>
         </is>
       </c>
       <c r="E410" s="6" t="n">
-        <v>-175153</v>
+        <v>-644997</v>
       </c>
       <c r="F410" s="10" t="inlineStr">
         <is>
@@ -9377,11 +9373,11 @@
         </is>
       </c>
       <c r="H410" s="6" t="n">
-        <v>-175153</v>
+        <v>-644997</v>
       </c>
       <c r="I410" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284200</t>
+          <t>Rechazo PMP1284119</t>
         </is>
       </c>
     </row>
@@ -9393,11 +9389,11 @@
       </c>
       <c r="D411" s="10" t="inlineStr">
         <is>
-          <t>PMP1284460</t>
+          <t>PMP1284200</t>
         </is>
       </c>
       <c r="E411" s="6" t="n">
-        <v>-167879</v>
+        <v>-175153</v>
       </c>
       <c r="F411" s="10" t="inlineStr">
         <is>
@@ -9410,11 +9406,11 @@
         </is>
       </c>
       <c r="H411" s="6" t="n">
-        <v>-167879</v>
+        <v>-175153</v>
       </c>
       <c r="I411" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284460</t>
+          <t>Rechazo PMP1284200</t>
         </is>
       </c>
     </row>
@@ -9426,11 +9422,11 @@
       </c>
       <c r="D412" s="10" t="inlineStr">
         <is>
-          <t>PMP1284462</t>
+          <t>PMP1284460</t>
         </is>
       </c>
       <c r="E412" s="6" t="n">
-        <v>-322931</v>
+        <v>-167879</v>
       </c>
       <c r="F412" s="10" t="inlineStr">
         <is>
@@ -9443,11 +9439,11 @@
         </is>
       </c>
       <c r="H412" s="6" t="n">
-        <v>-322931</v>
+        <v>-167879</v>
       </c>
       <c r="I412" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284462</t>
+          <t>Rechazo PMP1284460</t>
         </is>
       </c>
     </row>
@@ -9459,11 +9455,11 @@
       </c>
       <c r="D413" s="10" t="inlineStr">
         <is>
-          <t>PMP1284529</t>
+          <t>PMP1284462</t>
         </is>
       </c>
       <c r="E413" s="6" t="n">
-        <v>-276742</v>
+        <v>-322931</v>
       </c>
       <c r="F413" s="10" t="inlineStr">
         <is>
@@ -9476,11 +9472,11 @@
         </is>
       </c>
       <c r="H413" s="6" t="n">
-        <v>-276742</v>
+        <v>-322931</v>
       </c>
       <c r="I413" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284529</t>
+          <t>Rechazo PMP1284462</t>
         </is>
       </c>
     </row>
@@ -9492,11 +9488,11 @@
       </c>
       <c r="D414" s="10" t="inlineStr">
         <is>
-          <t>PMP1284543</t>
+          <t>PMP1284529</t>
         </is>
       </c>
       <c r="E414" s="6" t="n">
-        <v>-3015665</v>
+        <v>-276742</v>
       </c>
       <c r="F414" s="10" t="inlineStr">
         <is>
@@ -9509,11 +9505,11 @@
         </is>
       </c>
       <c r="H414" s="6" t="n">
-        <v>-3015665</v>
+        <v>-276742</v>
       </c>
       <c r="I414" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284543</t>
+          <t>Rechazo PMP1284529</t>
         </is>
       </c>
     </row>
@@ -9525,11 +9521,11 @@
       </c>
       <c r="D415" s="10" t="inlineStr">
         <is>
-          <t>PMP1284546</t>
+          <t>PMP1284543</t>
         </is>
       </c>
       <c r="E415" s="6" t="n">
-        <v>-135409</v>
+        <v>-3015665</v>
       </c>
       <c r="F415" s="10" t="inlineStr">
         <is>
@@ -9542,11 +9538,11 @@
         </is>
       </c>
       <c r="H415" s="6" t="n">
-        <v>-135409</v>
+        <v>-3015665</v>
       </c>
       <c r="I415" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284546</t>
+          <t>Rechazo PMP1284543</t>
         </is>
       </c>
     </row>
@@ -9558,11 +9554,11 @@
       </c>
       <c r="D416" s="10" t="inlineStr">
         <is>
-          <t>PMP1284602</t>
+          <t>PMP1284546</t>
         </is>
       </c>
       <c r="E416" s="6" t="n">
-        <v>-930108</v>
+        <v>-135409</v>
       </c>
       <c r="F416" s="10" t="inlineStr">
         <is>
@@ -9575,11 +9571,11 @@
         </is>
       </c>
       <c r="H416" s="6" t="n">
-        <v>-930108</v>
+        <v>-135409</v>
       </c>
       <c r="I416" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284602</t>
+          <t>Rechazo PMP1284546</t>
         </is>
       </c>
     </row>
@@ -9591,11 +9587,11 @@
       </c>
       <c r="D417" s="10" t="inlineStr">
         <is>
-          <t>PMP1284750</t>
+          <t>PMP1284602</t>
         </is>
       </c>
       <c r="E417" s="6" t="n">
-        <v>-405708</v>
+        <v>-930108</v>
       </c>
       <c r="F417" s="10" t="inlineStr">
         <is>
@@ -9608,11 +9604,11 @@
         </is>
       </c>
       <c r="H417" s="6" t="n">
-        <v>-405708</v>
+        <v>-930108</v>
       </c>
       <c r="I417" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284750</t>
+          <t>Rechazo PMP1284602</t>
         </is>
       </c>
     </row>
@@ -9624,11 +9620,11 @@
       </c>
       <c r="D418" s="10" t="inlineStr">
         <is>
-          <t>PMP1284800</t>
+          <t>PMP1284750</t>
         </is>
       </c>
       <c r="E418" s="6" t="n">
-        <v>-635980</v>
+        <v>-405708</v>
       </c>
       <c r="F418" s="10" t="inlineStr">
         <is>
@@ -9641,11 +9637,11 @@
         </is>
       </c>
       <c r="H418" s="6" t="n">
-        <v>-635980</v>
+        <v>-405708</v>
       </c>
       <c r="I418" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284800</t>
+          <t>Rechazo PMP1284750</t>
         </is>
       </c>
     </row>
@@ -9657,11 +9653,11 @@
       </c>
       <c r="D419" s="10" t="inlineStr">
         <is>
-          <t>PMP1284876</t>
+          <t>PMP1284800</t>
         </is>
       </c>
       <c r="E419" s="6" t="n">
-        <v>-689804</v>
+        <v>-635980</v>
       </c>
       <c r="F419" s="10" t="inlineStr">
         <is>
@@ -9674,11 +9670,11 @@
         </is>
       </c>
       <c r="H419" s="6" t="n">
-        <v>-689804</v>
+        <v>-635980</v>
       </c>
       <c r="I419" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284876</t>
+          <t>Rechazo PMP1284800</t>
         </is>
       </c>
     </row>
@@ -9690,11 +9686,11 @@
       </c>
       <c r="D420" s="10" t="inlineStr">
         <is>
-          <t>PMP1284878</t>
+          <t>PMP1284876</t>
         </is>
       </c>
       <c r="E420" s="6" t="n">
-        <v>-135533</v>
+        <v>-689804</v>
       </c>
       <c r="F420" s="10" t="inlineStr">
         <is>
@@ -9707,11 +9703,11 @@
         </is>
       </c>
       <c r="H420" s="6" t="n">
-        <v>-135533</v>
+        <v>-689804</v>
       </c>
       <c r="I420" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284878</t>
+          <t>Rechazo PMP1284876</t>
         </is>
       </c>
     </row>
@@ -9723,11 +9719,11 @@
       </c>
       <c r="D421" s="10" t="inlineStr">
         <is>
-          <t>PMP1284879</t>
+          <t>PMP1284878</t>
         </is>
       </c>
       <c r="E421" s="6" t="n">
-        <v>-732728</v>
+        <v>-135533</v>
       </c>
       <c r="F421" s="10" t="inlineStr">
         <is>
@@ -9740,11 +9736,11 @@
         </is>
       </c>
       <c r="H421" s="6" t="n">
-        <v>-732728</v>
+        <v>-135533</v>
       </c>
       <c r="I421" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284879</t>
+          <t>Rechazo PMP1284878</t>
         </is>
       </c>
     </row>
@@ -9756,11 +9752,11 @@
       </c>
       <c r="D422" s="10" t="inlineStr">
         <is>
-          <t>PMP1284948</t>
+          <t>PMP1284879</t>
         </is>
       </c>
       <c r="E422" s="6" t="n">
-        <v>-1060968</v>
+        <v>-732728</v>
       </c>
       <c r="F422" s="10" t="inlineStr">
         <is>
@@ -9773,11 +9769,11 @@
         </is>
       </c>
       <c r="H422" s="6" t="n">
-        <v>-1060968</v>
+        <v>-732728</v>
       </c>
       <c r="I422" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284948</t>
+          <t>Rechazo PMP1284879</t>
         </is>
       </c>
     </row>
@@ -9789,11 +9785,11 @@
       </c>
       <c r="D423" s="10" t="inlineStr">
         <is>
-          <t>PMP1284949</t>
+          <t>PMP1284948</t>
         </is>
       </c>
       <c r="E423" s="6" t="n">
-        <v>-215248</v>
+        <v>-1060968</v>
       </c>
       <c r="F423" s="10" t="inlineStr">
         <is>
@@ -9806,11 +9802,11 @@
         </is>
       </c>
       <c r="H423" s="6" t="n">
-        <v>-215248</v>
+        <v>-1060968</v>
       </c>
       <c r="I423" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284949</t>
+          <t>Rechazo PMP1284948</t>
         </is>
       </c>
     </row>
@@ -9822,11 +9818,11 @@
       </c>
       <c r="D424" s="10" t="inlineStr">
         <is>
-          <t>PMP1284950</t>
+          <t>PMP1284949</t>
         </is>
       </c>
       <c r="E424" s="6" t="n">
-        <v>-1297475</v>
+        <v>-215248</v>
       </c>
       <c r="F424" s="10" t="inlineStr">
         <is>
@@ -9839,11 +9835,11 @@
         </is>
       </c>
       <c r="H424" s="6" t="n">
-        <v>-1297475</v>
+        <v>-215248</v>
       </c>
       <c r="I424" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284950</t>
+          <t>Rechazo PMP1284949</t>
         </is>
       </c>
     </row>
@@ -9855,11 +9851,11 @@
       </c>
       <c r="D425" s="10" t="inlineStr">
         <is>
-          <t>PMP1284951</t>
+          <t>PMP1284950</t>
         </is>
       </c>
       <c r="E425" s="6" t="n">
-        <v>-5702098</v>
+        <v>-1297475</v>
       </c>
       <c r="F425" s="10" t="inlineStr">
         <is>
@@ -9872,11 +9868,11 @@
         </is>
       </c>
       <c r="H425" s="6" t="n">
-        <v>-5702098</v>
+        <v>-1297475</v>
       </c>
       <c r="I425" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284951</t>
+          <t>Rechazo PMP1284950</t>
         </is>
       </c>
     </row>
@@ -9888,11 +9884,11 @@
       </c>
       <c r="D426" s="10" t="inlineStr">
         <is>
-          <t>PMP1285048</t>
+          <t>PMP1284951</t>
         </is>
       </c>
       <c r="E426" s="6" t="n">
-        <v>-221603</v>
+        <v>-5702098</v>
       </c>
       <c r="F426" s="10" t="inlineStr">
         <is>
@@ -9905,11 +9901,11 @@
         </is>
       </c>
       <c r="H426" s="6" t="n">
-        <v>-221603</v>
+        <v>-5702098</v>
       </c>
       <c r="I426" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285048</t>
+          <t>Rechazo PMP1284951</t>
         </is>
       </c>
     </row>
@@ -9921,11 +9917,11 @@
       </c>
       <c r="D427" s="10" t="inlineStr">
         <is>
-          <t>PMP1285059</t>
+          <t>PMP1285048</t>
         </is>
       </c>
       <c r="E427" s="6" t="n">
-        <v>-160294</v>
+        <v>-221603</v>
       </c>
       <c r="F427" s="10" t="inlineStr">
         <is>
@@ -9938,11 +9934,11 @@
         </is>
       </c>
       <c r="H427" s="6" t="n">
-        <v>-160294</v>
+        <v>-221603</v>
       </c>
       <c r="I427" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285059</t>
+          <t>Rechazo PMP1285048</t>
         </is>
       </c>
     </row>
@@ -9954,11 +9950,11 @@
       </c>
       <c r="D428" s="10" t="inlineStr">
         <is>
-          <t>PMP1285065</t>
+          <t>PMP1285059</t>
         </is>
       </c>
       <c r="E428" s="6" t="n">
-        <v>-107552</v>
+        <v>-160294</v>
       </c>
       <c r="F428" s="10" t="inlineStr">
         <is>
@@ -9971,11 +9967,11 @@
         </is>
       </c>
       <c r="H428" s="6" t="n">
-        <v>-107552</v>
+        <v>-160294</v>
       </c>
       <c r="I428" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285065</t>
+          <t>Rechazo PMP1285059</t>
         </is>
       </c>
     </row>
@@ -9987,11 +9983,11 @@
       </c>
       <c r="D429" s="10" t="inlineStr">
         <is>
-          <t>PMP1285067</t>
+          <t>PMP1285065</t>
         </is>
       </c>
       <c r="E429" s="6" t="n">
-        <v>-135307</v>
+        <v>-107552</v>
       </c>
       <c r="F429" s="10" t="inlineStr">
         <is>
@@ -10004,11 +10000,11 @@
         </is>
       </c>
       <c r="H429" s="6" t="n">
-        <v>-135307</v>
+        <v>-107552</v>
       </c>
       <c r="I429" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285067</t>
+          <t>Rechazo PMP1285065</t>
         </is>
       </c>
     </row>
@@ -10020,11 +10016,11 @@
       </c>
       <c r="D430" s="10" t="inlineStr">
         <is>
-          <t>PMP1285071</t>
+          <t>PMP1285067</t>
         </is>
       </c>
       <c r="E430" s="6" t="n">
-        <v>-419436</v>
+        <v>-135307</v>
       </c>
       <c r="F430" s="10" t="inlineStr">
         <is>
@@ -10037,11 +10033,11 @@
         </is>
       </c>
       <c r="H430" s="6" t="n">
-        <v>-419436</v>
+        <v>-135307</v>
       </c>
       <c r="I430" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285071</t>
+          <t>Rechazo PMP1285067</t>
         </is>
       </c>
     </row>
@@ -10053,11 +10049,11 @@
       </c>
       <c r="D431" s="10" t="inlineStr">
         <is>
-          <t>PMP1285653</t>
+          <t>PMP1285071</t>
         </is>
       </c>
       <c r="E431" s="6" t="n">
-        <v>-558246</v>
+        <v>-419436</v>
       </c>
       <c r="F431" s="10" t="inlineStr">
         <is>
@@ -10070,11 +10066,11 @@
         </is>
       </c>
       <c r="H431" s="6" t="n">
-        <v>-558246</v>
+        <v>-419436</v>
       </c>
       <c r="I431" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285653</t>
+          <t>Rechazo PMP1285071</t>
         </is>
       </c>
     </row>
@@ -10086,11 +10082,11 @@
       </c>
       <c r="D432" s="10" t="inlineStr">
         <is>
-          <t>PMP1285659</t>
+          <t>PMP1285653</t>
         </is>
       </c>
       <c r="E432" s="6" t="n">
-        <v>-311765</v>
+        <v>-558246</v>
       </c>
       <c r="F432" s="10" t="inlineStr">
         <is>
@@ -10103,11 +10099,11 @@
         </is>
       </c>
       <c r="H432" s="6" t="n">
-        <v>-311765</v>
+        <v>-558246</v>
       </c>
       <c r="I432" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285659</t>
+          <t>Rechazo PMP1285653</t>
         </is>
       </c>
     </row>
@@ -10119,11 +10115,11 @@
       </c>
       <c r="D433" s="10" t="inlineStr">
         <is>
-          <t>PMP1285725</t>
+          <t>PMP1285659</t>
         </is>
       </c>
       <c r="E433" s="6" t="n">
-        <v>-679290</v>
+        <v>-311765</v>
       </c>
       <c r="F433" s="10" t="inlineStr">
         <is>
@@ -10136,11 +10132,11 @@
         </is>
       </c>
       <c r="H433" s="6" t="n">
-        <v>-679290</v>
+        <v>-311765</v>
       </c>
       <c r="I433" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285725</t>
+          <t>Rechazo PMP1285659</t>
         </is>
       </c>
     </row>
@@ -10152,11 +10148,11 @@
       </c>
       <c r="D434" s="10" t="inlineStr">
         <is>
-          <t>PMP1285898</t>
+          <t>PMP1285725</t>
         </is>
       </c>
       <c r="E434" s="6" t="n">
-        <v>-253685</v>
+        <v>-679290</v>
       </c>
       <c r="F434" s="10" t="inlineStr">
         <is>
@@ -10169,11 +10165,11 @@
         </is>
       </c>
       <c r="H434" s="6" t="n">
-        <v>-253685</v>
+        <v>-679290</v>
       </c>
       <c r="I434" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285898</t>
+          <t>Rechazo PMP1285725</t>
         </is>
       </c>
     </row>
@@ -10185,11 +10181,11 @@
       </c>
       <c r="D435" s="10" t="inlineStr">
         <is>
-          <t>PMP1285903</t>
+          <t>PMP1285898</t>
         </is>
       </c>
       <c r="E435" s="6" t="n">
-        <v>-322554</v>
+        <v>-253685</v>
       </c>
       <c r="F435" s="10" t="inlineStr">
         <is>
@@ -10202,11 +10198,11 @@
         </is>
       </c>
       <c r="H435" s="6" t="n">
-        <v>-322554</v>
+        <v>-253685</v>
       </c>
       <c r="I435" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285903</t>
+          <t>Rechazo PMP1285898</t>
         </is>
       </c>
     </row>
@@ -10218,11 +10214,11 @@
       </c>
       <c r="D436" s="10" t="inlineStr">
         <is>
-          <t>PMP1285908</t>
+          <t>PMP1285903</t>
         </is>
       </c>
       <c r="E436" s="6" t="n">
-        <v>-135255</v>
+        <v>-322554</v>
       </c>
       <c r="F436" s="10" t="inlineStr">
         <is>
@@ -10235,11 +10231,11 @@
         </is>
       </c>
       <c r="H436" s="6" t="n">
-        <v>-135255</v>
+        <v>-322554</v>
       </c>
       <c r="I436" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285908</t>
+          <t>Rechazo PMP1285903</t>
         </is>
       </c>
     </row>
@@ -10251,11 +10247,11 @@
       </c>
       <c r="D437" s="10" t="inlineStr">
         <is>
-          <t>PMP1286056</t>
+          <t>PMP1285908</t>
         </is>
       </c>
       <c r="E437" s="6" t="n">
-        <v>-556413</v>
+        <v>-135255</v>
       </c>
       <c r="F437" s="10" t="inlineStr">
         <is>
@@ -10268,11 +10264,11 @@
         </is>
       </c>
       <c r="H437" s="6" t="n">
-        <v>-556413</v>
+        <v>-135255</v>
       </c>
       <c r="I437" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286056</t>
+          <t>Rechazo PMP1285908</t>
         </is>
       </c>
     </row>
@@ -10284,11 +10280,11 @@
       </c>
       <c r="D438" s="10" t="inlineStr">
         <is>
-          <t>PMP1286208</t>
+          <t>PMP1286056</t>
         </is>
       </c>
       <c r="E438" s="6" t="n">
-        <v>-949123</v>
+        <v>-556413</v>
       </c>
       <c r="F438" s="10" t="inlineStr">
         <is>
@@ -10301,11 +10297,11 @@
         </is>
       </c>
       <c r="H438" s="6" t="n">
-        <v>-949123</v>
+        <v>-556413</v>
       </c>
       <c r="I438" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286208</t>
+          <t>Rechazo PMP1286056</t>
         </is>
       </c>
     </row>
@@ -10317,11 +10313,11 @@
       </c>
       <c r="D439" s="10" t="inlineStr">
         <is>
-          <t>PMP1286554</t>
+          <t>PMP1286208</t>
         </is>
       </c>
       <c r="E439" s="6" t="n">
-        <v>-354934</v>
+        <v>-949123</v>
       </c>
       <c r="F439" s="10" t="inlineStr">
         <is>
@@ -10334,11 +10330,11 @@
         </is>
       </c>
       <c r="H439" s="6" t="n">
-        <v>-354934</v>
+        <v>-949123</v>
       </c>
       <c r="I439" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286554</t>
+          <t>Rechazo PMP1286208</t>
         </is>
       </c>
     </row>
@@ -10350,11 +10346,11 @@
       </c>
       <c r="D440" s="10" t="inlineStr">
         <is>
-          <t>PMP1286556</t>
+          <t>PMP1286554</t>
         </is>
       </c>
       <c r="E440" s="6" t="n">
-        <v>-364001</v>
+        <v>-354934</v>
       </c>
       <c r="F440" s="10" t="inlineStr">
         <is>
@@ -10367,11 +10363,11 @@
         </is>
       </c>
       <c r="H440" s="6" t="n">
-        <v>-364001</v>
+        <v>-354934</v>
       </c>
       <c r="I440" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286556</t>
+          <t>Rechazo PMP1286554</t>
         </is>
       </c>
     </row>
@@ -10383,11 +10379,11 @@
       </c>
       <c r="D441" s="10" t="inlineStr">
         <is>
-          <t>PMP1286709</t>
+          <t>PMP1286556</t>
         </is>
       </c>
       <c r="E441" s="6" t="n">
-        <v>-33537478</v>
+        <v>-364001</v>
       </c>
       <c r="F441" s="10" t="inlineStr">
         <is>
@@ -10400,11 +10396,11 @@
         </is>
       </c>
       <c r="H441" s="6" t="n">
-        <v>-33537478</v>
+        <v>-364001</v>
       </c>
       <c r="I441" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286709</t>
+          <t>Rechazo PMP1286556</t>
         </is>
       </c>
     </row>
@@ -10416,11 +10412,11 @@
       </c>
       <c r="D442" s="10" t="inlineStr">
         <is>
-          <t>PMP1286710</t>
+          <t>PMP1286709</t>
         </is>
       </c>
       <c r="E442" s="6" t="n">
-        <v>-650618</v>
+        <v>-33537478</v>
       </c>
       <c r="F442" s="10" t="inlineStr">
         <is>
@@ -10433,11 +10429,11 @@
         </is>
       </c>
       <c r="H442" s="6" t="n">
-        <v>-650618</v>
+        <v>-33537478</v>
       </c>
       <c r="I442" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286710</t>
+          <t>Rechazo PMP1286709</t>
         </is>
       </c>
     </row>
@@ -10449,11 +10445,11 @@
       </c>
       <c r="D443" s="10" t="inlineStr">
         <is>
-          <t>PMP1286711</t>
+          <t>PMP1286710</t>
         </is>
       </c>
       <c r="E443" s="6" t="n">
-        <v>-6920570</v>
+        <v>-650618</v>
       </c>
       <c r="F443" s="10" t="inlineStr">
         <is>
@@ -10466,11 +10462,11 @@
         </is>
       </c>
       <c r="H443" s="6" t="n">
-        <v>-6920570</v>
+        <v>-650618</v>
       </c>
       <c r="I443" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286711</t>
+          <t>Rechazo PMP1286710</t>
         </is>
       </c>
     </row>
@@ -10482,11 +10478,11 @@
       </c>
       <c r="D444" s="10" t="inlineStr">
         <is>
-          <t>PMP1286712</t>
+          <t>PMP1286711</t>
         </is>
       </c>
       <c r="E444" s="6" t="n">
-        <v>-403395</v>
+        <v>-6920570</v>
       </c>
       <c r="F444" s="10" t="inlineStr">
         <is>
@@ -10499,11 +10495,11 @@
         </is>
       </c>
       <c r="H444" s="6" t="n">
-        <v>-403395</v>
+        <v>-6920570</v>
       </c>
       <c r="I444" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286712</t>
+          <t>Rechazo PMP1286711</t>
         </is>
       </c>
     </row>
@@ -10515,11 +10511,11 @@
       </c>
       <c r="D445" s="10" t="inlineStr">
         <is>
-          <t>PMP1286715</t>
+          <t>PMP1286712</t>
         </is>
       </c>
       <c r="E445" s="6" t="n">
-        <v>-4085189</v>
+        <v>-403395</v>
       </c>
       <c r="F445" s="10" t="inlineStr">
         <is>
@@ -10532,11 +10528,11 @@
         </is>
       </c>
       <c r="H445" s="6" t="n">
-        <v>-4085189</v>
+        <v>-403395</v>
       </c>
       <c r="I445" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286715</t>
+          <t>Rechazo PMP1286712</t>
         </is>
       </c>
     </row>
@@ -10548,11 +10544,11 @@
       </c>
       <c r="D446" s="10" t="inlineStr">
         <is>
-          <t>PMP1286716</t>
+          <t>PMP1286715</t>
         </is>
       </c>
       <c r="E446" s="6" t="n">
-        <v>-822039</v>
+        <v>-4085189</v>
       </c>
       <c r="F446" s="10" t="inlineStr">
         <is>
@@ -10565,11 +10561,11 @@
         </is>
       </c>
       <c r="H446" s="6" t="n">
-        <v>-822039</v>
+        <v>-4085189</v>
       </c>
       <c r="I446" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286716</t>
+          <t>Rechazo PMP1286715</t>
         </is>
       </c>
     </row>
@@ -10581,11 +10577,11 @@
       </c>
       <c r="D447" s="10" t="inlineStr">
         <is>
-          <t>PMP1287257</t>
+          <t>PMP1286716</t>
         </is>
       </c>
       <c r="E447" s="6" t="n">
-        <v>-156625</v>
+        <v>-822039</v>
       </c>
       <c r="F447" s="10" t="inlineStr">
         <is>
@@ -10598,11 +10594,11 @@
         </is>
       </c>
       <c r="H447" s="6" t="n">
-        <v>-156625</v>
+        <v>-822039</v>
       </c>
       <c r="I447" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287257</t>
+          <t>Rechazo PMP1286716</t>
         </is>
       </c>
     </row>
@@ -10614,11 +10610,11 @@
       </c>
       <c r="D448" s="10" t="inlineStr">
         <is>
-          <t>PMP1287321</t>
+          <t>PMP1287257</t>
         </is>
       </c>
       <c r="E448" s="6" t="n">
-        <v>-182163</v>
+        <v>-156625</v>
       </c>
       <c r="F448" s="10" t="inlineStr">
         <is>
@@ -10631,11 +10627,11 @@
         </is>
       </c>
       <c r="H448" s="6" t="n">
-        <v>-182163</v>
+        <v>-156625</v>
       </c>
       <c r="I448" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287321</t>
+          <t>Rechazo PMP1287257</t>
         </is>
       </c>
     </row>
@@ -10647,11 +10643,11 @@
       </c>
       <c r="D449" s="10" t="inlineStr">
         <is>
-          <t>PMP1287325</t>
+          <t>PMP1287321</t>
         </is>
       </c>
       <c r="E449" s="6" t="n">
-        <v>-118625</v>
+        <v>-182163</v>
       </c>
       <c r="F449" s="10" t="inlineStr">
         <is>
@@ -10664,11 +10660,11 @@
         </is>
       </c>
       <c r="H449" s="6" t="n">
-        <v>-118625</v>
+        <v>-182163</v>
       </c>
       <c r="I449" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287325</t>
+          <t>Rechazo PMP1287321</t>
         </is>
       </c>
     </row>
@@ -10680,11 +10676,11 @@
       </c>
       <c r="D450" s="10" t="inlineStr">
         <is>
-          <t>PMP1287335</t>
+          <t>PMP1287325</t>
         </is>
       </c>
       <c r="E450" s="6" t="n">
-        <v>-128620</v>
+        <v>-118625</v>
       </c>
       <c r="F450" s="10" t="inlineStr">
         <is>
@@ -10697,11 +10693,11 @@
         </is>
       </c>
       <c r="H450" s="6" t="n">
-        <v>-128620</v>
+        <v>-118625</v>
       </c>
       <c r="I450" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287335</t>
+          <t>Rechazo PMP1287325</t>
         </is>
       </c>
     </row>
@@ -10713,11 +10709,11 @@
       </c>
       <c r="D451" s="10" t="inlineStr">
         <is>
-          <t>PMP1287379</t>
+          <t>PMP1287335</t>
         </is>
       </c>
       <c r="E451" s="6" t="n">
-        <v>-271757</v>
+        <v>-128620</v>
       </c>
       <c r="F451" s="10" t="inlineStr">
         <is>
@@ -10730,11 +10726,11 @@
         </is>
       </c>
       <c r="H451" s="6" t="n">
-        <v>-271757</v>
+        <v>-128620</v>
       </c>
       <c r="I451" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287379</t>
+          <t>Rechazo PMP1287335</t>
         </is>
       </c>
     </row>
@@ -10746,11 +10742,11 @@
       </c>
       <c r="D452" s="10" t="inlineStr">
         <is>
-          <t>PMP1287385</t>
+          <t>PMP1287379</t>
         </is>
       </c>
       <c r="E452" s="6" t="n">
-        <v>-214996</v>
+        <v>-271757</v>
       </c>
       <c r="F452" s="10" t="inlineStr">
         <is>
@@ -10763,11 +10759,11 @@
         </is>
       </c>
       <c r="H452" s="6" t="n">
-        <v>-214996</v>
+        <v>-271757</v>
       </c>
       <c r="I452" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287385</t>
+          <t>Rechazo PMP1287379</t>
         </is>
       </c>
     </row>
@@ -10779,11 +10775,11 @@
       </c>
       <c r="D453" s="10" t="inlineStr">
         <is>
-          <t>PMP1287386</t>
+          <t>PMP1287385</t>
         </is>
       </c>
       <c r="E453" s="6" t="n">
-        <v>-267680</v>
+        <v>-214996</v>
       </c>
       <c r="F453" s="10" t="inlineStr">
         <is>
@@ -10796,11 +10792,11 @@
         </is>
       </c>
       <c r="H453" s="6" t="n">
-        <v>-267680</v>
+        <v>-214996</v>
       </c>
       <c r="I453" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287386</t>
+          <t>Rechazo PMP1287385</t>
         </is>
       </c>
     </row>
@@ -10812,11 +10808,11 @@
       </c>
       <c r="D454" s="10" t="inlineStr">
         <is>
-          <t>PMP1287574</t>
+          <t>PMP1287386</t>
         </is>
       </c>
       <c r="E454" s="6" t="n">
-        <v>-11940004</v>
+        <v>-267680</v>
       </c>
       <c r="F454" s="10" t="inlineStr">
         <is>
@@ -10829,11 +10825,11 @@
         </is>
       </c>
       <c r="H454" s="6" t="n">
-        <v>-11940004</v>
+        <v>-267680</v>
       </c>
       <c r="I454" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287574</t>
+          <t>Rechazo PMP1287386</t>
         </is>
       </c>
     </row>
@@ -10845,11 +10841,11 @@
       </c>
       <c r="D455" s="10" t="inlineStr">
         <is>
-          <t>PMP1287736</t>
+          <t>PMP1287574</t>
         </is>
       </c>
       <c r="E455" s="6" t="n">
-        <v>-93440</v>
+        <v>-11940004</v>
       </c>
       <c r="F455" s="10" t="inlineStr">
         <is>
@@ -10862,11 +10858,11 @@
         </is>
       </c>
       <c r="H455" s="6" t="n">
-        <v>-93440</v>
+        <v>-11940004</v>
       </c>
       <c r="I455" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287736</t>
+          <t>Rechazo PMP1287574</t>
         </is>
       </c>
     </row>
@@ -10878,11 +10874,11 @@
       </c>
       <c r="D456" s="10" t="inlineStr">
         <is>
-          <t>PMP128777746</t>
+          <t>PMP1287736</t>
         </is>
       </c>
       <c r="E456" s="6" t="n">
-        <v>-322500</v>
+        <v>-93440</v>
       </c>
       <c r="F456" s="10" t="inlineStr">
         <is>
@@ -10895,11 +10891,11 @@
         </is>
       </c>
       <c r="H456" s="6" t="n">
-        <v>-322500</v>
+        <v>-93440</v>
       </c>
       <c r="I456" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP128777746</t>
+          <t>Rechazo PMP1287736</t>
         </is>
       </c>
     </row>
@@ -10911,11 +10907,11 @@
       </c>
       <c r="D457" s="10" t="inlineStr">
         <is>
-          <t>PMP1287829</t>
+          <t>PMP128777746</t>
         </is>
       </c>
       <c r="E457" s="6" t="n">
-        <v>-290823</v>
+        <v>-322500</v>
       </c>
       <c r="F457" s="10" t="inlineStr">
         <is>
@@ -10928,11 +10924,11 @@
         </is>
       </c>
       <c r="H457" s="6" t="n">
-        <v>-290823</v>
+        <v>-322500</v>
       </c>
       <c r="I457" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287829</t>
+          <t>Rechazo PMP128777746</t>
         </is>
       </c>
     </row>
@@ -10944,11 +10940,11 @@
       </c>
       <c r="D458" s="10" t="inlineStr">
         <is>
-          <t>PMP1287903</t>
+          <t>PMP1287829</t>
         </is>
       </c>
       <c r="E458" s="6" t="n">
-        <v>-128514</v>
+        <v>-290823</v>
       </c>
       <c r="F458" s="10" t="inlineStr">
         <is>
@@ -10961,11 +10957,11 @@
         </is>
       </c>
       <c r="H458" s="6" t="n">
-        <v>-128514</v>
+        <v>-290823</v>
       </c>
       <c r="I458" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287903</t>
+          <t>Rechazo PMP1287829</t>
         </is>
       </c>
     </row>
@@ -10977,11 +10973,11 @@
       </c>
       <c r="D459" s="10" t="inlineStr">
         <is>
-          <t>PMP1287904</t>
+          <t>PMP1287903</t>
         </is>
       </c>
       <c r="E459" s="6" t="n">
-        <v>-80064</v>
+        <v>-128514</v>
       </c>
       <c r="F459" s="10" t="inlineStr">
         <is>
@@ -10994,11 +10990,11 @@
         </is>
       </c>
       <c r="H459" s="6" t="n">
-        <v>-80064</v>
+        <v>-128514</v>
       </c>
       <c r="I459" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287904</t>
+          <t>Rechazo PMP1287903</t>
         </is>
       </c>
     </row>
@@ -11010,11 +11006,11 @@
       </c>
       <c r="D460" s="10" t="inlineStr">
         <is>
-          <t>PMP1287920</t>
+          <t>PMP1287904</t>
         </is>
       </c>
       <c r="E460" s="6" t="n">
-        <v>-582605</v>
+        <v>-80064</v>
       </c>
       <c r="F460" s="10" t="inlineStr">
         <is>
@@ -11027,11 +11023,11 @@
         </is>
       </c>
       <c r="H460" s="6" t="n">
-        <v>-582605</v>
+        <v>-80064</v>
       </c>
       <c r="I460" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287920</t>
+          <t>Rechazo PMP1287904</t>
         </is>
       </c>
     </row>
@@ -11043,11 +11039,11 @@
       </c>
       <c r="D461" s="10" t="inlineStr">
         <is>
-          <t>PMP1287921</t>
+          <t>PMP1287920</t>
         </is>
       </c>
       <c r="E461" s="6" t="n">
-        <v>-124374</v>
+        <v>-582605</v>
       </c>
       <c r="F461" s="10" t="inlineStr">
         <is>
@@ -11060,11 +11056,11 @@
         </is>
       </c>
       <c r="H461" s="6" t="n">
-        <v>-124374</v>
+        <v>-582605</v>
       </c>
       <c r="I461" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287921</t>
+          <t>Rechazo PMP1287920</t>
         </is>
       </c>
     </row>
@@ -11076,11 +11072,11 @@
       </c>
       <c r="D462" s="10" t="inlineStr">
         <is>
-          <t>PMP1287928</t>
+          <t>PMP1287921</t>
         </is>
       </c>
       <c r="E462" s="6" t="n">
-        <v>-246230</v>
+        <v>-124374</v>
       </c>
       <c r="F462" s="10" t="inlineStr">
         <is>
@@ -11093,11 +11089,11 @@
         </is>
       </c>
       <c r="H462" s="6" t="n">
-        <v>-246230</v>
+        <v>-124374</v>
       </c>
       <c r="I462" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287928</t>
+          <t>Rechazo PMP1287921</t>
         </is>
       </c>
     </row>
@@ -11109,11 +11105,11 @@
       </c>
       <c r="D463" s="10" t="inlineStr">
         <is>
-          <t>PMP1287930</t>
+          <t>PMP1287928</t>
         </is>
       </c>
       <c r="E463" s="6" t="n">
-        <v>-91079</v>
+        <v>-246230</v>
       </c>
       <c r="F463" s="10" t="inlineStr">
         <is>
@@ -11126,11 +11122,11 @@
         </is>
       </c>
       <c r="H463" s="6" t="n">
-        <v>-91079</v>
+        <v>-246230</v>
       </c>
       <c r="I463" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287930</t>
+          <t>Rechazo PMP1287928</t>
         </is>
       </c>
     </row>
@@ -11142,11 +11138,11 @@
       </c>
       <c r="D464" s="10" t="inlineStr">
         <is>
-          <t>PMP1287931</t>
+          <t>PMP1287930</t>
         </is>
       </c>
       <c r="E464" s="6" t="n">
-        <v>-215025</v>
+        <v>-91079</v>
       </c>
       <c r="F464" s="10" t="inlineStr">
         <is>
@@ -11159,11 +11155,11 @@
         </is>
       </c>
       <c r="H464" s="6" t="n">
-        <v>-215025</v>
+        <v>-91079</v>
       </c>
       <c r="I464" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287931</t>
+          <t>Rechazo PMP1287930</t>
         </is>
       </c>
     </row>
@@ -11175,11 +11171,11 @@
       </c>
       <c r="D465" s="10" t="inlineStr">
         <is>
-          <t>PMP1287948</t>
+          <t>PMP1287931</t>
         </is>
       </c>
       <c r="E465" s="6" t="n">
-        <v>-354871</v>
+        <v>-215025</v>
       </c>
       <c r="F465" s="10" t="inlineStr">
         <is>
@@ -11192,11 +11188,11 @@
         </is>
       </c>
       <c r="H465" s="6" t="n">
-        <v>-354871</v>
+        <v>-215025</v>
       </c>
       <c r="I465" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287948</t>
+          <t>Rechazo PMP1287931</t>
         </is>
       </c>
     </row>
@@ -11208,11 +11204,11 @@
       </c>
       <c r="D466" s="10" t="inlineStr">
         <is>
-          <t>PMP1287949</t>
+          <t>PMP1287948</t>
         </is>
       </c>
       <c r="E466" s="6" t="n">
-        <v>-410669</v>
+        <v>-354871</v>
       </c>
       <c r="F466" s="10" t="inlineStr">
         <is>
@@ -11225,11 +11221,11 @@
         </is>
       </c>
       <c r="H466" s="6" t="n">
-        <v>-410669</v>
+        <v>-354871</v>
       </c>
       <c r="I466" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287949</t>
+          <t>Rechazo PMP1287948</t>
         </is>
       </c>
     </row>
@@ -11241,11 +11237,11 @@
       </c>
       <c r="D467" s="10" t="inlineStr">
         <is>
-          <t>PMP1287951</t>
+          <t>PMP1287949</t>
         </is>
       </c>
       <c r="E467" s="6" t="n">
-        <v>-29456389</v>
+        <v>-410669</v>
       </c>
       <c r="F467" s="10" t="inlineStr">
         <is>
@@ -11258,11 +11254,11 @@
         </is>
       </c>
       <c r="H467" s="6" t="n">
-        <v>-29456389</v>
+        <v>-410669</v>
       </c>
       <c r="I467" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287951</t>
+          <t>Rechazo PMP1287949</t>
         </is>
       </c>
     </row>
@@ -11274,11 +11270,11 @@
       </c>
       <c r="D468" s="10" t="inlineStr">
         <is>
-          <t>PMP1287957</t>
+          <t>PMP1287951</t>
         </is>
       </c>
       <c r="E468" s="6" t="n">
-        <v>-107492</v>
+        <v>-29456389</v>
       </c>
       <c r="F468" s="10" t="inlineStr">
         <is>
@@ -11291,11 +11287,11 @@
         </is>
       </c>
       <c r="H468" s="6" t="n">
-        <v>-107492</v>
+        <v>-29456389</v>
       </c>
       <c r="I468" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287957</t>
+          <t>Rechazo PMP1287951</t>
         </is>
       </c>
     </row>
@@ -11307,11 +11303,11 @@
       </c>
       <c r="D469" s="10" t="inlineStr">
         <is>
-          <t>PMP1288418</t>
+          <t>PMP1287957</t>
         </is>
       </c>
       <c r="E469" s="6" t="n">
-        <v>-2183651</v>
+        <v>-107492</v>
       </c>
       <c r="F469" s="10" t="inlineStr">
         <is>
@@ -11324,11 +11320,11 @@
         </is>
       </c>
       <c r="H469" s="6" t="n">
-        <v>-2183651</v>
+        <v>-107492</v>
       </c>
       <c r="I469" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288418</t>
+          <t>Rechazo PMP1287957</t>
         </is>
       </c>
     </row>
@@ -11340,11 +11336,11 @@
       </c>
       <c r="D470" s="10" t="inlineStr">
         <is>
-          <t>PMP1288731</t>
+          <t>PMP1288418</t>
         </is>
       </c>
       <c r="E470" s="6" t="n">
-        <v>-160222</v>
+        <v>-2183651</v>
       </c>
       <c r="F470" s="10" t="inlineStr">
         <is>
@@ -11357,11 +11353,11 @@
         </is>
       </c>
       <c r="H470" s="6" t="n">
-        <v>-160222</v>
+        <v>-2183651</v>
       </c>
       <c r="I470" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288731</t>
+          <t>Rechazo PMP1288418</t>
         </is>
       </c>
     </row>
@@ -11373,11 +11369,11 @@
       </c>
       <c r="D471" s="10" t="inlineStr">
         <is>
-          <t>PMP1288919</t>
+          <t>PMP1288731</t>
         </is>
       </c>
       <c r="E471" s="6" t="n">
-        <v>-9852</v>
+        <v>-160222</v>
       </c>
       <c r="F471" s="10" t="inlineStr">
         <is>
@@ -11390,11 +11386,11 @@
         </is>
       </c>
       <c r="H471" s="6" t="n">
-        <v>-9852</v>
+        <v>-160222</v>
       </c>
       <c r="I471" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288919</t>
+          <t>Rechazo PMP1288731</t>
         </is>
       </c>
     </row>
@@ -11406,11 +11402,11 @@
       </c>
       <c r="D472" s="10" t="inlineStr">
         <is>
-          <t>PMP1288926</t>
+          <t>PMP1288919</t>
         </is>
       </c>
       <c r="E472" s="6" t="n">
-        <v>-322749</v>
+        <v>-9852</v>
       </c>
       <c r="F472" s="10" t="inlineStr">
         <is>
@@ -11423,11 +11419,11 @@
         </is>
       </c>
       <c r="H472" s="6" t="n">
-        <v>-322749</v>
+        <v>-9852</v>
       </c>
       <c r="I472" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288926</t>
+          <t>Rechazo PMP1288919</t>
         </is>
       </c>
     </row>
@@ -11439,11 +11435,11 @@
       </c>
       <c r="D473" s="10" t="inlineStr">
         <is>
-          <t>PMP1288987</t>
+          <t>PMP1288926</t>
         </is>
       </c>
       <c r="E473" s="6" t="n">
-        <v>-1106307</v>
+        <v>-322749</v>
       </c>
       <c r="F473" s="10" t="inlineStr">
         <is>
@@ -11456,11 +11452,11 @@
         </is>
       </c>
       <c r="H473" s="6" t="n">
-        <v>-1106307</v>
+        <v>-322749</v>
       </c>
       <c r="I473" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288987</t>
+          <t>Rechazo PMP1288926</t>
         </is>
       </c>
     </row>
@@ -11472,11 +11468,11 @@
       </c>
       <c r="D474" s="10" t="inlineStr">
         <is>
-          <t>PMP1288988</t>
+          <t>PMP1288987</t>
         </is>
       </c>
       <c r="E474" s="6" t="n">
-        <v>-33894</v>
+        <v>-1106307</v>
       </c>
       <c r="F474" s="10" t="inlineStr">
         <is>
@@ -11489,11 +11485,11 @@
         </is>
       </c>
       <c r="H474" s="6" t="n">
-        <v>-33894</v>
+        <v>-1106307</v>
       </c>
       <c r="I474" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288988</t>
+          <t>Rechazo PMP1288987</t>
         </is>
       </c>
     </row>
@@ -11505,11 +11501,11 @@
       </c>
       <c r="D475" s="10" t="inlineStr">
         <is>
-          <t>PMP1288989</t>
+          <t>PMP1288988</t>
         </is>
       </c>
       <c r="E475" s="6" t="n">
-        <v>-2259163</v>
+        <v>-33894</v>
       </c>
       <c r="F475" s="10" t="inlineStr">
         <is>
@@ -11522,11 +11518,11 @@
         </is>
       </c>
       <c r="H475" s="6" t="n">
-        <v>-2259163</v>
+        <v>-33894</v>
       </c>
       <c r="I475" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288989</t>
+          <t>Rechazo PMP1288988</t>
         </is>
       </c>
     </row>
@@ -11538,11 +11534,11 @@
       </c>
       <c r="D476" s="10" t="inlineStr">
         <is>
-          <t>PMP1289251</t>
+          <t>PMP1288989</t>
         </is>
       </c>
       <c r="E476" s="6" t="n">
-        <v>-200703</v>
+        <v>-2259163</v>
       </c>
       <c r="F476" s="10" t="inlineStr">
         <is>
@@ -11555,11 +11551,11 @@
         </is>
       </c>
       <c r="H476" s="6" t="n">
-        <v>-200703</v>
+        <v>-2259163</v>
       </c>
       <c r="I476" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1289251</t>
+          <t>Rechazo PMP1288989</t>
         </is>
       </c>
     </row>
@@ -11571,11 +11567,11 @@
       </c>
       <c r="D477" s="10" t="inlineStr">
         <is>
-          <t>PMP1289253</t>
+          <t>PMP1289251</t>
         </is>
       </c>
       <c r="E477" s="6" t="n">
-        <v>-2482097</v>
+        <v>-200703</v>
       </c>
       <c r="F477" s="10" t="inlineStr">
         <is>
@@ -11588,11 +11584,11 @@
         </is>
       </c>
       <c r="H477" s="6" t="n">
-        <v>-2482097</v>
+        <v>-200703</v>
       </c>
       <c r="I477" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1289253</t>
+          <t>Rechazo PMP1289251</t>
         </is>
       </c>
     </row>
@@ -11604,11 +11600,11 @@
       </c>
       <c r="D478" s="10" t="inlineStr">
         <is>
-          <t>PMP1289324</t>
+          <t>PMP1289253</t>
         </is>
       </c>
       <c r="E478" s="6" t="n">
-        <v>-532656</v>
+        <v>-2482097</v>
       </c>
       <c r="F478" s="10" t="inlineStr">
         <is>
@@ -11621,11 +11617,11 @@
         </is>
       </c>
       <c r="H478" s="6" t="n">
-        <v>-532656</v>
+        <v>-2482097</v>
       </c>
       <c r="I478" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1289324</t>
+          <t>Rechazo PMP1289253</t>
         </is>
       </c>
     </row>
@@ -11637,11 +11633,11 @@
       </c>
       <c r="D479" s="10" t="inlineStr">
         <is>
-          <t>PMP1289326</t>
+          <t>PMP1289324</t>
         </is>
       </c>
       <c r="E479" s="6" t="n">
-        <v>-523796</v>
+        <v>-532656</v>
       </c>
       <c r="F479" s="10" t="inlineStr">
         <is>
@@ -11654,11 +11650,11 @@
         </is>
       </c>
       <c r="H479" s="6" t="n">
-        <v>-523796</v>
+        <v>-532656</v>
       </c>
       <c r="I479" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1289326</t>
+          <t>Rechazo PMP1289324</t>
         </is>
       </c>
     </row>
@@ -11670,11 +11666,11 @@
       </c>
       <c r="D480" s="10" t="inlineStr">
         <is>
-          <t>PMP1289328</t>
+          <t>PMP1289326</t>
         </is>
       </c>
       <c r="E480" s="6" t="n">
-        <v>-303757</v>
+        <v>-523796</v>
       </c>
       <c r="F480" s="10" t="inlineStr">
         <is>
@@ -11687,11 +11683,11 @@
         </is>
       </c>
       <c r="H480" s="6" t="n">
-        <v>-303757</v>
+        <v>-523796</v>
       </c>
       <c r="I480" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1289328</t>
+          <t>Rechazo PMP1289326</t>
         </is>
       </c>
     </row>
@@ -11703,11 +11699,11 @@
       </c>
       <c r="D481" s="10" t="inlineStr">
         <is>
-          <t>PMP1289507</t>
+          <t>PMP1289328</t>
         </is>
       </c>
       <c r="E481" s="6" t="n">
-        <v>-160184</v>
+        <v>-303757</v>
       </c>
       <c r="F481" s="10" t="inlineStr">
         <is>
@@ -11720,11 +11716,11 @@
         </is>
       </c>
       <c r="H481" s="6" t="n">
-        <v>-160184</v>
+        <v>-303757</v>
       </c>
       <c r="I481" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1289507</t>
+          <t>Rechazo PMP1289328</t>
         </is>
       </c>
     </row>
@@ -11736,26 +11732,59 @@
       </c>
       <c r="D482" s="10" t="inlineStr">
         <is>
+          <t>PMP1289507</t>
+        </is>
+      </c>
+      <c r="E482" s="6" t="n">
+        <v>-160184</v>
+      </c>
+      <c r="F482" s="10" t="inlineStr">
+        <is>
+          <t>Rechazo</t>
+        </is>
+      </c>
+      <c r="G482" s="10" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="H482" s="6" t="n">
+        <v>-160184</v>
+      </c>
+      <c r="I482" s="11" t="inlineStr">
+        <is>
+          <t>Rechazo PMP1289507</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="C483" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos Clientes</t>
+        </is>
+      </c>
+      <c r="D483" s="10" t="inlineStr">
+        <is>
           <t>Costo de Transferen</t>
         </is>
       </c>
-      <c r="E482" s="6" t="n">
+      <c r="E483" s="6" t="n">
         <v>-3000</v>
       </c>
-      <c r="F482" s="10" t="inlineStr">
+      <c r="F483" s="10" t="inlineStr">
         <is>
           <t>Costo de Transferen</t>
         </is>
       </c>
-      <c r="G482" s="10" t="inlineStr">
+      <c r="G483" s="10" t="inlineStr">
         <is>
           <t>WOB</t>
         </is>
       </c>
-      <c r="H482" s="6" t="n">
+      <c r="H483" s="6" t="n">
         <v>-3000</v>
       </c>
-      <c r="I482" s="11" t="inlineStr">
+      <c r="I483" s="11" t="inlineStr">
         <is>
           <t>MENORES VALORES</t>
         </is>

--- a/Pruebas/Archivos/Template/Colombia/Template_HRC_Cenco.xlsx
+++ b/Pruebas/Archivos/Template/Colombia/Template_HRC_Cenco.xlsx
@@ -583,7 +583,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -8003,28 +8003,28 @@
       </c>
       <c r="D369" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO APERTURA</t>
+          <t>PMP1286553</t>
         </is>
       </c>
       <c r="E369" s="6" t="n">
-        <v>-8594192</v>
+        <v>5910047.02</v>
       </c>
       <c r="F369" s="10" t="inlineStr">
         <is>
-          <t>DROGUER</t>
+          <t>Myr Vlr Pagado</t>
         </is>
       </c>
       <c r="G369" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>388</t>
         </is>
       </c>
       <c r="H369" s="6" t="n">
-        <v>-8594192</v>
+        <v>5910047.02</v>
       </c>
       <c r="I369" s="11" t="inlineStr">
         <is>
-          <t>DAV DSCTO 20.251.100.200.165 DESCUENTO APERTURA DROGUER</t>
+          <t>Myr Vlr Pagado PMP1286553</t>
         </is>
       </c>
     </row>
@@ -8036,28 +8036,28 @@
       </c>
       <c r="D370" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO CALENDARI</t>
+          <t>PMP1282099</t>
         </is>
       </c>
       <c r="E370" s="6" t="n">
-        <v>-117913970</v>
+        <v>-307519</v>
       </c>
       <c r="F370" s="10" t="inlineStr">
         <is>
-          <t>DROGUER</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G370" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H370" s="6" t="n">
-        <v>-117913970</v>
+        <v>-307519</v>
       </c>
       <c r="I370" s="11" t="inlineStr">
         <is>
-          <t>DCA DSCTO 20.251.100.199.887 DESCUENTO CALENDARI DROGUER</t>
+          <t>Rechazo PMP1282099</t>
         </is>
       </c>
     </row>
@@ -8069,28 +8069,28 @@
       </c>
       <c r="D371" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO CALENDARI</t>
+          <t>PMP1282353</t>
         </is>
       </c>
       <c r="E371" s="6" t="n">
-        <v>-343622707</v>
+        <v>-2659670</v>
       </c>
       <c r="F371" s="10" t="inlineStr">
         <is>
-          <t>DROGUER</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G371" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H371" s="6" t="n">
-        <v>-343622707</v>
+        <v>-2659670</v>
       </c>
       <c r="I371" s="11" t="inlineStr">
         <is>
-          <t>DCA DSCTO 20.251.100.199.918 DESCUENTO CALENDARI DROGUER</t>
+          <t>Rechazo PMP1282353</t>
         </is>
       </c>
     </row>
@@ -8102,28 +8102,28 @@
       </c>
       <c r="D372" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO CALENDARI</t>
+          <t>PMP1282964</t>
         </is>
       </c>
       <c r="E372" s="6" t="n">
-        <v>-272000000</v>
+        <v>-185365</v>
       </c>
       <c r="F372" s="10" t="inlineStr">
         <is>
-          <t>DROGUER</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G372" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H372" s="6" t="n">
-        <v>-272000000</v>
+        <v>-185365</v>
       </c>
       <c r="I372" s="11" t="inlineStr">
         <is>
-          <t>DCA DSCTO 20.251.100.199.957 DESCUENTO CALENDARI DROGUER</t>
+          <t>Rechazo PMP1282964</t>
         </is>
       </c>
     </row>
@@ -8135,28 +8135,28 @@
       </c>
       <c r="D373" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO CALENDARI</t>
+          <t>PMP1283008</t>
         </is>
       </c>
       <c r="E373" s="6" t="n">
-        <v>-63971913</v>
+        <v>-9788</v>
       </c>
       <c r="F373" s="10" t="inlineStr">
         <is>
-          <t>DROGUER</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G373" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H373" s="6" t="n">
-        <v>-63971913</v>
+        <v>-9788</v>
       </c>
       <c r="I373" s="11" t="inlineStr">
         <is>
-          <t>DCA DSCTO 20.251.100.200.097 DESCUENTO CALENDARI DROGUER</t>
+          <t>Rechazo PMP1283008</t>
         </is>
       </c>
     </row>
@@ -8168,28 +8168,28 @@
       </c>
       <c r="D374" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO CALENDARI</t>
+          <t>PMP1283012</t>
         </is>
       </c>
       <c r="E374" s="6" t="n">
-        <v>-20000000</v>
+        <v>-167913</v>
       </c>
       <c r="F374" s="10" t="inlineStr">
         <is>
-          <t>DROGUER</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G374" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H374" s="6" t="n">
-        <v>-20000000</v>
+        <v>-167913</v>
       </c>
       <c r="I374" s="11" t="inlineStr">
         <is>
-          <t>DCA DSCTO 20.251.100.200.166 DESCUENTO CALENDARI DROGUER</t>
+          <t>Rechazo PMP1283012</t>
         </is>
       </c>
     </row>
@@ -8201,28 +8201,28 @@
       </c>
       <c r="D375" s="10" t="inlineStr">
         <is>
-          <t>DEVOLUCIONES</t>
+          <t>PMP1283476</t>
         </is>
       </c>
       <c r="E375" s="6" t="n">
-        <v>-3354641</v>
+        <v>-836339</v>
       </c>
       <c r="F375" s="10" t="inlineStr">
         <is>
-          <t>DROGUER</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G375" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H375" s="6" t="n">
-        <v>-3354641</v>
+        <v>-836339</v>
       </c>
       <c r="I375" s="11" t="inlineStr">
         <is>
-          <t>DND DSCTO 20.171.100.014.225 DEVOLUCIONES DROGUER</t>
+          <t>Rechazo PMP1283476</t>
         </is>
       </c>
     </row>
@@ -8234,28 +8234,28 @@
       </c>
       <c r="D376" s="10" t="inlineStr">
         <is>
-          <t>DEVOLUCIONES</t>
+          <t>PMP1283500</t>
         </is>
       </c>
       <c r="E376" s="6" t="n">
-        <v>-157710</v>
+        <v>-473742856</v>
       </c>
       <c r="F376" s="10" t="inlineStr">
         <is>
-          <t>DROGUER</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G376" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H376" s="6" t="n">
-        <v>-157710</v>
+        <v>-473742856</v>
       </c>
       <c r="I376" s="11" t="inlineStr">
         <is>
-          <t>DND DSCTO 20.181.100.045.651 DEVOLUCIONES DROGUER</t>
+          <t>Rechazo PMP1283500</t>
         </is>
       </c>
     </row>
@@ -8267,28 +8267,28 @@
       </c>
       <c r="D377" s="10" t="inlineStr">
         <is>
-          <t>DSTO COMERCIAL FIJO</t>
+          <t>PMP1283784</t>
         </is>
       </c>
       <c r="E377" s="6" t="n">
-        <v>-39137474</v>
+        <v>-629893</v>
       </c>
       <c r="F377" s="10" t="inlineStr">
         <is>
-          <t>DROGUER</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G377" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H377" s="6" t="n">
-        <v>-39137474</v>
+        <v>-629893</v>
       </c>
       <c r="I377" s="11" t="inlineStr">
         <is>
-          <t>DCF DSCTO 20.171.100.014.225 DSTO COMERCIAL FIJO DROGUER</t>
+          <t>Rechazo PMP1283784</t>
         </is>
       </c>
     </row>
@@ -8300,28 +8300,28 @@
       </c>
       <c r="D378" s="10" t="inlineStr">
         <is>
-          <t>DSTO COMERCIAL FIJO</t>
+          <t>PMP1283785</t>
         </is>
       </c>
       <c r="E378" s="6" t="n">
-        <v>-6254394</v>
+        <v>-160273</v>
       </c>
       <c r="F378" s="10" t="inlineStr">
         <is>
-          <t>DROGUER</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G378" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H378" s="6" t="n">
-        <v>-6254394</v>
+        <v>-160273</v>
       </c>
       <c r="I378" s="11" t="inlineStr">
         <is>
-          <t>DCF DSCTO 20.181.100.032.054 DSTO COMERCIAL FIJO DROGUER</t>
+          <t>Rechazo PMP1283785</t>
         </is>
       </c>
     </row>
@@ -8333,28 +8333,28 @@
       </c>
       <c r="D379" s="10" t="inlineStr">
         <is>
-          <t>DSTO COMERCIAL FIJO</t>
+          <t>PMP1284114</t>
         </is>
       </c>
       <c r="E379" s="6" t="n">
-        <v>-2891340</v>
+        <v>-764103</v>
       </c>
       <c r="F379" s="10" t="inlineStr">
         <is>
-          <t>DROGUER</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G379" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H379" s="6" t="n">
-        <v>-2891340</v>
+        <v>-764103</v>
       </c>
       <c r="I379" s="11" t="inlineStr">
         <is>
-          <t>DCF DSCTO 20.181.100.045.651 DSTO COMERCIAL FIJO DROGUER</t>
+          <t>Rechazo PMP1284114</t>
         </is>
       </c>
     </row>
@@ -8366,28 +8366,28 @@
       </c>
       <c r="D380" s="10" t="inlineStr">
         <is>
-          <t>DTO POR ESCALA VOLU</t>
+          <t>PMP1284117</t>
         </is>
       </c>
       <c r="E380" s="6" t="n">
-        <v>-69868245</v>
+        <v>-177051</v>
       </c>
       <c r="F380" s="10" t="inlineStr">
         <is>
-          <t>DROGUER</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G380" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H380" s="6" t="n">
-        <v>-69868245</v>
+        <v>-177051</v>
       </c>
       <c r="I380" s="11" t="inlineStr">
         <is>
-          <t>DEC DSCTO 20.251.100.199.283 DTO POR ESCALA VOLU DROGUER</t>
+          <t>Rechazo PMP1284117</t>
         </is>
       </c>
     </row>
@@ -8399,28 +8399,28 @@
       </c>
       <c r="D381" s="10" t="inlineStr">
         <is>
-          <t>VPP1 2004529</t>
+          <t>PMP1284119</t>
         </is>
       </c>
       <c r="E381" s="6" t="n">
-        <v>-57239000</v>
+        <v>-644997</v>
       </c>
       <c r="F381" s="10" t="inlineStr">
         <is>
-          <t>FACT PROVEED</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G381" s="10" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H381" s="6" t="n">
-        <v>-57239000</v>
+        <v>-644997</v>
       </c>
       <c r="I381" s="11" t="inlineStr">
         <is>
-          <t>VPP1 2004529</t>
+          <t>Rechazo PMP1284119</t>
         </is>
       </c>
     </row>
@@ -8432,28 +8432,28 @@
       </c>
       <c r="D382" s="10" t="inlineStr">
         <is>
-          <t>VPP1 2004621</t>
+          <t>PMP1284200</t>
         </is>
       </c>
       <c r="E382" s="6" t="n">
-        <v>-6426000</v>
+        <v>-175153</v>
       </c>
       <c r="F382" s="10" t="inlineStr">
         <is>
-          <t>FACT PROVEED</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G382" s="10" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H382" s="6" t="n">
-        <v>-6426000</v>
+        <v>-175153</v>
       </c>
       <c r="I382" s="11" t="inlineStr">
         <is>
-          <t>VPP1 2004621</t>
+          <t>Rechazo PMP1284200</t>
         </is>
       </c>
     </row>
@@ -8465,28 +8465,28 @@
       </c>
       <c r="D383" s="10" t="inlineStr">
         <is>
-          <t>VPP1 2004622</t>
+          <t>PMP1284460</t>
         </is>
       </c>
       <c r="E383" s="6" t="n">
-        <v>-41650000</v>
+        <v>-167879</v>
       </c>
       <c r="F383" s="10" t="inlineStr">
         <is>
-          <t>FACT PROVEED</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G383" s="10" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H383" s="6" t="n">
-        <v>-41650000</v>
+        <v>-167879</v>
       </c>
       <c r="I383" s="11" t="inlineStr">
         <is>
-          <t>VPP1 2004622</t>
+          <t>Rechazo PMP1284460</t>
         </is>
       </c>
     </row>
@@ -8498,28 +8498,28 @@
       </c>
       <c r="D384" s="10" t="inlineStr">
         <is>
-          <t>VPP2 2021716</t>
+          <t>PMP1284462</t>
         </is>
       </c>
       <c r="E384" s="6" t="n">
-        <v>-2507098292</v>
+        <v>-322931</v>
       </c>
       <c r="F384" s="10" t="inlineStr">
         <is>
-          <t>FACT PROVEED</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G384" s="10" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H384" s="6" t="n">
-        <v>-2507098292</v>
+        <v>-322931</v>
       </c>
       <c r="I384" s="11" t="inlineStr">
         <is>
-          <t>VPP2 2021716</t>
+          <t>Rechazo PMP1284462</t>
         </is>
       </c>
     </row>
@@ -8531,28 +8531,28 @@
       </c>
       <c r="D385" s="10" t="inlineStr">
         <is>
-          <t>VPP2 2022342</t>
+          <t>PMP1284529</t>
         </is>
       </c>
       <c r="E385" s="6" t="n">
-        <v>-1075965191</v>
+        <v>-276742</v>
       </c>
       <c r="F385" s="10" t="inlineStr">
         <is>
-          <t>FACT PROVEED</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G385" s="10" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H385" s="6" t="n">
-        <v>-1075965191</v>
+        <v>-276742</v>
       </c>
       <c r="I385" s="11" t="inlineStr">
         <is>
-          <t>VPP2 2022342</t>
+          <t>Rechazo PMP1284529</t>
         </is>
       </c>
     </row>
@@ -8564,28 +8564,28 @@
       </c>
       <c r="D386" s="10" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
+          <t>PMP1284543</t>
         </is>
       </c>
       <c r="E386" s="6" t="n">
-        <v>-37.26000004360685</v>
+        <v>-3015665</v>
       </c>
       <c r="F386" s="10" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G386" s="10" t="inlineStr">
         <is>
-          <t>CSR</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H386" s="6" t="n">
-        <v>-37.26000004360685</v>
+        <v>-3015665</v>
       </c>
       <c r="I386" s="11" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
+          <t>Rechazo PMP1284543</t>
         </is>
       </c>
     </row>
@@ -8597,28 +8597,28 @@
       </c>
       <c r="D387" s="10" t="inlineStr">
         <is>
-          <t>PMP1286054</t>
+          <t>PMP1284546</t>
         </is>
       </c>
       <c r="E387" s="6" t="n">
-        <v>-864163</v>
+        <v>-135409</v>
       </c>
       <c r="F387" s="10" t="inlineStr">
         <is>
-          <t>Menor Vlr Pagado</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G387" s="10" t="inlineStr">
         <is>
-          <t>CSR</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H387" s="6" t="n">
-        <v>-864163</v>
+        <v>-135409</v>
       </c>
       <c r="I387" s="11" t="inlineStr">
         <is>
-          <t>Menor Vlr Pagado PMP1286054</t>
+          <t>Rechazo PMP1284546</t>
         </is>
       </c>
     </row>
@@ -8630,28 +8630,28 @@
       </c>
       <c r="D388" s="10" t="inlineStr">
         <is>
-          <t>PMP1286550</t>
+          <t>PMP1284602</t>
         </is>
       </c>
       <c r="E388" s="6" t="n">
-        <v>-5910046.859999999</v>
+        <v>-930108</v>
       </c>
       <c r="F388" s="10" t="inlineStr">
         <is>
-          <t>Menor Vlr Pagado</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G388" s="10" t="inlineStr">
         <is>
-          <t>CSR</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H388" s="6" t="n">
-        <v>-5910046.859999999</v>
+        <v>-930108</v>
       </c>
       <c r="I388" s="11" t="inlineStr">
         <is>
-          <t>Menor Vlr Pagado PMP1286550</t>
+          <t>Rechazo PMP1284602</t>
         </is>
       </c>
     </row>
@@ -8663,28 +8663,28 @@
       </c>
       <c r="D389" s="10" t="inlineStr">
         <is>
-          <t>PMP1286553</t>
+          <t>PMP1284750</t>
         </is>
       </c>
       <c r="E389" s="6" t="n">
-        <v>5910047.02</v>
+        <v>-405708</v>
       </c>
       <c r="F389" s="10" t="inlineStr">
         <is>
-          <t>Myr Vlr Pagado</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G389" s="10" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H389" s="6" t="n">
-        <v>5910047.02</v>
+        <v>-405708</v>
       </c>
       <c r="I389" s="11" t="inlineStr">
         <is>
-          <t>Myr Vlr Pagado PMP1286553</t>
+          <t>Rechazo PMP1284750</t>
         </is>
       </c>
     </row>
@@ -8696,28 +8696,28 @@
       </c>
       <c r="D390" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO APERTURA</t>
+          <t>PMP1284800</t>
         </is>
       </c>
       <c r="E390" s="6" t="n">
-        <v>-14258141</v>
+        <v>-635980</v>
       </c>
       <c r="F390" s="10" t="inlineStr">
         <is>
-          <t>PERFUME</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G390" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H390" s="6" t="n">
-        <v>-14258141</v>
+        <v>-635980</v>
       </c>
       <c r="I390" s="11" t="inlineStr">
         <is>
-          <t>DAV DSCTO 20.251.200.200.056 DESCUENTO APERTURA PERFUME</t>
+          <t>Rechazo PMP1284800</t>
         </is>
       </c>
     </row>
@@ -8729,28 +8729,28 @@
       </c>
       <c r="D391" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO CALENDARI</t>
+          <t>PMP1284876</t>
         </is>
       </c>
       <c r="E391" s="6" t="n">
-        <v>-408729662</v>
+        <v>-689804</v>
       </c>
       <c r="F391" s="10" t="inlineStr">
         <is>
-          <t>PERFUME</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G391" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H391" s="6" t="n">
-        <v>-408729662</v>
+        <v>-689804</v>
       </c>
       <c r="I391" s="11" t="inlineStr">
         <is>
-          <t>DCA DSCTO 20.251.200.199.218 DESCUENTO CALENDARI PERFUME</t>
+          <t>Rechazo PMP1284876</t>
         </is>
       </c>
     </row>
@@ -8762,28 +8762,28 @@
       </c>
       <c r="D392" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO CALENDARI</t>
+          <t>PMP1284878</t>
         </is>
       </c>
       <c r="E392" s="6" t="n">
-        <v>-532175699</v>
+        <v>-135533</v>
       </c>
       <c r="F392" s="10" t="inlineStr">
         <is>
-          <t>PERFUME</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G392" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H392" s="6" t="n">
-        <v>-532175699</v>
+        <v>-135533</v>
       </c>
       <c r="I392" s="11" t="inlineStr">
         <is>
-          <t>DCA DSCTO 20.251.200.199.219 DESCUENTO CALENDARI PERFUME</t>
+          <t>Rechazo PMP1284878</t>
         </is>
       </c>
     </row>
@@ -8795,28 +8795,28 @@
       </c>
       <c r="D393" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO CALENDARI</t>
+          <t>PMP1284879</t>
         </is>
       </c>
       <c r="E393" s="6" t="n">
-        <v>-542708897</v>
+        <v>-732728</v>
       </c>
       <c r="F393" s="10" t="inlineStr">
         <is>
-          <t>PERFUME</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G393" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H393" s="6" t="n">
-        <v>-542708897</v>
+        <v>-732728</v>
       </c>
       <c r="I393" s="11" t="inlineStr">
         <is>
-          <t>DCA DSCTO 20.251.200.199.221 DESCUENTO CALENDARI PERFUME</t>
+          <t>Rechazo PMP1284879</t>
         </is>
       </c>
     </row>
@@ -8828,28 +8828,28 @@
       </c>
       <c r="D394" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO CALENDARI</t>
+          <t>PMP1284948</t>
         </is>
       </c>
       <c r="E394" s="6" t="n">
-        <v>-1323072</v>
+        <v>-1060968</v>
       </c>
       <c r="F394" s="10" t="inlineStr">
         <is>
-          <t>PERFUME</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G394" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H394" s="6" t="n">
-        <v>-1323072</v>
+        <v>-1060968</v>
       </c>
       <c r="I394" s="11" t="inlineStr">
         <is>
-          <t>DCA DSCTO 20.251.200.199.280 DESCUENTO CALENDARI PERFUME</t>
+          <t>Rechazo PMP1284948</t>
         </is>
       </c>
     </row>
@@ -8861,28 +8861,28 @@
       </c>
       <c r="D395" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO CALENDARI</t>
+          <t>PMP1284949</t>
         </is>
       </c>
       <c r="E395" s="6" t="n">
-        <v>-254331040</v>
+        <v>-215248</v>
       </c>
       <c r="F395" s="10" t="inlineStr">
         <is>
-          <t>PERFUME</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G395" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H395" s="6" t="n">
-        <v>-254331040</v>
+        <v>-215248</v>
       </c>
       <c r="I395" s="11" t="inlineStr">
         <is>
-          <t>DCA DSCTO 20.251.200.200.036 DESCUENTO CALENDARI PERFUME</t>
+          <t>Rechazo PMP1284949</t>
         </is>
       </c>
     </row>
@@ -8894,28 +8894,28 @@
       </c>
       <c r="D396" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO CALENDARI</t>
+          <t>PMP1284950</t>
         </is>
       </c>
       <c r="E396" s="6" t="n">
-        <v>-19632788</v>
+        <v>-1297475</v>
       </c>
       <c r="F396" s="10" t="inlineStr">
         <is>
-          <t>PERFUME</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G396" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H396" s="6" t="n">
-        <v>-19632788</v>
+        <v>-1297475</v>
       </c>
       <c r="I396" s="11" t="inlineStr">
         <is>
-          <t>DCA DSCTO 20.251.200.200.064 DESCUENTO CALENDARI PERFUME</t>
+          <t>Rechazo PMP1284950</t>
         </is>
       </c>
     </row>
@@ -8927,28 +8927,28 @@
       </c>
       <c r="D397" s="10" t="inlineStr">
         <is>
-          <t>DEVOLUCIONES</t>
+          <t>PMP1284951</t>
         </is>
       </c>
       <c r="E397" s="6" t="n">
-        <v>-2074733</v>
+        <v>-5702098</v>
       </c>
       <c r="F397" s="10" t="inlineStr">
         <is>
-          <t>PERFUME</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G397" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H397" s="6" t="n">
-        <v>-2074733</v>
+        <v>-5702098</v>
       </c>
       <c r="I397" s="11" t="inlineStr">
         <is>
-          <t>DND DSCTO 20.171.200.014.220 DEVOLUCIONES PERFUME</t>
+          <t>Rechazo PMP1284951</t>
         </is>
       </c>
     </row>
@@ -8960,28 +8960,28 @@
       </c>
       <c r="D398" s="10" t="inlineStr">
         <is>
-          <t>DSTO COMERCIAL FIJO</t>
+          <t>PMP1285048</t>
         </is>
       </c>
       <c r="E398" s="6" t="n">
-        <v>-48410423</v>
+        <v>-221603</v>
       </c>
       <c r="F398" s="10" t="inlineStr">
         <is>
-          <t>PERFUME</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G398" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H398" s="6" t="n">
-        <v>-48410423</v>
+        <v>-221603</v>
       </c>
       <c r="I398" s="11" t="inlineStr">
         <is>
-          <t>DCF DSCTO 20.171.200.014.220 DSTO COMERCIAL FIJO PERFUME</t>
+          <t>Rechazo PMP1285048</t>
         </is>
       </c>
     </row>
@@ -8993,28 +8993,28 @@
       </c>
       <c r="D399" s="10" t="inlineStr">
         <is>
-          <t>DSTO COMERCIAL FIJO</t>
+          <t>PMP1285059</t>
         </is>
       </c>
       <c r="E399" s="6" t="n">
-        <v>-28246208</v>
+        <v>-160294</v>
       </c>
       <c r="F399" s="10" t="inlineStr">
         <is>
-          <t>PERFUME</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G399" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H399" s="6" t="n">
-        <v>-28246208</v>
+        <v>-160294</v>
       </c>
       <c r="I399" s="11" t="inlineStr">
         <is>
-          <t>DCF DSCTO 20.181.200.033.536 DSTO COMERCIAL FIJO PERFUME</t>
+          <t>Rechazo PMP1285059</t>
         </is>
       </c>
     </row>
@@ -9026,28 +9026,28 @@
       </c>
       <c r="D400" s="10" t="inlineStr">
         <is>
-          <t>DTO POR ESCALA VOLU</t>
+          <t>PMP1285065</t>
         </is>
       </c>
       <c r="E400" s="6" t="n">
-        <v>-128010036</v>
+        <v>-107552</v>
       </c>
       <c r="F400" s="10" t="inlineStr">
         <is>
-          <t>PERFUME</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G400" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H400" s="6" t="n">
-        <v>-128010036</v>
+        <v>-107552</v>
       </c>
       <c r="I400" s="11" t="inlineStr">
         <is>
-          <t>DEC DSCTO 20.251.200.199.299 DTO POR ESCALA VOLU PERFUME</t>
+          <t>Rechazo PMP1285065</t>
         </is>
       </c>
     </row>
@@ -9059,28 +9059,28 @@
       </c>
       <c r="D401" s="10" t="inlineStr">
         <is>
-          <t>DTO POR ESCALA VOLU</t>
+          <t>PMP1285067</t>
         </is>
       </c>
       <c r="E401" s="6" t="n">
-        <v>-29342807</v>
+        <v>-135307</v>
       </c>
       <c r="F401" s="10" t="inlineStr">
         <is>
-          <t>PERFUME</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G401" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H401" s="6" t="n">
-        <v>-29342807</v>
+        <v>-135307</v>
       </c>
       <c r="I401" s="11" t="inlineStr">
         <is>
-          <t>DEC DSCTO 20.251.200.199.300 DTO POR ESCALA VOLU PERFUME</t>
+          <t>Rechazo PMP1285067</t>
         </is>
       </c>
     </row>
@@ -9092,28 +9092,28 @@
       </c>
       <c r="D402" s="10" t="inlineStr">
         <is>
-          <t>DTO POR ESCALA VOLU</t>
+          <t>PMP1285071</t>
         </is>
       </c>
       <c r="E402" s="6" t="n">
-        <v>-1719421</v>
+        <v>-419436</v>
       </c>
       <c r="F402" s="10" t="inlineStr">
         <is>
-          <t>PERFUME</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G402" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H402" s="6" t="n">
-        <v>-1719421</v>
+        <v>-419436</v>
       </c>
       <c r="I402" s="11" t="inlineStr">
         <is>
-          <t>DEC DSCTO 20.251.200.199.301 DTO POR ESCALA VOLU PERFUME</t>
+          <t>Rechazo PMP1285071</t>
         </is>
       </c>
     </row>
@@ -9125,28 +9125,28 @@
       </c>
       <c r="D403" s="10" t="inlineStr">
         <is>
-          <t>DTO POR ESCALA VOLU</t>
+          <t>PMP1285653</t>
         </is>
       </c>
       <c r="E403" s="6" t="n">
-        <v>-10000000</v>
+        <v>-558246</v>
       </c>
       <c r="F403" s="10" t="inlineStr">
         <is>
-          <t>PERFUME</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G403" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H403" s="6" t="n">
-        <v>-10000000</v>
+        <v>-558246</v>
       </c>
       <c r="I403" s="11" t="inlineStr">
         <is>
-          <t>DEC DSCTO 20.251.200.200.041 DTO POR ESCALA VOLU PERFUME</t>
+          <t>Rechazo PMP1285653</t>
         </is>
       </c>
     </row>
@@ -9158,28 +9158,28 @@
       </c>
       <c r="D404" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO CALENDARI</t>
+          <t>PMP1285659</t>
         </is>
       </c>
       <c r="E404" s="6" t="n">
-        <v>-2074459</v>
+        <v>-311765</v>
       </c>
       <c r="F404" s="10" t="inlineStr">
         <is>
-          <t>PLATOS</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G404" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H404" s="6" t="n">
-        <v>-2074459</v>
+        <v>-311765</v>
       </c>
       <c r="I404" s="11" t="inlineStr">
         <is>
-          <t>DCA DSCTO 20.222.600.126.372 DESCUENTO CALENDARI PLATOS</t>
+          <t>Rechazo PMP1285659</t>
         </is>
       </c>
     </row>
@@ -9191,28 +9191,28 @@
       </c>
       <c r="D405" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO CALENDARI</t>
+          <t>PMP1285725</t>
         </is>
       </c>
       <c r="E405" s="6" t="n">
-        <v>-11353075</v>
+        <v>-679290</v>
       </c>
       <c r="F405" s="10" t="inlineStr">
         <is>
-          <t>PLATOS</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G405" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H405" s="6" t="n">
-        <v>-11353075</v>
+        <v>-679290</v>
       </c>
       <c r="I405" s="11" t="inlineStr">
         <is>
-          <t>DCA DSCTO 20.252.600.198.821 DESCUENTO CALENDARI PLATOS</t>
+          <t>Rechazo PMP1285725</t>
         </is>
       </c>
     </row>
@@ -9224,28 +9224,28 @@
       </c>
       <c r="D406" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO COMPRAS</t>
+          <t>PMP1285898</t>
         </is>
       </c>
       <c r="E406" s="6" t="n">
-        <v>-1394767</v>
+        <v>-253685</v>
       </c>
       <c r="F406" s="10" t="inlineStr">
         <is>
-          <t>PLATOS</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G406" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H406" s="6" t="n">
-        <v>-1394767</v>
+        <v>-253685</v>
       </c>
       <c r="I406" s="11" t="inlineStr">
         <is>
-          <t>DCC DSCTO 20.222.600.126.372 DESCUENTO COMPRAS PLATOS</t>
+          <t>Rechazo PMP1285898</t>
         </is>
       </c>
     </row>
@@ -9257,28 +9257,28 @@
       </c>
       <c r="D407" s="10" t="inlineStr">
         <is>
-          <t>DSTO COMERCIAL FIJO</t>
+          <t>PMP1285903</t>
         </is>
       </c>
       <c r="E407" s="6" t="n">
-        <v>-20921503</v>
+        <v>-322554</v>
       </c>
       <c r="F407" s="10" t="inlineStr">
         <is>
-          <t>PLATOS</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G407" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H407" s="6" t="n">
-        <v>-20921503</v>
+        <v>-322554</v>
       </c>
       <c r="I407" s="11" t="inlineStr">
         <is>
-          <t>DCF DSCTO 20.222.600.126.372 DSTO COMERCIAL FIJO PLATOS</t>
+          <t>Rechazo PMP1285903</t>
         </is>
       </c>
     </row>
@@ -9290,28 +9290,28 @@
       </c>
       <c r="D408" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO CALENDARI</t>
+          <t>PMP1285908</t>
         </is>
       </c>
       <c r="E408" s="6" t="n">
-        <v>-29638456</v>
+        <v>-135255</v>
       </c>
       <c r="F408" s="10" t="inlineStr">
         <is>
-          <t>RANCHO</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G408" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H408" s="6" t="n">
-        <v>-29638456</v>
+        <v>-135255</v>
       </c>
       <c r="I408" s="11" t="inlineStr">
         <is>
-          <t>DCA DSCTO 20.251.400.199.149 DESCUENTO CALENDARI RANCHO</t>
+          <t>Rechazo PMP1285908</t>
         </is>
       </c>
     </row>
@@ -9323,28 +9323,28 @@
       </c>
       <c r="D409" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO COMERCIAL</t>
+          <t>PMP1286056</t>
         </is>
       </c>
       <c r="E409" s="6" t="n">
-        <v>-61299192</v>
+        <v>-556413</v>
       </c>
       <c r="F409" s="10" t="inlineStr">
         <is>
-          <t>RANCHO</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G409" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H409" s="6" t="n">
-        <v>-61299192</v>
+        <v>-556413</v>
       </c>
       <c r="I409" s="11" t="inlineStr">
         <is>
-          <t>RPL DSCTO 0 DESCUENTO COMERCIAL RANCHO</t>
+          <t>Rechazo PMP1286056</t>
         </is>
       </c>
     </row>
@@ -9356,28 +9356,28 @@
       </c>
       <c r="D410" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO EN PRIMER</t>
+          <t>PMP1286208</t>
         </is>
       </c>
       <c r="E410" s="6" t="n">
-        <v>-10216531</v>
+        <v>-949123</v>
       </c>
       <c r="F410" s="10" t="inlineStr">
         <is>
-          <t>RANCHO</t>
+          <t>Rechazo</t>
         </is>
       </c>
       <c r="G410" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H410" s="6" t="n">
-        <v>-10216531</v>
+        <v>-949123</v>
       </c>
       <c r="I410" s="11" t="inlineStr">
         <is>
-          <t>DPC DSCTO 0 DESCUENTO EN PRIMER RANCHO</t>
+          <t>Rechazo PMP1286208</t>
         </is>
       </c>
     </row>
@@ -9389,11 +9389,11 @@
       </c>
       <c r="D411" s="10" t="inlineStr">
         <is>
-          <t>PMP1282099</t>
+          <t>PMP1286554</t>
         </is>
       </c>
       <c r="E411" s="6" t="n">
-        <v>-307519</v>
+        <v>-354934</v>
       </c>
       <c r="F411" s="10" t="inlineStr">
         <is>
@@ -9406,11 +9406,11 @@
         </is>
       </c>
       <c r="H411" s="6" t="n">
-        <v>-307519</v>
+        <v>-354934</v>
       </c>
       <c r="I411" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1282099</t>
+          <t>Rechazo PMP1286554</t>
         </is>
       </c>
     </row>
@@ -9422,11 +9422,11 @@
       </c>
       <c r="D412" s="10" t="inlineStr">
         <is>
-          <t>PMP1282353</t>
+          <t>PMP1286556</t>
         </is>
       </c>
       <c r="E412" s="6" t="n">
-        <v>-2659670</v>
+        <v>-364001</v>
       </c>
       <c r="F412" s="10" t="inlineStr">
         <is>
@@ -9439,11 +9439,11 @@
         </is>
       </c>
       <c r="H412" s="6" t="n">
-        <v>-2659670</v>
+        <v>-364001</v>
       </c>
       <c r="I412" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1282353</t>
+          <t>Rechazo PMP1286556</t>
         </is>
       </c>
     </row>
@@ -9455,11 +9455,11 @@
       </c>
       <c r="D413" s="10" t="inlineStr">
         <is>
-          <t>PMP1282964</t>
+          <t>PMP1286709</t>
         </is>
       </c>
       <c r="E413" s="6" t="n">
-        <v>-185365</v>
+        <v>-33537478</v>
       </c>
       <c r="F413" s="10" t="inlineStr">
         <is>
@@ -9472,11 +9472,11 @@
         </is>
       </c>
       <c r="H413" s="6" t="n">
-        <v>-185365</v>
+        <v>-33537478</v>
       </c>
       <c r="I413" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1282964</t>
+          <t>Rechazo PMP1286709</t>
         </is>
       </c>
     </row>
@@ -9488,11 +9488,11 @@
       </c>
       <c r="D414" s="10" t="inlineStr">
         <is>
-          <t>PMP1283008</t>
+          <t>PMP1286710</t>
         </is>
       </c>
       <c r="E414" s="6" t="n">
-        <v>-9788</v>
+        <v>-650618</v>
       </c>
       <c r="F414" s="10" t="inlineStr">
         <is>
@@ -9505,11 +9505,11 @@
         </is>
       </c>
       <c r="H414" s="6" t="n">
-        <v>-9788</v>
+        <v>-650618</v>
       </c>
       <c r="I414" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1283008</t>
+          <t>Rechazo PMP1286710</t>
         </is>
       </c>
     </row>
@@ -9521,11 +9521,11 @@
       </c>
       <c r="D415" s="10" t="inlineStr">
         <is>
-          <t>PMP1283012</t>
+          <t>PMP1286711</t>
         </is>
       </c>
       <c r="E415" s="6" t="n">
-        <v>-167913</v>
+        <v>-6920570</v>
       </c>
       <c r="F415" s="10" t="inlineStr">
         <is>
@@ -9538,11 +9538,11 @@
         </is>
       </c>
       <c r="H415" s="6" t="n">
-        <v>-167913</v>
+        <v>-6920570</v>
       </c>
       <c r="I415" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1283012</t>
+          <t>Rechazo PMP1286711</t>
         </is>
       </c>
     </row>
@@ -9554,11 +9554,11 @@
       </c>
       <c r="D416" s="10" t="inlineStr">
         <is>
-          <t>PMP1283476</t>
+          <t>PMP1286712</t>
         </is>
       </c>
       <c r="E416" s="6" t="n">
-        <v>-836339</v>
+        <v>-403395</v>
       </c>
       <c r="F416" s="10" t="inlineStr">
         <is>
@@ -9571,11 +9571,11 @@
         </is>
       </c>
       <c r="H416" s="6" t="n">
-        <v>-836339</v>
+        <v>-403395</v>
       </c>
       <c r="I416" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1283476</t>
+          <t>Rechazo PMP1286712</t>
         </is>
       </c>
     </row>
@@ -9587,11 +9587,11 @@
       </c>
       <c r="D417" s="10" t="inlineStr">
         <is>
-          <t>PMP1283500</t>
+          <t>PMP1286715</t>
         </is>
       </c>
       <c r="E417" s="6" t="n">
-        <v>-473742856</v>
+        <v>-4085189</v>
       </c>
       <c r="F417" s="10" t="inlineStr">
         <is>
@@ -9604,11 +9604,11 @@
         </is>
       </c>
       <c r="H417" s="6" t="n">
-        <v>-473742856</v>
+        <v>-4085189</v>
       </c>
       <c r="I417" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1283500</t>
+          <t>Rechazo PMP1286715</t>
         </is>
       </c>
     </row>
@@ -9620,11 +9620,11 @@
       </c>
       <c r="D418" s="10" t="inlineStr">
         <is>
-          <t>PMP1283784</t>
+          <t>PMP1286716</t>
         </is>
       </c>
       <c r="E418" s="6" t="n">
-        <v>-629893</v>
+        <v>-822039</v>
       </c>
       <c r="F418" s="10" t="inlineStr">
         <is>
@@ -9637,11 +9637,11 @@
         </is>
       </c>
       <c r="H418" s="6" t="n">
-        <v>-629893</v>
+        <v>-822039</v>
       </c>
       <c r="I418" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1283784</t>
+          <t>Rechazo PMP1286716</t>
         </is>
       </c>
     </row>
@@ -9653,11 +9653,11 @@
       </c>
       <c r="D419" s="10" t="inlineStr">
         <is>
-          <t>PMP1283785</t>
+          <t>PMP1287257</t>
         </is>
       </c>
       <c r="E419" s="6" t="n">
-        <v>-160273</v>
+        <v>-156625</v>
       </c>
       <c r="F419" s="10" t="inlineStr">
         <is>
@@ -9670,11 +9670,11 @@
         </is>
       </c>
       <c r="H419" s="6" t="n">
-        <v>-160273</v>
+        <v>-156625</v>
       </c>
       <c r="I419" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1283785</t>
+          <t>Rechazo PMP1287257</t>
         </is>
       </c>
     </row>
@@ -9686,11 +9686,11 @@
       </c>
       <c r="D420" s="10" t="inlineStr">
         <is>
-          <t>PMP1284114</t>
+          <t>PMP1287321</t>
         </is>
       </c>
       <c r="E420" s="6" t="n">
-        <v>-764103</v>
+        <v>-182163</v>
       </c>
       <c r="F420" s="10" t="inlineStr">
         <is>
@@ -9703,11 +9703,11 @@
         </is>
       </c>
       <c r="H420" s="6" t="n">
-        <v>-764103</v>
+        <v>-182163</v>
       </c>
       <c r="I420" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284114</t>
+          <t>Rechazo PMP1287321</t>
         </is>
       </c>
     </row>
@@ -9719,11 +9719,11 @@
       </c>
       <c r="D421" s="10" t="inlineStr">
         <is>
-          <t>PMP1284117</t>
+          <t>PMP1287325</t>
         </is>
       </c>
       <c r="E421" s="6" t="n">
-        <v>-177051</v>
+        <v>-118625</v>
       </c>
       <c r="F421" s="10" t="inlineStr">
         <is>
@@ -9736,11 +9736,11 @@
         </is>
       </c>
       <c r="H421" s="6" t="n">
-        <v>-177051</v>
+        <v>-118625</v>
       </c>
       <c r="I421" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284117</t>
+          <t>Rechazo PMP1287325</t>
         </is>
       </c>
     </row>
@@ -9752,11 +9752,11 @@
       </c>
       <c r="D422" s="10" t="inlineStr">
         <is>
-          <t>PMP1284119</t>
+          <t>PMP1287335</t>
         </is>
       </c>
       <c r="E422" s="6" t="n">
-        <v>-644997</v>
+        <v>-128620</v>
       </c>
       <c r="F422" s="10" t="inlineStr">
         <is>
@@ -9769,11 +9769,11 @@
         </is>
       </c>
       <c r="H422" s="6" t="n">
-        <v>-644997</v>
+        <v>-128620</v>
       </c>
       <c r="I422" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284119</t>
+          <t>Rechazo PMP1287335</t>
         </is>
       </c>
     </row>
@@ -9785,11 +9785,11 @@
       </c>
       <c r="D423" s="10" t="inlineStr">
         <is>
-          <t>PMP1284200</t>
+          <t>PMP1287379</t>
         </is>
       </c>
       <c r="E423" s="6" t="n">
-        <v>-175153</v>
+        <v>-271757</v>
       </c>
       <c r="F423" s="10" t="inlineStr">
         <is>
@@ -9802,11 +9802,11 @@
         </is>
       </c>
       <c r="H423" s="6" t="n">
-        <v>-175153</v>
+        <v>-271757</v>
       </c>
       <c r="I423" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284200</t>
+          <t>Rechazo PMP1287379</t>
         </is>
       </c>
     </row>
@@ -9818,11 +9818,11 @@
       </c>
       <c r="D424" s="10" t="inlineStr">
         <is>
-          <t>PMP1284460</t>
+          <t>PMP1287385</t>
         </is>
       </c>
       <c r="E424" s="6" t="n">
-        <v>-167879</v>
+        <v>-214996</v>
       </c>
       <c r="F424" s="10" t="inlineStr">
         <is>
@@ -9835,11 +9835,11 @@
         </is>
       </c>
       <c r="H424" s="6" t="n">
-        <v>-167879</v>
+        <v>-214996</v>
       </c>
       <c r="I424" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284460</t>
+          <t>Rechazo PMP1287385</t>
         </is>
       </c>
     </row>
@@ -9851,11 +9851,11 @@
       </c>
       <c r="D425" s="10" t="inlineStr">
         <is>
-          <t>PMP1284462</t>
+          <t>PMP1287386</t>
         </is>
       </c>
       <c r="E425" s="6" t="n">
-        <v>-322931</v>
+        <v>-267680</v>
       </c>
       <c r="F425" s="10" t="inlineStr">
         <is>
@@ -9868,11 +9868,11 @@
         </is>
       </c>
       <c r="H425" s="6" t="n">
-        <v>-322931</v>
+        <v>-267680</v>
       </c>
       <c r="I425" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284462</t>
+          <t>Rechazo PMP1287386</t>
         </is>
       </c>
     </row>
@@ -9884,11 +9884,11 @@
       </c>
       <c r="D426" s="10" t="inlineStr">
         <is>
-          <t>PMP1284529</t>
+          <t>PMP1287574</t>
         </is>
       </c>
       <c r="E426" s="6" t="n">
-        <v>-276742</v>
+        <v>-11940004</v>
       </c>
       <c r="F426" s="10" t="inlineStr">
         <is>
@@ -9901,11 +9901,11 @@
         </is>
       </c>
       <c r="H426" s="6" t="n">
-        <v>-276742</v>
+        <v>-11940004</v>
       </c>
       <c r="I426" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284529</t>
+          <t>Rechazo PMP1287574</t>
         </is>
       </c>
     </row>
@@ -9917,11 +9917,11 @@
       </c>
       <c r="D427" s="10" t="inlineStr">
         <is>
-          <t>PMP1284543</t>
+          <t>PMP1287736</t>
         </is>
       </c>
       <c r="E427" s="6" t="n">
-        <v>-3015665</v>
+        <v>-93440</v>
       </c>
       <c r="F427" s="10" t="inlineStr">
         <is>
@@ -9934,11 +9934,11 @@
         </is>
       </c>
       <c r="H427" s="6" t="n">
-        <v>-3015665</v>
+        <v>-93440</v>
       </c>
       <c r="I427" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284543</t>
+          <t>Rechazo PMP1287736</t>
         </is>
       </c>
     </row>
@@ -9950,11 +9950,11 @@
       </c>
       <c r="D428" s="10" t="inlineStr">
         <is>
-          <t>PMP1284546</t>
+          <t>PMP128777746</t>
         </is>
       </c>
       <c r="E428" s="6" t="n">
-        <v>-135409</v>
+        <v>-322500</v>
       </c>
       <c r="F428" s="10" t="inlineStr">
         <is>
@@ -9967,11 +9967,11 @@
         </is>
       </c>
       <c r="H428" s="6" t="n">
-        <v>-135409</v>
+        <v>-322500</v>
       </c>
       <c r="I428" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284546</t>
+          <t>Rechazo PMP128777746</t>
         </is>
       </c>
     </row>
@@ -9983,11 +9983,11 @@
       </c>
       <c r="D429" s="10" t="inlineStr">
         <is>
-          <t>PMP1284602</t>
+          <t>PMP1287829</t>
         </is>
       </c>
       <c r="E429" s="6" t="n">
-        <v>-930108</v>
+        <v>-290823</v>
       </c>
       <c r="F429" s="10" t="inlineStr">
         <is>
@@ -10000,11 +10000,11 @@
         </is>
       </c>
       <c r="H429" s="6" t="n">
-        <v>-930108</v>
+        <v>-290823</v>
       </c>
       <c r="I429" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284602</t>
+          <t>Rechazo PMP1287829</t>
         </is>
       </c>
     </row>
@@ -10016,11 +10016,11 @@
       </c>
       <c r="D430" s="10" t="inlineStr">
         <is>
-          <t>PMP1284750</t>
+          <t>PMP1287903</t>
         </is>
       </c>
       <c r="E430" s="6" t="n">
-        <v>-405708</v>
+        <v>-128514</v>
       </c>
       <c r="F430" s="10" t="inlineStr">
         <is>
@@ -10033,11 +10033,11 @@
         </is>
       </c>
       <c r="H430" s="6" t="n">
-        <v>-405708</v>
+        <v>-128514</v>
       </c>
       <c r="I430" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284750</t>
+          <t>Rechazo PMP1287903</t>
         </is>
       </c>
     </row>
@@ -10049,11 +10049,11 @@
       </c>
       <c r="D431" s="10" t="inlineStr">
         <is>
-          <t>PMP1284800</t>
+          <t>PMP1287904</t>
         </is>
       </c>
       <c r="E431" s="6" t="n">
-        <v>-635980</v>
+        <v>-80064</v>
       </c>
       <c r="F431" s="10" t="inlineStr">
         <is>
@@ -10066,11 +10066,11 @@
         </is>
       </c>
       <c r="H431" s="6" t="n">
-        <v>-635980</v>
+        <v>-80064</v>
       </c>
       <c r="I431" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284800</t>
+          <t>Rechazo PMP1287904</t>
         </is>
       </c>
     </row>
@@ -10082,11 +10082,11 @@
       </c>
       <c r="D432" s="10" t="inlineStr">
         <is>
-          <t>PMP1284876</t>
+          <t>PMP1287920</t>
         </is>
       </c>
       <c r="E432" s="6" t="n">
-        <v>-689804</v>
+        <v>-582605</v>
       </c>
       <c r="F432" s="10" t="inlineStr">
         <is>
@@ -10099,11 +10099,11 @@
         </is>
       </c>
       <c r="H432" s="6" t="n">
-        <v>-689804</v>
+        <v>-582605</v>
       </c>
       <c r="I432" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284876</t>
+          <t>Rechazo PMP1287920</t>
         </is>
       </c>
     </row>
@@ -10115,11 +10115,11 @@
       </c>
       <c r="D433" s="10" t="inlineStr">
         <is>
-          <t>PMP1284878</t>
+          <t>PMP1287921</t>
         </is>
       </c>
       <c r="E433" s="6" t="n">
-        <v>-135533</v>
+        <v>-124374</v>
       </c>
       <c r="F433" s="10" t="inlineStr">
         <is>
@@ -10132,11 +10132,11 @@
         </is>
       </c>
       <c r="H433" s="6" t="n">
-        <v>-135533</v>
+        <v>-124374</v>
       </c>
       <c r="I433" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284878</t>
+          <t>Rechazo PMP1287921</t>
         </is>
       </c>
     </row>
@@ -10148,11 +10148,11 @@
       </c>
       <c r="D434" s="10" t="inlineStr">
         <is>
-          <t>PMP1284879</t>
+          <t>PMP1287928</t>
         </is>
       </c>
       <c r="E434" s="6" t="n">
-        <v>-732728</v>
+        <v>-246230</v>
       </c>
       <c r="F434" s="10" t="inlineStr">
         <is>
@@ -10165,11 +10165,11 @@
         </is>
       </c>
       <c r="H434" s="6" t="n">
-        <v>-732728</v>
+        <v>-246230</v>
       </c>
       <c r="I434" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284879</t>
+          <t>Rechazo PMP1287928</t>
         </is>
       </c>
     </row>
@@ -10181,11 +10181,11 @@
       </c>
       <c r="D435" s="10" t="inlineStr">
         <is>
-          <t>PMP1284948</t>
+          <t>PMP1287930</t>
         </is>
       </c>
       <c r="E435" s="6" t="n">
-        <v>-1060968</v>
+        <v>-91079</v>
       </c>
       <c r="F435" s="10" t="inlineStr">
         <is>
@@ -10198,11 +10198,11 @@
         </is>
       </c>
       <c r="H435" s="6" t="n">
-        <v>-1060968</v>
+        <v>-91079</v>
       </c>
       <c r="I435" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284948</t>
+          <t>Rechazo PMP1287930</t>
         </is>
       </c>
     </row>
@@ -10214,11 +10214,11 @@
       </c>
       <c r="D436" s="10" t="inlineStr">
         <is>
-          <t>PMP1284949</t>
+          <t>PMP1287931</t>
         </is>
       </c>
       <c r="E436" s="6" t="n">
-        <v>-215248</v>
+        <v>-215025</v>
       </c>
       <c r="F436" s="10" t="inlineStr">
         <is>
@@ -10231,11 +10231,11 @@
         </is>
       </c>
       <c r="H436" s="6" t="n">
-        <v>-215248</v>
+        <v>-215025</v>
       </c>
       <c r="I436" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284949</t>
+          <t>Rechazo PMP1287931</t>
         </is>
       </c>
     </row>
@@ -10247,11 +10247,11 @@
       </c>
       <c r="D437" s="10" t="inlineStr">
         <is>
-          <t>PMP1284950</t>
+          <t>PMP1287948</t>
         </is>
       </c>
       <c r="E437" s="6" t="n">
-        <v>-1297475</v>
+        <v>-354871</v>
       </c>
       <c r="F437" s="10" t="inlineStr">
         <is>
@@ -10264,11 +10264,11 @@
         </is>
       </c>
       <c r="H437" s="6" t="n">
-        <v>-1297475</v>
+        <v>-354871</v>
       </c>
       <c r="I437" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284950</t>
+          <t>Rechazo PMP1287948</t>
         </is>
       </c>
     </row>
@@ -10280,11 +10280,11 @@
       </c>
       <c r="D438" s="10" t="inlineStr">
         <is>
-          <t>PMP1284951</t>
+          <t>PMP1287949</t>
         </is>
       </c>
       <c r="E438" s="6" t="n">
-        <v>-5702098</v>
+        <v>-410669</v>
       </c>
       <c r="F438" s="10" t="inlineStr">
         <is>
@@ -10297,11 +10297,11 @@
         </is>
       </c>
       <c r="H438" s="6" t="n">
-        <v>-5702098</v>
+        <v>-410669</v>
       </c>
       <c r="I438" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1284951</t>
+          <t>Rechazo PMP1287949</t>
         </is>
       </c>
     </row>
@@ -10313,11 +10313,11 @@
       </c>
       <c r="D439" s="10" t="inlineStr">
         <is>
-          <t>PMP1285048</t>
+          <t>PMP1287951</t>
         </is>
       </c>
       <c r="E439" s="6" t="n">
-        <v>-221603</v>
+        <v>-29456389</v>
       </c>
       <c r="F439" s="10" t="inlineStr">
         <is>
@@ -10330,11 +10330,11 @@
         </is>
       </c>
       <c r="H439" s="6" t="n">
-        <v>-221603</v>
+        <v>-29456389</v>
       </c>
       <c r="I439" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285048</t>
+          <t>Rechazo PMP1287951</t>
         </is>
       </c>
     </row>
@@ -10346,11 +10346,11 @@
       </c>
       <c r="D440" s="10" t="inlineStr">
         <is>
-          <t>PMP1285059</t>
+          <t>PMP1287957</t>
         </is>
       </c>
       <c r="E440" s="6" t="n">
-        <v>-160294</v>
+        <v>-107492</v>
       </c>
       <c r="F440" s="10" t="inlineStr">
         <is>
@@ -10363,11 +10363,11 @@
         </is>
       </c>
       <c r="H440" s="6" t="n">
-        <v>-160294</v>
+        <v>-107492</v>
       </c>
       <c r="I440" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285059</t>
+          <t>Rechazo PMP1287957</t>
         </is>
       </c>
     </row>
@@ -10379,11 +10379,11 @@
       </c>
       <c r="D441" s="10" t="inlineStr">
         <is>
-          <t>PMP1285065</t>
+          <t>PMP1288418</t>
         </is>
       </c>
       <c r="E441" s="6" t="n">
-        <v>-107552</v>
+        <v>-2183651</v>
       </c>
       <c r="F441" s="10" t="inlineStr">
         <is>
@@ -10396,11 +10396,11 @@
         </is>
       </c>
       <c r="H441" s="6" t="n">
-        <v>-107552</v>
+        <v>-2183651</v>
       </c>
       <c r="I441" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285065</t>
+          <t>Rechazo PMP1288418</t>
         </is>
       </c>
     </row>
@@ -10412,11 +10412,11 @@
       </c>
       <c r="D442" s="10" t="inlineStr">
         <is>
-          <t>PMP1285067</t>
+          <t>PMP1288731</t>
         </is>
       </c>
       <c r="E442" s="6" t="n">
-        <v>-135307</v>
+        <v>-160222</v>
       </c>
       <c r="F442" s="10" t="inlineStr">
         <is>
@@ -10429,11 +10429,11 @@
         </is>
       </c>
       <c r="H442" s="6" t="n">
-        <v>-135307</v>
+        <v>-160222</v>
       </c>
       <c r="I442" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285067</t>
+          <t>Rechazo PMP1288731</t>
         </is>
       </c>
     </row>
@@ -10445,11 +10445,11 @@
       </c>
       <c r="D443" s="10" t="inlineStr">
         <is>
-          <t>PMP1285071</t>
+          <t>PMP1288919</t>
         </is>
       </c>
       <c r="E443" s="6" t="n">
-        <v>-419436</v>
+        <v>-9852</v>
       </c>
       <c r="F443" s="10" t="inlineStr">
         <is>
@@ -10462,11 +10462,11 @@
         </is>
       </c>
       <c r="H443" s="6" t="n">
-        <v>-419436</v>
+        <v>-9852</v>
       </c>
       <c r="I443" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285071</t>
+          <t>Rechazo PMP1288919</t>
         </is>
       </c>
     </row>
@@ -10478,11 +10478,11 @@
       </c>
       <c r="D444" s="10" t="inlineStr">
         <is>
-          <t>PMP1285653</t>
+          <t>PMP1288926</t>
         </is>
       </c>
       <c r="E444" s="6" t="n">
-        <v>-558246</v>
+        <v>-322749</v>
       </c>
       <c r="F444" s="10" t="inlineStr">
         <is>
@@ -10495,11 +10495,11 @@
         </is>
       </c>
       <c r="H444" s="6" t="n">
-        <v>-558246</v>
+        <v>-322749</v>
       </c>
       <c r="I444" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285653</t>
+          <t>Rechazo PMP1288926</t>
         </is>
       </c>
     </row>
@@ -10511,11 +10511,11 @@
       </c>
       <c r="D445" s="10" t="inlineStr">
         <is>
-          <t>PMP1285659</t>
+          <t>PMP1288987</t>
         </is>
       </c>
       <c r="E445" s="6" t="n">
-        <v>-311765</v>
+        <v>-1106307</v>
       </c>
       <c r="F445" s="10" t="inlineStr">
         <is>
@@ -10528,11 +10528,11 @@
         </is>
       </c>
       <c r="H445" s="6" t="n">
-        <v>-311765</v>
+        <v>-1106307</v>
       </c>
       <c r="I445" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285659</t>
+          <t>Rechazo PMP1288987</t>
         </is>
       </c>
     </row>
@@ -10544,11 +10544,11 @@
       </c>
       <c r="D446" s="10" t="inlineStr">
         <is>
-          <t>PMP1285725</t>
+          <t>PMP1288988</t>
         </is>
       </c>
       <c r="E446" s="6" t="n">
-        <v>-679290</v>
+        <v>-33894</v>
       </c>
       <c r="F446" s="10" t="inlineStr">
         <is>
@@ -10561,11 +10561,11 @@
         </is>
       </c>
       <c r="H446" s="6" t="n">
-        <v>-679290</v>
+        <v>-33894</v>
       </c>
       <c r="I446" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285725</t>
+          <t>Rechazo PMP1288988</t>
         </is>
       </c>
     </row>
@@ -10577,11 +10577,11 @@
       </c>
       <c r="D447" s="10" t="inlineStr">
         <is>
-          <t>PMP1285898</t>
+          <t>PMP1288989</t>
         </is>
       </c>
       <c r="E447" s="6" t="n">
-        <v>-253685</v>
+        <v>-2259163</v>
       </c>
       <c r="F447" s="10" t="inlineStr">
         <is>
@@ -10594,11 +10594,11 @@
         </is>
       </c>
       <c r="H447" s="6" t="n">
-        <v>-253685</v>
+        <v>-2259163</v>
       </c>
       <c r="I447" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285898</t>
+          <t>Rechazo PMP1288989</t>
         </is>
       </c>
     </row>
@@ -10610,11 +10610,11 @@
       </c>
       <c r="D448" s="10" t="inlineStr">
         <is>
-          <t>PMP1285903</t>
+          <t>PMP1289251</t>
         </is>
       </c>
       <c r="E448" s="6" t="n">
-        <v>-322554</v>
+        <v>-200703</v>
       </c>
       <c r="F448" s="10" t="inlineStr">
         <is>
@@ -10627,11 +10627,11 @@
         </is>
       </c>
       <c r="H448" s="6" t="n">
-        <v>-322554</v>
+        <v>-200703</v>
       </c>
       <c r="I448" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285903</t>
+          <t>Rechazo PMP1289251</t>
         </is>
       </c>
     </row>
@@ -10643,11 +10643,11 @@
       </c>
       <c r="D449" s="10" t="inlineStr">
         <is>
-          <t>PMP1285908</t>
+          <t>PMP1289253</t>
         </is>
       </c>
       <c r="E449" s="6" t="n">
-        <v>-135255</v>
+        <v>-2482097</v>
       </c>
       <c r="F449" s="10" t="inlineStr">
         <is>
@@ -10660,11 +10660,11 @@
         </is>
       </c>
       <c r="H449" s="6" t="n">
-        <v>-135255</v>
+        <v>-2482097</v>
       </c>
       <c r="I449" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1285908</t>
+          <t>Rechazo PMP1289253</t>
         </is>
       </c>
     </row>
@@ -10676,11 +10676,11 @@
       </c>
       <c r="D450" s="10" t="inlineStr">
         <is>
-          <t>PMP1286056</t>
+          <t>PMP1289324</t>
         </is>
       </c>
       <c r="E450" s="6" t="n">
-        <v>-556413</v>
+        <v>-532656</v>
       </c>
       <c r="F450" s="10" t="inlineStr">
         <is>
@@ -10693,11 +10693,11 @@
         </is>
       </c>
       <c r="H450" s="6" t="n">
-        <v>-556413</v>
+        <v>-532656</v>
       </c>
       <c r="I450" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286056</t>
+          <t>Rechazo PMP1289324</t>
         </is>
       </c>
     </row>
@@ -10709,11 +10709,11 @@
       </c>
       <c r="D451" s="10" t="inlineStr">
         <is>
-          <t>PMP1286208</t>
+          <t>PMP1289326</t>
         </is>
       </c>
       <c r="E451" s="6" t="n">
-        <v>-949123</v>
+        <v>-523796</v>
       </c>
       <c r="F451" s="10" t="inlineStr">
         <is>
@@ -10726,11 +10726,11 @@
         </is>
       </c>
       <c r="H451" s="6" t="n">
-        <v>-949123</v>
+        <v>-523796</v>
       </c>
       <c r="I451" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286208</t>
+          <t>Rechazo PMP1289326</t>
         </is>
       </c>
     </row>
@@ -10742,11 +10742,11 @@
       </c>
       <c r="D452" s="10" t="inlineStr">
         <is>
-          <t>PMP1286554</t>
+          <t>PMP1289328</t>
         </is>
       </c>
       <c r="E452" s="6" t="n">
-        <v>-354934</v>
+        <v>-303757</v>
       </c>
       <c r="F452" s="10" t="inlineStr">
         <is>
@@ -10759,11 +10759,11 @@
         </is>
       </c>
       <c r="H452" s="6" t="n">
-        <v>-354934</v>
+        <v>-303757</v>
       </c>
       <c r="I452" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286554</t>
+          <t>Rechazo PMP1289328</t>
         </is>
       </c>
     </row>
@@ -10775,11 +10775,11 @@
       </c>
       <c r="D453" s="10" t="inlineStr">
         <is>
-          <t>PMP1286556</t>
+          <t>PMP1289507</t>
         </is>
       </c>
       <c r="E453" s="6" t="n">
-        <v>-364001</v>
+        <v>-160184</v>
       </c>
       <c r="F453" s="10" t="inlineStr">
         <is>
@@ -10792,11 +10792,11 @@
         </is>
       </c>
       <c r="H453" s="6" t="n">
-        <v>-364001</v>
+        <v>-160184</v>
       </c>
       <c r="I453" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286556</t>
+          <t>Rechazo PMP1289507</t>
         </is>
       </c>
     </row>
@@ -10808,28 +10808,28 @@
       </c>
       <c r="D454" s="10" t="inlineStr">
         <is>
-          <t>PMP1286709</t>
+          <t>DESCUENTO APERTURA</t>
         </is>
       </c>
       <c r="E454" s="6" t="n">
-        <v>-33537478</v>
+        <v>-8594192</v>
       </c>
       <c r="F454" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>DROGUER</t>
         </is>
       </c>
       <c r="G454" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H454" s="6" t="n">
-        <v>-33537478</v>
+        <v>-8594192</v>
       </c>
       <c r="I454" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286709</t>
+          <t>DAV DSCTO 20.251.100.200.165 DROGUER DESCUENTO APERTURA</t>
         </is>
       </c>
     </row>
@@ -10841,28 +10841,28 @@
       </c>
       <c r="D455" s="10" t="inlineStr">
         <is>
-          <t>PMP1286710</t>
+          <t>DESCUENTO CALENDARI</t>
         </is>
       </c>
       <c r="E455" s="6" t="n">
-        <v>-650618</v>
+        <v>-117913970</v>
       </c>
       <c r="F455" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>DROGUER</t>
         </is>
       </c>
       <c r="G455" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H455" s="6" t="n">
-        <v>-650618</v>
+        <v>-117913970</v>
       </c>
       <c r="I455" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286710</t>
+          <t>DCA DSCTO 20.251.100.199.887 DROGUER DESCUENTO CALENDARI</t>
         </is>
       </c>
     </row>
@@ -10874,28 +10874,28 @@
       </c>
       <c r="D456" s="10" t="inlineStr">
         <is>
-          <t>PMP1286711</t>
+          <t>DESCUENTO CALENDARI</t>
         </is>
       </c>
       <c r="E456" s="6" t="n">
-        <v>-6920570</v>
+        <v>-343622707</v>
       </c>
       <c r="F456" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>DROGUER</t>
         </is>
       </c>
       <c r="G456" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H456" s="6" t="n">
-        <v>-6920570</v>
+        <v>-343622707</v>
       </c>
       <c r="I456" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286711</t>
+          <t>DCA DSCTO 20.251.100.199.918 DROGUER DESCUENTO CALENDARI</t>
         </is>
       </c>
     </row>
@@ -10907,28 +10907,28 @@
       </c>
       <c r="D457" s="10" t="inlineStr">
         <is>
-          <t>PMP1286712</t>
+          <t>DESCUENTO CALENDARI</t>
         </is>
       </c>
       <c r="E457" s="6" t="n">
-        <v>-403395</v>
+        <v>-272000000</v>
       </c>
       <c r="F457" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>DROGUER</t>
         </is>
       </c>
       <c r="G457" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H457" s="6" t="n">
-        <v>-403395</v>
+        <v>-272000000</v>
       </c>
       <c r="I457" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286712</t>
+          <t>DCA DSCTO 20.251.100.199.957 DROGUER DESCUENTO CALENDARI</t>
         </is>
       </c>
     </row>
@@ -10940,28 +10940,28 @@
       </c>
       <c r="D458" s="10" t="inlineStr">
         <is>
-          <t>PMP1286715</t>
+          <t>DESCUENTO CALENDARI</t>
         </is>
       </c>
       <c r="E458" s="6" t="n">
-        <v>-4085189</v>
+        <v>-63971913</v>
       </c>
       <c r="F458" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>DROGUER</t>
         </is>
       </c>
       <c r="G458" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H458" s="6" t="n">
-        <v>-4085189</v>
+        <v>-63971913</v>
       </c>
       <c r="I458" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286715</t>
+          <t>DCA DSCTO 20.251.100.200.097 DROGUER DESCUENTO CALENDARI</t>
         </is>
       </c>
     </row>
@@ -10973,28 +10973,28 @@
       </c>
       <c r="D459" s="10" t="inlineStr">
         <is>
-          <t>PMP1286716</t>
+          <t>DESCUENTO CALENDARI</t>
         </is>
       </c>
       <c r="E459" s="6" t="n">
-        <v>-822039</v>
+        <v>-20000000</v>
       </c>
       <c r="F459" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>DROGUER</t>
         </is>
       </c>
       <c r="G459" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H459" s="6" t="n">
-        <v>-822039</v>
+        <v>-20000000</v>
       </c>
       <c r="I459" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1286716</t>
+          <t>DCA DSCTO 20.251.100.200.166 DROGUER DESCUENTO CALENDARI</t>
         </is>
       </c>
     </row>
@@ -11006,28 +11006,28 @@
       </c>
       <c r="D460" s="10" t="inlineStr">
         <is>
-          <t>PMP1287257</t>
+          <t>DEVOLUCIONES</t>
         </is>
       </c>
       <c r="E460" s="6" t="n">
-        <v>-156625</v>
+        <v>-3354641</v>
       </c>
       <c r="F460" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>DROGUER</t>
         </is>
       </c>
       <c r="G460" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H460" s="6" t="n">
-        <v>-156625</v>
+        <v>-3354641</v>
       </c>
       <c r="I460" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287257</t>
+          <t>DND DSCTO 20.171.100.014.225 DROGUER DEVOLUCIONES</t>
         </is>
       </c>
     </row>
@@ -11039,28 +11039,28 @@
       </c>
       <c r="D461" s="10" t="inlineStr">
         <is>
-          <t>PMP1287321</t>
+          <t>DEVOLUCIONES</t>
         </is>
       </c>
       <c r="E461" s="6" t="n">
-        <v>-182163</v>
+        <v>-157710</v>
       </c>
       <c r="F461" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>DROGUER</t>
         </is>
       </c>
       <c r="G461" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H461" s="6" t="n">
-        <v>-182163</v>
+        <v>-157710</v>
       </c>
       <c r="I461" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287321</t>
+          <t>DND DSCTO 20.181.100.045.651 DROGUER DEVOLUCIONES</t>
         </is>
       </c>
     </row>
@@ -11072,28 +11072,28 @@
       </c>
       <c r="D462" s="10" t="inlineStr">
         <is>
-          <t>PMP1287325</t>
+          <t>DSTO COMERCIAL FIJO</t>
         </is>
       </c>
       <c r="E462" s="6" t="n">
-        <v>-118625</v>
+        <v>-39137474</v>
       </c>
       <c r="F462" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>DROGUER</t>
         </is>
       </c>
       <c r="G462" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H462" s="6" t="n">
-        <v>-118625</v>
+        <v>-39137474</v>
       </c>
       <c r="I462" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287325</t>
+          <t>DCF DSCTO 20.171.100.014.225 DROGUER DSTO COMERCIAL FIJO</t>
         </is>
       </c>
     </row>
@@ -11105,28 +11105,28 @@
       </c>
       <c r="D463" s="10" t="inlineStr">
         <is>
-          <t>PMP1287335</t>
+          <t>DSTO COMERCIAL FIJO</t>
         </is>
       </c>
       <c r="E463" s="6" t="n">
-        <v>-128620</v>
+        <v>-6254394</v>
       </c>
       <c r="F463" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>DROGUER</t>
         </is>
       </c>
       <c r="G463" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H463" s="6" t="n">
-        <v>-128620</v>
+        <v>-6254394</v>
       </c>
       <c r="I463" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287335</t>
+          <t>DCF DSCTO 20.181.100.032.054 DROGUER DSTO COMERCIAL FIJO</t>
         </is>
       </c>
     </row>
@@ -11138,28 +11138,28 @@
       </c>
       <c r="D464" s="10" t="inlineStr">
         <is>
-          <t>PMP1287379</t>
+          <t>DSTO COMERCIAL FIJO</t>
         </is>
       </c>
       <c r="E464" s="6" t="n">
-        <v>-271757</v>
+        <v>-2891340</v>
       </c>
       <c r="F464" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>DROGUER</t>
         </is>
       </c>
       <c r="G464" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H464" s="6" t="n">
-        <v>-271757</v>
+        <v>-2891340</v>
       </c>
       <c r="I464" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287379</t>
+          <t>DCF DSCTO 20.181.100.045.651 DROGUER DSTO COMERCIAL FIJO</t>
         </is>
       </c>
     </row>
@@ -11171,28 +11171,28 @@
       </c>
       <c r="D465" s="10" t="inlineStr">
         <is>
-          <t>PMP1287385</t>
+          <t>DTO POR ESCALA VOLU</t>
         </is>
       </c>
       <c r="E465" s="6" t="n">
-        <v>-214996</v>
+        <v>-69868245</v>
       </c>
       <c r="F465" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>DROGUER</t>
         </is>
       </c>
       <c r="G465" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H465" s="6" t="n">
-        <v>-214996</v>
+        <v>-69868245</v>
       </c>
       <c r="I465" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287385</t>
+          <t>DEC DSCTO 20.251.100.199.283 DROGUER DTO POR ESCALA VOLU</t>
         </is>
       </c>
     </row>
@@ -11204,28 +11204,28 @@
       </c>
       <c r="D466" s="10" t="inlineStr">
         <is>
-          <t>PMP1287386</t>
+          <t>DESCUENTO APERTURA</t>
         </is>
       </c>
       <c r="E466" s="6" t="n">
-        <v>-267680</v>
+        <v>-14258141</v>
       </c>
       <c r="F466" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PERFUME</t>
         </is>
       </c>
       <c r="G466" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H466" s="6" t="n">
-        <v>-267680</v>
+        <v>-14258141</v>
       </c>
       <c r="I466" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287386</t>
+          <t>DAV DSCTO 20.251.200.200.056 PERFUME DESCUENTO APERTURA</t>
         </is>
       </c>
     </row>
@@ -11237,28 +11237,28 @@
       </c>
       <c r="D467" s="10" t="inlineStr">
         <is>
-          <t>PMP1287574</t>
+          <t>DESCUENTO CALENDARI</t>
         </is>
       </c>
       <c r="E467" s="6" t="n">
-        <v>-11940004</v>
+        <v>-408729662</v>
       </c>
       <c r="F467" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PERFUME</t>
         </is>
       </c>
       <c r="G467" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H467" s="6" t="n">
-        <v>-11940004</v>
+        <v>-408729662</v>
       </c>
       <c r="I467" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287574</t>
+          <t>DCA DSCTO 20.251.200.199.218 PERFUME DESCUENTO CALENDARI</t>
         </is>
       </c>
     </row>
@@ -11270,28 +11270,28 @@
       </c>
       <c r="D468" s="10" t="inlineStr">
         <is>
-          <t>PMP1287736</t>
+          <t>DESCUENTO CALENDARI</t>
         </is>
       </c>
       <c r="E468" s="6" t="n">
-        <v>-93440</v>
+        <v>-532175699</v>
       </c>
       <c r="F468" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PERFUME</t>
         </is>
       </c>
       <c r="G468" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H468" s="6" t="n">
-        <v>-93440</v>
+        <v>-532175699</v>
       </c>
       <c r="I468" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287736</t>
+          <t>DCA DSCTO 20.251.200.199.219 PERFUME DESCUENTO CALENDARI</t>
         </is>
       </c>
     </row>
@@ -11303,28 +11303,28 @@
       </c>
       <c r="D469" s="10" t="inlineStr">
         <is>
-          <t>PMP128777746</t>
+          <t>DESCUENTO CALENDARI</t>
         </is>
       </c>
       <c r="E469" s="6" t="n">
-        <v>-322500</v>
+        <v>-542708897</v>
       </c>
       <c r="F469" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PERFUME</t>
         </is>
       </c>
       <c r="G469" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H469" s="6" t="n">
-        <v>-322500</v>
+        <v>-542708897</v>
       </c>
       <c r="I469" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP128777746</t>
+          <t>DCA DSCTO 20.251.200.199.221 PERFUME DESCUENTO CALENDARI</t>
         </is>
       </c>
     </row>
@@ -11336,28 +11336,28 @@
       </c>
       <c r="D470" s="10" t="inlineStr">
         <is>
-          <t>PMP1287829</t>
+          <t>DESCUENTO CALENDARI</t>
         </is>
       </c>
       <c r="E470" s="6" t="n">
-        <v>-290823</v>
+        <v>-1323072</v>
       </c>
       <c r="F470" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PERFUME</t>
         </is>
       </c>
       <c r="G470" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H470" s="6" t="n">
-        <v>-290823</v>
+        <v>-1323072</v>
       </c>
       <c r="I470" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287829</t>
+          <t>DCA DSCTO 20.251.200.199.280 PERFUME DESCUENTO CALENDARI</t>
         </is>
       </c>
     </row>
@@ -11369,28 +11369,28 @@
       </c>
       <c r="D471" s="10" t="inlineStr">
         <is>
-          <t>PMP1287903</t>
+          <t>DESCUENTO CALENDARI</t>
         </is>
       </c>
       <c r="E471" s="6" t="n">
-        <v>-128514</v>
+        <v>-254331040</v>
       </c>
       <c r="F471" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PERFUME</t>
         </is>
       </c>
       <c r="G471" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H471" s="6" t="n">
-        <v>-128514</v>
+        <v>-254331040</v>
       </c>
       <c r="I471" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287903</t>
+          <t>DCA DSCTO 20.251.200.200.036 PERFUME DESCUENTO CALENDARI</t>
         </is>
       </c>
     </row>
@@ -11402,28 +11402,28 @@
       </c>
       <c r="D472" s="10" t="inlineStr">
         <is>
-          <t>PMP1287904</t>
+          <t>DESCUENTO CALENDARI</t>
         </is>
       </c>
       <c r="E472" s="6" t="n">
-        <v>-80064</v>
+        <v>-19632788</v>
       </c>
       <c r="F472" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PERFUME</t>
         </is>
       </c>
       <c r="G472" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H472" s="6" t="n">
-        <v>-80064</v>
+        <v>-19632788</v>
       </c>
       <c r="I472" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287904</t>
+          <t>DCA DSCTO 20.251.200.200.064 PERFUME DESCUENTO CALENDARI</t>
         </is>
       </c>
     </row>
@@ -11435,28 +11435,28 @@
       </c>
       <c r="D473" s="10" t="inlineStr">
         <is>
-          <t>PMP1287920</t>
+          <t>DEVOLUCIONES</t>
         </is>
       </c>
       <c r="E473" s="6" t="n">
-        <v>-582605</v>
+        <v>-2074733</v>
       </c>
       <c r="F473" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PERFUME</t>
         </is>
       </c>
       <c r="G473" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H473" s="6" t="n">
-        <v>-582605</v>
+        <v>-2074733</v>
       </c>
       <c r="I473" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287920</t>
+          <t>DND DSCTO 20.171.200.014.220 PERFUME DEVOLUCIONES</t>
         </is>
       </c>
     </row>
@@ -11468,28 +11468,28 @@
       </c>
       <c r="D474" s="10" t="inlineStr">
         <is>
-          <t>PMP1287921</t>
+          <t>DSTO COMERCIAL FIJO</t>
         </is>
       </c>
       <c r="E474" s="6" t="n">
-        <v>-124374</v>
+        <v>-48410423</v>
       </c>
       <c r="F474" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PERFUME</t>
         </is>
       </c>
       <c r="G474" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H474" s="6" t="n">
-        <v>-124374</v>
+        <v>-48410423</v>
       </c>
       <c r="I474" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287921</t>
+          <t>DCF DSCTO 20.171.200.014.220 PERFUME DSTO COMERCIAL FIJO</t>
         </is>
       </c>
     </row>
@@ -11501,28 +11501,28 @@
       </c>
       <c r="D475" s="10" t="inlineStr">
         <is>
-          <t>PMP1287928</t>
+          <t>DSTO COMERCIAL FIJO</t>
         </is>
       </c>
       <c r="E475" s="6" t="n">
-        <v>-246230</v>
+        <v>-28246208</v>
       </c>
       <c r="F475" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PERFUME</t>
         </is>
       </c>
       <c r="G475" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H475" s="6" t="n">
-        <v>-246230</v>
+        <v>-28246208</v>
       </c>
       <c r="I475" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287928</t>
+          <t>DCF DSCTO 20.181.200.033.536 PERFUME DSTO COMERCIAL FIJO</t>
         </is>
       </c>
     </row>
@@ -11534,28 +11534,28 @@
       </c>
       <c r="D476" s="10" t="inlineStr">
         <is>
-          <t>PMP1287930</t>
+          <t>DTO POR ESCALA VOLU</t>
         </is>
       </c>
       <c r="E476" s="6" t="n">
-        <v>-91079</v>
+        <v>-128010036</v>
       </c>
       <c r="F476" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PERFUME</t>
         </is>
       </c>
       <c r="G476" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H476" s="6" t="n">
-        <v>-91079</v>
+        <v>-128010036</v>
       </c>
       <c r="I476" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287930</t>
+          <t>DEC DSCTO 20.251.200.199.299 PERFUME DTO POR ESCALA VOLU</t>
         </is>
       </c>
     </row>
@@ -11567,28 +11567,28 @@
       </c>
       <c r="D477" s="10" t="inlineStr">
         <is>
-          <t>PMP1287931</t>
+          <t>DTO POR ESCALA VOLU</t>
         </is>
       </c>
       <c r="E477" s="6" t="n">
-        <v>-215025</v>
+        <v>-29342807</v>
       </c>
       <c r="F477" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PERFUME</t>
         </is>
       </c>
       <c r="G477" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H477" s="6" t="n">
-        <v>-215025</v>
+        <v>-29342807</v>
       </c>
       <c r="I477" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287931</t>
+          <t>DEC DSCTO 20.251.200.199.300 PERFUME DTO POR ESCALA VOLU</t>
         </is>
       </c>
     </row>
@@ -11600,28 +11600,28 @@
       </c>
       <c r="D478" s="10" t="inlineStr">
         <is>
-          <t>PMP1287948</t>
+          <t>DTO POR ESCALA VOLU</t>
         </is>
       </c>
       <c r="E478" s="6" t="n">
-        <v>-354871</v>
+        <v>-1719421</v>
       </c>
       <c r="F478" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PERFUME</t>
         </is>
       </c>
       <c r="G478" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H478" s="6" t="n">
-        <v>-354871</v>
+        <v>-1719421</v>
       </c>
       <c r="I478" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287948</t>
+          <t>DEC DSCTO 20.251.200.199.301 PERFUME DTO POR ESCALA VOLU</t>
         </is>
       </c>
     </row>
@@ -11633,28 +11633,28 @@
       </c>
       <c r="D479" s="10" t="inlineStr">
         <is>
-          <t>PMP1287949</t>
+          <t>DTO POR ESCALA VOLU</t>
         </is>
       </c>
       <c r="E479" s="6" t="n">
-        <v>-410669</v>
+        <v>-10000000</v>
       </c>
       <c r="F479" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PERFUME</t>
         </is>
       </c>
       <c r="G479" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H479" s="6" t="n">
-        <v>-410669</v>
+        <v>-10000000</v>
       </c>
       <c r="I479" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287949</t>
+          <t>DEC DSCTO 20.251.200.200.041 PERFUME DTO POR ESCALA VOLU</t>
         </is>
       </c>
     </row>
@@ -11666,28 +11666,28 @@
       </c>
       <c r="D480" s="10" t="inlineStr">
         <is>
-          <t>PMP1287951</t>
+          <t>DESCUENTO CALENDARI</t>
         </is>
       </c>
       <c r="E480" s="6" t="n">
-        <v>-29456389</v>
+        <v>-2074459</v>
       </c>
       <c r="F480" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PLATOS</t>
         </is>
       </c>
       <c r="G480" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H480" s="6" t="n">
-        <v>-29456389</v>
+        <v>-2074459</v>
       </c>
       <c r="I480" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287951</t>
+          <t>DCA DSCTO 20.222.600.126.372 PLATOS DESCUENTO CALENDARI</t>
         </is>
       </c>
     </row>
@@ -11699,28 +11699,28 @@
       </c>
       <c r="D481" s="10" t="inlineStr">
         <is>
-          <t>PMP1287957</t>
+          <t>DESCUENTO CALENDARI</t>
         </is>
       </c>
       <c r="E481" s="6" t="n">
-        <v>-107492</v>
+        <v>-11353075</v>
       </c>
       <c r="F481" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PLATOS</t>
         </is>
       </c>
       <c r="G481" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H481" s="6" t="n">
-        <v>-107492</v>
+        <v>-11353075</v>
       </c>
       <c r="I481" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1287957</t>
+          <t>DCA DSCTO 20.252.600.198.821 PLATOS DESCUENTO CALENDARI</t>
         </is>
       </c>
     </row>
@@ -11732,28 +11732,28 @@
       </c>
       <c r="D482" s="10" t="inlineStr">
         <is>
-          <t>PMP1288418</t>
+          <t>DESCUENTO COMPRAS</t>
         </is>
       </c>
       <c r="E482" s="6" t="n">
-        <v>-2183651</v>
+        <v>-1394767</v>
       </c>
       <c r="F482" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PLATOS</t>
         </is>
       </c>
       <c r="G482" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H482" s="6" t="n">
-        <v>-2183651</v>
+        <v>-1394767</v>
       </c>
       <c r="I482" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288418</t>
+          <t>DCC DSCTO 20.222.600.126.372 PLATOS DESCUENTO COMPRAS</t>
         </is>
       </c>
     </row>
@@ -11765,28 +11765,28 @@
       </c>
       <c r="D483" s="10" t="inlineStr">
         <is>
-          <t>PMP1288731</t>
+          <t>DSTO COMERCIAL FIJO</t>
         </is>
       </c>
       <c r="E483" s="6" t="n">
-        <v>-160222</v>
+        <v>-20921503</v>
       </c>
       <c r="F483" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>PLATOS</t>
         </is>
       </c>
       <c r="G483" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H483" s="6" t="n">
-        <v>-160222</v>
+        <v>-20921503</v>
       </c>
       <c r="I483" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288731</t>
+          <t>DCF DSCTO 20.222.600.126.372 PLATOS DSTO COMERCIAL FIJO</t>
         </is>
       </c>
     </row>
@@ -11798,28 +11798,28 @@
       </c>
       <c r="D484" s="10" t="inlineStr">
         <is>
-          <t>PMP1288919</t>
+          <t>DESCUENTO CALENDARI</t>
         </is>
       </c>
       <c r="E484" s="6" t="n">
-        <v>-9852</v>
+        <v>-29638456</v>
       </c>
       <c r="F484" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>RANCHO</t>
         </is>
       </c>
       <c r="G484" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H484" s="6" t="n">
-        <v>-9852</v>
+        <v>-29638456</v>
       </c>
       <c r="I484" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288919</t>
+          <t>DCA DSCTO 20.251.400.199.149 RANCHO DESCUENTO CALENDARI</t>
         </is>
       </c>
     </row>
@@ -11831,28 +11831,28 @@
       </c>
       <c r="D485" s="10" t="inlineStr">
         <is>
-          <t>PMP1288926</t>
+          <t>DESCUENTO COMERCIAL</t>
         </is>
       </c>
       <c r="E485" s="6" t="n">
-        <v>-322749</v>
+        <v>-61299192</v>
       </c>
       <c r="F485" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>RANCHO</t>
         </is>
       </c>
       <c r="G485" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H485" s="6" t="n">
-        <v>-322749</v>
+        <v>-61299192</v>
       </c>
       <c r="I485" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288926</t>
+          <t>RPL DSCTO 0 RANCHO DESCUENTO COMERCIAL</t>
         </is>
       </c>
     </row>
@@ -11864,28 +11864,28 @@
       </c>
       <c r="D486" s="10" t="inlineStr">
         <is>
-          <t>PMP1288987</t>
+          <t>DESCUENTO EN PRIMER</t>
         </is>
       </c>
       <c r="E486" s="6" t="n">
-        <v>-1106307</v>
+        <v>-10216531</v>
       </c>
       <c r="F486" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>RANCHO</t>
         </is>
       </c>
       <c r="G486" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>987</t>
         </is>
       </c>
       <c r="H486" s="6" t="n">
-        <v>-1106307</v>
+        <v>-10216531</v>
       </c>
       <c r="I486" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288987</t>
+          <t>DPC DSCTO 0 RANCHO DESCUENTO EN PRIMER</t>
         </is>
       </c>
     </row>
@@ -11897,28 +11897,28 @@
       </c>
       <c r="D487" s="10" t="inlineStr">
         <is>
-          <t>PMP1288988</t>
+          <t>VPP1 2004529</t>
         </is>
       </c>
       <c r="E487" s="6" t="n">
-        <v>-33894</v>
+        <v>-57239000</v>
       </c>
       <c r="F487" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>FACT PROVEED</t>
         </is>
       </c>
       <c r="G487" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>CSB</t>
         </is>
       </c>
       <c r="H487" s="6" t="n">
-        <v>-33894</v>
+        <v>-57239000</v>
       </c>
       <c r="I487" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288988</t>
+          <t>FACT PROVEED VPP1 2004529</t>
         </is>
       </c>
     </row>
@@ -11930,28 +11930,28 @@
       </c>
       <c r="D488" s="10" t="inlineStr">
         <is>
-          <t>PMP1288989</t>
+          <t>VPP1 2004621</t>
         </is>
       </c>
       <c r="E488" s="6" t="n">
-        <v>-2259163</v>
+        <v>-6426000</v>
       </c>
       <c r="F488" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>FACT PROVEED</t>
         </is>
       </c>
       <c r="G488" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>CSB</t>
         </is>
       </c>
       <c r="H488" s="6" t="n">
-        <v>-2259163</v>
+        <v>-6426000</v>
       </c>
       <c r="I488" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1288989</t>
+          <t>FACT PROVEED VPP1 2004621</t>
         </is>
       </c>
     </row>
@@ -11963,28 +11963,28 @@
       </c>
       <c r="D489" s="10" t="inlineStr">
         <is>
-          <t>PMP1289251</t>
+          <t>VPP1 2004622</t>
         </is>
       </c>
       <c r="E489" s="6" t="n">
-        <v>-200703</v>
+        <v>-41650000</v>
       </c>
       <c r="F489" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>FACT PROVEED</t>
         </is>
       </c>
       <c r="G489" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>CSB</t>
         </is>
       </c>
       <c r="H489" s="6" t="n">
-        <v>-200703</v>
+        <v>-41650000</v>
       </c>
       <c r="I489" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1289251</t>
+          <t>FACT PROVEED VPP1 2004622</t>
         </is>
       </c>
     </row>
@@ -11996,28 +11996,28 @@
       </c>
       <c r="D490" s="10" t="inlineStr">
         <is>
-          <t>PMP1289253</t>
+          <t>VPP2 2021716</t>
         </is>
       </c>
       <c r="E490" s="6" t="n">
-        <v>-2482097</v>
+        <v>-2507098292</v>
       </c>
       <c r="F490" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>FACT PROVEED</t>
         </is>
       </c>
       <c r="G490" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>CSB</t>
         </is>
       </c>
       <c r="H490" s="6" t="n">
-        <v>-2482097</v>
+        <v>-2507098292</v>
       </c>
       <c r="I490" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1289253</t>
+          <t>FACT PROVEED VPP2 2021716</t>
         </is>
       </c>
     </row>
@@ -12029,28 +12029,28 @@
       </c>
       <c r="D491" s="10" t="inlineStr">
         <is>
-          <t>PMP1289324</t>
+          <t>VPP2 2022342</t>
         </is>
       </c>
       <c r="E491" s="6" t="n">
-        <v>-532656</v>
+        <v>-1075965191</v>
       </c>
       <c r="F491" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>FACT PROVEED</t>
         </is>
       </c>
       <c r="G491" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>CSB</t>
         </is>
       </c>
       <c r="H491" s="6" t="n">
-        <v>-532656</v>
+        <v>-1075965191</v>
       </c>
       <c r="I491" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1289324</t>
+          <t>FACT PROVEED VPP2 2022342</t>
         </is>
       </c>
     </row>
@@ -12062,28 +12062,28 @@
       </c>
       <c r="D492" s="10" t="inlineStr">
         <is>
-          <t>PMP1289326</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="E492" s="6" t="n">
-        <v>-523796</v>
+        <v>-37.26000004360685</v>
       </c>
       <c r="F492" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G492" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>CSR</t>
         </is>
       </c>
       <c r="H492" s="6" t="n">
-        <v>-523796</v>
+        <v>-37.26000004360685</v>
       </c>
       <c r="I492" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1289326</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
@@ -12095,28 +12095,28 @@
       </c>
       <c r="D493" s="10" t="inlineStr">
         <is>
-          <t>PMP1289328</t>
+          <t>PMP1286054</t>
         </is>
       </c>
       <c r="E493" s="6" t="n">
-        <v>-303757</v>
+        <v>-864163</v>
       </c>
       <c r="F493" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>Menor Vlr Pagado</t>
         </is>
       </c>
       <c r="G493" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>CSR</t>
         </is>
       </c>
       <c r="H493" s="6" t="n">
-        <v>-303757</v>
+        <v>-864163</v>
       </c>
       <c r="I493" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1289328</t>
+          <t>Menor Vlr Pagado PMP1286054</t>
         </is>
       </c>
     </row>
@@ -12128,28 +12128,28 @@
       </c>
       <c r="D494" s="10" t="inlineStr">
         <is>
-          <t>PMP1289507</t>
+          <t>PMP1286550</t>
         </is>
       </c>
       <c r="E494" s="6" t="n">
-        <v>-160184</v>
+        <v>-5910046.859999999</v>
       </c>
       <c r="F494" s="10" t="inlineStr">
         <is>
-          <t>Rechazo</t>
+          <t>Menor Vlr Pagado</t>
         </is>
       </c>
       <c r="G494" s="10" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>CSR</t>
         </is>
       </c>
       <c r="H494" s="6" t="n">
-        <v>-160184</v>
+        <v>-5910046.859999999</v>
       </c>
       <c r="I494" s="11" t="inlineStr">
         <is>
-          <t>Rechazo PMP1289507</t>
+          <t>Menor Vlr Pagado PMP1286550</t>
         </is>
       </c>
     </row>

--- a/Pruebas/Archivos/Template/Colombia/Template_HRC_Cenco.xlsx
+++ b/Pruebas/Archivos/Template/Colombia/Template_HRC_Cenco.xlsx
@@ -583,7 +583,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
